--- a/data/temp.xlsx
+++ b/data/temp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB2EE54A-6F12-4C83-BFA2-5D35F3AEF889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DFD1C1CE-8050-4029-913E-25681B8A4E0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15600" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="완제품 임가공" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="949" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="821">
   <si>
     <t xml:space="preserve"> APBL2-AL22 G</t>
   </si>
@@ -3201,65 +3201,11 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3271,6 +3217,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3294,13 +3243,64 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6285,22 +6285,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="75" t="s">
         <v>716</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
@@ -6331,67 +6331,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="84" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="81" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="78" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="78" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="78" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="73" t="s">
         <v>723</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="73" t="s">
         <v>669</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="73" t="s">
         <v>673</v>
       </c>
-      <c r="I6" s="55" t="s">
+      <c r="I6" s="73" t="s">
         <v>680</v>
       </c>
-      <c r="J6" s="55" t="s">
+      <c r="J6" s="73" t="s">
         <v>681</v>
       </c>
-      <c r="K6" s="55" t="s">
+      <c r="K6" s="73" t="s">
         <v>682</v>
       </c>
-      <c r="L6" s="55" t="s">
+      <c r="L6" s="73" t="s">
         <v>700</v>
       </c>
-      <c r="M6" s="55" t="s">
+      <c r="M6" s="73" t="s">
         <v>724</v>
       </c>
-      <c r="N6" s="73" t="s">
+      <c r="N6" s="76" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="66"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="74"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="77"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="62" t="s">
+      <c r="A8" s="83" t="s">
         <v>178</v>
       </c>
       <c r="B8" s="25" t="s">
@@ -6413,7 +6413,7 @@
       <c r="N8" s="27"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="63"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="15" t="s">
         <v>218</v>
       </c>
@@ -6433,7 +6433,7 @@
       <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="63"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="18" t="s">
         <v>209</v>
       </c>
@@ -6453,7 +6453,7 @@
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="63"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="18" t="s">
         <v>250</v>
       </c>
@@ -6473,7 +6473,7 @@
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="63"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="22" t="s">
         <v>229</v>
       </c>
@@ -6493,7 +6493,7 @@
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="63"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="15" t="s">
         <v>327</v>
       </c>
@@ -6513,7 +6513,7 @@
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="63"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="15" t="s">
         <v>381</v>
       </c>
@@ -6533,7 +6533,7 @@
       <c r="N14" s="14"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="63"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="15" t="s">
         <v>353</v>
       </c>
@@ -6553,7 +6553,7 @@
       <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="63"/>
+      <c r="A16" s="61"/>
       <c r="B16" s="15" t="s">
         <v>351</v>
       </c>
@@ -6573,7 +6573,7 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="63"/>
+      <c r="A17" s="61"/>
       <c r="B17" s="15" t="s">
         <v>228</v>
       </c>
@@ -6593,7 +6593,7 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="63"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="15" t="s">
         <v>430</v>
       </c>
@@ -6613,46 +6613,25 @@
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="61" t="s">
+      <c r="A19" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="70"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
       <c r="F19" s="16"/>
-      <c r="G19" s="40">
-        <f>SUM(G8:G18)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="40">
-        <f t="shared" ref="H19:M19" si="0">SUM(H8:H18)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="G19" s="40"/>
+      <c r="H19" s="40"/>
+      <c r="I19" s="40"/>
+      <c r="J19" s="40"/>
+      <c r="K19" s="40"/>
+      <c r="L19" s="40"/>
+      <c r="M19" s="40"/>
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="64" t="s">
+      <c r="A20" s="80" t="s">
         <v>729</v>
       </c>
       <c r="B20" s="15" t="s">
@@ -6674,7 +6653,7 @@
       <c r="N20" s="14"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="63"/>
+      <c r="A21" s="61"/>
       <c r="B21" s="15" t="s">
         <v>415</v>
       </c>
@@ -6694,7 +6673,7 @@
       <c r="N21" s="14"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="63"/>
+      <c r="A22" s="61"/>
       <c r="B22" s="15" t="s">
         <v>506</v>
       </c>
@@ -6714,7 +6693,7 @@
       <c r="N22" s="14"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="63"/>
+      <c r="A23" s="61"/>
       <c r="B23" s="15" t="s">
         <v>242</v>
       </c>
@@ -6734,46 +6713,25 @@
       <c r="N23" s="14"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="61" t="s">
+      <c r="A24" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="61"/>
-      <c r="C24" s="61"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="70"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
       <c r="F24" s="16"/>
-      <c r="G24" s="40">
-        <f>SUM(G20:G23)</f>
-        <v>0</v>
-      </c>
-      <c r="H24" s="40">
-        <f t="shared" ref="H24:M24" si="1">SUM(H20:H23)</f>
-        <v>0</v>
-      </c>
-      <c r="I24" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J24" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K24" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L24" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M24" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="G24" s="40"/>
+      <c r="H24" s="40"/>
+      <c r="I24" s="40"/>
+      <c r="J24" s="40"/>
+      <c r="K24" s="40"/>
+      <c r="L24" s="40"/>
+      <c r="M24" s="40"/>
       <c r="N24" s="14"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="64" t="s">
+      <c r="A25" s="80" t="s">
         <v>486</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -6795,7 +6753,7 @@
       <c r="N25" s="14"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="64"/>
+      <c r="A26" s="80"/>
       <c r="B26" s="15" t="s">
         <v>396</v>
       </c>
@@ -6815,7 +6773,7 @@
       <c r="N26" s="14"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="64"/>
+      <c r="A27" s="80"/>
       <c r="B27" s="15" t="s">
         <v>409</v>
       </c>
@@ -6835,7 +6793,7 @@
       <c r="N27" s="14"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="64"/>
+      <c r="A28" s="80"/>
       <c r="B28" s="15" t="s">
         <v>514</v>
       </c>
@@ -6855,7 +6813,7 @@
       <c r="N28" s="14"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="64"/>
+      <c r="A29" s="80"/>
       <c r="B29" s="15" t="s">
         <v>502</v>
       </c>
@@ -6875,7 +6833,7 @@
       <c r="N29" s="14"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="64"/>
+      <c r="A30" s="80"/>
       <c r="B30" s="15" t="s">
         <v>597</v>
       </c>
@@ -6895,7 +6853,7 @@
       <c r="N30" s="14"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="64"/>
+      <c r="A31" s="80"/>
       <c r="B31" s="15" t="s">
         <v>489</v>
       </c>
@@ -6915,7 +6873,7 @@
       <c r="N31" s="14"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="64"/>
+      <c r="A32" s="80"/>
       <c r="B32" s="15" t="s">
         <v>487</v>
       </c>
@@ -6935,7 +6893,7 @@
       <c r="N32" s="14"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="64"/>
+      <c r="A33" s="80"/>
       <c r="B33" s="15" t="s">
         <v>365</v>
       </c>
@@ -6955,7 +6913,7 @@
       <c r="N33" s="14"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="64"/>
+      <c r="A34" s="80"/>
       <c r="B34" s="15" t="s">
         <v>380</v>
       </c>
@@ -6975,7 +6933,7 @@
       <c r="N34" s="14"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="64"/>
+      <c r="A35" s="80"/>
       <c r="B35" s="15" t="s">
         <v>448</v>
       </c>
@@ -6995,7 +6953,7 @@
       <c r="N35" s="14"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="64"/>
+      <c r="A36" s="80"/>
       <c r="B36" s="15" t="s">
         <v>372</v>
       </c>
@@ -7015,7 +6973,7 @@
       <c r="N36" s="14"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="64"/>
+      <c r="A37" s="80"/>
       <c r="B37" s="15" t="s">
         <v>393</v>
       </c>
@@ -7035,7 +6993,7 @@
       <c r="N37" s="14"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="64"/>
+      <c r="A38" s="80"/>
       <c r="B38" s="15" t="s">
         <v>405</v>
       </c>
@@ -7055,7 +7013,7 @@
       <c r="N38" s="14"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="64"/>
+      <c r="A39" s="80"/>
       <c r="B39" s="15" t="s">
         <v>517</v>
       </c>
@@ -7075,7 +7033,7 @@
       <c r="N39" s="14"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="64"/>
+      <c r="A40" s="80"/>
       <c r="B40" s="15" t="s">
         <v>475</v>
       </c>
@@ -7095,7 +7053,7 @@
       <c r="N40" s="14"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="64"/>
+      <c r="A41" s="80"/>
       <c r="B41" s="15" t="s">
         <v>529</v>
       </c>
@@ -7115,7 +7073,7 @@
       <c r="N41" s="14"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="64"/>
+      <c r="A42" s="80"/>
       <c r="B42" s="15" t="s">
         <v>495</v>
       </c>
@@ -7135,7 +7093,7 @@
       <c r="N42" s="14"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="64"/>
+      <c r="A43" s="80"/>
       <c r="B43" s="15" t="s">
         <v>361</v>
       </c>
@@ -7155,7 +7113,7 @@
       <c r="N43" s="14"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="64"/>
+      <c r="A44" s="80"/>
       <c r="B44" s="15" t="s">
         <v>375</v>
       </c>
@@ -7175,7 +7133,7 @@
       <c r="N44" s="14"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="64"/>
+      <c r="A45" s="80"/>
       <c r="B45" s="15" t="s">
         <v>354</v>
       </c>
@@ -7195,7 +7153,7 @@
       <c r="N45" s="14"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="64"/>
+      <c r="A46" s="80"/>
       <c r="B46" s="15" t="s">
         <v>491</v>
       </c>
@@ -7215,7 +7173,7 @@
       <c r="N46" s="14"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="64"/>
+      <c r="A47" s="80"/>
       <c r="B47" s="15" t="s">
         <v>384</v>
       </c>
@@ -7235,7 +7193,7 @@
       <c r="N47" s="14"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="64"/>
+      <c r="A48" s="80"/>
       <c r="B48" s="15" t="s">
         <v>536</v>
       </c>
@@ -7255,7 +7213,7 @@
       <c r="N48" s="14"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="64"/>
+      <c r="A49" s="80"/>
       <c r="B49" s="15" t="s">
         <v>451</v>
       </c>
@@ -7275,7 +7233,7 @@
       <c r="N49" s="14"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="64"/>
+      <c r="A50" s="80"/>
       <c r="B50" s="15" t="s">
         <v>440</v>
       </c>
@@ -7295,46 +7253,25 @@
       <c r="N50" s="14"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="61" t="s">
+      <c r="A51" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B51" s="61"/>
-      <c r="C51" s="61"/>
+      <c r="B51" s="70"/>
+      <c r="C51" s="70"/>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="16"/>
-      <c r="G51" s="40">
-        <f>SUM(G25:G50)</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="40">
-        <f t="shared" ref="H51:M51" si="2">SUM(H25:H50)</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="40"/>
+      <c r="M51" s="40"/>
       <c r="N51" s="14"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="63" t="s">
+      <c r="A52" s="61" t="s">
         <v>526</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -7356,7 +7293,7 @@
       <c r="N52" s="14"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="63"/>
+      <c r="A53" s="61"/>
       <c r="B53" s="15" t="s">
         <v>360</v>
       </c>
@@ -7376,7 +7313,7 @@
       <c r="N53" s="14"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="63"/>
+      <c r="A54" s="61"/>
       <c r="B54" s="15" t="s">
         <v>546</v>
       </c>
@@ -7396,7 +7333,7 @@
       <c r="N54" s="14"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="63"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="15" t="s">
         <v>531</v>
       </c>
@@ -7416,7 +7353,7 @@
       <c r="N55" s="14"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="63"/>
+      <c r="A56" s="61"/>
       <c r="B56" s="15" t="s">
         <v>522</v>
       </c>
@@ -7436,7 +7373,7 @@
       <c r="N56" s="14"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="63"/>
+      <c r="A57" s="61"/>
       <c r="B57" s="15" t="s">
         <v>472</v>
       </c>
@@ -7456,7 +7393,7 @@
       <c r="N57" s="14"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="63" t="s">
+      <c r="A58" s="61" t="s">
         <v>520</v>
       </c>
       <c r="B58" s="15" t="s">
@@ -7478,7 +7415,7 @@
       <c r="N58" s="14"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="63"/>
+      <c r="A59" s="61"/>
       <c r="B59" s="15" t="s">
         <v>482</v>
       </c>
@@ -7498,7 +7435,7 @@
       <c r="N59" s="14"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="63"/>
+      <c r="A60" s="61"/>
       <c r="B60" s="15" t="s">
         <v>508</v>
       </c>
@@ -7518,7 +7455,7 @@
       <c r="N60" s="14"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="63"/>
+      <c r="A61" s="61"/>
       <c r="B61" s="15" t="s">
         <v>490</v>
       </c>
@@ -7538,7 +7475,7 @@
       <c r="N61" s="14"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="63"/>
+      <c r="A62" s="61"/>
       <c r="B62" s="15" t="s">
         <v>503</v>
       </c>
@@ -7558,7 +7495,7 @@
       <c r="N62" s="14"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="63"/>
+      <c r="A63" s="61"/>
       <c r="B63" s="15" t="s">
         <v>511</v>
       </c>
@@ -7578,7 +7515,7 @@
       <c r="N63" s="14"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="64" t="s">
+      <c r="A64" s="80" t="s">
         <v>109</v>
       </c>
       <c r="B64" s="31" t="s">
@@ -7600,7 +7537,7 @@
       <c r="N64" s="14"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="64"/>
+      <c r="A65" s="80"/>
       <c r="B65" s="31" t="s">
         <v>387</v>
       </c>
@@ -7620,7 +7557,7 @@
       <c r="N65" s="14"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="64"/>
+      <c r="A66" s="80"/>
       <c r="B66" s="31" t="s">
         <v>397</v>
       </c>
@@ -7640,7 +7577,7 @@
       <c r="N66" s="14"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="64"/>
+      <c r="A67" s="80"/>
       <c r="B67" s="31" t="s">
         <v>496</v>
       </c>
@@ -7660,7 +7597,7 @@
       <c r="N67" s="14"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="64" t="s">
+      <c r="A68" s="80" t="s">
         <v>109</v>
       </c>
       <c r="B68" s="31" t="s">
@@ -7682,7 +7619,7 @@
       <c r="N68" s="14"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="64"/>
+      <c r="A69" s="80"/>
       <c r="B69" s="31" t="s">
         <v>501</v>
       </c>
@@ -7702,7 +7639,7 @@
       <c r="N69" s="14"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="64"/>
+      <c r="A70" s="80"/>
       <c r="B70" s="31" t="s">
         <v>450</v>
       </c>
@@ -7722,7 +7659,7 @@
       <c r="N70" s="14"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="64"/>
+      <c r="A71" s="80"/>
       <c r="B71" s="31" t="s">
         <v>480</v>
       </c>
@@ -7742,7 +7679,7 @@
       <c r="N71" s="14"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="64" t="s">
+      <c r="A72" s="80" t="s">
         <v>41</v>
       </c>
       <c r="B72" s="31" t="s">
@@ -7764,7 +7701,7 @@
       <c r="N72" s="14"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="64"/>
+      <c r="A73" s="80"/>
       <c r="B73" s="31" t="s">
         <v>545</v>
       </c>
@@ -7784,7 +7721,7 @@
       <c r="N73" s="14"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="64"/>
+      <c r="A74" s="80"/>
       <c r="B74" s="31" t="s">
         <v>470</v>
       </c>
@@ -7804,7 +7741,7 @@
       <c r="N74" s="14"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="64" t="s">
+      <c r="A75" s="80" t="s">
         <v>41</v>
       </c>
       <c r="B75" s="31" t="s">
@@ -7826,7 +7763,7 @@
       <c r="N75" s="14"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="64"/>
+      <c r="A76" s="80"/>
       <c r="B76" s="31" t="s">
         <v>494</v>
       </c>
@@ -7846,7 +7783,7 @@
       <c r="N76" s="14"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="64"/>
+      <c r="A77" s="80"/>
       <c r="B77" s="31" t="s">
         <v>544</v>
       </c>
@@ -7866,7 +7803,7 @@
       <c r="N77" s="14"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="64"/>
+      <c r="A78" s="80"/>
       <c r="B78" s="31" t="s">
         <v>558</v>
       </c>
@@ -7886,7 +7823,7 @@
       <c r="N78" s="14"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="64"/>
+      <c r="A79" s="80"/>
       <c r="B79" s="31" t="s">
         <v>542</v>
       </c>
@@ -7906,7 +7843,7 @@
       <c r="N79" s="14"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="64"/>
+      <c r="A80" s="80"/>
       <c r="B80" s="31" t="s">
         <v>534</v>
       </c>
@@ -7926,7 +7863,7 @@
       <c r="N80" s="14"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="64"/>
+      <c r="A81" s="80"/>
       <c r="B81" s="31" t="s">
         <v>519</v>
       </c>
@@ -7946,7 +7883,7 @@
       <c r="N81" s="14"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="64"/>
+      <c r="A82" s="80"/>
       <c r="B82" s="31" t="s">
         <v>541</v>
       </c>
@@ -7966,46 +7903,25 @@
       <c r="N82" s="14"/>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="61" t="s">
+      <c r="A83" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B83" s="61"/>
-      <c r="C83" s="61"/>
+      <c r="B83" s="70"/>
+      <c r="C83" s="70"/>
       <c r="D83" s="14"/>
       <c r="E83" s="14"/>
       <c r="F83" s="16"/>
-      <c r="G83" s="40">
-        <f>SUM(G52:G82)</f>
-        <v>0</v>
-      </c>
-      <c r="H83" s="40">
-        <f t="shared" ref="H83:M83" si="3">SUM(H52:H82)</f>
-        <v>0</v>
-      </c>
-      <c r="I83" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J83" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K83" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L83" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M83" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="G83" s="40"/>
+      <c r="H83" s="40"/>
+      <c r="I83" s="40"/>
+      <c r="J83" s="40"/>
+      <c r="K83" s="40"/>
+      <c r="L83" s="40"/>
+      <c r="M83" s="40"/>
       <c r="N83" s="14"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="63" t="s">
+      <c r="A84" s="61" t="s">
         <v>605</v>
       </c>
       <c r="B84" s="15" t="s">
@@ -8027,7 +7943,7 @@
       <c r="N84" s="14"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="63"/>
+      <c r="A85" s="61"/>
       <c r="B85" s="15" t="s">
         <v>349</v>
       </c>
@@ -8047,7 +7963,7 @@
       <c r="N85" s="14"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="63"/>
+      <c r="A86" s="61"/>
       <c r="B86" s="15" t="s">
         <v>507</v>
       </c>
@@ -8067,7 +7983,7 @@
       <c r="N86" s="14"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="63"/>
+      <c r="A87" s="61"/>
       <c r="B87" s="15" t="s">
         <v>326</v>
       </c>
@@ -8087,7 +8003,7 @@
       <c r="N87" s="14"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="63"/>
+      <c r="A88" s="61"/>
       <c r="B88" s="15" t="s">
         <v>549</v>
       </c>
@@ -8107,7 +8023,7 @@
       <c r="N88" s="14"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="63"/>
+      <c r="A89" s="61"/>
       <c r="B89" s="15" t="s">
         <v>334</v>
       </c>
@@ -8127,7 +8043,7 @@
       <c r="N89" s="14"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="63"/>
+      <c r="A90" s="61"/>
       <c r="B90" s="15" t="s">
         <v>330</v>
       </c>
@@ -8147,7 +8063,7 @@
       <c r="N90" s="14"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="63"/>
+      <c r="A91" s="61"/>
       <c r="B91" s="15" t="s">
         <v>305</v>
       </c>
@@ -8167,46 +8083,25 @@
       <c r="N91" s="14"/>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="61" t="s">
+      <c r="A92" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B92" s="61"/>
-      <c r="C92" s="61"/>
+      <c r="B92" s="70"/>
+      <c r="C92" s="70"/>
       <c r="D92" s="14"/>
       <c r="E92" s="14"/>
       <c r="F92" s="16"/>
-      <c r="G92" s="40">
-        <f>SUM(G84:G91)</f>
-        <v>0</v>
-      </c>
-      <c r="H92" s="40">
-        <f t="shared" ref="H92:M92" si="4">SUM(H84:H91)</f>
-        <v>0</v>
-      </c>
-      <c r="I92" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J92" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K92" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L92" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M92" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="G92" s="40"/>
+      <c r="H92" s="40"/>
+      <c r="I92" s="40"/>
+      <c r="J92" s="40"/>
+      <c r="K92" s="40"/>
+      <c r="L92" s="40"/>
+      <c r="M92" s="40"/>
       <c r="N92" s="14"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="63" t="s">
+      <c r="A93" s="61" t="s">
         <v>504</v>
       </c>
       <c r="B93" s="15" t="s">
@@ -8228,7 +8123,7 @@
       <c r="N93" s="14"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="63"/>
+      <c r="A94" s="61"/>
       <c r="B94" s="15" t="s">
         <v>434</v>
       </c>
@@ -8248,7 +8143,7 @@
       <c r="N94" s="14"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="63"/>
+      <c r="A95" s="61"/>
       <c r="B95" s="15" t="s">
         <v>512</v>
       </c>
@@ -8268,7 +8163,7 @@
       <c r="N95" s="14"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="63"/>
+      <c r="A96" s="61"/>
       <c r="B96" s="15" t="s">
         <v>510</v>
       </c>
@@ -8288,7 +8183,7 @@
       <c r="N96" s="14"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="63"/>
+      <c r="A97" s="61"/>
       <c r="B97" s="15" t="s">
         <v>554</v>
       </c>
@@ -8308,7 +8203,7 @@
       <c r="N97" s="14"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="63"/>
+      <c r="A98" s="61"/>
       <c r="B98" s="15" t="s">
         <v>560</v>
       </c>
@@ -8328,7 +8223,7 @@
       <c r="N98" s="14"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="63"/>
+      <c r="A99" s="61"/>
       <c r="B99" s="15" t="s">
         <v>523</v>
       </c>
@@ -8348,7 +8243,7 @@
       <c r="N99" s="14"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="63"/>
+      <c r="A100" s="61"/>
       <c r="B100" s="15" t="s">
         <v>564</v>
       </c>
@@ -8368,7 +8263,7 @@
       <c r="N100" s="14"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="63"/>
+      <c r="A101" s="61"/>
       <c r="B101" s="15" t="s">
         <v>509</v>
       </c>
@@ -8388,7 +8283,7 @@
       <c r="N101" s="14"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="63"/>
+      <c r="A102" s="61"/>
       <c r="B102" s="15" t="s">
         <v>473</v>
       </c>
@@ -8408,7 +8303,7 @@
       <c r="N102" s="14"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="63"/>
+      <c r="A103" s="61"/>
       <c r="B103" s="15" t="s">
         <v>476</v>
       </c>
@@ -8428,7 +8323,7 @@
       <c r="N103" s="14"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="63"/>
+      <c r="A104" s="61"/>
       <c r="B104" s="15" t="s">
         <v>532</v>
       </c>
@@ -8448,7 +8343,7 @@
       <c r="N104" s="14"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="63"/>
+      <c r="A105" s="61"/>
       <c r="B105" s="15" t="s">
         <v>524</v>
       </c>
@@ -8468,7 +8363,7 @@
       <c r="N105" s="14"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="63"/>
+      <c r="A106" s="61"/>
       <c r="B106" s="15" t="s">
         <v>528</v>
       </c>
@@ -8488,7 +8383,7 @@
       <c r="N106" s="14"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="63"/>
+      <c r="A107" s="61"/>
       <c r="B107" s="15" t="s">
         <v>521</v>
       </c>
@@ -8508,7 +8403,7 @@
       <c r="N107" s="14"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="63"/>
+      <c r="A108" s="61"/>
       <c r="B108" s="15" t="s">
         <v>515</v>
       </c>
@@ -8528,46 +8423,25 @@
       <c r="N108" s="14"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="61" t="s">
+      <c r="A109" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B109" s="61"/>
-      <c r="C109" s="61"/>
+      <c r="B109" s="70"/>
+      <c r="C109" s="70"/>
       <c r="D109" s="14"/>
       <c r="E109" s="14"/>
       <c r="F109" s="16"/>
-      <c r="G109" s="40">
-        <f>SUM(G93:G108)</f>
-        <v>0</v>
-      </c>
-      <c r="H109" s="40">
-        <f t="shared" ref="H109:M109" si="5">SUM(H93:H108)</f>
-        <v>0</v>
-      </c>
-      <c r="I109" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J109" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K109" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L109" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M109" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="G109" s="40"/>
+      <c r="H109" s="40"/>
+      <c r="I109" s="40"/>
+      <c r="J109" s="40"/>
+      <c r="K109" s="40"/>
+      <c r="L109" s="40"/>
+      <c r="M109" s="40"/>
       <c r="N109" s="14"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="64" t="s">
+      <c r="A110" s="80" t="s">
         <v>2</v>
       </c>
       <c r="B110" s="31" t="s">
@@ -8589,7 +8463,7 @@
       <c r="N110" s="14"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="64"/>
+      <c r="A111" s="80"/>
       <c r="B111" s="31" t="s">
         <v>547</v>
       </c>
@@ -8609,7 +8483,7 @@
       <c r="N111" s="14"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="64"/>
+      <c r="A112" s="80"/>
       <c r="B112" s="31" t="s">
         <v>540</v>
       </c>
@@ -8629,7 +8503,7 @@
       <c r="N112" s="14"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="64"/>
+      <c r="A113" s="80"/>
       <c r="B113" s="31" t="s">
         <v>543</v>
       </c>
@@ -8649,7 +8523,7 @@
       <c r="N113" s="14"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="64"/>
+      <c r="A114" s="80"/>
       <c r="B114" s="31" t="s">
         <v>538</v>
       </c>
@@ -8669,7 +8543,7 @@
       <c r="N114" s="14"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="64"/>
+      <c r="A115" s="80"/>
       <c r="B115" s="31" t="s">
         <v>537</v>
       </c>
@@ -8689,7 +8563,7 @@
       <c r="N115" s="14"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="64"/>
+      <c r="A116" s="80"/>
       <c r="B116" s="31" t="s">
         <v>261</v>
       </c>
@@ -8709,46 +8583,25 @@
       <c r="N116" s="14"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="61" t="s">
+      <c r="A117" s="70" t="s">
         <v>595</v>
       </c>
-      <c r="B117" s="61"/>
-      <c r="C117" s="61"/>
+      <c r="B117" s="70"/>
+      <c r="C117" s="70"/>
       <c r="D117" s="14"/>
       <c r="E117" s="14"/>
       <c r="F117" s="16"/>
-      <c r="G117" s="40">
-        <f>SUM(G110:G116)</f>
-        <v>0</v>
-      </c>
-      <c r="H117" s="40">
-        <f t="shared" ref="H117:M117" si="6">SUM(H110:H116)</f>
-        <v>0</v>
-      </c>
-      <c r="I117" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J117" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K117" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L117" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M117" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+      <c r="G117" s="40"/>
+      <c r="H117" s="40"/>
+      <c r="I117" s="40"/>
+      <c r="J117" s="40"/>
+      <c r="K117" s="40"/>
+      <c r="L117" s="40"/>
+      <c r="M117" s="40"/>
       <c r="N117" s="14"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="63" t="s">
+      <c r="A118" s="61" t="s">
         <v>257</v>
       </c>
       <c r="B118" s="31" t="s">
@@ -8770,7 +8623,7 @@
       <c r="N118" s="14"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="63"/>
+      <c r="A119" s="61"/>
       <c r="B119" s="31" t="s">
         <v>311</v>
       </c>
@@ -8790,7 +8643,7 @@
       <c r="N119" s="14"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="63"/>
+      <c r="A120" s="61"/>
       <c r="B120" s="32" t="s">
         <v>587</v>
       </c>
@@ -8810,7 +8663,7 @@
       <c r="N120" s="14"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="63"/>
+      <c r="A121" s="61"/>
       <c r="B121" s="32" t="s">
         <v>217</v>
       </c>
@@ -8830,46 +8683,25 @@
       <c r="N121" s="14"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="61" t="s">
+      <c r="A122" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B122" s="61"/>
-      <c r="C122" s="61"/>
+      <c r="B122" s="70"/>
+      <c r="C122" s="70"/>
       <c r="D122" s="14"/>
       <c r="E122" s="14"/>
       <c r="F122" s="16"/>
-      <c r="G122" s="40">
-        <f>SUM(G118:G121)</f>
-        <v>0</v>
-      </c>
-      <c r="H122" s="40">
-        <f t="shared" ref="H122:M122" si="7">SUM(H118:H121)</f>
-        <v>0</v>
-      </c>
-      <c r="I122" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J122" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K122" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L122" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M122" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="G122" s="40"/>
+      <c r="H122" s="40"/>
+      <c r="I122" s="40"/>
+      <c r="J122" s="40"/>
+      <c r="K122" s="40"/>
+      <c r="L122" s="40"/>
+      <c r="M122" s="40"/>
       <c r="N122" s="14"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="63" t="s">
+      <c r="A123" s="61" t="s">
         <v>252</v>
       </c>
       <c r="B123" s="15" t="s">
@@ -8891,7 +8723,7 @@
       <c r="N123" s="14"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="63"/>
+      <c r="A124" s="61"/>
       <c r="B124" s="15" t="s">
         <v>319</v>
       </c>
@@ -8911,7 +8743,7 @@
       <c r="N124" s="14"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="63"/>
+      <c r="A125" s="61"/>
       <c r="B125" s="15" t="s">
         <v>588</v>
       </c>
@@ -8931,7 +8763,7 @@
       <c r="N125" s="14"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="63"/>
+      <c r="A126" s="61"/>
       <c r="B126" s="15" t="s">
         <v>207</v>
       </c>
@@ -8951,7 +8783,7 @@
       <c r="N126" s="14"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="63"/>
+      <c r="A127" s="61"/>
       <c r="B127" s="15" t="s">
         <v>376</v>
       </c>
@@ -8971,7 +8803,7 @@
       <c r="N127" s="14"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="63"/>
+      <c r="A128" s="61"/>
       <c r="B128" s="15" t="s">
         <v>234</v>
       </c>
@@ -8991,7 +8823,7 @@
       <c r="N128" s="14"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="63"/>
+      <c r="A129" s="61"/>
       <c r="B129" s="15" t="s">
         <v>239</v>
       </c>
@@ -9011,7 +8843,7 @@
       <c r="N129" s="14"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="63"/>
+      <c r="A130" s="61"/>
       <c r="B130" s="15" t="s">
         <v>373</v>
       </c>
@@ -9031,7 +8863,7 @@
       <c r="N130" s="14"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="63"/>
+      <c r="A131" s="61"/>
       <c r="B131" s="15" t="s">
         <v>593</v>
       </c>
@@ -9051,7 +8883,7 @@
       <c r="N131" s="14"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="63"/>
+      <c r="A132" s="61"/>
       <c r="B132" s="32" t="s">
         <v>406</v>
       </c>
@@ -9071,7 +8903,7 @@
       <c r="N132" s="14"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="63"/>
+      <c r="A133" s="61"/>
       <c r="B133" s="32" t="s">
         <v>348</v>
       </c>
@@ -9091,7 +8923,7 @@
       <c r="N133" s="14"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="63"/>
+      <c r="A134" s="61"/>
       <c r="B134" s="32" t="s">
         <v>395</v>
       </c>
@@ -9111,46 +8943,25 @@
       <c r="N134" s="14"/>
     </row>
     <row r="135" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="61" t="s">
+      <c r="A135" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="61"/>
-      <c r="C135" s="61"/>
+      <c r="B135" s="70"/>
+      <c r="C135" s="70"/>
       <c r="D135" s="14"/>
       <c r="E135" s="14"/>
       <c r="F135" s="16"/>
-      <c r="G135" s="40">
-        <f>SUM(G123:G134)</f>
-        <v>0</v>
-      </c>
-      <c r="H135" s="40">
-        <f t="shared" ref="H135:M135" si="8">SUM(H123:H134)</f>
-        <v>0</v>
-      </c>
-      <c r="I135" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J135" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K135" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L135" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M135" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="G135" s="40"/>
+      <c r="H135" s="40"/>
+      <c r="I135" s="40"/>
+      <c r="J135" s="40"/>
+      <c r="K135" s="40"/>
+      <c r="L135" s="40"/>
+      <c r="M135" s="40"/>
       <c r="N135" s="14"/>
     </row>
     <row r="136" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="63" t="s">
+      <c r="A136" s="61" t="s">
         <v>603</v>
       </c>
       <c r="B136" s="15" t="s">
@@ -9172,7 +8983,7 @@
       <c r="N136" s="14"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="63"/>
+      <c r="A137" s="61"/>
       <c r="B137" s="15" t="s">
         <v>368</v>
       </c>
@@ -9192,7 +9003,7 @@
       <c r="N137" s="14"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="63"/>
+      <c r="A138" s="61"/>
       <c r="B138" s="15" t="s">
         <v>235</v>
       </c>
@@ -9212,7 +9023,7 @@
       <c r="N138" s="14"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="63"/>
+      <c r="A139" s="61"/>
       <c r="B139" s="31" t="s">
         <v>221</v>
       </c>
@@ -9232,7 +9043,7 @@
       <c r="N139" s="14"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="63"/>
+      <c r="A140" s="61"/>
       <c r="B140" s="15" t="s">
         <v>320</v>
       </c>
@@ -9252,7 +9063,7 @@
       <c r="N140" s="14"/>
     </row>
     <row r="141" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="63"/>
+      <c r="A141" s="61"/>
       <c r="B141" s="15" t="s">
         <v>236</v>
       </c>
@@ -9272,7 +9083,7 @@
       <c r="N141" s="14"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="63"/>
+      <c r="A142" s="61"/>
       <c r="B142" s="31" t="s">
         <v>251</v>
       </c>
@@ -9292,7 +9103,7 @@
       <c r="N142" s="14"/>
     </row>
     <row r="143" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="63" t="s">
+      <c r="A143" s="61" t="s">
         <v>603</v>
       </c>
       <c r="B143" s="15" t="s">
@@ -9314,7 +9125,7 @@
       <c r="N143" s="14"/>
     </row>
     <row r="144" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="63"/>
+      <c r="A144" s="61"/>
       <c r="B144" s="15" t="s">
         <v>201</v>
       </c>
@@ -9334,7 +9145,7 @@
       <c r="N144" s="14"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="63"/>
+      <c r="A145" s="61"/>
       <c r="B145" s="15" t="s">
         <v>364</v>
       </c>
@@ -9354,7 +9165,7 @@
       <c r="N145" s="14"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="63"/>
+      <c r="A146" s="61"/>
       <c r="B146" s="15" t="s">
         <v>388</v>
       </c>
@@ -9374,7 +9185,7 @@
       <c r="N146" s="14"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="63"/>
+      <c r="A147" s="61"/>
       <c r="B147" s="15" t="s">
         <v>358</v>
       </c>
@@ -9394,7 +9205,7 @@
       <c r="N147" s="14"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="63"/>
+      <c r="A148" s="61"/>
       <c r="B148" s="15" t="s">
         <v>377</v>
       </c>
@@ -9414,7 +9225,7 @@
       <c r="N148" s="14"/>
     </row>
     <row r="149" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="63"/>
+      <c r="A149" s="61"/>
       <c r="B149" s="15" t="s">
         <v>370</v>
       </c>
@@ -9434,7 +9245,7 @@
       <c r="N149" s="14"/>
     </row>
     <row r="150" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="63"/>
+      <c r="A150" s="61"/>
       <c r="B150" s="15" t="s">
         <v>199</v>
       </c>
@@ -9454,7 +9265,7 @@
       <c r="N150" s="14"/>
     </row>
     <row r="151" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="63"/>
+      <c r="A151" s="61"/>
       <c r="B151" s="15" t="s">
         <v>260</v>
       </c>
@@ -9474,46 +9285,25 @@
       <c r="N151" s="14"/>
     </row>
     <row r="152" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="61" t="s">
+      <c r="A152" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B152" s="61"/>
-      <c r="C152" s="61"/>
+      <c r="B152" s="70"/>
+      <c r="C152" s="70"/>
       <c r="D152" s="14"/>
       <c r="E152" s="14"/>
       <c r="F152" s="16"/>
-      <c r="G152" s="40">
-        <f>SUM(G136:G151)</f>
-        <v>0</v>
-      </c>
-      <c r="H152" s="40">
-        <f t="shared" ref="H152:M152" si="9">SUM(H136:H151)</f>
-        <v>0</v>
-      </c>
-      <c r="I152" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J152" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K152" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L152" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M152" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="G152" s="40"/>
+      <c r="H152" s="40"/>
+      <c r="I152" s="40"/>
+      <c r="J152" s="40"/>
+      <c r="K152" s="40"/>
+      <c r="L152" s="40"/>
+      <c r="M152" s="40"/>
       <c r="N152" s="14"/>
     </row>
     <row r="153" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="63" t="s">
+      <c r="A153" s="61" t="s">
         <v>599</v>
       </c>
       <c r="B153" s="15" t="s">
@@ -9535,7 +9325,7 @@
       <c r="N153" s="14"/>
     </row>
     <row r="154" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="63"/>
+      <c r="A154" s="61"/>
       <c r="B154" s="15">
         <v>25034</v>
       </c>
@@ -9555,7 +9345,7 @@
       <c r="N154" s="14"/>
     </row>
     <row r="155" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="63"/>
+      <c r="A155" s="61"/>
       <c r="B155" s="15" t="s">
         <v>309</v>
       </c>
@@ -9597,7 +9387,7 @@
       <c r="N156" s="14"/>
     </row>
     <row r="157" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="63" t="s">
+      <c r="A157" s="61" t="s">
         <v>300</v>
       </c>
       <c r="B157" s="15" t="s">
@@ -9619,7 +9409,7 @@
       <c r="N157" s="14"/>
     </row>
     <row r="158" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="63"/>
+      <c r="A158" s="61"/>
       <c r="B158" s="31" t="s">
         <v>346</v>
       </c>
@@ -9639,7 +9429,7 @@
       <c r="N158" s="14"/>
     </row>
     <row r="159" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="63"/>
+      <c r="A159" s="61"/>
       <c r="B159" s="31" t="s">
         <v>670</v>
       </c>
@@ -9681,46 +9471,25 @@
       <c r="N160" s="14"/>
     </row>
     <row r="161" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="61" t="s">
+      <c r="A161" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B161" s="61"/>
-      <c r="C161" s="61"/>
+      <c r="B161" s="70"/>
+      <c r="C161" s="70"/>
       <c r="D161" s="14"/>
       <c r="E161" s="14"/>
       <c r="F161" s="16"/>
-      <c r="G161" s="40">
-        <f>SUM(G153:G160)</f>
-        <v>0</v>
-      </c>
-      <c r="H161" s="40">
-        <f t="shared" ref="H161:M161" si="10">SUM(H153:H160)</f>
-        <v>0</v>
-      </c>
-      <c r="I161" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J161" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K161" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L161" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M161" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
+      <c r="G161" s="40"/>
+      <c r="H161" s="40"/>
+      <c r="I161" s="40"/>
+      <c r="J161" s="40"/>
+      <c r="K161" s="40"/>
+      <c r="L161" s="40"/>
+      <c r="M161" s="40"/>
       <c r="N161" s="14"/>
     </row>
     <row r="162" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="64" t="s">
+      <c r="A162" s="80" t="s">
         <v>59</v>
       </c>
       <c r="B162" s="15" t="s">
@@ -9742,7 +9511,7 @@
       <c r="N162" s="14"/>
     </row>
     <row r="163" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="64"/>
+      <c r="A163" s="80"/>
       <c r="B163" s="15" t="s">
         <v>347</v>
       </c>
@@ -9762,7 +9531,7 @@
       <c r="N163" s="14"/>
     </row>
     <row r="164" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="64"/>
+      <c r="A164" s="80"/>
       <c r="B164" s="15" t="s">
         <v>421</v>
       </c>
@@ -9782,7 +9551,7 @@
       <c r="N164" s="14"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="64"/>
+      <c r="A165" s="80"/>
       <c r="B165" s="15" t="s">
         <v>323</v>
       </c>
@@ -9802,7 +9571,7 @@
       <c r="N165" s="14"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="64"/>
+      <c r="A166" s="80"/>
       <c r="B166" s="15" t="s">
         <v>342</v>
       </c>
@@ -9822,7 +9591,7 @@
       <c r="N166" s="14"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="64"/>
+      <c r="A167" s="80"/>
       <c r="B167" s="15" t="s">
         <v>322</v>
       </c>
@@ -9842,7 +9611,7 @@
       <c r="N167" s="14"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="64"/>
+      <c r="A168" s="80"/>
       <c r="B168" s="15" t="s">
         <v>291</v>
       </c>
@@ -9862,7 +9631,7 @@
       <c r="N168" s="14"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="64"/>
+      <c r="A169" s="80"/>
       <c r="B169" s="15" t="s">
         <v>331</v>
       </c>
@@ -9882,46 +9651,25 @@
       <c r="N169" s="14"/>
     </row>
     <row r="170" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="61" t="s">
+      <c r="A170" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B170" s="61"/>
-      <c r="C170" s="61"/>
+      <c r="B170" s="70"/>
+      <c r="C170" s="70"/>
       <c r="D170" s="14"/>
       <c r="E170" s="14"/>
       <c r="F170" s="16"/>
-      <c r="G170" s="40">
-        <f>SUM(G162:G169)</f>
-        <v>0</v>
-      </c>
-      <c r="H170" s="40">
-        <f t="shared" ref="H170:M170" si="11">SUM(H162:H169)</f>
-        <v>0</v>
-      </c>
-      <c r="I170" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J170" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K170" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L170" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M170" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+      <c r="G170" s="40"/>
+      <c r="H170" s="40"/>
+      <c r="I170" s="40"/>
+      <c r="J170" s="40"/>
+      <c r="K170" s="40"/>
+      <c r="L170" s="40"/>
+      <c r="M170" s="40"/>
       <c r="N170" s="14"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="63" t="s">
+      <c r="A171" s="61" t="s">
         <v>604</v>
       </c>
       <c r="B171" s="15" t="s">
@@ -9943,7 +9691,7 @@
       <c r="N171" s="14"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="63"/>
+      <c r="A172" s="61"/>
       <c r="B172" s="15" t="s">
         <v>266</v>
       </c>
@@ -9963,7 +9711,7 @@
       <c r="N172" s="14"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="63"/>
+      <c r="A173" s="61"/>
       <c r="B173" s="15" t="s">
         <v>362</v>
       </c>
@@ -9983,7 +9731,7 @@
       <c r="N173" s="14"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="63"/>
+      <c r="A174" s="61"/>
       <c r="B174" s="15" t="s">
         <v>379</v>
       </c>
@@ -10003,46 +9751,25 @@
       <c r="N174" s="14"/>
     </row>
     <row r="175" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="61" t="s">
+      <c r="A175" s="70" t="s">
         <v>135</v>
       </c>
-      <c r="B175" s="61"/>
-      <c r="C175" s="61"/>
+      <c r="B175" s="70"/>
+      <c r="C175" s="70"/>
       <c r="D175" s="14"/>
       <c r="E175" s="14"/>
       <c r="F175" s="16"/>
-      <c r="G175" s="40">
-        <f>SUM(G171:G174)</f>
-        <v>0</v>
-      </c>
-      <c r="H175" s="40">
-        <f t="shared" ref="H175:M175" si="12">SUM(H171:H174)</f>
-        <v>0</v>
-      </c>
-      <c r="I175" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J175" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K175" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L175" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M175" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+      <c r="G175" s="40"/>
+      <c r="H175" s="40"/>
+      <c r="I175" s="40"/>
+      <c r="J175" s="40"/>
+      <c r="K175" s="40"/>
+      <c r="L175" s="40"/>
+      <c r="M175" s="40"/>
       <c r="N175" s="14"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="63" t="s">
+      <c r="A176" s="61" t="s">
         <v>324</v>
       </c>
       <c r="B176" s="15" t="s">
@@ -10064,7 +9791,7 @@
       <c r="N176" s="14"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="63"/>
+      <c r="A177" s="61"/>
       <c r="B177" s="15" t="s">
         <v>445</v>
       </c>
@@ -10084,81 +9811,39 @@
       <c r="N177" s="14"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="71" t="s">
+      <c r="A178" s="72" t="s">
         <v>135</v>
       </c>
-      <c r="B178" s="71"/>
-      <c r="C178" s="71"/>
+      <c r="B178" s="72"/>
+      <c r="C178" s="72"/>
       <c r="D178" s="24"/>
       <c r="E178" s="24"/>
       <c r="F178" s="23"/>
-      <c r="G178" s="49">
-        <f>SUM(G176:G177)</f>
-        <v>0</v>
-      </c>
-      <c r="H178" s="49">
-        <f t="shared" ref="H178:M178" si="13">SUM(H176:H177)</f>
-        <v>0</v>
-      </c>
-      <c r="I178" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="J178" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="K178" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L178" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M178" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
+      <c r="G178" s="49"/>
+      <c r="H178" s="49"/>
+      <c r="I178" s="49"/>
+      <c r="J178" s="49"/>
+      <c r="K178" s="49"/>
+      <c r="L178" s="49"/>
+      <c r="M178" s="49"/>
       <c r="N178" s="24"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="67" t="s">
+      <c r="A179" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="B179" s="68"/>
-      <c r="C179" s="68"/>
+      <c r="B179" s="56"/>
+      <c r="C179" s="56"/>
       <c r="D179" s="51"/>
       <c r="E179" s="51"/>
       <c r="F179" s="53"/>
-      <c r="G179" s="50">
-        <f>SUM(G178,G175,G170,G161,G152,G135,G122,G117,G109,G92,G83,G51,G24,G19)</f>
-        <v>0</v>
-      </c>
-      <c r="H179" s="50">
-        <f t="shared" ref="H179:M179" si="14">SUM(H178,H175,H170,H161,H152,H135,H122,H117,H109,H92,H83,H51,H24,H19)</f>
-        <v>0</v>
-      </c>
-      <c r="I179" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="J179" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="K179" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="L179" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M179" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
+      <c r="G179" s="50"/>
+      <c r="H179" s="50"/>
+      <c r="I179" s="50"/>
+      <c r="J179" s="50"/>
+      <c r="K179" s="50"/>
+      <c r="L179" s="50"/>
+      <c r="M179" s="50"/>
       <c r="N179" s="52"/>
     </row>
     <row r="180" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -10181,105 +9866,128 @@
       <c r="A181" s="3"/>
       <c r="B181" s="1"/>
       <c r="C181" s="5"/>
-      <c r="D181" s="82"/>
-      <c r="E181" s="83"/>
-      <c r="F181" s="83"/>
-      <c r="G181" s="75"/>
-      <c r="H181" s="75"/>
-      <c r="I181" s="75"/>
-      <c r="J181" s="76"/>
+      <c r="D181" s="65"/>
+      <c r="E181" s="66"/>
+      <c r="F181" s="66"/>
+      <c r="G181" s="57"/>
+      <c r="H181" s="57"/>
+      <c r="I181" s="57"/>
+      <c r="J181" s="58"/>
       <c r="K181" s="8"/>
       <c r="L181" s="8"/>
       <c r="M181" s="8"/>
       <c r="N181" s="8"/>
     </row>
     <row r="182" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D182" s="84" t="s">
+      <c r="D182" s="67" t="s">
         <v>777</v>
       </c>
-      <c r="E182" s="85"/>
-      <c r="F182" s="85"/>
-      <c r="G182" s="77">
-        <f>N4</f>
-        <v>0</v>
-      </c>
-      <c r="H182" s="77"/>
-      <c r="I182" s="77">
-        <f>G182</f>
-        <v>0</v>
-      </c>
-      <c r="J182" s="78"/>
+      <c r="E182" s="68"/>
+      <c r="F182" s="68"/>
+      <c r="G182" s="59"/>
+      <c r="H182" s="59"/>
+      <c r="I182" s="59"/>
+      <c r="J182" s="60"/>
     </row>
     <row r="183" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D183" s="69" t="s">
         <v>778</v>
       </c>
-      <c r="E183" s="61"/>
-      <c r="F183" s="61"/>
-      <c r="G183" s="63">
-        <f>'반제품 임가공'!N4</f>
-        <v>0</v>
-      </c>
-      <c r="H183" s="63"/>
-      <c r="I183" s="63">
-        <f>G183</f>
-        <v>0</v>
-      </c>
-      <c r="J183" s="80"/>
+      <c r="E183" s="70"/>
+      <c r="F183" s="70"/>
+      <c r="G183" s="61"/>
+      <c r="H183" s="61"/>
+      <c r="I183" s="61"/>
+      <c r="J183" s="63"/>
     </row>
     <row r="184" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D184" s="69" t="s">
         <v>779</v>
       </c>
-      <c r="E184" s="61"/>
-      <c r="F184" s="61"/>
-      <c r="G184" s="63">
-        <f>'완제품 일반무역'!N4</f>
-        <v>0</v>
-      </c>
-      <c r="H184" s="63"/>
-      <c r="I184" s="63">
-        <f>G184</f>
-        <v>0</v>
-      </c>
-      <c r="J184" s="80"/>
+      <c r="E184" s="70"/>
+      <c r="F184" s="70"/>
+      <c r="G184" s="61"/>
+      <c r="H184" s="61"/>
+      <c r="I184" s="61"/>
+      <c r="J184" s="63"/>
     </row>
     <row r="185" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D185" s="70" t="s">
+      <c r="D185" s="71" t="s">
         <v>780</v>
       </c>
-      <c r="E185" s="71"/>
-      <c r="F185" s="71"/>
-      <c r="G185" s="79">
-        <f>'반제품 일반무역'!N4</f>
-        <v>0</v>
-      </c>
-      <c r="H185" s="79"/>
-      <c r="I185" s="79">
-        <f>G185</f>
-        <v>0</v>
-      </c>
-      <c r="J185" s="81"/>
+      <c r="E185" s="72"/>
+      <c r="F185" s="72"/>
+      <c r="G185" s="62"/>
+      <c r="H185" s="62"/>
+      <c r="I185" s="62"/>
+      <c r="J185" s="64"/>
     </row>
     <row r="186" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D186" s="67" t="s">
+      <c r="D186" s="55" t="s">
         <v>781</v>
       </c>
-      <c r="E186" s="68"/>
-      <c r="F186" s="68"/>
-      <c r="G186" s="75">
-        <f>SUM(G182:H185)</f>
-        <v>0</v>
-      </c>
-      <c r="H186" s="75"/>
-      <c r="I186" s="75">
-        <f>SUM(I182:J185)</f>
-        <v>0</v>
-      </c>
-      <c r="J186" s="75"/>
+      <c r="E186" s="56"/>
+      <c r="F186" s="56"/>
+      <c r="G186" s="57"/>
+      <c r="H186" s="57"/>
+      <c r="I186" s="57"/>
+      <c r="J186" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="69">
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A8:A18"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A25:A50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A75:A82"/>
+    <mergeCell ref="A83:C83"/>
+    <mergeCell ref="A84:A91"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="A93:A108"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="A110:A116"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A179:C179"/>
+    <mergeCell ref="A170:C170"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="A122:C122"/>
+    <mergeCell ref="A123:A134"/>
+    <mergeCell ref="A135:C135"/>
+    <mergeCell ref="A136:A142"/>
+    <mergeCell ref="A143:A151"/>
+    <mergeCell ref="A152:C152"/>
+    <mergeCell ref="A157:A159"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="A153:A155"/>
+    <mergeCell ref="A162:A169"/>
+    <mergeCell ref="D184:F184"/>
+    <mergeCell ref="D185:F185"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A171:A174"/>
+    <mergeCell ref="A175:C175"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A178:C178"/>
     <mergeCell ref="D186:F186"/>
     <mergeCell ref="G181:H181"/>
     <mergeCell ref="I181:J181"/>
@@ -10296,59 +10004,6 @@
     <mergeCell ref="D181:F181"/>
     <mergeCell ref="D182:F182"/>
     <mergeCell ref="D183:F183"/>
-    <mergeCell ref="D184:F184"/>
-    <mergeCell ref="D185:F185"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="A171:A174"/>
-    <mergeCell ref="A175:C175"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A178:C178"/>
-    <mergeCell ref="A179:C179"/>
-    <mergeCell ref="A170:C170"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="A122:C122"/>
-    <mergeCell ref="A123:A134"/>
-    <mergeCell ref="A135:C135"/>
-    <mergeCell ref="A136:A142"/>
-    <mergeCell ref="A143:A151"/>
-    <mergeCell ref="A152:C152"/>
-    <mergeCell ref="A157:A159"/>
-    <mergeCell ref="A161:C161"/>
-    <mergeCell ref="A153:A155"/>
-    <mergeCell ref="A162:A169"/>
-    <mergeCell ref="A25:A50"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A58:A63"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="A75:A82"/>
-    <mergeCell ref="A83:C83"/>
-    <mergeCell ref="A84:A91"/>
-    <mergeCell ref="A92:C92"/>
-    <mergeCell ref="A93:A108"/>
-    <mergeCell ref="A109:C109"/>
-    <mergeCell ref="A110:A116"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A8:A18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -12830,22 +12485,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="75" t="s">
         <v>717</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
@@ -12876,67 +12531,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="84" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="81" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="78" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="78" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="78" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="73" t="s">
         <v>723</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="73" t="s">
         <v>669</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="73" t="s">
         <v>673</v>
       </c>
-      <c r="I6" s="55" t="s">
+      <c r="I6" s="73" t="s">
         <v>680</v>
       </c>
-      <c r="J6" s="55" t="s">
+      <c r="J6" s="73" t="s">
         <v>681</v>
       </c>
-      <c r="K6" s="55" t="s">
+      <c r="K6" s="73" t="s">
         <v>682</v>
       </c>
-      <c r="L6" s="55" t="s">
+      <c r="L6" s="73" t="s">
         <v>700</v>
       </c>
-      <c r="M6" s="55" t="s">
+      <c r="M6" s="73" t="s">
         <v>724</v>
       </c>
-      <c r="N6" s="73" t="s">
+      <c r="N6" s="76" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="66"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="74"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="77"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="88" t="s">
         <v>728</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -12958,7 +12613,7 @@
       <c r="N8" s="29"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="87"/>
+      <c r="A9" s="86"/>
       <c r="B9" s="13" t="s">
         <v>410</v>
       </c>
@@ -12978,7 +12633,7 @@
       <c r="N9" s="28"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="87"/>
+      <c r="A10" s="86"/>
       <c r="B10" s="11" t="s">
         <v>341</v>
       </c>
@@ -12998,7 +12653,7 @@
       <c r="N10" s="28"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="87"/>
+      <c r="A11" s="86"/>
       <c r="B11" s="11" t="s">
         <v>293</v>
       </c>
@@ -13018,7 +12673,7 @@
       <c r="N11" s="28"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="87"/>
+      <c r="A12" s="86"/>
       <c r="B12" s="11" t="s">
         <v>391</v>
       </c>
@@ -13038,7 +12693,7 @@
       <c r="N12" s="28"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="87"/>
+      <c r="A13" s="86"/>
       <c r="B13" s="11" t="s">
         <v>420</v>
       </c>
@@ -13058,7 +12713,7 @@
       <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="87"/>
+      <c r="A14" s="86"/>
       <c r="B14" s="11" t="s">
         <v>426</v>
       </c>
@@ -13078,7 +12733,7 @@
       <c r="N14" s="28"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="87"/>
+      <c r="A15" s="86"/>
       <c r="B15" s="11" t="s">
         <v>424</v>
       </c>
@@ -13098,7 +12753,7 @@
       <c r="N15" s="28"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="87"/>
+      <c r="A16" s="86"/>
       <c r="B16" s="11" t="s">
         <v>290</v>
       </c>
@@ -13118,7 +12773,7 @@
       <c r="N16" s="28"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="87"/>
+      <c r="A17" s="86"/>
       <c r="B17" s="11" t="s">
         <v>497</v>
       </c>
@@ -13138,7 +12793,7 @@
       <c r="N17" s="28"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="87"/>
+      <c r="A18" s="86"/>
       <c r="B18" s="11" t="s">
         <v>425</v>
       </c>
@@ -13158,7 +12813,7 @@
       <c r="N18" s="28"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="87"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="11" t="s">
         <v>703</v>
       </c>
@@ -13181,43 +12836,22 @@
       <c r="A20" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="61"/>
-      <c r="C20" s="61"/>
+      <c r="B20" s="70"/>
+      <c r="C20" s="70"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
       <c r="F20" s="16"/>
-      <c r="G20" s="40">
-        <f t="shared" ref="G20:M20" si="0">SUM(G8:G19)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I20" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="G20" s="40"/>
+      <c r="H20" s="40"/>
+      <c r="I20" s="40"/>
+      <c r="J20" s="40"/>
+      <c r="K20" s="40"/>
+      <c r="L20" s="40"/>
+      <c r="M20" s="40"/>
       <c r="N20" s="28"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87" t="s">
+      <c r="A21" s="86" t="s">
         <v>730</v>
       </c>
       <c r="B21" s="41" t="s">
@@ -13239,7 +12873,7 @@
       <c r="N21" s="28"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="87"/>
+      <c r="A22" s="86"/>
       <c r="B22" s="42" t="s">
         <v>413</v>
       </c>
@@ -13259,7 +12893,7 @@
       <c r="N22" s="28"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
+      <c r="A23" s="86"/>
       <c r="B23" s="41" t="s">
         <v>439</v>
       </c>
@@ -13279,7 +12913,7 @@
       <c r="N23" s="28"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
+      <c r="A24" s="86"/>
       <c r="B24" s="41" t="s">
         <v>444</v>
       </c>
@@ -13299,7 +12933,7 @@
       <c r="N24" s="28"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="87"/>
+      <c r="A25" s="86"/>
       <c r="B25" s="41" t="s">
         <v>289</v>
       </c>
@@ -13319,7 +12953,7 @@
       <c r="N25" s="28"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
+      <c r="A26" s="86"/>
       <c r="B26" s="41" t="s">
         <v>477</v>
       </c>
@@ -13339,7 +12973,7 @@
       <c r="N26" s="28"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
+      <c r="A27" s="86"/>
       <c r="B27" s="41" t="s">
         <v>284</v>
       </c>
@@ -13359,7 +12993,7 @@
       <c r="N27" s="28"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
+      <c r="A28" s="86"/>
       <c r="B28" s="41" t="s">
         <v>731</v>
       </c>
@@ -13382,43 +13016,22 @@
       <c r="A29" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
       <c r="F29" s="16"/>
-      <c r="G29" s="40">
-        <f t="shared" ref="G29:M29" si="1">SUM(G21:G28)</f>
-        <v>0</v>
-      </c>
-      <c r="H29" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I29" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J29" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K29" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L29" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M29" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="G29" s="40"/>
+      <c r="H29" s="40"/>
+      <c r="I29" s="40"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="40"/>
+      <c r="L29" s="40"/>
+      <c r="M29" s="40"/>
       <c r="N29" s="28"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="87" t="s">
+      <c r="A30" s="86" t="s">
         <v>732</v>
       </c>
       <c r="B30" s="43" t="s">
@@ -13440,7 +13053,7 @@
       <c r="N30" s="28"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="87"/>
+      <c r="A31" s="86"/>
       <c r="B31" s="43" t="s">
         <v>383</v>
       </c>
@@ -13460,7 +13073,7 @@
       <c r="N31" s="28"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="87"/>
+      <c r="A32" s="86"/>
       <c r="B32" s="45" t="s">
         <v>419</v>
       </c>
@@ -13480,7 +13093,7 @@
       <c r="N32" s="28"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="87"/>
+      <c r="A33" s="86"/>
       <c r="B33" s="43" t="s">
         <v>449</v>
       </c>
@@ -13503,43 +13116,22 @@
       <c r="A34" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
+      <c r="B34" s="70"/>
+      <c r="C34" s="70"/>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
       <c r="F34" s="16"/>
-      <c r="G34" s="40">
-        <f>SUM(G30:G33)</f>
-        <v>0</v>
-      </c>
-      <c r="H34" s="40">
-        <f t="shared" ref="H34:M34" si="2">SUM(H30:H33)</f>
-        <v>0</v>
-      </c>
-      <c r="I34" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J34" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K34" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L34" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M34" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="G34" s="40"/>
+      <c r="H34" s="40"/>
+      <c r="I34" s="40"/>
+      <c r="J34" s="40"/>
+      <c r="K34" s="40"/>
+      <c r="L34" s="40"/>
+      <c r="M34" s="40"/>
       <c r="N34" s="28"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="88" t="s">
+      <c r="A35" s="87" t="s">
         <v>733</v>
       </c>
       <c r="B35" s="41" t="s">
@@ -13561,7 +13153,7 @@
       <c r="N35" s="28"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="88"/>
+      <c r="A36" s="87"/>
       <c r="B36" s="42" t="s">
         <v>461</v>
       </c>
@@ -13581,7 +13173,7 @@
       <c r="N36" s="28"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="88"/>
+      <c r="A37" s="87"/>
       <c r="B37" s="41" t="s">
         <v>274</v>
       </c>
@@ -13601,7 +13193,7 @@
       <c r="N37" s="28"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="88"/>
+      <c r="A38" s="87"/>
       <c r="B38" s="41" t="s">
         <v>248</v>
       </c>
@@ -13621,7 +13213,7 @@
       <c r="N38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="88"/>
+      <c r="A39" s="87"/>
       <c r="B39" s="41" t="s">
         <v>273</v>
       </c>
@@ -13641,7 +13233,7 @@
       <c r="N39" s="28"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="88"/>
+      <c r="A40" s="87"/>
       <c r="B40" s="41" t="s">
         <v>241</v>
       </c>
@@ -13661,7 +13253,7 @@
       <c r="N40" s="28"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="88"/>
+      <c r="A41" s="87"/>
       <c r="B41" s="41" t="s">
         <v>269</v>
       </c>
@@ -13681,7 +13273,7 @@
       <c r="N41" s="28"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="88"/>
+      <c r="A42" s="87"/>
       <c r="B42" s="41" t="s">
         <v>267</v>
       </c>
@@ -13701,7 +13293,7 @@
       <c r="N42" s="28"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="88"/>
+      <c r="A43" s="87"/>
       <c r="B43" s="41" t="s">
         <v>407</v>
       </c>
@@ -13721,7 +13313,7 @@
       <c r="N43" s="28"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="88"/>
+      <c r="A44" s="87"/>
       <c r="B44" s="41" t="s">
         <v>443</v>
       </c>
@@ -13741,7 +13333,7 @@
       <c r="N44" s="28"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="88"/>
+      <c r="A45" s="87"/>
       <c r="B45" s="41" t="s">
         <v>249</v>
       </c>
@@ -13761,7 +13353,7 @@
       <c r="N45" s="28"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="88"/>
+      <c r="A46" s="87"/>
       <c r="B46" s="41" t="s">
         <v>478</v>
       </c>
@@ -13784,43 +13376,22 @@
       <c r="A47" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="61"/>
-      <c r="C47" s="61"/>
+      <c r="B47" s="70"/>
+      <c r="C47" s="70"/>
       <c r="D47" s="14"/>
       <c r="E47" s="14"/>
       <c r="F47" s="16"/>
-      <c r="G47" s="40">
-        <f t="shared" ref="G47:M47" si="3">SUM(G35:G46)</f>
-        <v>0</v>
-      </c>
-      <c r="H47" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="I47" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J47" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K47" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L47" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M47" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="G47" s="40"/>
+      <c r="H47" s="40"/>
+      <c r="I47" s="40"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="40"/>
+      <c r="M47" s="40"/>
       <c r="N47" s="28"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="88" t="s">
+      <c r="A48" s="87" t="s">
         <v>734</v>
       </c>
       <c r="B48" s="15" t="s">
@@ -13842,7 +13413,7 @@
       <c r="N48" s="28"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="88"/>
+      <c r="A49" s="87"/>
       <c r="B49" s="15" t="s">
         <v>592</v>
       </c>
@@ -13862,7 +13433,7 @@
       <c r="N49" s="28"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="88"/>
+      <c r="A50" s="87"/>
       <c r="B50" s="15" t="s">
         <v>591</v>
       </c>
@@ -13882,7 +13453,7 @@
       <c r="N50" s="28"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="88"/>
+      <c r="A51" s="87"/>
       <c r="B51" s="15" t="s">
         <v>586</v>
       </c>
@@ -13902,7 +13473,7 @@
       <c r="N51" s="28"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="88"/>
+      <c r="A52" s="87"/>
       <c r="B52" s="15" t="s">
         <v>562</v>
       </c>
@@ -13922,7 +13493,7 @@
       <c r="N52" s="28"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="88"/>
+      <c r="A53" s="87"/>
       <c r="B53" s="15" t="s">
         <v>563</v>
       </c>
@@ -13942,7 +13513,7 @@
       <c r="N53" s="28"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="88"/>
+      <c r="A54" s="87"/>
       <c r="B54" s="15" t="s">
         <v>567</v>
       </c>
@@ -13962,7 +13533,7 @@
       <c r="N54" s="28"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="88"/>
+      <c r="A55" s="87"/>
       <c r="B55" s="15" t="s">
         <v>213</v>
       </c>
@@ -13982,7 +13553,7 @@
       <c r="N55" s="28"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="88"/>
+      <c r="A56" s="87"/>
       <c r="B56" s="15" t="s">
         <v>568</v>
       </c>
@@ -14002,7 +13573,7 @@
       <c r="N56" s="28"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="87"/>
+      <c r="A57" s="86"/>
       <c r="B57" s="15" t="s">
         <v>576</v>
       </c>
@@ -14022,7 +13593,7 @@
       <c r="N57" s="28"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="87"/>
+      <c r="A58" s="86"/>
       <c r="B58" s="15" t="s">
         <v>454</v>
       </c>
@@ -14045,43 +13616,22 @@
       <c r="A59" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B59" s="61"/>
-      <c r="C59" s="61"/>
+      <c r="B59" s="70"/>
+      <c r="C59" s="70"/>
       <c r="D59" s="14"/>
       <c r="E59" s="14"/>
       <c r="F59" s="16"/>
-      <c r="G59" s="40">
-        <f>SUM(G48:G58)</f>
-        <v>0</v>
-      </c>
-      <c r="H59" s="40">
-        <f t="shared" ref="H59:M59" si="4">SUM(H48:H58)</f>
-        <v>0</v>
-      </c>
-      <c r="I59" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J59" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K59" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L59" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M59" s="40">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="G59" s="40"/>
+      <c r="H59" s="40"/>
+      <c r="I59" s="40"/>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="40"/>
+      <c r="M59" s="40"/>
       <c r="N59" s="28"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="88" t="s">
+      <c r="A60" s="87" t="s">
         <v>736</v>
       </c>
       <c r="B60" s="15" t="s">
@@ -14103,7 +13653,7 @@
       <c r="N60" s="28"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="87"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="15" t="s">
         <v>469</v>
       </c>
@@ -14123,7 +13673,7 @@
       <c r="N61" s="28"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="87"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="15" t="s">
         <v>705</v>
       </c>
@@ -14143,7 +13693,7 @@
       <c r="N62" s="28"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="87"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="15" t="s">
         <v>457</v>
       </c>
@@ -14163,7 +13713,7 @@
       <c r="N63" s="28"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="87"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="15" t="s">
         <v>707</v>
       </c>
@@ -14183,7 +13733,7 @@
       <c r="N64" s="28"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="87"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="15" t="s">
         <v>438</v>
       </c>
@@ -14203,7 +13753,7 @@
       <c r="N65" s="28"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="87"/>
+      <c r="A66" s="86"/>
       <c r="B66" s="15" t="s">
         <v>709</v>
       </c>
@@ -14223,7 +13773,7 @@
       <c r="N66" s="28"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="87"/>
+      <c r="A67" s="86"/>
       <c r="B67" s="15" t="s">
         <v>694</v>
       </c>
@@ -14243,7 +13793,7 @@
       <c r="N67" s="28"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="87"/>
+      <c r="A68" s="86"/>
       <c r="B68" s="15" t="s">
         <v>441</v>
       </c>
@@ -14263,7 +13813,7 @@
       <c r="N68" s="28"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="87"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="15" t="s">
         <v>206</v>
       </c>
@@ -14283,7 +13833,7 @@
       <c r="N69" s="28"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="87"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="15" t="s">
         <v>711</v>
       </c>
@@ -14303,7 +13853,7 @@
       <c r="N70" s="28"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="87"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="15" t="s">
         <v>459</v>
       </c>
@@ -14323,7 +13873,7 @@
       <c r="N71" s="28"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="87"/>
+      <c r="A72" s="86"/>
       <c r="B72" s="15" t="s">
         <v>713</v>
       </c>
@@ -14343,7 +13893,7 @@
       <c r="N72" s="28"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="87"/>
+      <c r="A73" s="86"/>
       <c r="B73" s="15" t="s">
         <v>559</v>
       </c>
@@ -14363,7 +13913,7 @@
       <c r="N73" s="28"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="87"/>
+      <c r="A74" s="86"/>
       <c r="B74" s="15" t="s">
         <v>585</v>
       </c>
@@ -14386,43 +13936,22 @@
       <c r="A75" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B75" s="61"/>
-      <c r="C75" s="61"/>
+      <c r="B75" s="70"/>
+      <c r="C75" s="70"/>
       <c r="D75" s="14"/>
       <c r="E75" s="14"/>
       <c r="F75" s="16"/>
-      <c r="G75" s="40">
-        <f>SUM(G60:G74)</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="40">
-        <f t="shared" ref="H75:M75" si="5">SUM(H60:H74)</f>
-        <v>0</v>
-      </c>
-      <c r="I75" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J75" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K75" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L75" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M75" s="40">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="G75" s="40"/>
+      <c r="H75" s="40"/>
+      <c r="I75" s="40"/>
+      <c r="J75" s="40"/>
+      <c r="K75" s="40"/>
+      <c r="L75" s="40"/>
+      <c r="M75" s="40"/>
       <c r="N75" s="28"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="88" t="s">
+      <c r="A76" s="87" t="s">
         <v>737</v>
       </c>
       <c r="B76" s="46" t="s">
@@ -14444,7 +13973,7 @@
       <c r="N76" s="28"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="88"/>
+      <c r="A77" s="87"/>
       <c r="B77" s="41" t="s">
         <v>570</v>
       </c>
@@ -14464,7 +13993,7 @@
       <c r="N77" s="28"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="88"/>
+      <c r="A78" s="87"/>
       <c r="B78" s="46" t="s">
         <v>594</v>
       </c>
@@ -14484,7 +14013,7 @@
       <c r="N78" s="28"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="88"/>
+      <c r="A79" s="87"/>
       <c r="B79" s="46" t="s">
         <v>231</v>
       </c>
@@ -14504,7 +14033,7 @@
       <c r="N79" s="28"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="88"/>
+      <c r="A80" s="87"/>
       <c r="B80" s="46" t="s">
         <v>219</v>
       </c>
@@ -14524,7 +14053,7 @@
       <c r="N80" s="28"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="88"/>
+      <c r="A81" s="87"/>
       <c r="B81" s="46" t="s">
         <v>237</v>
       </c>
@@ -14547,43 +14076,22 @@
       <c r="A82" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B82" s="61"/>
-      <c r="C82" s="61"/>
+      <c r="B82" s="70"/>
+      <c r="C82" s="70"/>
       <c r="D82" s="14"/>
       <c r="E82" s="14"/>
       <c r="F82" s="16"/>
-      <c r="G82" s="40">
-        <f>SUM(G76:G81)</f>
-        <v>0</v>
-      </c>
-      <c r="H82" s="40">
-        <f t="shared" ref="H82:M82" si="6">SUM(H76:H81)</f>
-        <v>0</v>
-      </c>
-      <c r="I82" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="J82" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="K82" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="L82" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M82" s="40">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+      <c r="G82" s="40"/>
+      <c r="H82" s="40"/>
+      <c r="I82" s="40"/>
+      <c r="J82" s="40"/>
+      <c r="K82" s="40"/>
+      <c r="L82" s="40"/>
+      <c r="M82" s="40"/>
       <c r="N82" s="28"/>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="88" t="s">
+      <c r="A83" s="87" t="s">
         <v>738</v>
       </c>
       <c r="B83" s="46" t="s">
@@ -14605,7 +14113,7 @@
       <c r="N83" s="28"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="88"/>
+      <c r="A84" s="87"/>
       <c r="B84" s="46" t="s">
         <v>205</v>
       </c>
@@ -14625,7 +14133,7 @@
       <c r="N84" s="28"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="88"/>
+      <c r="A85" s="87"/>
       <c r="B85" s="46" t="s">
         <v>233</v>
       </c>
@@ -14645,7 +14153,7 @@
       <c r="N85" s="28"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="88"/>
+      <c r="A86" s="87"/>
       <c r="B86" s="46" t="s">
         <v>211</v>
       </c>
@@ -14668,43 +14176,22 @@
       <c r="A87" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B87" s="61"/>
-      <c r="C87" s="61"/>
+      <c r="B87" s="70"/>
+      <c r="C87" s="70"/>
       <c r="D87" s="14"/>
       <c r="E87" s="14"/>
       <c r="F87" s="16"/>
-      <c r="G87" s="40">
-        <f>SUM(G83:G86)</f>
-        <v>0</v>
-      </c>
-      <c r="H87" s="40">
-        <f t="shared" ref="H87:M87" si="7">SUM(H83:H86)</f>
-        <v>0</v>
-      </c>
-      <c r="I87" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="J87" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="K87" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="L87" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="M87" s="40">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
+      <c r="G87" s="40"/>
+      <c r="H87" s="40"/>
+      <c r="I87" s="40"/>
+      <c r="J87" s="40"/>
+      <c r="K87" s="40"/>
+      <c r="L87" s="40"/>
+      <c r="M87" s="40"/>
       <c r="N87" s="28"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="88" t="s">
+      <c r="A88" s="87" t="s">
         <v>739</v>
       </c>
       <c r="B88" s="31" t="s">
@@ -14726,7 +14213,7 @@
       <c r="N88" s="28"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="88"/>
+      <c r="A89" s="87"/>
       <c r="B89" s="31" t="s">
         <v>275</v>
       </c>
@@ -14746,7 +14233,7 @@
       <c r="N89" s="28"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="88"/>
+      <c r="A90" s="87"/>
       <c r="B90" s="31" t="s">
         <v>389</v>
       </c>
@@ -14766,7 +14253,7 @@
       <c r="N90" s="28"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="88"/>
+      <c r="A91" s="87"/>
       <c r="B91" s="31" t="s">
         <v>313</v>
       </c>
@@ -14786,7 +14273,7 @@
       <c r="N91" s="28"/>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="88"/>
+      <c r="A92" s="87"/>
       <c r="B92" s="31" t="s">
         <v>385</v>
       </c>
@@ -14806,7 +14293,7 @@
       <c r="N92" s="28"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="88"/>
+      <c r="A93" s="87"/>
       <c r="B93" s="31" t="s">
         <v>693</v>
       </c>
@@ -14829,43 +14316,22 @@
       <c r="A94" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B94" s="61"/>
-      <c r="C94" s="61"/>
+      <c r="B94" s="70"/>
+      <c r="C94" s="70"/>
       <c r="D94" s="14"/>
       <c r="E94" s="14"/>
       <c r="F94" s="16"/>
-      <c r="G94" s="40">
-        <f>SUM(G88:G93)</f>
-        <v>0</v>
-      </c>
-      <c r="H94" s="40">
-        <f t="shared" ref="H94:M94" si="8">SUM(H88:H93)</f>
-        <v>0</v>
-      </c>
-      <c r="I94" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="J94" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="K94" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="L94" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="M94" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
+      <c r="G94" s="40"/>
+      <c r="H94" s="40"/>
+      <c r="I94" s="40"/>
+      <c r="J94" s="40"/>
+      <c r="K94" s="40"/>
+      <c r="L94" s="40"/>
+      <c r="M94" s="40"/>
       <c r="N94" s="28"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="88" t="s">
+      <c r="A95" s="87" t="s">
         <v>740</v>
       </c>
       <c r="B95" s="15" t="s">
@@ -14887,7 +14353,7 @@
       <c r="N95" s="28"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="88"/>
+      <c r="A96" s="87"/>
       <c r="B96" s="15" t="s">
         <v>315</v>
       </c>
@@ -14907,7 +14373,7 @@
       <c r="N96" s="28"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="88" t="s">
+      <c r="A97" s="87" t="s">
         <v>741</v>
       </c>
       <c r="B97" s="15" t="s">
@@ -14929,7 +14395,7 @@
       <c r="N97" s="28"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="87"/>
+      <c r="A98" s="86"/>
       <c r="B98" s="15" t="s">
         <v>277</v>
       </c>
@@ -14952,43 +14418,22 @@
       <c r="A99" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B99" s="61"/>
-      <c r="C99" s="61"/>
+      <c r="B99" s="70"/>
+      <c r="C99" s="70"/>
       <c r="D99" s="14"/>
       <c r="E99" s="14"/>
       <c r="F99" s="16"/>
-      <c r="G99" s="40">
-        <f>SUM(G95:G98)</f>
-        <v>0</v>
-      </c>
-      <c r="H99" s="40">
-        <f t="shared" ref="H99:M99" si="9">SUM(H95:H98)</f>
-        <v>0</v>
-      </c>
-      <c r="I99" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="J99" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="K99" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="L99" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="M99" s="40">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
+      <c r="G99" s="40"/>
+      <c r="H99" s="40"/>
+      <c r="I99" s="40"/>
+      <c r="J99" s="40"/>
+      <c r="K99" s="40"/>
+      <c r="L99" s="40"/>
+      <c r="M99" s="40"/>
       <c r="N99" s="28"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="88" t="s">
+      <c r="A100" s="87" t="s">
         <v>743</v>
       </c>
       <c r="B100" s="15" t="s">
@@ -15010,7 +14455,7 @@
       <c r="N100" s="28"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="87"/>
+      <c r="A101" s="86"/>
       <c r="B101" s="15" t="s">
         <v>467</v>
       </c>
@@ -15030,7 +14475,7 @@
       <c r="N101" s="28"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="87"/>
+      <c r="A102" s="86"/>
       <c r="B102" s="15" t="s">
         <v>464</v>
       </c>
@@ -15050,7 +14495,7 @@
       <c r="N102" s="28"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="87"/>
+      <c r="A103" s="86"/>
       <c r="B103" s="15" t="s">
         <v>408</v>
       </c>
@@ -15070,7 +14515,7 @@
       <c r="N103" s="28"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="87"/>
+      <c r="A104" s="86"/>
       <c r="B104" s="15" t="s">
         <v>692</v>
       </c>
@@ -15090,7 +14535,7 @@
       <c r="N104" s="28"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="87"/>
+      <c r="A105" s="86"/>
       <c r="B105" s="15" t="s">
         <v>691</v>
       </c>
@@ -15110,7 +14555,7 @@
       <c r="N105" s="28"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="87"/>
+      <c r="A106" s="86"/>
       <c r="B106" s="15" t="s">
         <v>437</v>
       </c>
@@ -15130,7 +14575,7 @@
       <c r="N106" s="28"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="87"/>
+      <c r="A107" s="86"/>
       <c r="B107" s="15" t="s">
         <v>416</v>
       </c>
@@ -15150,7 +14595,7 @@
       <c r="N107" s="28"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="87"/>
+      <c r="A108" s="86"/>
       <c r="B108" s="15" t="s">
         <v>292</v>
       </c>
@@ -15170,7 +14615,7 @@
       <c r="N108" s="28"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="87"/>
+      <c r="A109" s="86"/>
       <c r="B109" s="15" t="s">
         <v>378</v>
       </c>
@@ -15190,7 +14635,7 @@
       <c r="N109" s="28"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="87"/>
+      <c r="A110" s="86"/>
       <c r="B110" s="15" t="s">
         <v>287</v>
       </c>
@@ -15210,7 +14655,7 @@
       <c r="N110" s="28"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="87"/>
+      <c r="A111" s="86"/>
       <c r="B111" s="15" t="s">
         <v>481</v>
       </c>
@@ -15230,7 +14675,7 @@
       <c r="N111" s="28"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="87"/>
+      <c r="A112" s="86"/>
       <c r="B112" s="15" t="s">
         <v>271</v>
       </c>
@@ -15250,7 +14695,7 @@
       <c r="N112" s="28"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="87"/>
+      <c r="A113" s="86"/>
       <c r="B113" s="15" t="s">
         <v>422</v>
       </c>
@@ -15270,7 +14715,7 @@
       <c r="N113" s="28"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="87"/>
+      <c r="A114" s="86"/>
       <c r="B114" s="15" t="s">
         <v>282</v>
       </c>
@@ -15290,7 +14735,7 @@
       <c r="N114" s="28"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="88" t="s">
+      <c r="A115" s="87" t="s">
         <v>744</v>
       </c>
       <c r="B115" s="15" t="s">
@@ -15312,7 +14757,7 @@
       <c r="N115" s="28"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="87"/>
+      <c r="A116" s="86"/>
       <c r="B116" s="15" t="s">
         <v>447</v>
       </c>
@@ -15332,7 +14777,7 @@
       <c r="N116" s="28"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="87"/>
+      <c r="A117" s="86"/>
       <c r="B117" s="15" t="s">
         <v>402</v>
       </c>
@@ -15352,7 +14797,7 @@
       <c r="N117" s="28"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="87"/>
+      <c r="A118" s="86"/>
       <c r="B118" s="15" t="s">
         <v>435</v>
       </c>
@@ -15372,7 +14817,7 @@
       <c r="N118" s="28"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="87"/>
+      <c r="A119" s="86"/>
       <c r="B119" s="15" t="s">
         <v>427</v>
       </c>
@@ -15392,7 +14837,7 @@
       <c r="N119" s="28"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="87"/>
+      <c r="A120" s="86"/>
       <c r="B120" s="15" t="s">
         <v>488</v>
       </c>
@@ -15412,7 +14857,7 @@
       <c r="N120" s="28"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="87"/>
+      <c r="A121" s="86"/>
       <c r="B121" s="15" t="s">
         <v>493</v>
       </c>
@@ -15432,7 +14877,7 @@
       <c r="N121" s="28"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="87"/>
+      <c r="A122" s="86"/>
       <c r="B122" s="15" t="s">
         <v>452</v>
       </c>
@@ -15452,7 +14897,7 @@
       <c r="N122" s="28"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="87"/>
+      <c r="A123" s="86"/>
       <c r="B123" s="15" t="s">
         <v>268</v>
       </c>
@@ -15472,7 +14917,7 @@
       <c r="N123" s="28"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="88" t="s">
+      <c r="A124" s="87" t="s">
         <v>745</v>
       </c>
       <c r="B124" s="15" t="s">
@@ -15494,7 +14939,7 @@
       <c r="N124" s="28"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="87"/>
+      <c r="A125" s="86"/>
       <c r="B125" s="15" t="s">
         <v>484</v>
       </c>
@@ -15514,7 +14959,7 @@
       <c r="N125" s="28"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="87"/>
+      <c r="A126" s="86"/>
       <c r="B126" s="15" t="s">
         <v>297</v>
       </c>
@@ -15534,7 +14979,7 @@
       <c r="N126" s="28"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="87"/>
+      <c r="A127" s="86"/>
       <c r="B127" s="15" t="s">
         <v>468</v>
       </c>
@@ -15554,7 +14999,7 @@
       <c r="N127" s="28"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="87"/>
+      <c r="A128" s="86"/>
       <c r="B128" s="15" t="s">
         <v>283</v>
       </c>
@@ -15574,7 +15019,7 @@
       <c r="N128" s="28"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="87"/>
+      <c r="A129" s="86"/>
       <c r="B129" s="15" t="s">
         <v>288</v>
       </c>
@@ -15594,7 +15039,7 @@
       <c r="N129" s="28"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="87"/>
+      <c r="A130" s="86"/>
       <c r="B130" s="15" t="s">
         <v>471</v>
       </c>
@@ -15614,7 +15059,7 @@
       <c r="N130" s="28"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="87"/>
+      <c r="A131" s="86"/>
       <c r="B131" s="15" t="s">
         <v>270</v>
       </c>
@@ -15634,7 +15079,7 @@
       <c r="N131" s="28"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="87"/>
+      <c r="A132" s="86"/>
       <c r="B132" s="15" t="s">
         <v>317</v>
       </c>
@@ -15654,7 +15099,7 @@
       <c r="N132" s="28"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="87"/>
+      <c r="A133" s="86"/>
       <c r="B133" s="15" t="s">
         <v>303</v>
       </c>
@@ -15674,7 +15119,7 @@
       <c r="N133" s="28"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="87"/>
+      <c r="A134" s="86"/>
       <c r="B134" s="15" t="s">
         <v>307</v>
       </c>
@@ -15694,7 +15139,7 @@
       <c r="N134" s="28"/>
     </row>
     <row r="135" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="87"/>
+      <c r="A135" s="86"/>
       <c r="B135" s="15" t="s">
         <v>247</v>
       </c>
@@ -15714,7 +15159,7 @@
       <c r="N135" s="28"/>
     </row>
     <row r="136" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="88" t="s">
+      <c r="A136" s="87" t="s">
         <v>746</v>
       </c>
       <c r="B136" s="15" t="s">
@@ -15736,7 +15181,7 @@
       <c r="N136" s="28"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="87"/>
+      <c r="A137" s="86"/>
       <c r="B137" s="15" t="s">
         <v>246</v>
       </c>
@@ -15756,7 +15201,7 @@
       <c r="N137" s="28"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="87"/>
+      <c r="A138" s="86"/>
       <c r="B138" s="15" t="s">
         <v>343</v>
       </c>
@@ -15776,7 +15221,7 @@
       <c r="N138" s="28"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="87"/>
+      <c r="A139" s="86"/>
       <c r="B139" s="15" t="s">
         <v>329</v>
       </c>
@@ -15796,7 +15241,7 @@
       <c r="N139" s="28"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="87"/>
+      <c r="A140" s="86"/>
       <c r="B140" s="15" t="s">
         <v>279</v>
       </c>
@@ -15816,7 +15261,7 @@
       <c r="N140" s="28"/>
     </row>
     <row r="141" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="87"/>
+      <c r="A141" s="86"/>
       <c r="B141" s="15" t="s">
         <v>328</v>
       </c>
@@ -15836,7 +15281,7 @@
       <c r="N141" s="28"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="87"/>
+      <c r="A142" s="86"/>
       <c r="B142" s="15" t="s">
         <v>272</v>
       </c>
@@ -15878,7 +15323,7 @@
       <c r="N143" s="28"/>
     </row>
     <row r="144" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="88" t="s">
+      <c r="A144" s="87" t="s">
         <v>748</v>
       </c>
       <c r="B144" s="15" t="s">
@@ -15900,7 +15345,7 @@
       <c r="N144" s="28"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="87"/>
+      <c r="A145" s="86"/>
       <c r="B145" s="15" t="s">
         <v>338</v>
       </c>
@@ -15920,7 +15365,7 @@
       <c r="N145" s="28"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="87"/>
+      <c r="A146" s="86"/>
       <c r="B146" s="15" t="s">
         <v>301</v>
       </c>
@@ -15940,7 +15385,7 @@
       <c r="N146" s="28"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="87"/>
+      <c r="A147" s="86"/>
       <c r="B147" s="15" t="s">
         <v>432</v>
       </c>
@@ -15960,7 +15405,7 @@
       <c r="N147" s="28"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="87"/>
+      <c r="A148" s="86"/>
       <c r="B148" s="15" t="s">
         <v>264</v>
       </c>
@@ -15983,43 +15428,22 @@
       <c r="A149" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B149" s="61"/>
-      <c r="C149" s="61"/>
+      <c r="B149" s="70"/>
+      <c r="C149" s="70"/>
       <c r="D149" s="14"/>
       <c r="E149" s="14"/>
       <c r="F149" s="16"/>
-      <c r="G149" s="40">
-        <f>SUM(G100:G148)</f>
-        <v>0</v>
-      </c>
-      <c r="H149" s="40">
-        <f t="shared" ref="H149:M149" si="10">SUM(H100:H148)</f>
-        <v>0</v>
-      </c>
-      <c r="I149" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="J149" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="K149" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="L149" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="M149" s="40">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
+      <c r="G149" s="40"/>
+      <c r="H149" s="40"/>
+      <c r="I149" s="40"/>
+      <c r="J149" s="40"/>
+      <c r="K149" s="40"/>
+      <c r="L149" s="40"/>
+      <c r="M149" s="40"/>
       <c r="N149" s="28"/>
     </row>
     <row r="150" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="88" t="s">
+      <c r="A150" s="87" t="s">
         <v>750</v>
       </c>
       <c r="B150" s="31" t="s">
@@ -16041,7 +15465,7 @@
       <c r="N150" s="28"/>
     </row>
     <row r="151" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="88"/>
+      <c r="A151" s="87"/>
       <c r="B151" s="31" t="s">
         <v>423</v>
       </c>
@@ -16061,7 +15485,7 @@
       <c r="N151" s="28"/>
     </row>
     <row r="152" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="88"/>
+      <c r="A152" s="87"/>
       <c r="B152" s="31" t="s">
         <v>340</v>
       </c>
@@ -16081,7 +15505,7 @@
       <c r="N152" s="28"/>
     </row>
     <row r="153" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="88"/>
+      <c r="A153" s="87"/>
       <c r="B153" s="31" t="s">
         <v>310</v>
       </c>
@@ -16101,7 +15525,7 @@
       <c r="N153" s="28"/>
     </row>
     <row r="154" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="88"/>
+      <c r="A154" s="87"/>
       <c r="B154" s="31" t="s">
         <v>276</v>
       </c>
@@ -16121,7 +15545,7 @@
       <c r="N154" s="28"/>
     </row>
     <row r="155" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="88"/>
+      <c r="A155" s="87"/>
       <c r="B155" s="31" t="s">
         <v>382</v>
       </c>
@@ -16141,7 +15565,7 @@
       <c r="N155" s="28"/>
     </row>
     <row r="156" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="88" t="s">
+      <c r="A156" s="87" t="s">
         <v>751</v>
       </c>
       <c r="B156" s="31" t="s">
@@ -16163,7 +15587,7 @@
       <c r="N156" s="28"/>
     </row>
     <row r="157" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="88"/>
+      <c r="A157" s="87"/>
       <c r="B157" s="31" t="s">
         <v>306</v>
       </c>
@@ -16183,7 +15607,7 @@
       <c r="N157" s="28"/>
     </row>
     <row r="158" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="88"/>
+      <c r="A158" s="87"/>
       <c r="B158" s="31" t="s">
         <v>278</v>
       </c>
@@ -16203,7 +15627,7 @@
       <c r="N158" s="28"/>
     </row>
     <row r="159" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="88"/>
+      <c r="A159" s="87"/>
       <c r="B159" s="31" t="s">
         <v>265</v>
       </c>
@@ -16223,7 +15647,7 @@
       <c r="N159" s="28"/>
     </row>
     <row r="160" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="88"/>
+      <c r="A160" s="87"/>
       <c r="B160" s="31" t="s">
         <v>417</v>
       </c>
@@ -16243,7 +15667,7 @@
       <c r="N160" s="28"/>
     </row>
     <row r="161" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="88"/>
+      <c r="A161" s="87"/>
       <c r="B161" s="31" t="s">
         <v>332</v>
       </c>
@@ -16263,7 +15687,7 @@
       <c r="N161" s="28"/>
     </row>
     <row r="162" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="88" t="s">
+      <c r="A162" s="87" t="s">
         <v>752</v>
       </c>
       <c r="B162" s="31" t="s">
@@ -16285,7 +15709,7 @@
       <c r="N162" s="28"/>
     </row>
     <row r="163" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="88"/>
+      <c r="A163" s="87"/>
       <c r="B163" s="31" t="s">
         <v>701</v>
       </c>
@@ -16308,43 +15732,22 @@
       <c r="A164" s="69" t="s">
         <v>595</v>
       </c>
-      <c r="B164" s="61"/>
-      <c r="C164" s="61"/>
+      <c r="B164" s="70"/>
+      <c r="C164" s="70"/>
       <c r="D164" s="14"/>
       <c r="E164" s="14"/>
       <c r="F164" s="16"/>
-      <c r="G164" s="40">
-        <f>SUM(G150:G163)</f>
-        <v>0</v>
-      </c>
-      <c r="H164" s="40">
-        <f t="shared" ref="H164:M164" si="11">SUM(H150:H163)</f>
-        <v>0</v>
-      </c>
-      <c r="I164" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="J164" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="K164" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="L164" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
-      <c r="M164" s="40">
-        <f t="shared" si="11"/>
-        <v>0</v>
-      </c>
+      <c r="G164" s="40"/>
+      <c r="H164" s="40"/>
+      <c r="I164" s="40"/>
+      <c r="J164" s="40"/>
+      <c r="K164" s="40"/>
+      <c r="L164" s="40"/>
+      <c r="M164" s="40"/>
       <c r="N164" s="28"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="87" t="s">
+      <c r="A165" s="86" t="s">
         <v>252</v>
       </c>
       <c r="B165" s="15" t="s">
@@ -16366,7 +15769,7 @@
       <c r="N165" s="28"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="87"/>
+      <c r="A166" s="86"/>
       <c r="B166" s="15" t="s">
         <v>294</v>
       </c>
@@ -16386,7 +15789,7 @@
       <c r="N166" s="28"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="87"/>
+      <c r="A167" s="86"/>
       <c r="B167" s="15" t="s">
         <v>294</v>
       </c>
@@ -16406,7 +15809,7 @@
       <c r="N167" s="28"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="87" t="s">
+      <c r="A168" s="86" t="s">
         <v>768</v>
       </c>
       <c r="B168" s="15" t="s">
@@ -16428,7 +15831,7 @@
       <c r="N168" s="28"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="87"/>
+      <c r="A169" s="86"/>
       <c r="B169" s="15" t="s">
         <v>428</v>
       </c>
@@ -16448,7 +15851,7 @@
       <c r="N169" s="28"/>
     </row>
     <row r="170" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="87" t="s">
+      <c r="A170" s="86" t="s">
         <v>767</v>
       </c>
       <c r="B170" s="15" t="s">
@@ -16470,7 +15873,7 @@
       <c r="N170" s="28"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="87"/>
+      <c r="A171" s="86"/>
       <c r="B171" s="15" t="s">
         <v>412</v>
       </c>
@@ -16490,7 +15893,7 @@
       <c r="N171" s="28"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="87" t="s">
+      <c r="A172" s="86" t="s">
         <v>766</v>
       </c>
       <c r="B172" s="15" t="s">
@@ -16512,7 +15915,7 @@
       <c r="N172" s="28"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="87"/>
+      <c r="A173" s="86"/>
       <c r="B173" s="15" t="s">
         <v>369</v>
       </c>
@@ -16532,7 +15935,7 @@
       <c r="N173" s="28"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="87" t="s">
+      <c r="A174" s="86" t="s">
         <v>765</v>
       </c>
       <c r="B174" s="15" t="s">
@@ -16554,7 +15957,7 @@
       <c r="N174" s="28"/>
     </row>
     <row r="175" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="87"/>
+      <c r="A175" s="86"/>
       <c r="B175" s="15" t="s">
         <v>696</v>
       </c>
@@ -16574,7 +15977,7 @@
       <c r="N175" s="28"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="87"/>
+      <c r="A176" s="86"/>
       <c r="B176" s="15" t="s">
         <v>697</v>
       </c>
@@ -16594,7 +15997,7 @@
       <c r="N176" s="28"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="87"/>
+      <c r="A177" s="86"/>
       <c r="B177" s="15" t="s">
         <v>698</v>
       </c>
@@ -16614,7 +16017,7 @@
       <c r="N177" s="28"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="87"/>
+      <c r="A178" s="86"/>
       <c r="B178" s="15" t="s">
         <v>699</v>
       </c>
@@ -16634,7 +16037,7 @@
       <c r="N178" s="28"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="87" t="s">
+      <c r="A179" s="86" t="s">
         <v>764</v>
       </c>
       <c r="B179" s="15" t="s">
@@ -16656,7 +16059,7 @@
       <c r="N179" s="28"/>
     </row>
     <row r="180" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="87"/>
+      <c r="A180" s="86"/>
       <c r="B180" s="15" t="s">
         <v>344</v>
       </c>
@@ -16676,7 +16079,7 @@
       <c r="N180" s="28"/>
     </row>
     <row r="181" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="87" t="s">
+      <c r="A181" s="86" t="s">
         <v>763</v>
       </c>
       <c r="B181" s="15" t="s">
@@ -16698,7 +16101,7 @@
       <c r="N181" s="28"/>
     </row>
     <row r="182" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="87"/>
+      <c r="A182" s="86"/>
       <c r="B182" s="15" t="s">
         <v>296</v>
       </c>
@@ -16718,7 +16121,7 @@
       <c r="N182" s="28"/>
     </row>
     <row r="183" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="87"/>
+      <c r="A183" s="86"/>
       <c r="B183" s="15" t="s">
         <v>316</v>
       </c>
@@ -16741,43 +16144,22 @@
       <c r="A184" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B184" s="61"/>
-      <c r="C184" s="61"/>
+      <c r="B184" s="70"/>
+      <c r="C184" s="70"/>
       <c r="D184" s="14"/>
       <c r="E184" s="14"/>
       <c r="F184" s="16"/>
-      <c r="G184" s="40">
-        <f>SUM(G165:G183)</f>
-        <v>0</v>
-      </c>
-      <c r="H184" s="40">
-        <f t="shared" ref="H184:M184" si="12">SUM(H165:H183)</f>
-        <v>0</v>
-      </c>
-      <c r="I184" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="J184" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="K184" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="L184" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
-      <c r="M184" s="40">
-        <f t="shared" si="12"/>
-        <v>0</v>
-      </c>
+      <c r="G184" s="40"/>
+      <c r="H184" s="40"/>
+      <c r="I184" s="40"/>
+      <c r="J184" s="40"/>
+      <c r="K184" s="40"/>
+      <c r="L184" s="40"/>
+      <c r="M184" s="40"/>
       <c r="N184" s="28"/>
     </row>
     <row r="185" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="87" t="s">
+      <c r="A185" s="86" t="s">
         <v>775</v>
       </c>
       <c r="B185" s="15" t="s">
@@ -16799,7 +16181,7 @@
       <c r="N185" s="28"/>
     </row>
     <row r="186" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="87"/>
+      <c r="A186" s="86"/>
       <c r="B186" s="15" t="s">
         <v>527</v>
       </c>
@@ -16819,7 +16201,7 @@
       <c r="N186" s="28"/>
     </row>
     <row r="187" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="87" t="s">
+      <c r="A187" s="86" t="s">
         <v>776</v>
       </c>
       <c r="B187" s="15" t="s">
@@ -16841,7 +16223,7 @@
       <c r="N187" s="28"/>
     </row>
     <row r="188" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="87"/>
+      <c r="A188" s="86"/>
       <c r="B188" s="15" t="s">
         <v>513</v>
       </c>
@@ -16861,7 +16243,7 @@
       <c r="N188" s="28"/>
     </row>
     <row r="189" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="87"/>
+      <c r="A189" s="86"/>
       <c r="B189" s="15" t="s">
         <v>518</v>
       </c>
@@ -16881,7 +16263,7 @@
       <c r="N189" s="28"/>
     </row>
     <row r="190" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="87"/>
+      <c r="A190" s="86"/>
       <c r="B190" s="15" t="s">
         <v>525</v>
       </c>
@@ -16901,7 +16283,7 @@
       <c r="N190" s="28"/>
     </row>
     <row r="191" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="87"/>
+      <c r="A191" s="86"/>
       <c r="B191" s="15" t="s">
         <v>499</v>
       </c>
@@ -16921,7 +16303,7 @@
       <c r="N191" s="28"/>
     </row>
     <row r="192" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="87"/>
+      <c r="A192" s="86"/>
       <c r="B192" s="15" t="s">
         <v>516</v>
       </c>
@@ -16941,7 +16323,7 @@
       <c r="N192" s="28"/>
     </row>
     <row r="193" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="87" t="s">
+      <c r="A193" s="86" t="s">
         <v>715</v>
       </c>
       <c r="B193" s="15" t="s">
@@ -16963,7 +16345,7 @@
       <c r="N193" s="28"/>
     </row>
     <row r="194" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="87"/>
+      <c r="A194" s="86"/>
       <c r="B194" s="15" t="s">
         <v>771</v>
       </c>
@@ -16983,7 +16365,7 @@
       <c r="N194" s="28"/>
     </row>
     <row r="195" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="87"/>
+      <c r="A195" s="86"/>
       <c r="B195" s="15" t="s">
         <v>773</v>
       </c>
@@ -17003,81 +16385,39 @@
       <c r="N195" s="28"/>
     </row>
     <row r="196" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="70" t="s">
+      <c r="A196" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="B196" s="71"/>
-      <c r="C196" s="71"/>
+      <c r="B196" s="72"/>
+      <c r="C196" s="72"/>
       <c r="D196" s="24"/>
       <c r="E196" s="24"/>
       <c r="F196" s="23"/>
-      <c r="G196" s="49">
-        <f>SUM(G185:G195)</f>
-        <v>0</v>
-      </c>
-      <c r="H196" s="49">
-        <f t="shared" ref="H196:M196" si="13">SUM(H185:H195)</f>
-        <v>0</v>
-      </c>
-      <c r="I196" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="J196" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="K196" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="L196" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="M196" s="49">
-        <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
+      <c r="G196" s="49"/>
+      <c r="H196" s="49"/>
+      <c r="I196" s="49"/>
+      <c r="J196" s="49"/>
+      <c r="K196" s="49"/>
+      <c r="L196" s="49"/>
+      <c r="M196" s="49"/>
       <c r="N196" s="30"/>
     </row>
     <row r="197" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="67" t="s">
+      <c r="A197" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="B197" s="68"/>
-      <c r="C197" s="68"/>
+      <c r="B197" s="56"/>
+      <c r="C197" s="56"/>
       <c r="D197" s="51"/>
       <c r="E197" s="51"/>
       <c r="F197" s="53"/>
-      <c r="G197" s="50">
-        <f>SUM(G196,G184,G164,G149,G99,G94,G87,G82,G75,G59,G47,G34,G29,G20)</f>
-        <v>0</v>
-      </c>
-      <c r="H197" s="50">
-        <f t="shared" ref="H197:M197" si="14">SUM(H196,H184,H164,H149,H99,H94,H87,H82,H75,H59,H47,H34,H29,H20)</f>
-        <v>0</v>
-      </c>
-      <c r="I197" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="J197" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="K197" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="L197" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="M197" s="50">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
+      <c r="G197" s="50"/>
+      <c r="H197" s="50"/>
+      <c r="I197" s="50"/>
+      <c r="J197" s="50"/>
+      <c r="K197" s="50"/>
+      <c r="L197" s="50"/>
+      <c r="M197" s="50"/>
       <c r="N197" s="52"/>
     </row>
     <row r="198" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -17114,6 +16454,49 @@
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="A8:A19"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A21:A28"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:A46"/>
+    <mergeCell ref="A47:C47"/>
+    <mergeCell ref="A48:A58"/>
+    <mergeCell ref="A60:A74"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="A94:C94"/>
+    <mergeCell ref="A99:C99"/>
+    <mergeCell ref="A149:C149"/>
+    <mergeCell ref="A124:A135"/>
+    <mergeCell ref="A136:A142"/>
+    <mergeCell ref="A144:A148"/>
+    <mergeCell ref="A184:C184"/>
+    <mergeCell ref="A150:A155"/>
+    <mergeCell ref="A156:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A165:A167"/>
+    <mergeCell ref="A181:A183"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A174:A178"/>
+    <mergeCell ref="A179:A180"/>
     <mergeCell ref="A197:C197"/>
     <mergeCell ref="A30:A33"/>
     <mergeCell ref="A59:C59"/>
@@ -17130,49 +16513,6 @@
     <mergeCell ref="A193:A195"/>
     <mergeCell ref="A164:C164"/>
     <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A184:C184"/>
-    <mergeCell ref="A150:A155"/>
-    <mergeCell ref="A156:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="A181:A183"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A178"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="A94:C94"/>
-    <mergeCell ref="A99:C99"/>
-    <mergeCell ref="A149:C149"/>
-    <mergeCell ref="A124:A135"/>
-    <mergeCell ref="A136:A142"/>
-    <mergeCell ref="A144:A148"/>
-    <mergeCell ref="A47:C47"/>
-    <mergeCell ref="A48:A58"/>
-    <mergeCell ref="A60:A74"/>
-    <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:A28"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:A46"/>
-    <mergeCell ref="A8:A19"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -17182,7 +16522,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9DEE9D-E018-49EA-AD01-F6853D9BB462}">
-  <dimension ref="A2:N75"/>
+  <dimension ref="A2:N69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.625" style="36" customWidth="1"/>
@@ -19654,22 +18994,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="75" t="s">
         <v>718</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
@@ -19700,67 +19040,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="84" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="81" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="78" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="78" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="78" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="73" t="s">
         <v>723</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="73" t="s">
         <v>669</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="73" t="s">
         <v>673</v>
       </c>
-      <c r="I6" s="55" t="s">
+      <c r="I6" s="73" t="s">
         <v>680</v>
       </c>
-      <c r="J6" s="55" t="s">
+      <c r="J6" s="73" t="s">
         <v>681</v>
       </c>
-      <c r="K6" s="55" t="s">
+      <c r="K6" s="73" t="s">
         <v>682</v>
       </c>
-      <c r="L6" s="55" t="s">
+      <c r="L6" s="73" t="s">
         <v>700</v>
       </c>
-      <c r="M6" s="55" t="s">
+      <c r="M6" s="73" t="s">
         <v>724</v>
       </c>
-      <c r="N6" s="73" t="s">
+      <c r="N6" s="76" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="66"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="74"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="77"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="88" t="s">
         <v>805</v>
       </c>
       <c r="B8" s="25">
@@ -19782,7 +19122,7 @@
       <c r="N8" s="29"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="87"/>
+      <c r="A9" s="86"/>
       <c r="B9" s="15">
         <v>7427</v>
       </c>
@@ -19802,7 +19142,7 @@
       <c r="N9" s="28"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="87"/>
+      <c r="A10" s="86"/>
       <c r="B10" s="18">
         <v>7429</v>
       </c>
@@ -19822,7 +19162,7 @@
       <c r="N10" s="28"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="87"/>
+      <c r="A11" s="86"/>
       <c r="B11" s="18">
         <v>7431</v>
       </c>
@@ -19842,7 +19182,7 @@
       <c r="N11" s="28"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="87"/>
+      <c r="A12" s="86"/>
       <c r="B12" s="18">
         <v>7433</v>
       </c>
@@ -19862,7 +19202,7 @@
       <c r="N12" s="28"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="87"/>
+      <c r="A13" s="86"/>
       <c r="B13" s="18">
         <v>7435</v>
       </c>
@@ -19882,7 +19222,7 @@
       <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="87"/>
+      <c r="A14" s="86"/>
       <c r="B14" s="18">
         <v>7437</v>
       </c>
@@ -19902,7 +19242,7 @@
       <c r="N14" s="28"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="87"/>
+      <c r="A15" s="86"/>
       <c r="B15" s="18">
         <v>7439</v>
       </c>
@@ -19922,7 +19262,7 @@
       <c r="N15" s="28"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="87"/>
+      <c r="A16" s="86"/>
       <c r="B16" s="18">
         <v>7441</v>
       </c>
@@ -19942,7 +19282,7 @@
       <c r="N16" s="28"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="87"/>
+      <c r="A17" s="86"/>
       <c r="B17" s="18">
         <v>7426</v>
       </c>
@@ -19962,7 +19302,7 @@
       <c r="N17" s="28"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="87"/>
+      <c r="A18" s="86"/>
       <c r="B18" s="18">
         <v>7430</v>
       </c>
@@ -19982,7 +19322,7 @@
       <c r="N18" s="28"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="87"/>
+      <c r="A19" s="86"/>
       <c r="B19" s="18">
         <v>7432</v>
       </c>
@@ -20002,7 +19342,7 @@
       <c r="N19" s="28"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="87"/>
+      <c r="A20" s="86"/>
       <c r="B20" s="18">
         <v>7434</v>
       </c>
@@ -20022,7 +19362,7 @@
       <c r="N20" s="28"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="87"/>
+      <c r="A21" s="86"/>
       <c r="B21" s="18">
         <v>7436</v>
       </c>
@@ -20042,7 +19382,7 @@
       <c r="N21" s="28"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="87"/>
+      <c r="A22" s="86"/>
       <c r="B22" s="18">
         <v>7438</v>
       </c>
@@ -20062,7 +19402,7 @@
       <c r="N22" s="28"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="87"/>
+      <c r="A23" s="86"/>
       <c r="B23" s="18">
         <v>7440</v>
       </c>
@@ -20082,7 +19422,7 @@
       <c r="N23" s="28"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="87"/>
+      <c r="A24" s="86"/>
       <c r="B24" s="18">
         <v>7442</v>
       </c>
@@ -20102,7 +19442,7 @@
       <c r="N24" s="28"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="87"/>
+      <c r="A25" s="86"/>
       <c r="B25" s="18">
         <v>7443</v>
       </c>
@@ -20122,7 +19462,7 @@
       <c r="N25" s="28"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="87"/>
+      <c r="A26" s="86"/>
       <c r="B26" s="18">
         <v>7445</v>
       </c>
@@ -20142,7 +19482,7 @@
       <c r="N26" s="28"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="87"/>
+      <c r="A27" s="86"/>
       <c r="B27" s="18">
         <v>7444</v>
       </c>
@@ -20162,7 +19502,7 @@
       <c r="N27" s="28"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="87"/>
+      <c r="A28" s="86"/>
       <c r="B28" s="18">
         <v>7446</v>
       </c>
@@ -20182,7 +19522,7 @@
       <c r="N28" s="28"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="87"/>
+      <c r="A29" s="86"/>
       <c r="B29" s="18">
         <v>7448</v>
       </c>
@@ -20202,7 +19542,7 @@
       <c r="N29" s="28"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="87"/>
+      <c r="A30" s="86"/>
       <c r="B30" s="18">
         <v>7450</v>
       </c>
@@ -20225,43 +19565,22 @@
       <c r="A31" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
+      <c r="B31" s="70"/>
+      <c r="C31" s="70"/>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
       <c r="F31" s="16"/>
-      <c r="G31" s="40">
-        <f>SUM(G8:G30)</f>
-        <v>0</v>
-      </c>
-      <c r="H31" s="40">
-        <f t="shared" ref="H31:M31" si="0">SUM(H8:H30)</f>
-        <v>0</v>
-      </c>
-      <c r="I31" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J31" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L31" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M31" s="40">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="40"/>
+      <c r="K31" s="40"/>
+      <c r="L31" s="40"/>
+      <c r="M31" s="40"/>
       <c r="N31" s="28"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="87" t="s">
+      <c r="A32" s="86" t="s">
         <v>806</v>
       </c>
       <c r="B32" s="15" t="s">
@@ -20283,7 +19602,7 @@
       <c r="N32" s="28"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="87"/>
+      <c r="A33" s="86"/>
       <c r="B33" s="15" t="s">
         <v>577</v>
       </c>
@@ -20303,7 +19622,7 @@
       <c r="N33" s="28"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="87"/>
+      <c r="A34" s="86"/>
       <c r="B34" s="15" t="s">
         <v>574</v>
       </c>
@@ -20323,7 +19642,7 @@
       <c r="N34" s="28"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="87"/>
+      <c r="A35" s="86"/>
       <c r="B35" s="15" t="s">
         <v>552</v>
       </c>
@@ -20343,7 +19662,7 @@
       <c r="N35" s="28"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="87"/>
+      <c r="A36" s="86"/>
       <c r="B36" s="15" t="s">
         <v>431</v>
       </c>
@@ -20363,7 +19682,7 @@
       <c r="N36" s="28"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="87"/>
+      <c r="A37" s="86"/>
       <c r="B37" s="15" t="s">
         <v>436</v>
       </c>
@@ -20383,7 +19702,7 @@
       <c r="N37" s="28"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="87"/>
+      <c r="A38" s="86"/>
       <c r="B38" s="15" t="s">
         <v>505</v>
       </c>
@@ -20403,7 +19722,7 @@
       <c r="N38" s="28"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="87"/>
+      <c r="A39" s="86"/>
       <c r="B39" s="15" t="s">
         <v>566</v>
       </c>
@@ -20426,43 +19745,22 @@
       <c r="A40" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
       <c r="D40" s="14"/>
       <c r="E40" s="14"/>
       <c r="F40" s="16"/>
-      <c r="G40" s="40">
-        <f>SUM(G32:G39)</f>
-        <v>0</v>
-      </c>
-      <c r="H40" s="40">
-        <f t="shared" ref="H40:M40" si="1">SUM(H32:H39)</f>
-        <v>0</v>
-      </c>
-      <c r="I40" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J40" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K40" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L40" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M40" s="40">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="40"/>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40"/>
+      <c r="M40" s="40"/>
       <c r="N40" s="28"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="88" t="s">
+      <c r="A41" s="87" t="s">
         <v>808</v>
       </c>
       <c r="B41" s="31" t="s">
@@ -20484,7 +19782,7 @@
       <c r="N41" s="28"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="88"/>
+      <c r="A42" s="87"/>
       <c r="B42" s="31" t="s">
         <v>581</v>
       </c>
@@ -20504,7 +19802,7 @@
       <c r="N42" s="28"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="88"/>
+      <c r="A43" s="87"/>
       <c r="B43" s="31" t="s">
         <v>590</v>
       </c>
@@ -20524,7 +19822,7 @@
       <c r="N43" s="28"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="88"/>
+      <c r="A44" s="87"/>
       <c r="B44" s="31" t="s">
         <v>548</v>
       </c>
@@ -20544,7 +19842,7 @@
       <c r="N44" s="28"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="88"/>
+      <c r="A45" s="87"/>
       <c r="B45" s="31" t="s">
         <v>583</v>
       </c>
@@ -20564,7 +19862,7 @@
       <c r="N45" s="28"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="88"/>
+      <c r="A46" s="87"/>
       <c r="B46" s="31" t="s">
         <v>453</v>
       </c>
@@ -20584,7 +19882,7 @@
       <c r="N46" s="28"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="88"/>
+      <c r="A47" s="87"/>
       <c r="B47" s="31" t="s">
         <v>671</v>
       </c>
@@ -20604,7 +19902,7 @@
       <c r="N47" s="28"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="88"/>
+      <c r="A48" s="87"/>
       <c r="B48" s="31" t="s">
         <v>582</v>
       </c>
@@ -20624,7 +19922,7 @@
       <c r="N48" s="28"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="88"/>
+      <c r="A49" s="87"/>
       <c r="B49" s="31" t="s">
         <v>553</v>
       </c>
@@ -20644,7 +19942,7 @@
       <c r="N49" s="28"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="88"/>
+      <c r="A50" s="87"/>
       <c r="B50" s="31" t="s">
         <v>573</v>
       </c>
@@ -20667,43 +19965,22 @@
       <c r="A51" s="69" t="s">
         <v>595</v>
       </c>
-      <c r="B51" s="61"/>
-      <c r="C51" s="61"/>
+      <c r="B51" s="70"/>
+      <c r="C51" s="70"/>
       <c r="D51" s="14"/>
       <c r="E51" s="14"/>
       <c r="F51" s="16"/>
-      <c r="G51" s="40">
-        <f>SUM(G41:G50)</f>
-        <v>0</v>
-      </c>
-      <c r="H51" s="40">
-        <f t="shared" ref="H51:M51" si="2">SUM(H41:H50)</f>
-        <v>0</v>
-      </c>
-      <c r="I51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="J51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="K51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="L51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="M51" s="40">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
+      <c r="G51" s="40"/>
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="40"/>
+      <c r="M51" s="40"/>
       <c r="N51" s="28"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="87" t="s">
+      <c r="A52" s="86" t="s">
         <v>810</v>
       </c>
       <c r="B52" s="31" t="s">
@@ -20725,7 +20002,7 @@
       <c r="N52" s="28"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="87"/>
+      <c r="A53" s="86"/>
       <c r="B53" s="31" t="s">
         <v>571</v>
       </c>
@@ -20745,7 +20022,7 @@
       <c r="N53" s="28"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="87"/>
+      <c r="A54" s="86"/>
       <c r="B54" s="31" t="s">
         <v>392</v>
       </c>
@@ -20765,7 +20042,7 @@
       <c r="N54" s="28"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="87"/>
+      <c r="A55" s="86"/>
       <c r="B55" s="31" t="s">
         <v>429</v>
       </c>
@@ -20785,7 +20062,7 @@
       <c r="N55" s="28"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="87"/>
+      <c r="A56" s="86"/>
       <c r="B56" s="31" t="s">
         <v>672</v>
       </c>
@@ -20808,43 +20085,22 @@
       <c r="A57" s="69" t="s">
         <v>135</v>
       </c>
-      <c r="B57" s="61"/>
-      <c r="C57" s="61"/>
+      <c r="B57" s="70"/>
+      <c r="C57" s="70"/>
       <c r="D57" s="14"/>
       <c r="E57" s="14"/>
       <c r="F57" s="16"/>
-      <c r="G57" s="40">
-        <f>SUM(G52:G56)</f>
-        <v>0</v>
-      </c>
-      <c r="H57" s="40">
-        <f t="shared" ref="H57:M57" si="3">SUM(H52:H56)</f>
-        <v>0</v>
-      </c>
-      <c r="I57" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J57" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="K57" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="L57" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="M57" s="40">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
+      <c r="G57" s="40"/>
+      <c r="H57" s="40"/>
+      <c r="I57" s="40"/>
+      <c r="J57" s="40"/>
+      <c r="K57" s="40"/>
+      <c r="L57" s="40"/>
+      <c r="M57" s="40"/>
       <c r="N57" s="28"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="87" t="s">
+      <c r="A58" s="86" t="s">
         <v>811</v>
       </c>
       <c r="B58" s="15" t="s">
@@ -20866,7 +20122,7 @@
       <c r="N58" s="28"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="87"/>
+      <c r="A59" s="86"/>
       <c r="B59" s="15" t="s">
         <v>812</v>
       </c>
@@ -20886,7 +20142,7 @@
       <c r="N59" s="28"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="87"/>
+      <c r="A60" s="86"/>
       <c r="B60" s="15" t="s">
         <v>813</v>
       </c>
@@ -20906,7 +20162,7 @@
       <c r="N60" s="28"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="87"/>
+      <c r="A61" s="86"/>
       <c r="B61" s="15" t="s">
         <v>814</v>
       </c>
@@ -20926,7 +20182,7 @@
       <c r="N61" s="28"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="87"/>
+      <c r="A62" s="86"/>
       <c r="B62" s="15" t="s">
         <v>815</v>
       </c>
@@ -20946,7 +20202,7 @@
       <c r="N62" s="28"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="87"/>
+      <c r="A63" s="86"/>
       <c r="B63" s="15" t="s">
         <v>676</v>
       </c>
@@ -20966,7 +20222,7 @@
       <c r="N63" s="28"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="87"/>
+      <c r="A64" s="86"/>
       <c r="B64" s="15" t="s">
         <v>677</v>
       </c>
@@ -20986,7 +20242,7 @@
       <c r="N64" s="28"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="87"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="15" t="s">
         <v>679</v>
       </c>
@@ -21006,7 +20262,7 @@
       <c r="N65" s="28"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="87"/>
+      <c r="A66" s="86"/>
       <c r="B66" s="15" t="s">
         <v>678</v>
       </c>
@@ -21026,84 +20282,42 @@
       <c r="N66" s="28"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="70" t="s">
+      <c r="A67" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="B67" s="71"/>
-      <c r="C67" s="71"/>
+      <c r="B67" s="72"/>
+      <c r="C67" s="72"/>
       <c r="D67" s="24"/>
       <c r="E67" s="24"/>
       <c r="F67" s="23"/>
-      <c r="G67" s="49">
-        <f>SUM(G58:G66)</f>
-        <v>0</v>
-      </c>
-      <c r="H67" s="49">
-        <f t="shared" ref="H67:M67" si="4">SUM(H58:H66)</f>
-        <v>0</v>
-      </c>
-      <c r="I67" s="49">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="J67" s="49">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K67" s="49">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="L67" s="49">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="M67" s="49">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
+      <c r="G67" s="49"/>
+      <c r="H67" s="49"/>
+      <c r="I67" s="49"/>
+      <c r="J67" s="49"/>
+      <c r="K67" s="49"/>
+      <c r="L67" s="49"/>
+      <c r="M67" s="49"/>
       <c r="N67" s="30"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="B68" s="68"/>
-      <c r="C68" s="68"/>
+      <c r="B68" s="56"/>
+      <c r="C68" s="56"/>
       <c r="D68" s="51"/>
       <c r="E68" s="51"/>
       <c r="F68" s="53"/>
-      <c r="G68" s="50">
-        <f>SUM(G67,G57,G51,G40)</f>
-        <v>0</v>
-      </c>
-      <c r="H68" s="50">
-        <f t="shared" ref="H68:M68" si="5">SUM(H67,H57,H51,H40)</f>
-        <v>0</v>
-      </c>
-      <c r="I68" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="J68" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="K68" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L68" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="M68" s="50">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="G68" s="50"/>
+      <c r="H68" s="50"/>
+      <c r="I68" s="50"/>
+      <c r="J68" s="50"/>
+      <c r="K68" s="50"/>
+      <c r="L68" s="50"/>
+      <c r="M68" s="50"/>
       <c r="N68" s="52"/>
     </row>
-    <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="1"/>
       <c r="C69" s="5"/>
@@ -21119,113 +20333,8 @@
       <c r="M69" s="8"/>
       <c r="N69" s="8"/>
     </row>
-    <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="3"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="5"/>
-      <c r="D70" s="82"/>
-      <c r="E70" s="83"/>
-      <c r="F70" s="83"/>
-      <c r="G70" s="75"/>
-      <c r="H70" s="75"/>
-      <c r="I70" s="75"/>
-      <c r="J70" s="76"/>
-      <c r="K70" s="8"/>
-      <c r="L70" s="8"/>
-      <c r="M70" s="8"/>
-      <c r="N70" s="8"/>
-    </row>
-    <row r="71" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D71" s="84" t="s">
-        <v>777</v>
-      </c>
-      <c r="E71" s="85"/>
-      <c r="F71" s="85"/>
-      <c r="G71" s="77"/>
-      <c r="H71" s="77"/>
-      <c r="I71" s="77"/>
-      <c r="J71" s="78"/>
-    </row>
-    <row r="72" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D72" s="69" t="s">
-        <v>778</v>
-      </c>
-      <c r="E72" s="61"/>
-      <c r="F72" s="61"/>
-      <c r="G72" s="63"/>
-      <c r="H72" s="63"/>
-      <c r="I72" s="63"/>
-      <c r="J72" s="80"/>
-    </row>
-    <row r="73" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D73" s="69" t="s">
-        <v>779</v>
-      </c>
-      <c r="E73" s="61"/>
-      <c r="F73" s="61"/>
-      <c r="G73" s="63"/>
-      <c r="H73" s="63"/>
-      <c r="I73" s="63"/>
-      <c r="J73" s="80"/>
-    </row>
-    <row r="74" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D74" s="70" t="s">
-        <v>780</v>
-      </c>
-      <c r="E74" s="71"/>
-      <c r="F74" s="71"/>
-      <c r="G74" s="79"/>
-      <c r="H74" s="79"/>
-      <c r="I74" s="79"/>
-      <c r="J74" s="81"/>
-    </row>
-    <row r="75" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D75" s="67" t="s">
-        <v>781</v>
-      </c>
-      <c r="E75" s="68"/>
-      <c r="F75" s="68"/>
-      <c r="G75" s="75">
-        <f>SUM(G71:H74)</f>
-        <v>0</v>
-      </c>
-      <c r="H75" s="75"/>
-      <c r="I75" s="75">
-        <f>SUM(I71:J74)</f>
-        <v>0</v>
-      </c>
-      <c r="J75" s="75"/>
-    </row>
   </sheetData>
-  <mergeCells count="44">
-    <mergeCell ref="D75:F75"/>
-    <mergeCell ref="G75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="D73:F73"/>
-    <mergeCell ref="G73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="D74:F74"/>
-    <mergeCell ref="G74:H74"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="D72:F72"/>
-    <mergeCell ref="G72:H72"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="A67:C67"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="D70:F70"/>
-    <mergeCell ref="G70:H70"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="D71:F71"/>
-    <mergeCell ref="G71:H71"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="A57:C57"/>
-    <mergeCell ref="A58:A66"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="A40:C40"/>
-    <mergeCell ref="A41:A50"/>
-    <mergeCell ref="A51:C51"/>
+  <mergeCells count="26">
     <mergeCell ref="A8:A30"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A6:A7"/>
@@ -21242,6 +20351,16 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="A58:A66"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A41:A50"/>
+    <mergeCell ref="A51:C51"/>
+    <mergeCell ref="A67:C67"/>
+    <mergeCell ref="A68:C68"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -23723,22 +22842,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="75" t="s">
         <v>717</v>
       </c>
-      <c r="B2" s="72"/>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
+      <c r="B2" s="75"/>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="75"/>
+      <c r="K2" s="75"/>
+      <c r="L2" s="75"/>
+      <c r="M2" s="75"/>
+      <c r="N2" s="75"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="33"/>
@@ -23769,67 +22888,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="65" t="s">
+      <c r="A6" s="84" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="81" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="59" t="s">
+      <c r="C6" s="78" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="78" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="78" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="73" t="s">
         <v>723</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="73" t="s">
         <v>669</v>
       </c>
-      <c r="H6" s="55" t="s">
+      <c r="H6" s="73" t="s">
         <v>673</v>
       </c>
-      <c r="I6" s="55" t="s">
+      <c r="I6" s="73" t="s">
         <v>680</v>
       </c>
-      <c r="J6" s="55" t="s">
+      <c r="J6" s="73" t="s">
         <v>681</v>
       </c>
-      <c r="K6" s="55" t="s">
+      <c r="K6" s="73" t="s">
         <v>682</v>
       </c>
-      <c r="L6" s="55" t="s">
+      <c r="L6" s="73" t="s">
         <v>700</v>
       </c>
-      <c r="M6" s="55" t="s">
+      <c r="M6" s="73" t="s">
         <v>724</v>
       </c>
-      <c r="N6" s="73" t="s">
+      <c r="N6" s="76" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="66"/>
-      <c r="B7" s="58"/>
-      <c r="C7" s="60"/>
-      <c r="D7" s="60"/>
-      <c r="E7" s="60"/>
-      <c r="F7" s="56"/>
-      <c r="G7" s="56"/>
-      <c r="H7" s="56"/>
-      <c r="I7" s="56"/>
-      <c r="J7" s="56"/>
-      <c r="K7" s="56"/>
-      <c r="L7" s="56"/>
-      <c r="M7" s="56"/>
-      <c r="N7" s="74"/>
+      <c r="A7" s="85"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="79"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="79"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
+      <c r="J7" s="74"/>
+      <c r="K7" s="74"/>
+      <c r="L7" s="74"/>
+      <c r="M7" s="74"/>
+      <c r="N7" s="77"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="86" t="s">
+      <c r="A8" s="88" t="s">
         <v>819</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -23851,7 +22970,7 @@
       <c r="N8" s="29"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="88"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="13" t="s">
         <v>584</v>
       </c>
@@ -23871,7 +22990,7 @@
       <c r="N9" s="28"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="88"/>
+      <c r="A10" s="87"/>
       <c r="B10" s="11" t="s">
         <v>215</v>
       </c>
@@ -23891,7 +23010,7 @@
       <c r="N10" s="28"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="88"/>
+      <c r="A11" s="87"/>
       <c r="B11" s="11" t="s">
         <v>578</v>
       </c>
@@ -23911,7 +23030,7 @@
       <c r="N11" s="28"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="88"/>
+      <c r="A12" s="87"/>
       <c r="B12" s="11" t="s">
         <v>220</v>
       </c>
@@ -23931,7 +23050,7 @@
       <c r="N12" s="28"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="88"/>
+      <c r="A13" s="87"/>
       <c r="B13" s="11" t="s">
         <v>455</v>
       </c>
@@ -23951,7 +23070,7 @@
       <c r="N13" s="28"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="88" t="s">
+      <c r="A14" s="87" t="s">
         <v>820</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -23973,7 +23092,7 @@
       <c r="N14" s="28"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="88"/>
+      <c r="A15" s="87"/>
       <c r="B15" s="11" t="s">
         <v>226</v>
       </c>
@@ -23993,7 +23112,7 @@
       <c r="N15" s="28"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="88"/>
+      <c r="A16" s="87"/>
       <c r="B16" s="11" t="s">
         <v>210</v>
       </c>
@@ -24013,7 +23132,7 @@
       <c r="N16" s="28"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="88"/>
+      <c r="A17" s="87"/>
       <c r="B17" s="11" t="s">
         <v>204</v>
       </c>
@@ -24055,81 +23174,39 @@
       <c r="N18" s="28"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="70" t="s">
+      <c r="A19" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="B19" s="71"/>
-      <c r="C19" s="71"/>
+      <c r="B19" s="72"/>
+      <c r="C19" s="72"/>
       <c r="D19" s="24"/>
       <c r="E19" s="24"/>
       <c r="F19" s="23"/>
-      <c r="G19" s="49">
-        <f>SUM(G8:G18)</f>
-        <v>0</v>
-      </c>
-      <c r="H19" s="49">
-        <f t="shared" ref="H19:M19" si="0">SUM(H8:H18)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="49">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="49">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="49">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="49">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="49">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+      <c r="G19" s="49"/>
+      <c r="H19" s="49"/>
+      <c r="I19" s="49"/>
+      <c r="J19" s="49"/>
+      <c r="K19" s="49"/>
+      <c r="L19" s="49"/>
+      <c r="M19" s="49"/>
       <c r="N19" s="30"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="67" t="s">
+      <c r="A20" s="55" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="68"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="56"/>
       <c r="D20" s="51"/>
       <c r="E20" s="51"/>
       <c r="F20" s="53"/>
-      <c r="G20" s="50">
-        <f>SUM(G19)</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="50">
-        <f t="shared" ref="H20:M20" si="1">SUM(H19)</f>
-        <v>0</v>
-      </c>
-      <c r="I20" s="50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="50">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
+      <c r="G20" s="50"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+      <c r="J20" s="50"/>
+      <c r="K20" s="50"/>
+      <c r="L20" s="50"/>
+      <c r="M20" s="50"/>
       <c r="N20" s="52"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
@@ -24166,11 +23243,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="J6:J7"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
@@ -24185,6 +23257,11 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="J6:J7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/data/temp.xlsx
+++ b/data/temp.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAC5C3C-A92C-4930-9941-F3490B1623CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD9E666-C947-429B-BDE4-5DA4A992616F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="613" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="완제품 임가공" sheetId="1" r:id="rId1"/>
@@ -3329,108 +3329,6 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3458,11 +3356,113 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6446,22 +6446,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="81" t="s">
         <v>716</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32"/>
@@ -6492,67 +6492,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="90" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="87" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="84" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="84" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="84" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="79" t="s">
         <v>723</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="79" t="s">
         <v>669</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="79" t="s">
         <v>673</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="79" t="s">
         <v>680</v>
       </c>
-      <c r="J6" s="52" t="s">
+      <c r="J6" s="79" t="s">
         <v>681</v>
       </c>
-      <c r="K6" s="52" t="s">
+      <c r="K6" s="79" t="s">
         <v>682</v>
       </c>
-      <c r="L6" s="52" t="s">
+      <c r="L6" s="79" t="s">
         <v>700</v>
       </c>
-      <c r="M6" s="52" t="s">
+      <c r="M6" s="79" t="s">
         <v>724</v>
       </c>
-      <c r="N6" s="70" t="s">
+      <c r="N6" s="82" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="63"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="71"/>
+      <c r="A7" s="91"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="83"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="59" t="s">
+      <c r="A8" s="89" t="s">
         <v>178</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -6574,7 +6574,7 @@
       <c r="N8" s="26"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="60"/>
+      <c r="A9" s="67"/>
       <c r="B9" s="15" t="s">
         <v>218</v>
       </c>
@@ -6594,7 +6594,7 @@
       <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="60"/>
+      <c r="A10" s="67"/>
       <c r="B10" s="18" t="s">
         <v>209</v>
       </c>
@@ -6614,7 +6614,7 @@
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="60"/>
+      <c r="A11" s="67"/>
       <c r="B11" s="18" t="s">
         <v>250</v>
       </c>
@@ -6634,7 +6634,7 @@
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="60"/>
+      <c r="A12" s="67"/>
       <c r="B12" s="22" t="s">
         <v>229</v>
       </c>
@@ -6654,7 +6654,7 @@
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60"/>
+      <c r="A13" s="67"/>
       <c r="B13" s="15" t="s">
         <v>327</v>
       </c>
@@ -6674,7 +6674,7 @@
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="60"/>
+      <c r="A14" s="67"/>
       <c r="B14" s="15" t="s">
         <v>381</v>
       </c>
@@ -6694,7 +6694,7 @@
       <c r="N14" s="14"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="60"/>
+      <c r="A15" s="67"/>
       <c r="B15" s="15" t="s">
         <v>353</v>
       </c>
@@ -6714,7 +6714,7 @@
       <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="60"/>
+      <c r="A16" s="67"/>
       <c r="B16" s="15" t="s">
         <v>351</v>
       </c>
@@ -6734,7 +6734,7 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="60"/>
+      <c r="A17" s="67"/>
       <c r="B17" s="15" t="s">
         <v>228</v>
       </c>
@@ -6754,7 +6754,7 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
+      <c r="A18" s="67"/>
       <c r="B18" s="15" t="s">
         <v>430</v>
       </c>
@@ -6774,14 +6774,14 @@
       <c r="N18" s="14"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="86" t="s">
+      <c r="A19" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B19" s="87"/>
-      <c r="C19" s="87"/>
-      <c r="D19" s="87"/>
-      <c r="E19" s="87"/>
-      <c r="F19" s="88"/>
+      <c r="B19" s="53"/>
+      <c r="C19" s="53"/>
+      <c r="D19" s="53"/>
+      <c r="E19" s="53"/>
+      <c r="F19" s="54"/>
       <c r="G19" s="39"/>
       <c r="H19" s="39"/>
       <c r="I19" s="39"/>
@@ -6792,7 +6792,7 @@
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="61" t="s">
+      <c r="A20" s="86" t="s">
         <v>729</v>
       </c>
       <c r="B20" s="15" t="s">
@@ -6814,7 +6814,7 @@
       <c r="N20" s="14"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="60"/>
+      <c r="A21" s="67"/>
       <c r="B21" s="15" t="s">
         <v>415</v>
       </c>
@@ -6834,7 +6834,7 @@
       <c r="N21" s="14"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="60"/>
+      <c r="A22" s="67"/>
       <c r="B22" s="15" t="s">
         <v>506</v>
       </c>
@@ -6854,7 +6854,7 @@
       <c r="N22" s="14"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="60"/>
+      <c r="A23" s="67"/>
       <c r="B23" s="15" t="s">
         <v>242</v>
       </c>
@@ -6874,14 +6874,14 @@
       <c r="N23" s="14"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="86" t="s">
+      <c r="A24" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B24" s="87"/>
-      <c r="C24" s="87"/>
-      <c r="D24" s="87"/>
-      <c r="E24" s="87"/>
-      <c r="F24" s="88"/>
+      <c r="B24" s="53"/>
+      <c r="C24" s="53"/>
+      <c r="D24" s="53"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="54"/>
       <c r="G24" s="39"/>
       <c r="H24" s="39"/>
       <c r="I24" s="39"/>
@@ -6892,7 +6892,7 @@
       <c r="N24" s="14"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="61" t="s">
+      <c r="A25" s="86" t="s">
         <v>486</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -6914,7 +6914,7 @@
       <c r="N25" s="14"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="61"/>
+      <c r="A26" s="86"/>
       <c r="B26" s="15" t="s">
         <v>396</v>
       </c>
@@ -6934,7 +6934,7 @@
       <c r="N26" s="14"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="61"/>
+      <c r="A27" s="86"/>
       <c r="B27" s="15" t="s">
         <v>409</v>
       </c>
@@ -6954,7 +6954,7 @@
       <c r="N27" s="14"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="61"/>
+      <c r="A28" s="86"/>
       <c r="B28" s="15" t="s">
         <v>514</v>
       </c>
@@ -6974,7 +6974,7 @@
       <c r="N28" s="14"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="61"/>
+      <c r="A29" s="86"/>
       <c r="B29" s="15" t="s">
         <v>502</v>
       </c>
@@ -6994,7 +6994,7 @@
       <c r="N29" s="14"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="61"/>
+      <c r="A30" s="86"/>
       <c r="B30" s="15" t="s">
         <v>597</v>
       </c>
@@ -7014,7 +7014,7 @@
       <c r="N30" s="14"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="61"/>
+      <c r="A31" s="86"/>
       <c r="B31" s="15" t="s">
         <v>489</v>
       </c>
@@ -7034,7 +7034,7 @@
       <c r="N31" s="14"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="61"/>
+      <c r="A32" s="86"/>
       <c r="B32" s="15" t="s">
         <v>487</v>
       </c>
@@ -7054,7 +7054,7 @@
       <c r="N32" s="14"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="61"/>
+      <c r="A33" s="86"/>
       <c r="B33" s="15" t="s">
         <v>365</v>
       </c>
@@ -7074,7 +7074,7 @@
       <c r="N33" s="14"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="61"/>
+      <c r="A34" s="86"/>
       <c r="B34" s="15" t="s">
         <v>380</v>
       </c>
@@ -7094,7 +7094,7 @@
       <c r="N34" s="14"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="61"/>
+      <c r="A35" s="86"/>
       <c r="B35" s="15" t="s">
         <v>448</v>
       </c>
@@ -7114,7 +7114,7 @@
       <c r="N35" s="14"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="61"/>
+      <c r="A36" s="86"/>
       <c r="B36" s="15" t="s">
         <v>372</v>
       </c>
@@ -7134,7 +7134,7 @@
       <c r="N36" s="14"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="61"/>
+      <c r="A37" s="86"/>
       <c r="B37" s="15" t="s">
         <v>393</v>
       </c>
@@ -7154,7 +7154,7 @@
       <c r="N37" s="14"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="61"/>
+      <c r="A38" s="86"/>
       <c r="B38" s="15" t="s">
         <v>405</v>
       </c>
@@ -7174,7 +7174,7 @@
       <c r="N38" s="14"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="61"/>
+      <c r="A39" s="86"/>
       <c r="B39" s="15" t="s">
         <v>517</v>
       </c>
@@ -7194,7 +7194,7 @@
       <c r="N39" s="14"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="61"/>
+      <c r="A40" s="86"/>
       <c r="B40" s="15" t="s">
         <v>475</v>
       </c>
@@ -7214,7 +7214,7 @@
       <c r="N40" s="14"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="61"/>
+      <c r="A41" s="86"/>
       <c r="B41" s="15" t="s">
         <v>529</v>
       </c>
@@ -7234,7 +7234,7 @@
       <c r="N41" s="14"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="61"/>
+      <c r="A42" s="86"/>
       <c r="B42" s="15" t="s">
         <v>495</v>
       </c>
@@ -7254,7 +7254,7 @@
       <c r="N42" s="14"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="61"/>
+      <c r="A43" s="86"/>
       <c r="B43" s="15" t="s">
         <v>361</v>
       </c>
@@ -7274,7 +7274,7 @@
       <c r="N43" s="14"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="61"/>
+      <c r="A44" s="86"/>
       <c r="B44" s="15" t="s">
         <v>375</v>
       </c>
@@ -7294,7 +7294,7 @@
       <c r="N44" s="14"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="61"/>
+      <c r="A45" s="86"/>
       <c r="B45" s="15" t="s">
         <v>354</v>
       </c>
@@ -7314,7 +7314,7 @@
       <c r="N45" s="14"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="61"/>
+      <c r="A46" s="86"/>
       <c r="B46" s="15" t="s">
         <v>491</v>
       </c>
@@ -7334,7 +7334,7 @@
       <c r="N46" s="14"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="61"/>
+      <c r="A47" s="86"/>
       <c r="B47" s="15" t="s">
         <v>384</v>
       </c>
@@ -7354,7 +7354,7 @@
       <c r="N47" s="14"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="61"/>
+      <c r="A48" s="86"/>
       <c r="B48" s="15" t="s">
         <v>536</v>
       </c>
@@ -7374,7 +7374,7 @@
       <c r="N48" s="14"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="61"/>
+      <c r="A49" s="86"/>
       <c r="B49" s="15" t="s">
         <v>451</v>
       </c>
@@ -7394,7 +7394,7 @@
       <c r="N49" s="14"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="61"/>
+      <c r="A50" s="86"/>
       <c r="B50" s="15" t="s">
         <v>440</v>
       </c>
@@ -7414,14 +7414,14 @@
       <c r="N50" s="14"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="86" t="s">
+      <c r="A51" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B51" s="87"/>
-      <c r="C51" s="87"/>
-      <c r="D51" s="87"/>
-      <c r="E51" s="87"/>
-      <c r="F51" s="88"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
       <c r="G51" s="39"/>
       <c r="H51" s="39"/>
       <c r="I51" s="39"/>
@@ -7432,7 +7432,7 @@
       <c r="N51" s="14"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="60" t="s">
+      <c r="A52" s="67" t="s">
         <v>526</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -7454,7 +7454,7 @@
       <c r="N52" s="14"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="60"/>
+      <c r="A53" s="67"/>
       <c r="B53" s="15" t="s">
         <v>360</v>
       </c>
@@ -7474,7 +7474,7 @@
       <c r="N53" s="14"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="60"/>
+      <c r="A54" s="67"/>
       <c r="B54" s="15" t="s">
         <v>546</v>
       </c>
@@ -7494,7 +7494,7 @@
       <c r="N54" s="14"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="60"/>
+      <c r="A55" s="67"/>
       <c r="B55" s="15" t="s">
         <v>531</v>
       </c>
@@ -7514,7 +7514,7 @@
       <c r="N55" s="14"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="60"/>
+      <c r="A56" s="67"/>
       <c r="B56" s="15" t="s">
         <v>522</v>
       </c>
@@ -7534,7 +7534,7 @@
       <c r="N56" s="14"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="60"/>
+      <c r="A57" s="67"/>
       <c r="B57" s="15" t="s">
         <v>472</v>
       </c>
@@ -7554,7 +7554,7 @@
       <c r="N57" s="14"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="60" t="s">
+      <c r="A58" s="67" t="s">
         <v>520</v>
       </c>
       <c r="B58" s="15" t="s">
@@ -7576,7 +7576,7 @@
       <c r="N58" s="14"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="60"/>
+      <c r="A59" s="67"/>
       <c r="B59" s="15" t="s">
         <v>482</v>
       </c>
@@ -7596,7 +7596,7 @@
       <c r="N59" s="14"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="60"/>
+      <c r="A60" s="67"/>
       <c r="B60" s="15" t="s">
         <v>508</v>
       </c>
@@ -7616,7 +7616,7 @@
       <c r="N60" s="14"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="60"/>
+      <c r="A61" s="67"/>
       <c r="B61" s="15" t="s">
         <v>490</v>
       </c>
@@ -7636,7 +7636,7 @@
       <c r="N61" s="14"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="60"/>
+      <c r="A62" s="67"/>
       <c r="B62" s="15" t="s">
         <v>503</v>
       </c>
@@ -7656,7 +7656,7 @@
       <c r="N62" s="14"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="60"/>
+      <c r="A63" s="67"/>
       <c r="B63" s="15" t="s">
         <v>511</v>
       </c>
@@ -7676,7 +7676,7 @@
       <c r="N63" s="14"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="61" t="s">
+      <c r="A64" s="86" t="s">
         <v>109</v>
       </c>
       <c r="B64" s="30" t="s">
@@ -7698,7 +7698,7 @@
       <c r="N64" s="14"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="61"/>
+      <c r="A65" s="86"/>
       <c r="B65" s="30" t="s">
         <v>387</v>
       </c>
@@ -7718,7 +7718,7 @@
       <c r="N65" s="14"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="61"/>
+      <c r="A66" s="86"/>
       <c r="B66" s="30" t="s">
         <v>397</v>
       </c>
@@ -7738,7 +7738,7 @@
       <c r="N66" s="14"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="61"/>
+      <c r="A67" s="86"/>
       <c r="B67" s="30" t="s">
         <v>496</v>
       </c>
@@ -7758,7 +7758,7 @@
       <c r="N67" s="14"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="61" t="s">
+      <c r="A68" s="86" t="s">
         <v>109</v>
       </c>
       <c r="B68" s="30" t="s">
@@ -7780,7 +7780,7 @@
       <c r="N68" s="14"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="61"/>
+      <c r="A69" s="86"/>
       <c r="B69" s="30" t="s">
         <v>501</v>
       </c>
@@ -7800,7 +7800,7 @@
       <c r="N69" s="14"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="61"/>
+      <c r="A70" s="86"/>
       <c r="B70" s="30" t="s">
         <v>450</v>
       </c>
@@ -7820,7 +7820,7 @@
       <c r="N70" s="14"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="61"/>
+      <c r="A71" s="86"/>
       <c r="B71" s="30" t="s">
         <v>480</v>
       </c>
@@ -7840,7 +7840,7 @@
       <c r="N71" s="14"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="61" t="s">
+      <c r="A72" s="86" t="s">
         <v>41</v>
       </c>
       <c r="B72" s="30" t="s">
@@ -7862,7 +7862,7 @@
       <c r="N72" s="14"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="61"/>
+      <c r="A73" s="86"/>
       <c r="B73" s="30" t="s">
         <v>545</v>
       </c>
@@ -7882,7 +7882,7 @@
       <c r="N73" s="14"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="61"/>
+      <c r="A74" s="86"/>
       <c r="B74" s="30" t="s">
         <v>470</v>
       </c>
@@ -7902,7 +7902,7 @@
       <c r="N74" s="14"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="61" t="s">
+      <c r="A75" s="86" t="s">
         <v>41</v>
       </c>
       <c r="B75" s="30" t="s">
@@ -7924,7 +7924,7 @@
       <c r="N75" s="14"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="61"/>
+      <c r="A76" s="86"/>
       <c r="B76" s="30" t="s">
         <v>494</v>
       </c>
@@ -7944,7 +7944,7 @@
       <c r="N76" s="14"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="61"/>
+      <c r="A77" s="86"/>
       <c r="B77" s="30" t="s">
         <v>544</v>
       </c>
@@ -7964,7 +7964,7 @@
       <c r="N77" s="14"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="61"/>
+      <c r="A78" s="86"/>
       <c r="B78" s="30" t="s">
         <v>558</v>
       </c>
@@ -7984,7 +7984,7 @@
       <c r="N78" s="14"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="61"/>
+      <c r="A79" s="86"/>
       <c r="B79" s="30" t="s">
         <v>542</v>
       </c>
@@ -8004,7 +8004,7 @@
       <c r="N79" s="14"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="61"/>
+      <c r="A80" s="86"/>
       <c r="B80" s="30" t="s">
         <v>534</v>
       </c>
@@ -8024,7 +8024,7 @@
       <c r="N80" s="14"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="61"/>
+      <c r="A81" s="86"/>
       <c r="B81" s="30" t="s">
         <v>519</v>
       </c>
@@ -8044,7 +8044,7 @@
       <c r="N81" s="14"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="61"/>
+      <c r="A82" s="86"/>
       <c r="B82" s="30" t="s">
         <v>541</v>
       </c>
@@ -8064,14 +8064,14 @@
       <c r="N82" s="14"/>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="86" t="s">
+      <c r="A83" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B83" s="87"/>
-      <c r="C83" s="87"/>
-      <c r="D83" s="87"/>
-      <c r="E83" s="87"/>
-      <c r="F83" s="88"/>
+      <c r="B83" s="53"/>
+      <c r="C83" s="53"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="53"/>
+      <c r="F83" s="54"/>
       <c r="G83" s="39"/>
       <c r="H83" s="39"/>
       <c r="I83" s="39"/>
@@ -8082,7 +8082,7 @@
       <c r="N83" s="14"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="60" t="s">
+      <c r="A84" s="67" t="s">
         <v>605</v>
       </c>
       <c r="B84" s="15" t="s">
@@ -8104,7 +8104,7 @@
       <c r="N84" s="14"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="60"/>
+      <c r="A85" s="67"/>
       <c r="B85" s="15" t="s">
         <v>349</v>
       </c>
@@ -8124,7 +8124,7 @@
       <c r="N85" s="14"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="60"/>
+      <c r="A86" s="67"/>
       <c r="B86" s="15" t="s">
         <v>507</v>
       </c>
@@ -8144,7 +8144,7 @@
       <c r="N86" s="14"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="60"/>
+      <c r="A87" s="67"/>
       <c r="B87" s="15" t="s">
         <v>326</v>
       </c>
@@ -8164,7 +8164,7 @@
       <c r="N87" s="14"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="60"/>
+      <c r="A88" s="67"/>
       <c r="B88" s="15" t="s">
         <v>549</v>
       </c>
@@ -8184,7 +8184,7 @@
       <c r="N88" s="14"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="60"/>
+      <c r="A89" s="67"/>
       <c r="B89" s="15" t="s">
         <v>334</v>
       </c>
@@ -8204,7 +8204,7 @@
       <c r="N89" s="14"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="60"/>
+      <c r="A90" s="67"/>
       <c r="B90" s="15" t="s">
         <v>330</v>
       </c>
@@ -8224,7 +8224,7 @@
       <c r="N90" s="14"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="60"/>
+      <c r="A91" s="67"/>
       <c r="B91" s="15" t="s">
         <v>305</v>
       </c>
@@ -8244,14 +8244,14 @@
       <c r="N91" s="14"/>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="86" t="s">
+      <c r="A92" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B92" s="87"/>
-      <c r="C92" s="87"/>
-      <c r="D92" s="87"/>
-      <c r="E92" s="87"/>
-      <c r="F92" s="88"/>
+      <c r="B92" s="53"/>
+      <c r="C92" s="53"/>
+      <c r="D92" s="53"/>
+      <c r="E92" s="53"/>
+      <c r="F92" s="54"/>
       <c r="G92" s="39"/>
       <c r="H92" s="39"/>
       <c r="I92" s="39"/>
@@ -8262,7 +8262,7 @@
       <c r="N92" s="14"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="60" t="s">
+      <c r="A93" s="67" t="s">
         <v>504</v>
       </c>
       <c r="B93" s="15" t="s">
@@ -8284,7 +8284,7 @@
       <c r="N93" s="14"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="60"/>
+      <c r="A94" s="67"/>
       <c r="B94" s="15" t="s">
         <v>434</v>
       </c>
@@ -8304,7 +8304,7 @@
       <c r="N94" s="14"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="60"/>
+      <c r="A95" s="67"/>
       <c r="B95" s="15" t="s">
         <v>512</v>
       </c>
@@ -8324,7 +8324,7 @@
       <c r="N95" s="14"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="60"/>
+      <c r="A96" s="67"/>
       <c r="B96" s="15" t="s">
         <v>510</v>
       </c>
@@ -8344,7 +8344,7 @@
       <c r="N96" s="14"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="60"/>
+      <c r="A97" s="67"/>
       <c r="B97" s="15" t="s">
         <v>554</v>
       </c>
@@ -8364,7 +8364,7 @@
       <c r="N97" s="14"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="60"/>
+      <c r="A98" s="67"/>
       <c r="B98" s="15" t="s">
         <v>560</v>
       </c>
@@ -8384,7 +8384,7 @@
       <c r="N98" s="14"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="60"/>
+      <c r="A99" s="67"/>
       <c r="B99" s="15" t="s">
         <v>523</v>
       </c>
@@ -8404,7 +8404,7 @@
       <c r="N99" s="14"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="60"/>
+      <c r="A100" s="67"/>
       <c r="B100" s="15" t="s">
         <v>564</v>
       </c>
@@ -8424,7 +8424,7 @@
       <c r="N100" s="14"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="60"/>
+      <c r="A101" s="67"/>
       <c r="B101" s="15" t="s">
         <v>509</v>
       </c>
@@ -8444,7 +8444,7 @@
       <c r="N101" s="14"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="60"/>
+      <c r="A102" s="67"/>
       <c r="B102" s="15" t="s">
         <v>473</v>
       </c>
@@ -8464,7 +8464,7 @@
       <c r="N102" s="14"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="60"/>
+      <c r="A103" s="67"/>
       <c r="B103" s="15" t="s">
         <v>476</v>
       </c>
@@ -8484,7 +8484,7 @@
       <c r="N103" s="14"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="60"/>
+      <c r="A104" s="67"/>
       <c r="B104" s="15" t="s">
         <v>532</v>
       </c>
@@ -8504,7 +8504,7 @@
       <c r="N104" s="14"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="60"/>
+      <c r="A105" s="67"/>
       <c r="B105" s="15" t="s">
         <v>524</v>
       </c>
@@ -8524,7 +8524,7 @@
       <c r="N105" s="14"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="60"/>
+      <c r="A106" s="67"/>
       <c r="B106" s="15" t="s">
         <v>528</v>
       </c>
@@ -8544,7 +8544,7 @@
       <c r="N106" s="14"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="60"/>
+      <c r="A107" s="67"/>
       <c r="B107" s="15" t="s">
         <v>521</v>
       </c>
@@ -8564,7 +8564,7 @@
       <c r="N107" s="14"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="60"/>
+      <c r="A108" s="67"/>
       <c r="B108" s="15" t="s">
         <v>515</v>
       </c>
@@ -8584,14 +8584,14 @@
       <c r="N108" s="14"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="86" t="s">
+      <c r="A109" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B109" s="87"/>
-      <c r="C109" s="87"/>
-      <c r="D109" s="87"/>
-      <c r="E109" s="87"/>
-      <c r="F109" s="88"/>
+      <c r="B109" s="53"/>
+      <c r="C109" s="53"/>
+      <c r="D109" s="53"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="54"/>
       <c r="G109" s="39"/>
       <c r="H109" s="39"/>
       <c r="I109" s="39"/>
@@ -8602,7 +8602,7 @@
       <c r="N109" s="14"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="61" t="s">
+      <c r="A110" s="86" t="s">
         <v>2</v>
       </c>
       <c r="B110" s="30" t="s">
@@ -8624,7 +8624,7 @@
       <c r="N110" s="14"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="61"/>
+      <c r="A111" s="86"/>
       <c r="B111" s="30" t="s">
         <v>547</v>
       </c>
@@ -8644,7 +8644,7 @@
       <c r="N111" s="14"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="61"/>
+      <c r="A112" s="86"/>
       <c r="B112" s="30" t="s">
         <v>540</v>
       </c>
@@ -8664,7 +8664,7 @@
       <c r="N112" s="14"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="61"/>
+      <c r="A113" s="86"/>
       <c r="B113" s="30" t="s">
         <v>543</v>
       </c>
@@ -8684,7 +8684,7 @@
       <c r="N113" s="14"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="61"/>
+      <c r="A114" s="86"/>
       <c r="B114" s="30" t="s">
         <v>538</v>
       </c>
@@ -8704,7 +8704,7 @@
       <c r="N114" s="14"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="61"/>
+      <c r="A115" s="86"/>
       <c r="B115" s="30" t="s">
         <v>537</v>
       </c>
@@ -8724,7 +8724,7 @@
       <c r="N115" s="14"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="61"/>
+      <c r="A116" s="86"/>
       <c r="B116" s="30" t="s">
         <v>261</v>
       </c>
@@ -8744,14 +8744,14 @@
       <c r="N116" s="14"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="86" t="s">
+      <c r="A117" s="52" t="s">
         <v>595</v>
       </c>
-      <c r="B117" s="87"/>
-      <c r="C117" s="87"/>
-      <c r="D117" s="87"/>
-      <c r="E117" s="87"/>
-      <c r="F117" s="88"/>
+      <c r="B117" s="53"/>
+      <c r="C117" s="53"/>
+      <c r="D117" s="53"/>
+      <c r="E117" s="53"/>
+      <c r="F117" s="54"/>
       <c r="G117" s="39"/>
       <c r="H117" s="39"/>
       <c r="I117" s="39"/>
@@ -8762,7 +8762,7 @@
       <c r="N117" s="14"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="60" t="s">
+      <c r="A118" s="67" t="s">
         <v>257</v>
       </c>
       <c r="B118" s="30" t="s">
@@ -8784,7 +8784,7 @@
       <c r="N118" s="14"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="60"/>
+      <c r="A119" s="67"/>
       <c r="B119" s="30" t="s">
         <v>311</v>
       </c>
@@ -8804,7 +8804,7 @@
       <c r="N119" s="14"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="60"/>
+      <c r="A120" s="67"/>
       <c r="B120" s="31" t="s">
         <v>587</v>
       </c>
@@ -8824,7 +8824,7 @@
       <c r="N120" s="14"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="60"/>
+      <c r="A121" s="67"/>
       <c r="B121" s="31" t="s">
         <v>217</v>
       </c>
@@ -8844,14 +8844,14 @@
       <c r="N121" s="14"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="86" t="s">
+      <c r="A122" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B122" s="87"/>
-      <c r="C122" s="87"/>
-      <c r="D122" s="87"/>
-      <c r="E122" s="87"/>
-      <c r="F122" s="88"/>
+      <c r="B122" s="53"/>
+      <c r="C122" s="53"/>
+      <c r="D122" s="53"/>
+      <c r="E122" s="53"/>
+      <c r="F122" s="54"/>
       <c r="G122" s="39"/>
       <c r="H122" s="39"/>
       <c r="I122" s="39"/>
@@ -8862,7 +8862,7 @@
       <c r="N122" s="14"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="60" t="s">
+      <c r="A123" s="67" t="s">
         <v>252</v>
       </c>
       <c r="B123" s="15" t="s">
@@ -8884,7 +8884,7 @@
       <c r="N123" s="14"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="60"/>
+      <c r="A124" s="67"/>
       <c r="B124" s="15" t="s">
         <v>319</v>
       </c>
@@ -8904,7 +8904,7 @@
       <c r="N124" s="14"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="60"/>
+      <c r="A125" s="67"/>
       <c r="B125" s="15" t="s">
         <v>588</v>
       </c>
@@ -8924,7 +8924,7 @@
       <c r="N125" s="14"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="60"/>
+      <c r="A126" s="67"/>
       <c r="B126" s="15" t="s">
         <v>207</v>
       </c>
@@ -8944,7 +8944,7 @@
       <c r="N126" s="14"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="60"/>
+      <c r="A127" s="67"/>
       <c r="B127" s="15" t="s">
         <v>376</v>
       </c>
@@ -8964,7 +8964,7 @@
       <c r="N127" s="14"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="60"/>
+      <c r="A128" s="67"/>
       <c r="B128" s="15" t="s">
         <v>234</v>
       </c>
@@ -8984,7 +8984,7 @@
       <c r="N128" s="14"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="60"/>
+      <c r="A129" s="67"/>
       <c r="B129" s="15" t="s">
         <v>239</v>
       </c>
@@ -9004,7 +9004,7 @@
       <c r="N129" s="14"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="60"/>
+      <c r="A130" s="67"/>
       <c r="B130" s="15" t="s">
         <v>373</v>
       </c>
@@ -9024,7 +9024,7 @@
       <c r="N130" s="14"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="60"/>
+      <c r="A131" s="67"/>
       <c r="B131" s="15" t="s">
         <v>593</v>
       </c>
@@ -9044,7 +9044,7 @@
       <c r="N131" s="14"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="60"/>
+      <c r="A132" s="67"/>
       <c r="B132" s="31" t="s">
         <v>406</v>
       </c>
@@ -9064,7 +9064,7 @@
       <c r="N132" s="14"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="60"/>
+      <c r="A133" s="67"/>
       <c r="B133" s="31" t="s">
         <v>348</v>
       </c>
@@ -9084,7 +9084,7 @@
       <c r="N133" s="14"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="60"/>
+      <c r="A134" s="67"/>
       <c r="B134" s="31" t="s">
         <v>395</v>
       </c>
@@ -9104,14 +9104,14 @@
       <c r="N134" s="14"/>
     </row>
     <row r="135" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="86" t="s">
+      <c r="A135" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B135" s="87"/>
-      <c r="C135" s="87"/>
-      <c r="D135" s="87"/>
-      <c r="E135" s="87"/>
-      <c r="F135" s="88"/>
+      <c r="B135" s="53"/>
+      <c r="C135" s="53"/>
+      <c r="D135" s="53"/>
+      <c r="E135" s="53"/>
+      <c r="F135" s="54"/>
       <c r="G135" s="39"/>
       <c r="H135" s="39"/>
       <c r="I135" s="39"/>
@@ -9122,7 +9122,7 @@
       <c r="N135" s="14"/>
     </row>
     <row r="136" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="60" t="s">
+      <c r="A136" s="67" t="s">
         <v>603</v>
       </c>
       <c r="B136" s="15" t="s">
@@ -9144,7 +9144,7 @@
       <c r="N136" s="14"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="60"/>
+      <c r="A137" s="67"/>
       <c r="B137" s="15" t="s">
         <v>368</v>
       </c>
@@ -9164,7 +9164,7 @@
       <c r="N137" s="14"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="60"/>
+      <c r="A138" s="67"/>
       <c r="B138" s="15" t="s">
         <v>235</v>
       </c>
@@ -9184,7 +9184,7 @@
       <c r="N138" s="14"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="60"/>
+      <c r="A139" s="67"/>
       <c r="B139" s="30" t="s">
         <v>221</v>
       </c>
@@ -9204,7 +9204,7 @@
       <c r="N139" s="14"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="60"/>
+      <c r="A140" s="67"/>
       <c r="B140" s="15" t="s">
         <v>320</v>
       </c>
@@ -9224,7 +9224,7 @@
       <c r="N140" s="14"/>
     </row>
     <row r="141" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="60"/>
+      <c r="A141" s="67"/>
       <c r="B141" s="15" t="s">
         <v>236</v>
       </c>
@@ -9244,7 +9244,7 @@
       <c r="N141" s="14"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="60"/>
+      <c r="A142" s="67"/>
       <c r="B142" s="30" t="s">
         <v>251</v>
       </c>
@@ -9264,7 +9264,7 @@
       <c r="N142" s="14"/>
     </row>
     <row r="143" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="60" t="s">
+      <c r="A143" s="67" t="s">
         <v>603</v>
       </c>
       <c r="B143" s="15" t="s">
@@ -9286,7 +9286,7 @@
       <c r="N143" s="14"/>
     </row>
     <row r="144" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="60"/>
+      <c r="A144" s="67"/>
       <c r="B144" s="15" t="s">
         <v>201</v>
       </c>
@@ -9306,7 +9306,7 @@
       <c r="N144" s="14"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="60"/>
+      <c r="A145" s="67"/>
       <c r="B145" s="15" t="s">
         <v>364</v>
       </c>
@@ -9326,7 +9326,7 @@
       <c r="N145" s="14"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="60"/>
+      <c r="A146" s="67"/>
       <c r="B146" s="15" t="s">
         <v>388</v>
       </c>
@@ -9346,7 +9346,7 @@
       <c r="N146" s="14"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="60"/>
+      <c r="A147" s="67"/>
       <c r="B147" s="15" t="s">
         <v>358</v>
       </c>
@@ -9366,7 +9366,7 @@
       <c r="N147" s="14"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="60"/>
+      <c r="A148" s="67"/>
       <c r="B148" s="15" t="s">
         <v>377</v>
       </c>
@@ -9386,7 +9386,7 @@
       <c r="N148" s="14"/>
     </row>
     <row r="149" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="60"/>
+      <c r="A149" s="67"/>
       <c r="B149" s="15" t="s">
         <v>370</v>
       </c>
@@ -9406,7 +9406,7 @@
       <c r="N149" s="14"/>
     </row>
     <row r="150" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="60"/>
+      <c r="A150" s="67"/>
       <c r="B150" s="15" t="s">
         <v>199</v>
       </c>
@@ -9426,7 +9426,7 @@
       <c r="N150" s="14"/>
     </row>
     <row r="151" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="60"/>
+      <c r="A151" s="67"/>
       <c r="B151" s="15" t="s">
         <v>260</v>
       </c>
@@ -9446,14 +9446,14 @@
       <c r="N151" s="14"/>
     </row>
     <row r="152" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="86" t="s">
+      <c r="A152" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B152" s="87"/>
-      <c r="C152" s="87"/>
-      <c r="D152" s="87"/>
-      <c r="E152" s="87"/>
-      <c r="F152" s="88"/>
+      <c r="B152" s="53"/>
+      <c r="C152" s="53"/>
+      <c r="D152" s="53"/>
+      <c r="E152" s="53"/>
+      <c r="F152" s="54"/>
       <c r="G152" s="39"/>
       <c r="H152" s="39"/>
       <c r="I152" s="39"/>
@@ -9464,7 +9464,7 @@
       <c r="N152" s="14"/>
     </row>
     <row r="153" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="60" t="s">
+      <c r="A153" s="67" t="s">
         <v>599</v>
       </c>
       <c r="B153" s="15" t="s">
@@ -9486,7 +9486,7 @@
       <c r="N153" s="14"/>
     </row>
     <row r="154" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="60"/>
+      <c r="A154" s="67"/>
       <c r="B154" s="15">
         <v>25034</v>
       </c>
@@ -9506,7 +9506,7 @@
       <c r="N154" s="14"/>
     </row>
     <row r="155" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="60"/>
+      <c r="A155" s="67"/>
       <c r="B155" s="15" t="s">
         <v>309</v>
       </c>
@@ -9548,7 +9548,7 @@
       <c r="N156" s="14"/>
     </row>
     <row r="157" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="60" t="s">
+      <c r="A157" s="67" t="s">
         <v>300</v>
       </c>
       <c r="B157" s="15" t="s">
@@ -9570,7 +9570,7 @@
       <c r="N157" s="14"/>
     </row>
     <row r="158" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="60"/>
+      <c r="A158" s="67"/>
       <c r="B158" s="30" t="s">
         <v>346</v>
       </c>
@@ -9590,7 +9590,7 @@
       <c r="N158" s="14"/>
     </row>
     <row r="159" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="60"/>
+      <c r="A159" s="67"/>
       <c r="B159" s="30" t="s">
         <v>670</v>
       </c>
@@ -9632,14 +9632,14 @@
       <c r="N160" s="14"/>
     </row>
     <row r="161" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="86" t="s">
+      <c r="A161" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B161" s="87"/>
-      <c r="C161" s="87"/>
-      <c r="D161" s="87"/>
-      <c r="E161" s="87"/>
-      <c r="F161" s="88"/>
+      <c r="B161" s="53"/>
+      <c r="C161" s="53"/>
+      <c r="D161" s="53"/>
+      <c r="E161" s="53"/>
+      <c r="F161" s="54"/>
       <c r="G161" s="39"/>
       <c r="H161" s="39"/>
       <c r="I161" s="39"/>
@@ -9650,7 +9650,7 @@
       <c r="N161" s="14"/>
     </row>
     <row r="162" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="61" t="s">
+      <c r="A162" s="86" t="s">
         <v>59</v>
       </c>
       <c r="B162" s="15" t="s">
@@ -9672,7 +9672,7 @@
       <c r="N162" s="14"/>
     </row>
     <row r="163" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="61"/>
+      <c r="A163" s="86"/>
       <c r="B163" s="15" t="s">
         <v>347</v>
       </c>
@@ -9692,7 +9692,7 @@
       <c r="N163" s="14"/>
     </row>
     <row r="164" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="61"/>
+      <c r="A164" s="86"/>
       <c r="B164" s="15" t="s">
         <v>421</v>
       </c>
@@ -9712,7 +9712,7 @@
       <c r="N164" s="14"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="61"/>
+      <c r="A165" s="86"/>
       <c r="B165" s="15" t="s">
         <v>323</v>
       </c>
@@ -9732,7 +9732,7 @@
       <c r="N165" s="14"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="61"/>
+      <c r="A166" s="86"/>
       <c r="B166" s="15" t="s">
         <v>342</v>
       </c>
@@ -9752,7 +9752,7 @@
       <c r="N166" s="14"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="61"/>
+      <c r="A167" s="86"/>
       <c r="B167" s="15" t="s">
         <v>322</v>
       </c>
@@ -9772,7 +9772,7 @@
       <c r="N167" s="14"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="61"/>
+      <c r="A168" s="86"/>
       <c r="B168" s="15" t="s">
         <v>291</v>
       </c>
@@ -9792,7 +9792,7 @@
       <c r="N168" s="14"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="61"/>
+      <c r="A169" s="86"/>
       <c r="B169" s="15" t="s">
         <v>331</v>
       </c>
@@ -9812,14 +9812,14 @@
       <c r="N169" s="14"/>
     </row>
     <row r="170" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="86" t="s">
+      <c r="A170" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B170" s="87"/>
-      <c r="C170" s="87"/>
-      <c r="D170" s="87"/>
-      <c r="E170" s="87"/>
-      <c r="F170" s="88"/>
+      <c r="B170" s="53"/>
+      <c r="C170" s="53"/>
+      <c r="D170" s="53"/>
+      <c r="E170" s="53"/>
+      <c r="F170" s="54"/>
       <c r="G170" s="39"/>
       <c r="H170" s="39"/>
       <c r="I170" s="39"/>
@@ -9830,7 +9830,7 @@
       <c r="N170" s="14"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="60" t="s">
+      <c r="A171" s="67" t="s">
         <v>604</v>
       </c>
       <c r="B171" s="15" t="s">
@@ -9852,7 +9852,7 @@
       <c r="N171" s="14"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="60"/>
+      <c r="A172" s="67"/>
       <c r="B172" s="15" t="s">
         <v>266</v>
       </c>
@@ -9872,7 +9872,7 @@
       <c r="N172" s="14"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="60"/>
+      <c r="A173" s="67"/>
       <c r="B173" s="15" t="s">
         <v>362</v>
       </c>
@@ -9892,7 +9892,7 @@
       <c r="N173" s="14"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="60"/>
+      <c r="A174" s="67"/>
       <c r="B174" s="15" t="s">
         <v>379</v>
       </c>
@@ -9912,14 +9912,14 @@
       <c r="N174" s="14"/>
     </row>
     <row r="175" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="86" t="s">
+      <c r="A175" s="52" t="s">
         <v>135</v>
       </c>
-      <c r="B175" s="87"/>
-      <c r="C175" s="87"/>
-      <c r="D175" s="87"/>
-      <c r="E175" s="87"/>
-      <c r="F175" s="88"/>
+      <c r="B175" s="53"/>
+      <c r="C175" s="53"/>
+      <c r="D175" s="53"/>
+      <c r="E175" s="53"/>
+      <c r="F175" s="54"/>
       <c r="G175" s="39"/>
       <c r="H175" s="39"/>
       <c r="I175" s="39"/>
@@ -9930,7 +9930,7 @@
       <c r="N175" s="14"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="60" t="s">
+      <c r="A176" s="67" t="s">
         <v>324</v>
       </c>
       <c r="B176" s="15" t="s">
@@ -9952,7 +9952,7 @@
       <c r="N176" s="14"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="60"/>
+      <c r="A177" s="67"/>
       <c r="B177" s="15" t="s">
         <v>445</v>
       </c>
@@ -9972,14 +9972,14 @@
       <c r="N177" s="14"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="89" t="s">
+      <c r="A178" s="55" t="s">
         <v>135</v>
       </c>
-      <c r="B178" s="90"/>
-      <c r="C178" s="90"/>
-      <c r="D178" s="90"/>
-      <c r="E178" s="90"/>
-      <c r="F178" s="91"/>
+      <c r="B178" s="56"/>
+      <c r="C178" s="56"/>
+      <c r="D178" s="56"/>
+      <c r="E178" s="56"/>
+      <c r="F178" s="57"/>
       <c r="G178" s="48"/>
       <c r="H178" s="48"/>
       <c r="I178" s="48"/>
@@ -9990,14 +9990,14 @@
       <c r="N178" s="23"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="92" t="s">
+      <c r="A179" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="B179" s="93"/>
-      <c r="C179" s="93"/>
-      <c r="D179" s="93"/>
-      <c r="E179" s="93"/>
-      <c r="F179" s="94"/>
+      <c r="B179" s="59"/>
+      <c r="C179" s="59"/>
+      <c r="D179" s="59"/>
+      <c r="E179" s="59"/>
+      <c r="F179" s="60"/>
       <c r="G179" s="49"/>
       <c r="H179" s="49"/>
       <c r="I179" s="49"/>
@@ -10027,84 +10027,112 @@
       <c r="A181" s="3"/>
       <c r="B181" s="1"/>
       <c r="C181" s="5"/>
-      <c r="D181" s="79"/>
-      <c r="E181" s="80"/>
-      <c r="F181" s="80"/>
-      <c r="G181" s="72"/>
-      <c r="H181" s="72"/>
-      <c r="I181" s="72"/>
-      <c r="J181" s="73"/>
+      <c r="D181" s="71"/>
+      <c r="E181" s="72"/>
+      <c r="F181" s="72"/>
+      <c r="G181" s="63"/>
+      <c r="H181" s="63"/>
+      <c r="I181" s="63"/>
+      <c r="J181" s="64"/>
       <c r="K181" s="8"/>
       <c r="L181" s="8"/>
       <c r="M181" s="8"/>
       <c r="N181" s="8"/>
     </row>
     <row r="182" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D182" s="81" t="s">
+      <c r="D182" s="73" t="s">
         <v>777</v>
       </c>
-      <c r="E182" s="82"/>
-      <c r="F182" s="82"/>
-      <c r="G182" s="74"/>
-      <c r="H182" s="74"/>
-      <c r="I182" s="74"/>
-      <c r="J182" s="75"/>
+      <c r="E182" s="74"/>
+      <c r="F182" s="74"/>
+      <c r="G182" s="65"/>
+      <c r="H182" s="65"/>
+      <c r="I182" s="65"/>
+      <c r="J182" s="66"/>
     </row>
     <row r="183" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D183" s="66" t="s">
+      <c r="D183" s="75" t="s">
         <v>778</v>
       </c>
-      <c r="E183" s="58"/>
-      <c r="F183" s="58"/>
-      <c r="G183" s="60"/>
-      <c r="H183" s="60"/>
-      <c r="I183" s="60"/>
-      <c r="J183" s="77"/>
+      <c r="E183" s="76"/>
+      <c r="F183" s="76"/>
+      <c r="G183" s="67"/>
+      <c r="H183" s="67"/>
+      <c r="I183" s="67"/>
+      <c r="J183" s="69"/>
     </row>
     <row r="184" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D184" s="66" t="s">
+      <c r="D184" s="75" t="s">
         <v>779</v>
       </c>
-      <c r="E184" s="58"/>
-      <c r="F184" s="58"/>
-      <c r="G184" s="60"/>
-      <c r="H184" s="60"/>
-      <c r="I184" s="60"/>
-      <c r="J184" s="77"/>
+      <c r="E184" s="76"/>
+      <c r="F184" s="76"/>
+      <c r="G184" s="67"/>
+      <c r="H184" s="67"/>
+      <c r="I184" s="67"/>
+      <c r="J184" s="69"/>
     </row>
     <row r="185" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D185" s="67" t="s">
+      <c r="D185" s="77" t="s">
         <v>780</v>
       </c>
-      <c r="E185" s="68"/>
-      <c r="F185" s="68"/>
-      <c r="G185" s="76"/>
-      <c r="H185" s="76"/>
-      <c r="I185" s="76"/>
-      <c r="J185" s="78"/>
+      <c r="E185" s="78"/>
+      <c r="F185" s="78"/>
+      <c r="G185" s="68"/>
+      <c r="H185" s="68"/>
+      <c r="I185" s="68"/>
+      <c r="J185" s="70"/>
     </row>
     <row r="186" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D186" s="64" t="s">
+      <c r="D186" s="61" t="s">
         <v>781</v>
       </c>
-      <c r="E186" s="65"/>
-      <c r="F186" s="65"/>
-      <c r="G186" s="72"/>
-      <c r="H186" s="72"/>
-      <c r="I186" s="72"/>
-      <c r="J186" s="72"/>
+      <c r="E186" s="62"/>
+      <c r="F186" s="62"/>
+      <c r="G186" s="63"/>
+      <c r="H186" s="63"/>
+      <c r="I186" s="63"/>
+      <c r="J186" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="A170:F170"/>
-    <mergeCell ref="A175:F175"/>
-    <mergeCell ref="A178:F178"/>
-    <mergeCell ref="A179:F179"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A117:F117"/>
-    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A8:A18"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A25:A50"/>
+    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A75:A82"/>
+    <mergeCell ref="A84:A91"/>
+    <mergeCell ref="A93:A108"/>
+    <mergeCell ref="A110:A116"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="D184:F184"/>
+    <mergeCell ref="D185:F185"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="A171:A174"/>
+    <mergeCell ref="A176:A177"/>
+    <mergeCell ref="A118:A121"/>
+    <mergeCell ref="A123:A134"/>
     <mergeCell ref="D186:F186"/>
     <mergeCell ref="G181:H181"/>
     <mergeCell ref="I181:J181"/>
@@ -10121,22 +10149,15 @@
     <mergeCell ref="D181:F181"/>
     <mergeCell ref="D182:F182"/>
     <mergeCell ref="D183:F183"/>
-    <mergeCell ref="D184:F184"/>
-    <mergeCell ref="D185:F185"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="A171:A174"/>
-    <mergeCell ref="A176:A177"/>
-    <mergeCell ref="A118:A121"/>
-    <mergeCell ref="A123:A134"/>
+    <mergeCell ref="A170:F170"/>
+    <mergeCell ref="A175:F175"/>
+    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="A179:F179"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A122:F122"/>
     <mergeCell ref="A136:A142"/>
     <mergeCell ref="A143:A151"/>
     <mergeCell ref="A157:A159"/>
@@ -10144,27 +10165,6 @@
     <mergeCell ref="A162:A169"/>
     <mergeCell ref="A135:F135"/>
     <mergeCell ref="A152:F152"/>
-    <mergeCell ref="A161:F161"/>
-    <mergeCell ref="A25:A50"/>
-    <mergeCell ref="A58:A63"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="A75:A82"/>
-    <mergeCell ref="A84:A91"/>
-    <mergeCell ref="A93:A108"/>
-    <mergeCell ref="A110:A116"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A8:A18"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A24:F24"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -12646,22 +12646,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="81" t="s">
         <v>717</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32"/>
@@ -12692,67 +12692,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="90" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="87" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="84" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="84" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="84" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="79" t="s">
         <v>723</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="79" t="s">
         <v>669</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="79" t="s">
         <v>673</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="79" t="s">
         <v>680</v>
       </c>
-      <c r="J6" s="52" t="s">
+      <c r="J6" s="79" t="s">
         <v>681</v>
       </c>
-      <c r="K6" s="52" t="s">
+      <c r="K6" s="79" t="s">
         <v>682</v>
       </c>
-      <c r="L6" s="52" t="s">
+      <c r="L6" s="79" t="s">
         <v>700</v>
       </c>
-      <c r="M6" s="52" t="s">
+      <c r="M6" s="79" t="s">
         <v>724</v>
       </c>
-      <c r="N6" s="70" t="s">
+      <c r="N6" s="82" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="63"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="71"/>
+      <c r="A7" s="91"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="83"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="96" t="s">
         <v>728</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -12774,7 +12774,7 @@
       <c r="N8" s="28"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="84"/>
+      <c r="A9" s="94"/>
       <c r="B9" s="13" t="s">
         <v>410</v>
       </c>
@@ -12794,7 +12794,7 @@
       <c r="N9" s="27"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="84"/>
+      <c r="A10" s="94"/>
       <c r="B10" s="11" t="s">
         <v>341</v>
       </c>
@@ -12814,7 +12814,7 @@
       <c r="N10" s="27"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="84"/>
+      <c r="A11" s="94"/>
       <c r="B11" s="11" t="s">
         <v>293</v>
       </c>
@@ -12834,7 +12834,7 @@
       <c r="N11" s="27"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
+      <c r="A12" s="94"/>
       <c r="B12" s="11" t="s">
         <v>391</v>
       </c>
@@ -12854,7 +12854,7 @@
       <c r="N12" s="27"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="84"/>
+      <c r="A13" s="94"/>
       <c r="B13" s="11" t="s">
         <v>420</v>
       </c>
@@ -12874,7 +12874,7 @@
       <c r="N13" s="27"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="84"/>
+      <c r="A14" s="94"/>
       <c r="B14" s="11" t="s">
         <v>426</v>
       </c>
@@ -12894,7 +12894,7 @@
       <c r="N14" s="27"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="84"/>
+      <c r="A15" s="94"/>
       <c r="B15" s="11" t="s">
         <v>424</v>
       </c>
@@ -12914,7 +12914,7 @@
       <c r="N15" s="27"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="84"/>
+      <c r="A16" s="94"/>
       <c r="B16" s="11" t="s">
         <v>290</v>
       </c>
@@ -12934,7 +12934,7 @@
       <c r="N16" s="27"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="84"/>
+      <c r="A17" s="94"/>
       <c r="B17" s="11" t="s">
         <v>497</v>
       </c>
@@ -12954,7 +12954,7 @@
       <c r="N17" s="27"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="84"/>
+      <c r="A18" s="94"/>
       <c r="B18" s="11" t="s">
         <v>425</v>
       </c>
@@ -12974,7 +12974,7 @@
       <c r="N18" s="27"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="84"/>
+      <c r="A19" s="94"/>
       <c r="B19" s="11" t="s">
         <v>703</v>
       </c>
@@ -12994,14 +12994,14 @@
       <c r="N19" s="27"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="96" t="s">
+      <c r="A20" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B20" s="87"/>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-      <c r="F20" s="88"/>
+      <c r="B20" s="53"/>
+      <c r="C20" s="53"/>
+      <c r="D20" s="53"/>
+      <c r="E20" s="53"/>
+      <c r="F20" s="54"/>
       <c r="G20" s="39"/>
       <c r="H20" s="39"/>
       <c r="I20" s="39"/>
@@ -13012,7 +13012,7 @@
       <c r="N20" s="27"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="84" t="s">
+      <c r="A21" s="94" t="s">
         <v>730</v>
       </c>
       <c r="B21" s="40" t="s">
@@ -13034,7 +13034,7 @@
       <c r="N21" s="27"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="84"/>
+      <c r="A22" s="94"/>
       <c r="B22" s="41" t="s">
         <v>413</v>
       </c>
@@ -13054,7 +13054,7 @@
       <c r="N22" s="27"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="84"/>
+      <c r="A23" s="94"/>
       <c r="B23" s="40" t="s">
         <v>439</v>
       </c>
@@ -13074,7 +13074,7 @@
       <c r="N23" s="27"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="84"/>
+      <c r="A24" s="94"/>
       <c r="B24" s="40" t="s">
         <v>444</v>
       </c>
@@ -13094,7 +13094,7 @@
       <c r="N24" s="27"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="84"/>
+      <c r="A25" s="94"/>
       <c r="B25" s="40" t="s">
         <v>289</v>
       </c>
@@ -13114,7 +13114,7 @@
       <c r="N25" s="27"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="84"/>
+      <c r="A26" s="94"/>
       <c r="B26" s="40" t="s">
         <v>477</v>
       </c>
@@ -13134,7 +13134,7 @@
       <c r="N26" s="27"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="84"/>
+      <c r="A27" s="94"/>
       <c r="B27" s="40" t="s">
         <v>284</v>
       </c>
@@ -13154,7 +13154,7 @@
       <c r="N27" s="27"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="84"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="40" t="s">
         <v>731</v>
       </c>
@@ -13174,14 +13174,14 @@
       <c r="N28" s="27"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="96" t="s">
+      <c r="A29" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B29" s="87"/>
-      <c r="C29" s="87"/>
-      <c r="D29" s="87"/>
-      <c r="E29" s="87"/>
-      <c r="F29" s="88"/>
+      <c r="B29" s="53"/>
+      <c r="C29" s="53"/>
+      <c r="D29" s="53"/>
+      <c r="E29" s="53"/>
+      <c r="F29" s="54"/>
       <c r="G29" s="39"/>
       <c r="H29" s="39"/>
       <c r="I29" s="39"/>
@@ -13192,7 +13192,7 @@
       <c r="N29" s="27"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="84" t="s">
+      <c r="A30" s="94" t="s">
         <v>732</v>
       </c>
       <c r="B30" s="42" t="s">
@@ -13214,7 +13214,7 @@
       <c r="N30" s="27"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="84"/>
+      <c r="A31" s="94"/>
       <c r="B31" s="42" t="s">
         <v>383</v>
       </c>
@@ -13234,7 +13234,7 @@
       <c r="N31" s="27"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="84"/>
+      <c r="A32" s="94"/>
       <c r="B32" s="44" t="s">
         <v>419</v>
       </c>
@@ -13254,7 +13254,7 @@
       <c r="N32" s="27"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="84"/>
+      <c r="A33" s="94"/>
       <c r="B33" s="42" t="s">
         <v>449</v>
       </c>
@@ -13274,14 +13274,14 @@
       <c r="N33" s="27"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="96" t="s">
+      <c r="A34" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B34" s="87"/>
-      <c r="C34" s="87"/>
-      <c r="D34" s="87"/>
-      <c r="E34" s="87"/>
-      <c r="F34" s="88"/>
+      <c r="B34" s="53"/>
+      <c r="C34" s="53"/>
+      <c r="D34" s="53"/>
+      <c r="E34" s="53"/>
+      <c r="F34" s="54"/>
       <c r="G34" s="39"/>
       <c r="H34" s="39"/>
       <c r="I34" s="39"/>
@@ -13292,7 +13292,7 @@
       <c r="N34" s="27"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="85" t="s">
+      <c r="A35" s="95" t="s">
         <v>733</v>
       </c>
       <c r="B35" s="40" t="s">
@@ -13314,7 +13314,7 @@
       <c r="N35" s="27"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="85"/>
+      <c r="A36" s="95"/>
       <c r="B36" s="41" t="s">
         <v>461</v>
       </c>
@@ -13334,7 +13334,7 @@
       <c r="N36" s="27"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="85"/>
+      <c r="A37" s="95"/>
       <c r="B37" s="40" t="s">
         <v>274</v>
       </c>
@@ -13354,7 +13354,7 @@
       <c r="N37" s="27"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="85"/>
+      <c r="A38" s="95"/>
       <c r="B38" s="40" t="s">
         <v>248</v>
       </c>
@@ -13374,7 +13374,7 @@
       <c r="N38" s="27"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="85"/>
+      <c r="A39" s="95"/>
       <c r="B39" s="40" t="s">
         <v>273</v>
       </c>
@@ -13394,7 +13394,7 @@
       <c r="N39" s="27"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="85"/>
+      <c r="A40" s="95"/>
       <c r="B40" s="40" t="s">
         <v>241</v>
       </c>
@@ -13414,7 +13414,7 @@
       <c r="N40" s="27"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="85"/>
+      <c r="A41" s="95"/>
       <c r="B41" s="40" t="s">
         <v>269</v>
       </c>
@@ -13434,7 +13434,7 @@
       <c r="N41" s="27"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="85"/>
+      <c r="A42" s="95"/>
       <c r="B42" s="40" t="s">
         <v>267</v>
       </c>
@@ -13454,7 +13454,7 @@
       <c r="N42" s="27"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="85"/>
+      <c r="A43" s="95"/>
       <c r="B43" s="40" t="s">
         <v>407</v>
       </c>
@@ -13474,7 +13474,7 @@
       <c r="N43" s="27"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="85"/>
+      <c r="A44" s="95"/>
       <c r="B44" s="40" t="s">
         <v>443</v>
       </c>
@@ -13494,7 +13494,7 @@
       <c r="N44" s="27"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="85"/>
+      <c r="A45" s="95"/>
       <c r="B45" s="40" t="s">
         <v>249</v>
       </c>
@@ -13514,7 +13514,7 @@
       <c r="N45" s="27"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="85"/>
+      <c r="A46" s="95"/>
       <c r="B46" s="40" t="s">
         <v>478</v>
       </c>
@@ -13534,14 +13534,14 @@
       <c r="N46" s="27"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="96" t="s">
+      <c r="A47" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="87"/>
-      <c r="C47" s="87"/>
-      <c r="D47" s="87"/>
-      <c r="E47" s="87"/>
-      <c r="F47" s="88"/>
+      <c r="B47" s="53"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
       <c r="G47" s="39"/>
       <c r="H47" s="39"/>
       <c r="I47" s="39"/>
@@ -13552,7 +13552,7 @@
       <c r="N47" s="27"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="85" t="s">
+      <c r="A48" s="95" t="s">
         <v>734</v>
       </c>
       <c r="B48" s="15" t="s">
@@ -13574,7 +13574,7 @@
       <c r="N48" s="27"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="85"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="15" t="s">
         <v>592</v>
       </c>
@@ -13594,7 +13594,7 @@
       <c r="N49" s="27"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="85"/>
+      <c r="A50" s="95"/>
       <c r="B50" s="15" t="s">
         <v>591</v>
       </c>
@@ -13614,7 +13614,7 @@
       <c r="N50" s="27"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="85"/>
+      <c r="A51" s="95"/>
       <c r="B51" s="15" t="s">
         <v>586</v>
       </c>
@@ -13634,7 +13634,7 @@
       <c r="N51" s="27"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="85"/>
+      <c r="A52" s="95"/>
       <c r="B52" s="15" t="s">
         <v>562</v>
       </c>
@@ -13654,7 +13654,7 @@
       <c r="N52" s="27"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="85"/>
+      <c r="A53" s="95"/>
       <c r="B53" s="15" t="s">
         <v>563</v>
       </c>
@@ -13674,7 +13674,7 @@
       <c r="N53" s="27"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="85"/>
+      <c r="A54" s="95"/>
       <c r="B54" s="15" t="s">
         <v>567</v>
       </c>
@@ -13694,7 +13694,7 @@
       <c r="N54" s="27"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="85"/>
+      <c r="A55" s="95"/>
       <c r="B55" s="15" t="s">
         <v>213</v>
       </c>
@@ -13714,7 +13714,7 @@
       <c r="N55" s="27"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="85"/>
+      <c r="A56" s="95"/>
       <c r="B56" s="15" t="s">
         <v>568</v>
       </c>
@@ -13734,7 +13734,7 @@
       <c r="N56" s="27"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="84"/>
+      <c r="A57" s="94"/>
       <c r="B57" s="15" t="s">
         <v>576</v>
       </c>
@@ -13754,7 +13754,7 @@
       <c r="N57" s="27"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="84"/>
+      <c r="A58" s="94"/>
       <c r="B58" s="15" t="s">
         <v>454</v>
       </c>
@@ -13774,14 +13774,14 @@
       <c r="N58" s="27"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="96" t="s">
+      <c r="A59" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B59" s="87"/>
-      <c r="C59" s="87"/>
-      <c r="D59" s="87"/>
-      <c r="E59" s="87"/>
-      <c r="F59" s="88"/>
+      <c r="B59" s="53"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="54"/>
       <c r="G59" s="39"/>
       <c r="H59" s="39"/>
       <c r="I59" s="39"/>
@@ -13792,7 +13792,7 @@
       <c r="N59" s="27"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="85" t="s">
+      <c r="A60" s="95" t="s">
         <v>736</v>
       </c>
       <c r="B60" s="15" t="s">
@@ -13814,7 +13814,7 @@
       <c r="N60" s="27"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="84"/>
+      <c r="A61" s="94"/>
       <c r="B61" s="15" t="s">
         <v>469</v>
       </c>
@@ -13834,7 +13834,7 @@
       <c r="N61" s="27"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="84"/>
+      <c r="A62" s="94"/>
       <c r="B62" s="15" t="s">
         <v>705</v>
       </c>
@@ -13854,7 +13854,7 @@
       <c r="N62" s="27"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="84"/>
+      <c r="A63" s="94"/>
       <c r="B63" s="15" t="s">
         <v>457</v>
       </c>
@@ -13874,7 +13874,7 @@
       <c r="N63" s="27"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="84"/>
+      <c r="A64" s="94"/>
       <c r="B64" s="15" t="s">
         <v>707</v>
       </c>
@@ -13894,7 +13894,7 @@
       <c r="N64" s="27"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="84"/>
+      <c r="A65" s="94"/>
       <c r="B65" s="15" t="s">
         <v>438</v>
       </c>
@@ -13914,7 +13914,7 @@
       <c r="N65" s="27"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="84"/>
+      <c r="A66" s="94"/>
       <c r="B66" s="15" t="s">
         <v>709</v>
       </c>
@@ -13934,7 +13934,7 @@
       <c r="N66" s="27"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="84"/>
+      <c r="A67" s="94"/>
       <c r="B67" s="15" t="s">
         <v>694</v>
       </c>
@@ -13954,7 +13954,7 @@
       <c r="N67" s="27"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="84"/>
+      <c r="A68" s="94"/>
       <c r="B68" s="15" t="s">
         <v>441</v>
       </c>
@@ -13974,7 +13974,7 @@
       <c r="N68" s="27"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="84"/>
+      <c r="A69" s="94"/>
       <c r="B69" s="15" t="s">
         <v>206</v>
       </c>
@@ -13994,7 +13994,7 @@
       <c r="N69" s="27"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="84"/>
+      <c r="A70" s="94"/>
       <c r="B70" s="15" t="s">
         <v>711</v>
       </c>
@@ -14014,7 +14014,7 @@
       <c r="N70" s="27"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="84"/>
+      <c r="A71" s="94"/>
       <c r="B71" s="15" t="s">
         <v>459</v>
       </c>
@@ -14034,7 +14034,7 @@
       <c r="N71" s="27"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="84"/>
+      <c r="A72" s="94"/>
       <c r="B72" s="15" t="s">
         <v>713</v>
       </c>
@@ -14054,7 +14054,7 @@
       <c r="N72" s="27"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="84"/>
+      <c r="A73" s="94"/>
       <c r="B73" s="15" t="s">
         <v>559</v>
       </c>
@@ -14074,7 +14074,7 @@
       <c r="N73" s="27"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="84"/>
+      <c r="A74" s="94"/>
       <c r="B74" s="15" t="s">
         <v>585</v>
       </c>
@@ -14094,14 +14094,14 @@
       <c r="N74" s="27"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="96" t="s">
+      <c r="A75" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B75" s="87"/>
-      <c r="C75" s="87"/>
-      <c r="D75" s="87"/>
-      <c r="E75" s="87"/>
-      <c r="F75" s="88"/>
+      <c r="B75" s="53"/>
+      <c r="C75" s="53"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="54"/>
       <c r="G75" s="39"/>
       <c r="H75" s="39"/>
       <c r="I75" s="39"/>
@@ -14112,7 +14112,7 @@
       <c r="N75" s="27"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="85" t="s">
+      <c r="A76" s="95" t="s">
         <v>737</v>
       </c>
       <c r="B76" s="45" t="s">
@@ -14134,7 +14134,7 @@
       <c r="N76" s="27"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="85"/>
+      <c r="A77" s="95"/>
       <c r="B77" s="40" t="s">
         <v>570</v>
       </c>
@@ -14154,7 +14154,7 @@
       <c r="N77" s="27"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="85"/>
+      <c r="A78" s="95"/>
       <c r="B78" s="45" t="s">
         <v>594</v>
       </c>
@@ -14174,7 +14174,7 @@
       <c r="N78" s="27"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="85"/>
+      <c r="A79" s="95"/>
       <c r="B79" s="45" t="s">
         <v>231</v>
       </c>
@@ -14194,7 +14194,7 @@
       <c r="N79" s="27"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="85"/>
+      <c r="A80" s="95"/>
       <c r="B80" s="45" t="s">
         <v>219</v>
       </c>
@@ -14214,7 +14214,7 @@
       <c r="N80" s="27"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="85"/>
+      <c r="A81" s="95"/>
       <c r="B81" s="45" t="s">
         <v>237</v>
       </c>
@@ -14234,14 +14234,14 @@
       <c r="N81" s="27"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="96" t="s">
+      <c r="A82" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B82" s="87"/>
-      <c r="C82" s="87"/>
-      <c r="D82" s="87"/>
-      <c r="E82" s="87"/>
-      <c r="F82" s="88"/>
+      <c r="B82" s="53"/>
+      <c r="C82" s="53"/>
+      <c r="D82" s="53"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="54"/>
       <c r="G82" s="39"/>
       <c r="H82" s="39"/>
       <c r="I82" s="39"/>
@@ -14252,7 +14252,7 @@
       <c r="N82" s="27"/>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="85" t="s">
+      <c r="A83" s="95" t="s">
         <v>738</v>
       </c>
       <c r="B83" s="45" t="s">
@@ -14274,7 +14274,7 @@
       <c r="N83" s="27"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="85"/>
+      <c r="A84" s="95"/>
       <c r="B84" s="45" t="s">
         <v>205</v>
       </c>
@@ -14294,7 +14294,7 @@
       <c r="N84" s="27"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="85"/>
+      <c r="A85" s="95"/>
       <c r="B85" s="45" t="s">
         <v>233</v>
       </c>
@@ -14314,7 +14314,7 @@
       <c r="N85" s="27"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="85"/>
+      <c r="A86" s="95"/>
       <c r="B86" s="45" t="s">
         <v>211</v>
       </c>
@@ -14334,14 +14334,14 @@
       <c r="N86" s="27"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="96" t="s">
+      <c r="A87" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B87" s="87"/>
-      <c r="C87" s="87"/>
-      <c r="D87" s="87"/>
-      <c r="E87" s="87"/>
-      <c r="F87" s="88"/>
+      <c r="B87" s="53"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="54"/>
       <c r="G87" s="39"/>
       <c r="H87" s="39"/>
       <c r="I87" s="39"/>
@@ -14352,7 +14352,7 @@
       <c r="N87" s="27"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="85" t="s">
+      <c r="A88" s="95" t="s">
         <v>739</v>
       </c>
       <c r="B88" s="30" t="s">
@@ -14374,7 +14374,7 @@
       <c r="N88" s="27"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="85"/>
+      <c r="A89" s="95"/>
       <c r="B89" s="30" t="s">
         <v>275</v>
       </c>
@@ -14394,7 +14394,7 @@
       <c r="N89" s="27"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="85"/>
+      <c r="A90" s="95"/>
       <c r="B90" s="30" t="s">
         <v>389</v>
       </c>
@@ -14414,7 +14414,7 @@
       <c r="N90" s="27"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="85"/>
+      <c r="A91" s="95"/>
       <c r="B91" s="30" t="s">
         <v>313</v>
       </c>
@@ -14434,7 +14434,7 @@
       <c r="N91" s="27"/>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="85"/>
+      <c r="A92" s="95"/>
       <c r="B92" s="30" t="s">
         <v>385</v>
       </c>
@@ -14454,7 +14454,7 @@
       <c r="N92" s="27"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="85"/>
+      <c r="A93" s="95"/>
       <c r="B93" s="30" t="s">
         <v>693</v>
       </c>
@@ -14474,14 +14474,14 @@
       <c r="N93" s="27"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="96" t="s">
+      <c r="A94" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B94" s="87"/>
-      <c r="C94" s="87"/>
-      <c r="D94" s="87"/>
-      <c r="E94" s="87"/>
-      <c r="F94" s="88"/>
+      <c r="B94" s="53"/>
+      <c r="C94" s="53"/>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="54"/>
       <c r="G94" s="39"/>
       <c r="H94" s="39"/>
       <c r="I94" s="39"/>
@@ -14492,7 +14492,7 @@
       <c r="N94" s="27"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="85" t="s">
+      <c r="A95" s="95" t="s">
         <v>740</v>
       </c>
       <c r="B95" s="15" t="s">
@@ -14514,7 +14514,7 @@
       <c r="N95" s="27"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="85"/>
+      <c r="A96" s="95"/>
       <c r="B96" s="15" t="s">
         <v>315</v>
       </c>
@@ -14534,7 +14534,7 @@
       <c r="N96" s="27"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="85" t="s">
+      <c r="A97" s="95" t="s">
         <v>741</v>
       </c>
       <c r="B97" s="15" t="s">
@@ -14556,7 +14556,7 @@
       <c r="N97" s="27"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="84"/>
+      <c r="A98" s="94"/>
       <c r="B98" s="15" t="s">
         <v>277</v>
       </c>
@@ -14576,14 +14576,14 @@
       <c r="N98" s="27"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="96" t="s">
+      <c r="A99" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B99" s="87"/>
-      <c r="C99" s="87"/>
-      <c r="D99" s="87"/>
-      <c r="E99" s="87"/>
-      <c r="F99" s="88"/>
+      <c r="B99" s="53"/>
+      <c r="C99" s="53"/>
+      <c r="D99" s="53"/>
+      <c r="E99" s="53"/>
+      <c r="F99" s="54"/>
       <c r="G99" s="39"/>
       <c r="H99" s="39"/>
       <c r="I99" s="39"/>
@@ -14594,7 +14594,7 @@
       <c r="N99" s="27"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="85" t="s">
+      <c r="A100" s="95" t="s">
         <v>743</v>
       </c>
       <c r="B100" s="15" t="s">
@@ -14616,7 +14616,7 @@
       <c r="N100" s="27"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="84"/>
+      <c r="A101" s="94"/>
       <c r="B101" s="15" t="s">
         <v>467</v>
       </c>
@@ -14636,7 +14636,7 @@
       <c r="N101" s="27"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="84"/>
+      <c r="A102" s="94"/>
       <c r="B102" s="15" t="s">
         <v>464</v>
       </c>
@@ -14656,7 +14656,7 @@
       <c r="N102" s="27"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="84"/>
+      <c r="A103" s="94"/>
       <c r="B103" s="15" t="s">
         <v>408</v>
       </c>
@@ -14676,7 +14676,7 @@
       <c r="N103" s="27"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="84"/>
+      <c r="A104" s="94"/>
       <c r="B104" s="15" t="s">
         <v>692</v>
       </c>
@@ -14696,7 +14696,7 @@
       <c r="N104" s="27"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="84"/>
+      <c r="A105" s="94"/>
       <c r="B105" s="15" t="s">
         <v>691</v>
       </c>
@@ -14716,7 +14716,7 @@
       <c r="N105" s="27"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="84"/>
+      <c r="A106" s="94"/>
       <c r="B106" s="15" t="s">
         <v>437</v>
       </c>
@@ -14736,7 +14736,7 @@
       <c r="N106" s="27"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="84"/>
+      <c r="A107" s="94"/>
       <c r="B107" s="15" t="s">
         <v>416</v>
       </c>
@@ -14756,7 +14756,7 @@
       <c r="N107" s="27"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="84"/>
+      <c r="A108" s="94"/>
       <c r="B108" s="15" t="s">
         <v>292</v>
       </c>
@@ -14776,7 +14776,7 @@
       <c r="N108" s="27"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="84"/>
+      <c r="A109" s="94"/>
       <c r="B109" s="15" t="s">
         <v>378</v>
       </c>
@@ -14796,7 +14796,7 @@
       <c r="N109" s="27"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="84"/>
+      <c r="A110" s="94"/>
       <c r="B110" s="15" t="s">
         <v>287</v>
       </c>
@@ -14816,7 +14816,7 @@
       <c r="N110" s="27"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="84"/>
+      <c r="A111" s="94"/>
       <c r="B111" s="15" t="s">
         <v>481</v>
       </c>
@@ -14836,7 +14836,7 @@
       <c r="N111" s="27"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="84"/>
+      <c r="A112" s="94"/>
       <c r="B112" s="15" t="s">
         <v>271</v>
       </c>
@@ -14856,7 +14856,7 @@
       <c r="N112" s="27"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="84"/>
+      <c r="A113" s="94"/>
       <c r="B113" s="15" t="s">
         <v>422</v>
       </c>
@@ -14876,7 +14876,7 @@
       <c r="N113" s="27"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="84"/>
+      <c r="A114" s="94"/>
       <c r="B114" s="15" t="s">
         <v>282</v>
       </c>
@@ -14896,7 +14896,7 @@
       <c r="N114" s="27"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="85" t="s">
+      <c r="A115" s="95" t="s">
         <v>744</v>
       </c>
       <c r="B115" s="15" t="s">
@@ -14918,7 +14918,7 @@
       <c r="N115" s="27"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="84"/>
+      <c r="A116" s="94"/>
       <c r="B116" s="15" t="s">
         <v>447</v>
       </c>
@@ -14938,7 +14938,7 @@
       <c r="N116" s="27"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="84"/>
+      <c r="A117" s="94"/>
       <c r="B117" s="15" t="s">
         <v>402</v>
       </c>
@@ -14958,7 +14958,7 @@
       <c r="N117" s="27"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="84"/>
+      <c r="A118" s="94"/>
       <c r="B118" s="15" t="s">
         <v>435</v>
       </c>
@@ -14978,7 +14978,7 @@
       <c r="N118" s="27"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="84"/>
+      <c r="A119" s="94"/>
       <c r="B119" s="15" t="s">
         <v>427</v>
       </c>
@@ -14998,7 +14998,7 @@
       <c r="N119" s="27"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="84"/>
+      <c r="A120" s="94"/>
       <c r="B120" s="15" t="s">
         <v>488</v>
       </c>
@@ -15018,7 +15018,7 @@
       <c r="N120" s="27"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="84"/>
+      <c r="A121" s="94"/>
       <c r="B121" s="15" t="s">
         <v>493</v>
       </c>
@@ -15038,7 +15038,7 @@
       <c r="N121" s="27"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="84"/>
+      <c r="A122" s="94"/>
       <c r="B122" s="15" t="s">
         <v>452</v>
       </c>
@@ -15058,7 +15058,7 @@
       <c r="N122" s="27"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="84"/>
+      <c r="A123" s="94"/>
       <c r="B123" s="15" t="s">
         <v>268</v>
       </c>
@@ -15078,7 +15078,7 @@
       <c r="N123" s="27"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="85" t="s">
+      <c r="A124" s="95" t="s">
         <v>745</v>
       </c>
       <c r="B124" s="15" t="s">
@@ -15100,7 +15100,7 @@
       <c r="N124" s="27"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="84"/>
+      <c r="A125" s="94"/>
       <c r="B125" s="15" t="s">
         <v>484</v>
       </c>
@@ -15120,7 +15120,7 @@
       <c r="N125" s="27"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="84"/>
+      <c r="A126" s="94"/>
       <c r="B126" s="15" t="s">
         <v>297</v>
       </c>
@@ -15140,7 +15140,7 @@
       <c r="N126" s="27"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="84"/>
+      <c r="A127" s="94"/>
       <c r="B127" s="15" t="s">
         <v>468</v>
       </c>
@@ -15160,7 +15160,7 @@
       <c r="N127" s="27"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="84"/>
+      <c r="A128" s="94"/>
       <c r="B128" s="15" t="s">
         <v>283</v>
       </c>
@@ -15180,7 +15180,7 @@
       <c r="N128" s="27"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="84"/>
+      <c r="A129" s="94"/>
       <c r="B129" s="15" t="s">
         <v>288</v>
       </c>
@@ -15200,7 +15200,7 @@
       <c r="N129" s="27"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="84"/>
+      <c r="A130" s="94"/>
       <c r="B130" s="15" t="s">
         <v>471</v>
       </c>
@@ -15220,7 +15220,7 @@
       <c r="N130" s="27"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="84"/>
+      <c r="A131" s="94"/>
       <c r="B131" s="15" t="s">
         <v>270</v>
       </c>
@@ -15240,7 +15240,7 @@
       <c r="N131" s="27"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="84"/>
+      <c r="A132" s="94"/>
       <c r="B132" s="15" t="s">
         <v>317</v>
       </c>
@@ -15260,7 +15260,7 @@
       <c r="N132" s="27"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="84"/>
+      <c r="A133" s="94"/>
       <c r="B133" s="15" t="s">
         <v>303</v>
       </c>
@@ -15280,7 +15280,7 @@
       <c r="N133" s="27"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="84"/>
+      <c r="A134" s="94"/>
       <c r="B134" s="15" t="s">
         <v>307</v>
       </c>
@@ -15300,7 +15300,7 @@
       <c r="N134" s="27"/>
     </row>
     <row r="135" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="84"/>
+      <c r="A135" s="94"/>
       <c r="B135" s="15" t="s">
         <v>247</v>
       </c>
@@ -15320,7 +15320,7 @@
       <c r="N135" s="27"/>
     </row>
     <row r="136" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="85" t="s">
+      <c r="A136" s="95" t="s">
         <v>746</v>
       </c>
       <c r="B136" s="15" t="s">
@@ -15342,7 +15342,7 @@
       <c r="N136" s="27"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="84"/>
+      <c r="A137" s="94"/>
       <c r="B137" s="15" t="s">
         <v>246</v>
       </c>
@@ -15362,7 +15362,7 @@
       <c r="N137" s="27"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="84"/>
+      <c r="A138" s="94"/>
       <c r="B138" s="15" t="s">
         <v>343</v>
       </c>
@@ -15382,7 +15382,7 @@
       <c r="N138" s="27"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="84"/>
+      <c r="A139" s="94"/>
       <c r="B139" s="15" t="s">
         <v>329</v>
       </c>
@@ -15402,7 +15402,7 @@
       <c r="N139" s="27"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="84"/>
+      <c r="A140" s="94"/>
       <c r="B140" s="15" t="s">
         <v>279</v>
       </c>
@@ -15422,7 +15422,7 @@
       <c r="N140" s="27"/>
     </row>
     <row r="141" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="84"/>
+      <c r="A141" s="94"/>
       <c r="B141" s="15" t="s">
         <v>328</v>
       </c>
@@ -15442,7 +15442,7 @@
       <c r="N141" s="27"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="84"/>
+      <c r="A142" s="94"/>
       <c r="B142" s="15" t="s">
         <v>272</v>
       </c>
@@ -15484,7 +15484,7 @@
       <c r="N143" s="27"/>
     </row>
     <row r="144" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="85" t="s">
+      <c r="A144" s="95" t="s">
         <v>748</v>
       </c>
       <c r="B144" s="15" t="s">
@@ -15506,7 +15506,7 @@
       <c r="N144" s="27"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="84"/>
+      <c r="A145" s="94"/>
       <c r="B145" s="15" t="s">
         <v>338</v>
       </c>
@@ -15526,7 +15526,7 @@
       <c r="N145" s="27"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="84"/>
+      <c r="A146" s="94"/>
       <c r="B146" s="15" t="s">
         <v>301</v>
       </c>
@@ -15546,7 +15546,7 @@
       <c r="N146" s="27"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="84"/>
+      <c r="A147" s="94"/>
       <c r="B147" s="15" t="s">
         <v>432</v>
       </c>
@@ -15566,7 +15566,7 @@
       <c r="N147" s="27"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="84"/>
+      <c r="A148" s="94"/>
       <c r="B148" s="15" t="s">
         <v>264</v>
       </c>
@@ -15586,14 +15586,14 @@
       <c r="N148" s="27"/>
     </row>
     <row r="149" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="96" t="s">
+      <c r="A149" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B149" s="87"/>
-      <c r="C149" s="87"/>
-      <c r="D149" s="87"/>
-      <c r="E149" s="87"/>
-      <c r="F149" s="88"/>
+      <c r="B149" s="53"/>
+      <c r="C149" s="53"/>
+      <c r="D149" s="53"/>
+      <c r="E149" s="53"/>
+      <c r="F149" s="54"/>
       <c r="G149" s="39"/>
       <c r="H149" s="39"/>
       <c r="I149" s="39"/>
@@ -15604,7 +15604,7 @@
       <c r="N149" s="27"/>
     </row>
     <row r="150" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="85" t="s">
+      <c r="A150" s="95" t="s">
         <v>750</v>
       </c>
       <c r="B150" s="30" t="s">
@@ -15626,7 +15626,7 @@
       <c r="N150" s="27"/>
     </row>
     <row r="151" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="85"/>
+      <c r="A151" s="95"/>
       <c r="B151" s="30" t="s">
         <v>423</v>
       </c>
@@ -15646,7 +15646,7 @@
       <c r="N151" s="27"/>
     </row>
     <row r="152" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="85"/>
+      <c r="A152" s="95"/>
       <c r="B152" s="30" t="s">
         <v>340</v>
       </c>
@@ -15666,7 +15666,7 @@
       <c r="N152" s="27"/>
     </row>
     <row r="153" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="85"/>
+      <c r="A153" s="95"/>
       <c r="B153" s="30" t="s">
         <v>310</v>
       </c>
@@ -15686,7 +15686,7 @@
       <c r="N153" s="27"/>
     </row>
     <row r="154" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="85"/>
+      <c r="A154" s="95"/>
       <c r="B154" s="30" t="s">
         <v>276</v>
       </c>
@@ -15706,7 +15706,7 @@
       <c r="N154" s="27"/>
     </row>
     <row r="155" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="85"/>
+      <c r="A155" s="95"/>
       <c r="B155" s="30" t="s">
         <v>382</v>
       </c>
@@ -15726,7 +15726,7 @@
       <c r="N155" s="27"/>
     </row>
     <row r="156" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="85" t="s">
+      <c r="A156" s="95" t="s">
         <v>751</v>
       </c>
       <c r="B156" s="30" t="s">
@@ -15748,7 +15748,7 @@
       <c r="N156" s="27"/>
     </row>
     <row r="157" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="85"/>
+      <c r="A157" s="95"/>
       <c r="B157" s="30" t="s">
         <v>306</v>
       </c>
@@ -15768,7 +15768,7 @@
       <c r="N157" s="27"/>
     </row>
     <row r="158" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="85"/>
+      <c r="A158" s="95"/>
       <c r="B158" s="30" t="s">
         <v>278</v>
       </c>
@@ -15788,7 +15788,7 @@
       <c r="N158" s="27"/>
     </row>
     <row r="159" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="85"/>
+      <c r="A159" s="95"/>
       <c r="B159" s="30" t="s">
         <v>265</v>
       </c>
@@ -15808,7 +15808,7 @@
       <c r="N159" s="27"/>
     </row>
     <row r="160" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="85"/>
+      <c r="A160" s="95"/>
       <c r="B160" s="30" t="s">
         <v>417</v>
       </c>
@@ -15828,7 +15828,7 @@
       <c r="N160" s="27"/>
     </row>
     <row r="161" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="85"/>
+      <c r="A161" s="95"/>
       <c r="B161" s="30" t="s">
         <v>332</v>
       </c>
@@ -15848,7 +15848,7 @@
       <c r="N161" s="27"/>
     </row>
     <row r="162" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="85" t="s">
+      <c r="A162" s="95" t="s">
         <v>752</v>
       </c>
       <c r="B162" s="30" t="s">
@@ -15870,7 +15870,7 @@
       <c r="N162" s="27"/>
     </row>
     <row r="163" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="85"/>
+      <c r="A163" s="95"/>
       <c r="B163" s="30" t="s">
         <v>701</v>
       </c>
@@ -15890,14 +15890,14 @@
       <c r="N163" s="27"/>
     </row>
     <row r="164" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="96" t="s">
+      <c r="A164" s="92" t="s">
         <v>595</v>
       </c>
-      <c r="B164" s="87"/>
-      <c r="C164" s="87"/>
-      <c r="D164" s="87"/>
-      <c r="E164" s="87"/>
-      <c r="F164" s="88"/>
+      <c r="B164" s="53"/>
+      <c r="C164" s="53"/>
+      <c r="D164" s="53"/>
+      <c r="E164" s="53"/>
+      <c r="F164" s="54"/>
       <c r="G164" s="39"/>
       <c r="H164" s="39"/>
       <c r="I164" s="39"/>
@@ -15908,7 +15908,7 @@
       <c r="N164" s="27"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="84" t="s">
+      <c r="A165" s="94" t="s">
         <v>252</v>
       </c>
       <c r="B165" s="15" t="s">
@@ -15930,7 +15930,7 @@
       <c r="N165" s="27"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="84"/>
+      <c r="A166" s="94"/>
       <c r="B166" s="15" t="s">
         <v>294</v>
       </c>
@@ -15950,7 +15950,7 @@
       <c r="N166" s="27"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="84"/>
+      <c r="A167" s="94"/>
       <c r="B167" s="15" t="s">
         <v>294</v>
       </c>
@@ -15970,7 +15970,7 @@
       <c r="N167" s="27"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="84" t="s">
+      <c r="A168" s="94" t="s">
         <v>768</v>
       </c>
       <c r="B168" s="15" t="s">
@@ -15992,7 +15992,7 @@
       <c r="N168" s="27"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="84"/>
+      <c r="A169" s="94"/>
       <c r="B169" s="15" t="s">
         <v>428</v>
       </c>
@@ -16012,7 +16012,7 @@
       <c r="N169" s="27"/>
     </row>
     <row r="170" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="84" t="s">
+      <c r="A170" s="94" t="s">
         <v>767</v>
       </c>
       <c r="B170" s="15" t="s">
@@ -16034,7 +16034,7 @@
       <c r="N170" s="27"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="84"/>
+      <c r="A171" s="94"/>
       <c r="B171" s="15" t="s">
         <v>412</v>
       </c>
@@ -16054,7 +16054,7 @@
       <c r="N171" s="27"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="84" t="s">
+      <c r="A172" s="94" t="s">
         <v>766</v>
       </c>
       <c r="B172" s="15" t="s">
@@ -16076,7 +16076,7 @@
       <c r="N172" s="27"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="84"/>
+      <c r="A173" s="94"/>
       <c r="B173" s="15" t="s">
         <v>369</v>
       </c>
@@ -16096,7 +16096,7 @@
       <c r="N173" s="27"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="84" t="s">
+      <c r="A174" s="94" t="s">
         <v>765</v>
       </c>
       <c r="B174" s="15" t="s">
@@ -16118,7 +16118,7 @@
       <c r="N174" s="27"/>
     </row>
     <row r="175" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="84"/>
+      <c r="A175" s="94"/>
       <c r="B175" s="15" t="s">
         <v>696</v>
       </c>
@@ -16138,7 +16138,7 @@
       <c r="N175" s="27"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="84"/>
+      <c r="A176" s="94"/>
       <c r="B176" s="15" t="s">
         <v>697</v>
       </c>
@@ -16158,7 +16158,7 @@
       <c r="N176" s="27"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="84"/>
+      <c r="A177" s="94"/>
       <c r="B177" s="15" t="s">
         <v>698</v>
       </c>
@@ -16178,7 +16178,7 @@
       <c r="N177" s="27"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="84"/>
+      <c r="A178" s="94"/>
       <c r="B178" s="15" t="s">
         <v>699</v>
       </c>
@@ -16198,7 +16198,7 @@
       <c r="N178" s="27"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="84" t="s">
+      <c r="A179" s="94" t="s">
         <v>764</v>
       </c>
       <c r="B179" s="15" t="s">
@@ -16220,7 +16220,7 @@
       <c r="N179" s="27"/>
     </row>
     <row r="180" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="84"/>
+      <c r="A180" s="94"/>
       <c r="B180" s="15" t="s">
         <v>344</v>
       </c>
@@ -16240,7 +16240,7 @@
       <c r="N180" s="27"/>
     </row>
     <row r="181" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="84" t="s">
+      <c r="A181" s="94" t="s">
         <v>763</v>
       </c>
       <c r="B181" s="15" t="s">
@@ -16262,7 +16262,7 @@
       <c r="N181" s="27"/>
     </row>
     <row r="182" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="84"/>
+      <c r="A182" s="94"/>
       <c r="B182" s="15" t="s">
         <v>296</v>
       </c>
@@ -16282,7 +16282,7 @@
       <c r="N182" s="27"/>
     </row>
     <row r="183" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="84"/>
+      <c r="A183" s="94"/>
       <c r="B183" s="15" t="s">
         <v>316</v>
       </c>
@@ -16302,14 +16302,14 @@
       <c r="N183" s="27"/>
     </row>
     <row r="184" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="96" t="s">
+      <c r="A184" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B184" s="87"/>
-      <c r="C184" s="87"/>
-      <c r="D184" s="87"/>
-      <c r="E184" s="87"/>
-      <c r="F184" s="88"/>
+      <c r="B184" s="53"/>
+      <c r="C184" s="53"/>
+      <c r="D184" s="53"/>
+      <c r="E184" s="53"/>
+      <c r="F184" s="54"/>
       <c r="G184" s="39"/>
       <c r="H184" s="39"/>
       <c r="I184" s="39"/>
@@ -16320,7 +16320,7 @@
       <c r="N184" s="27"/>
     </row>
     <row r="185" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="84" t="s">
+      <c r="A185" s="94" t="s">
         <v>775</v>
       </c>
       <c r="B185" s="15" t="s">
@@ -16342,7 +16342,7 @@
       <c r="N185" s="27"/>
     </row>
     <row r="186" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="84"/>
+      <c r="A186" s="94"/>
       <c r="B186" s="15" t="s">
         <v>527</v>
       </c>
@@ -16362,7 +16362,7 @@
       <c r="N186" s="27"/>
     </row>
     <row r="187" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="84" t="s">
+      <c r="A187" s="94" t="s">
         <v>776</v>
       </c>
       <c r="B187" s="15" t="s">
@@ -16384,7 +16384,7 @@
       <c r="N187" s="27"/>
     </row>
     <row r="188" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="84"/>
+      <c r="A188" s="94"/>
       <c r="B188" s="15" t="s">
         <v>513</v>
       </c>
@@ -16404,7 +16404,7 @@
       <c r="N188" s="27"/>
     </row>
     <row r="189" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="84"/>
+      <c r="A189" s="94"/>
       <c r="B189" s="15" t="s">
         <v>518</v>
       </c>
@@ -16424,7 +16424,7 @@
       <c r="N189" s="27"/>
     </row>
     <row r="190" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="84"/>
+      <c r="A190" s="94"/>
       <c r="B190" s="15" t="s">
         <v>525</v>
       </c>
@@ -16444,7 +16444,7 @@
       <c r="N190" s="27"/>
     </row>
     <row r="191" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="84"/>
+      <c r="A191" s="94"/>
       <c r="B191" s="15" t="s">
         <v>499</v>
       </c>
@@ -16464,7 +16464,7 @@
       <c r="N191" s="27"/>
     </row>
     <row r="192" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="84"/>
+      <c r="A192" s="94"/>
       <c r="B192" s="15" t="s">
         <v>516</v>
       </c>
@@ -16484,7 +16484,7 @@
       <c r="N192" s="27"/>
     </row>
     <row r="193" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="84" t="s">
+      <c r="A193" s="94" t="s">
         <v>715</v>
       </c>
       <c r="B193" s="15" t="s">
@@ -16506,7 +16506,7 @@
       <c r="N193" s="27"/>
     </row>
     <row r="194" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="84"/>
+      <c r="A194" s="94"/>
       <c r="B194" s="15" t="s">
         <v>771</v>
       </c>
@@ -16526,7 +16526,7 @@
       <c r="N194" s="27"/>
     </row>
     <row r="195" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="84"/>
+      <c r="A195" s="94"/>
       <c r="B195" s="15" t="s">
         <v>773</v>
       </c>
@@ -16546,14 +16546,14 @@
       <c r="N195" s="27"/>
     </row>
     <row r="196" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="95" t="s">
+      <c r="A196" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="B196" s="90"/>
-      <c r="C196" s="90"/>
-      <c r="D196" s="90"/>
-      <c r="E196" s="90"/>
-      <c r="F196" s="91"/>
+      <c r="B196" s="56"/>
+      <c r="C196" s="56"/>
+      <c r="D196" s="56"/>
+      <c r="E196" s="56"/>
+      <c r="F196" s="57"/>
       <c r="G196" s="48"/>
       <c r="H196" s="48"/>
       <c r="I196" s="48"/>
@@ -16564,14 +16564,14 @@
       <c r="N196" s="29"/>
     </row>
     <row r="197" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="92" t="s">
+      <c r="A197" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="B197" s="93"/>
-      <c r="C197" s="93"/>
-      <c r="D197" s="93"/>
-      <c r="E197" s="93"/>
-      <c r="F197" s="94"/>
+      <c r="B197" s="59"/>
+      <c r="C197" s="59"/>
+      <c r="D197" s="59"/>
+      <c r="E197" s="59"/>
+      <c r="F197" s="60"/>
       <c r="G197" s="49"/>
       <c r="H197" s="49"/>
       <c r="I197" s="49"/>
@@ -16615,49 +16615,6 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="A196:F196"/>
-    <mergeCell ref="A184:F184"/>
-    <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A149:F149"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A100:A114"/>
-    <mergeCell ref="A115:A123"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A187:A192"/>
-    <mergeCell ref="A193:A195"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A150:A155"/>
-    <mergeCell ref="A156:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="A181:A183"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A174:A178"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="A124:A135"/>
-    <mergeCell ref="A136:A142"/>
-    <mergeCell ref="A144:A148"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A48:A58"/>
-    <mergeCell ref="A60:A74"/>
-    <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A21:A28"/>
-    <mergeCell ref="A35:A46"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="A8:A19"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A6:A7"/>
@@ -16674,6 +16631,49 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A21:A28"/>
+    <mergeCell ref="A35:A46"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A174:A178"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="A124:A135"/>
+    <mergeCell ref="A136:A142"/>
+    <mergeCell ref="A144:A148"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A100:A114"/>
+    <mergeCell ref="A115:A123"/>
+    <mergeCell ref="A48:A58"/>
+    <mergeCell ref="A60:A74"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A196:F196"/>
+    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A187:A192"/>
+    <mergeCell ref="A193:A195"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A150:A155"/>
+    <mergeCell ref="A156:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A165:A167"/>
+    <mergeCell ref="A181:A183"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A47:F47"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -19155,22 +19155,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="81" t="s">
         <v>718</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32"/>
@@ -19201,67 +19201,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="90" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="87" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="84" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="84" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="84" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="79" t="s">
         <v>723</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="79" t="s">
         <v>669</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="79" t="s">
         <v>673</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="79" t="s">
         <v>680</v>
       </c>
-      <c r="J6" s="52" t="s">
+      <c r="J6" s="79" t="s">
         <v>681</v>
       </c>
-      <c r="K6" s="52" t="s">
+      <c r="K6" s="79" t="s">
         <v>682</v>
       </c>
-      <c r="L6" s="52" t="s">
+      <c r="L6" s="79" t="s">
         <v>700</v>
       </c>
-      <c r="M6" s="52" t="s">
+      <c r="M6" s="79" t="s">
         <v>724</v>
       </c>
-      <c r="N6" s="70" t="s">
+      <c r="N6" s="82" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="63"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="71"/>
+      <c r="A7" s="91"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="83"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="96" t="s">
         <v>805</v>
       </c>
       <c r="B8" s="24">
@@ -19283,7 +19283,7 @@
       <c r="N8" s="28"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="84"/>
+      <c r="A9" s="94"/>
       <c r="B9" s="15">
         <v>7427</v>
       </c>
@@ -19303,7 +19303,7 @@
       <c r="N9" s="27"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="84"/>
+      <c r="A10" s="94"/>
       <c r="B10" s="18">
         <v>7429</v>
       </c>
@@ -19323,7 +19323,7 @@
       <c r="N10" s="27"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="84"/>
+      <c r="A11" s="94"/>
       <c r="B11" s="18">
         <v>7431</v>
       </c>
@@ -19343,7 +19343,7 @@
       <c r="N11" s="27"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="84"/>
+      <c r="A12" s="94"/>
       <c r="B12" s="18">
         <v>7433</v>
       </c>
@@ -19363,7 +19363,7 @@
       <c r="N12" s="27"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="84"/>
+      <c r="A13" s="94"/>
       <c r="B13" s="18">
         <v>7435</v>
       </c>
@@ -19383,7 +19383,7 @@
       <c r="N13" s="27"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="84"/>
+      <c r="A14" s="94"/>
       <c r="B14" s="18">
         <v>7437</v>
       </c>
@@ -19403,7 +19403,7 @@
       <c r="N14" s="27"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="84"/>
+      <c r="A15" s="94"/>
       <c r="B15" s="18">
         <v>7439</v>
       </c>
@@ -19423,7 +19423,7 @@
       <c r="N15" s="27"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="84"/>
+      <c r="A16" s="94"/>
       <c r="B16" s="18">
         <v>7441</v>
       </c>
@@ -19443,7 +19443,7 @@
       <c r="N16" s="27"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="84"/>
+      <c r="A17" s="94"/>
       <c r="B17" s="18">
         <v>7426</v>
       </c>
@@ -19463,7 +19463,7 @@
       <c r="N17" s="27"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="84"/>
+      <c r="A18" s="94"/>
       <c r="B18" s="18">
         <v>7430</v>
       </c>
@@ -19483,7 +19483,7 @@
       <c r="N18" s="27"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="84"/>
+      <c r="A19" s="94"/>
       <c r="B19" s="18">
         <v>7432</v>
       </c>
@@ -19503,7 +19503,7 @@
       <c r="N19" s="27"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="84"/>
+      <c r="A20" s="94"/>
       <c r="B20" s="18">
         <v>7434</v>
       </c>
@@ -19523,7 +19523,7 @@
       <c r="N20" s="27"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="84"/>
+      <c r="A21" s="94"/>
       <c r="B21" s="18">
         <v>7436</v>
       </c>
@@ -19543,7 +19543,7 @@
       <c r="N21" s="27"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="84"/>
+      <c r="A22" s="94"/>
       <c r="B22" s="18">
         <v>7438</v>
       </c>
@@ -19563,7 +19563,7 @@
       <c r="N22" s="27"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="84"/>
+      <c r="A23" s="94"/>
       <c r="B23" s="18">
         <v>7440</v>
       </c>
@@ -19583,7 +19583,7 @@
       <c r="N23" s="27"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="84"/>
+      <c r="A24" s="94"/>
       <c r="B24" s="18">
         <v>7442</v>
       </c>
@@ -19603,7 +19603,7 @@
       <c r="N24" s="27"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="84"/>
+      <c r="A25" s="94"/>
       <c r="B25" s="18">
         <v>7443</v>
       </c>
@@ -19623,7 +19623,7 @@
       <c r="N25" s="27"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="84"/>
+      <c r="A26" s="94"/>
       <c r="B26" s="18">
         <v>7445</v>
       </c>
@@ -19643,7 +19643,7 @@
       <c r="N26" s="27"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="84"/>
+      <c r="A27" s="94"/>
       <c r="B27" s="18">
         <v>7444</v>
       </c>
@@ -19663,7 +19663,7 @@
       <c r="N27" s="27"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="84"/>
+      <c r="A28" s="94"/>
       <c r="B28" s="18">
         <v>7446</v>
       </c>
@@ -19683,7 +19683,7 @@
       <c r="N28" s="27"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="84"/>
+      <c r="A29" s="94"/>
       <c r="B29" s="18">
         <v>7448</v>
       </c>
@@ -19703,7 +19703,7 @@
       <c r="N29" s="27"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="84"/>
+      <c r="A30" s="94"/>
       <c r="B30" s="18">
         <v>7450</v>
       </c>
@@ -19723,14 +19723,14 @@
       <c r="N30" s="27"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B31" s="87"/>
-      <c r="C31" s="87"/>
-      <c r="D31" s="87"/>
-      <c r="E31" s="87"/>
-      <c r="F31" s="88"/>
+      <c r="B31" s="53"/>
+      <c r="C31" s="53"/>
+      <c r="D31" s="53"/>
+      <c r="E31" s="53"/>
+      <c r="F31" s="54"/>
       <c r="G31" s="39"/>
       <c r="H31" s="39"/>
       <c r="I31" s="39"/>
@@ -19741,7 +19741,7 @@
       <c r="N31" s="27"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="84" t="s">
+      <c r="A32" s="94" t="s">
         <v>806</v>
       </c>
       <c r="B32" s="15" t="s">
@@ -19763,7 +19763,7 @@
       <c r="N32" s="27"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="84"/>
+      <c r="A33" s="94"/>
       <c r="B33" s="15" t="s">
         <v>577</v>
       </c>
@@ -19783,7 +19783,7 @@
       <c r="N33" s="27"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="84"/>
+      <c r="A34" s="94"/>
       <c r="B34" s="15" t="s">
         <v>574</v>
       </c>
@@ -19803,7 +19803,7 @@
       <c r="N34" s="27"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="84"/>
+      <c r="A35" s="94"/>
       <c r="B35" s="15" t="s">
         <v>552</v>
       </c>
@@ -19823,7 +19823,7 @@
       <c r="N35" s="27"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="84"/>
+      <c r="A36" s="94"/>
       <c r="B36" s="15" t="s">
         <v>431</v>
       </c>
@@ -19843,7 +19843,7 @@
       <c r="N36" s="27"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="84"/>
+      <c r="A37" s="94"/>
       <c r="B37" s="15" t="s">
         <v>436</v>
       </c>
@@ -19863,7 +19863,7 @@
       <c r="N37" s="27"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="84"/>
+      <c r="A38" s="94"/>
       <c r="B38" s="15" t="s">
         <v>505</v>
       </c>
@@ -19883,7 +19883,7 @@
       <c r="N38" s="27"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="84"/>
+      <c r="A39" s="94"/>
       <c r="B39" s="15" t="s">
         <v>566</v>
       </c>
@@ -19903,14 +19903,14 @@
       <c r="N39" s="27"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="96" t="s">
+      <c r="A40" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B40" s="87"/>
-      <c r="C40" s="87"/>
-      <c r="D40" s="87"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="88"/>
+      <c r="B40" s="53"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="53"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="54"/>
       <c r="G40" s="39"/>
       <c r="H40" s="39"/>
       <c r="I40" s="39"/>
@@ -19921,7 +19921,7 @@
       <c r="N40" s="27"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="85" t="s">
+      <c r="A41" s="95" t="s">
         <v>808</v>
       </c>
       <c r="B41" s="30" t="s">
@@ -19943,7 +19943,7 @@
       <c r="N41" s="27"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="85"/>
+      <c r="A42" s="95"/>
       <c r="B42" s="30" t="s">
         <v>581</v>
       </c>
@@ -19963,7 +19963,7 @@
       <c r="N42" s="27"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="85"/>
+      <c r="A43" s="95"/>
       <c r="B43" s="30" t="s">
         <v>590</v>
       </c>
@@ -19983,7 +19983,7 @@
       <c r="N43" s="27"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="85"/>
+      <c r="A44" s="95"/>
       <c r="B44" s="30" t="s">
         <v>548</v>
       </c>
@@ -20003,7 +20003,7 @@
       <c r="N44" s="27"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="85"/>
+      <c r="A45" s="95"/>
       <c r="B45" s="30" t="s">
         <v>583</v>
       </c>
@@ -20023,7 +20023,7 @@
       <c r="N45" s="27"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="85"/>
+      <c r="A46" s="95"/>
       <c r="B46" s="30" t="s">
         <v>453</v>
       </c>
@@ -20043,7 +20043,7 @@
       <c r="N46" s="27"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="85"/>
+      <c r="A47" s="95"/>
       <c r="B47" s="30" t="s">
         <v>671</v>
       </c>
@@ -20063,7 +20063,7 @@
       <c r="N47" s="27"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="85"/>
+      <c r="A48" s="95"/>
       <c r="B48" s="30" t="s">
         <v>582</v>
       </c>
@@ -20083,7 +20083,7 @@
       <c r="N48" s="27"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="85"/>
+      <c r="A49" s="95"/>
       <c r="B49" s="30" t="s">
         <v>553</v>
       </c>
@@ -20103,7 +20103,7 @@
       <c r="N49" s="27"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="85"/>
+      <c r="A50" s="95"/>
       <c r="B50" s="30" t="s">
         <v>573</v>
       </c>
@@ -20123,14 +20123,14 @@
       <c r="N50" s="27"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="96" t="s">
+      <c r="A51" s="92" t="s">
         <v>595</v>
       </c>
-      <c r="B51" s="87"/>
-      <c r="C51" s="87"/>
-      <c r="D51" s="87"/>
-      <c r="E51" s="87"/>
-      <c r="F51" s="88"/>
+      <c r="B51" s="53"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
       <c r="G51" s="39"/>
       <c r="H51" s="39"/>
       <c r="I51" s="39"/>
@@ -20141,7 +20141,7 @@
       <c r="N51" s="27"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="84" t="s">
+      <c r="A52" s="94" t="s">
         <v>810</v>
       </c>
       <c r="B52" s="30" t="s">
@@ -20163,7 +20163,7 @@
       <c r="N52" s="27"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="84"/>
+      <c r="A53" s="94"/>
       <c r="B53" s="30" t="s">
         <v>571</v>
       </c>
@@ -20183,7 +20183,7 @@
       <c r="N53" s="27"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="84"/>
+      <c r="A54" s="94"/>
       <c r="B54" s="30" t="s">
         <v>392</v>
       </c>
@@ -20203,7 +20203,7 @@
       <c r="N54" s="27"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="84"/>
+      <c r="A55" s="94"/>
       <c r="B55" s="30" t="s">
         <v>429</v>
       </c>
@@ -20223,7 +20223,7 @@
       <c r="N55" s="27"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="84"/>
+      <c r="A56" s="94"/>
       <c r="B56" s="30" t="s">
         <v>672</v>
       </c>
@@ -20243,14 +20243,14 @@
       <c r="N56" s="27"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="96" t="s">
+      <c r="A57" s="92" t="s">
         <v>135</v>
       </c>
-      <c r="B57" s="87"/>
-      <c r="C57" s="87"/>
-      <c r="D57" s="87"/>
-      <c r="E57" s="87"/>
-      <c r="F57" s="88"/>
+      <c r="B57" s="53"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="54"/>
       <c r="G57" s="39"/>
       <c r="H57" s="39"/>
       <c r="I57" s="39"/>
@@ -20261,7 +20261,7 @@
       <c r="N57" s="27"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="84" t="s">
+      <c r="A58" s="94" t="s">
         <v>811</v>
       </c>
       <c r="B58" s="15" t="s">
@@ -20283,7 +20283,7 @@
       <c r="N58" s="27"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="84"/>
+      <c r="A59" s="94"/>
       <c r="B59" s="15" t="s">
         <v>812</v>
       </c>
@@ -20303,7 +20303,7 @@
       <c r="N59" s="27"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="84"/>
+      <c r="A60" s="94"/>
       <c r="B60" s="15" t="s">
         <v>813</v>
       </c>
@@ -20323,7 +20323,7 @@
       <c r="N60" s="27"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="84"/>
+      <c r="A61" s="94"/>
       <c r="B61" s="15" t="s">
         <v>814</v>
       </c>
@@ -20343,7 +20343,7 @@
       <c r="N61" s="27"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="84"/>
+      <c r="A62" s="94"/>
       <c r="B62" s="15" t="s">
         <v>815</v>
       </c>
@@ -20363,7 +20363,7 @@
       <c r="N62" s="27"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="84"/>
+      <c r="A63" s="94"/>
       <c r="B63" s="15" t="s">
         <v>676</v>
       </c>
@@ -20383,7 +20383,7 @@
       <c r="N63" s="27"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="84"/>
+      <c r="A64" s="94"/>
       <c r="B64" s="15" t="s">
         <v>677</v>
       </c>
@@ -20403,7 +20403,7 @@
       <c r="N64" s="27"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="84"/>
+      <c r="A65" s="94"/>
       <c r="B65" s="15" t="s">
         <v>679</v>
       </c>
@@ -20423,7 +20423,7 @@
       <c r="N65" s="27"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="84"/>
+      <c r="A66" s="94"/>
       <c r="B66" s="15" t="s">
         <v>678</v>
       </c>
@@ -20443,14 +20443,14 @@
       <c r="N66" s="27"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="95" t="s">
+      <c r="A67" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="B67" s="90"/>
-      <c r="C67" s="90"/>
-      <c r="D67" s="90"/>
-      <c r="E67" s="90"/>
-      <c r="F67" s="91"/>
+      <c r="B67" s="56"/>
+      <c r="C67" s="56"/>
+      <c r="D67" s="56"/>
+      <c r="E67" s="56"/>
+      <c r="F67" s="57"/>
       <c r="G67" s="48"/>
       <c r="H67" s="48"/>
       <c r="I67" s="48"/>
@@ -20461,14 +20461,14 @@
       <c r="N67" s="29"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="92" t="s">
+      <c r="A68" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="B68" s="93"/>
-      <c r="C68" s="93"/>
-      <c r="D68" s="93"/>
-      <c r="E68" s="93"/>
-      <c r="F68" s="94"/>
+      <c r="B68" s="59"/>
+      <c r="C68" s="59"/>
+      <c r="D68" s="59"/>
+      <c r="E68" s="59"/>
+      <c r="F68" s="60"/>
       <c r="G68" s="49"/>
       <c r="H68" s="49"/>
       <c r="I68" s="49"/>
@@ -20496,16 +20496,6 @@
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A67:F67"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="A58:A66"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="A41:A50"/>
     <mergeCell ref="A8:A30"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A6:A7"/>
@@ -20522,6 +20512,16 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="A58:A66"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A41:A50"/>
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A67:F67"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
@@ -23003,22 +23003,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="81" t="s">
         <v>717</v>
       </c>
-      <c r="B2" s="69"/>
-      <c r="C2" s="69"/>
-      <c r="D2" s="69"/>
-      <c r="E2" s="69"/>
-      <c r="F2" s="69"/>
-      <c r="G2" s="69"/>
-      <c r="H2" s="69"/>
-      <c r="I2" s="69"/>
-      <c r="J2" s="69"/>
-      <c r="K2" s="69"/>
-      <c r="L2" s="69"/>
-      <c r="M2" s="69"/>
-      <c r="N2" s="69"/>
+      <c r="B2" s="81"/>
+      <c r="C2" s="81"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="81"/>
+      <c r="H2" s="81"/>
+      <c r="I2" s="81"/>
+      <c r="J2" s="81"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="81"/>
+      <c r="M2" s="81"/>
+      <c r="N2" s="81"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32"/>
@@ -23049,67 +23049,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62" t="s">
+      <c r="A6" s="90" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="54" t="s">
+      <c r="B6" s="87" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="84" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="84" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="84" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="52" t="s">
+      <c r="F6" s="79" t="s">
         <v>723</v>
       </c>
-      <c r="G6" s="52" t="s">
+      <c r="G6" s="79" t="s">
         <v>669</v>
       </c>
-      <c r="H6" s="52" t="s">
+      <c r="H6" s="79" t="s">
         <v>673</v>
       </c>
-      <c r="I6" s="52" t="s">
+      <c r="I6" s="79" t="s">
         <v>680</v>
       </c>
-      <c r="J6" s="52" t="s">
+      <c r="J6" s="79" t="s">
         <v>681</v>
       </c>
-      <c r="K6" s="52" t="s">
+      <c r="K6" s="79" t="s">
         <v>682</v>
       </c>
-      <c r="L6" s="52" t="s">
+      <c r="L6" s="79" t="s">
         <v>700</v>
       </c>
-      <c r="M6" s="52" t="s">
+      <c r="M6" s="79" t="s">
         <v>724</v>
       </c>
-      <c r="N6" s="70" t="s">
+      <c r="N6" s="82" t="s">
         <v>725</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="63"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-      <c r="M7" s="53"/>
-      <c r="N7" s="71"/>
+      <c r="A7" s="91"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="85"/>
+      <c r="D7" s="85"/>
+      <c r="E7" s="85"/>
+      <c r="F7" s="80"/>
+      <c r="G7" s="80"/>
+      <c r="H7" s="80"/>
+      <c r="I7" s="80"/>
+      <c r="J7" s="80"/>
+      <c r="K7" s="80"/>
+      <c r="L7" s="80"/>
+      <c r="M7" s="80"/>
+      <c r="N7" s="83"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="96" t="s">
         <v>819</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -23131,7 +23131,7 @@
       <c r="N8" s="28"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="85"/>
+      <c r="A9" s="95"/>
       <c r="B9" s="13" t="s">
         <v>584</v>
       </c>
@@ -23151,7 +23151,7 @@
       <c r="N9" s="27"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="85"/>
+      <c r="A10" s="95"/>
       <c r="B10" s="11" t="s">
         <v>215</v>
       </c>
@@ -23171,7 +23171,7 @@
       <c r="N10" s="27"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="85"/>
+      <c r="A11" s="95"/>
       <c r="B11" s="11" t="s">
         <v>578</v>
       </c>
@@ -23191,7 +23191,7 @@
       <c r="N11" s="27"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="85"/>
+      <c r="A12" s="95"/>
       <c r="B12" s="11" t="s">
         <v>220</v>
       </c>
@@ -23211,7 +23211,7 @@
       <c r="N12" s="27"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="85"/>
+      <c r="A13" s="95"/>
       <c r="B13" s="11" t="s">
         <v>455</v>
       </c>
@@ -23231,7 +23231,7 @@
       <c r="N13" s="27"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="95" t="s">
         <v>820</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -23253,7 +23253,7 @@
       <c r="N14" s="27"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="85"/>
+      <c r="A15" s="95"/>
       <c r="B15" s="11" t="s">
         <v>226</v>
       </c>
@@ -23273,7 +23273,7 @@
       <c r="N15" s="27"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="85"/>
+      <c r="A16" s="95"/>
       <c r="B16" s="11" t="s">
         <v>210</v>
       </c>
@@ -23293,7 +23293,7 @@
       <c r="N16" s="27"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="85"/>
+      <c r="A17" s="95"/>
       <c r="B17" s="11" t="s">
         <v>204</v>
       </c>
@@ -23335,14 +23335,14 @@
       <c r="N18" s="27"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="95" t="s">
+      <c r="A19" s="93" t="s">
         <v>135</v>
       </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="91"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="56"/>
+      <c r="D19" s="56"/>
+      <c r="E19" s="56"/>
+      <c r="F19" s="57"/>
       <c r="G19" s="48"/>
       <c r="H19" s="48"/>
       <c r="I19" s="48"/>
@@ -23353,14 +23353,14 @@
       <c r="N19" s="29"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="58" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="93"/>
-      <c r="C20" s="93"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="93"/>
-      <c r="F20" s="94"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="60"/>
       <c r="G20" s="49"/>
       <c r="H20" s="49"/>
       <c r="I20" s="49"/>
@@ -23404,11 +23404,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
@@ -23423,6 +23418,11 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>

--- a/data/temp.xlsx
+++ b/data/temp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD9E666-C947-429B-BDE4-5DA4A992616F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A190B1F2-9288-4775-856A-E68F34B2B424}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="15600" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="완제품 임가공" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="944" uniqueCount="821">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="940" uniqueCount="818">
   <si>
     <t xml:space="preserve"> APBL2-AL22 G</t>
   </si>
@@ -2208,18 +2208,6 @@
   </si>
   <si>
     <t>AR</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025년 중국 생산 완제품 임가공 의뢰 품목</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025년 중국 생산 반제품 임가공 의뢰 품목</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2025년 중국 생산 완제품 일반무역 의뢰 품목</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -3338,23 +3326,59 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3372,9 +3396,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3398,62 +3419,26 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3461,8 +3446,11 @@
     <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -3973,7 +3961,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr codeName="Sheet1"/>
+  <sheetPr codeName="Sheet1">
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:N186"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -6446,22 +6436,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81" t="s">
-        <v>716</v>
-      </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32"/>
@@ -6477,13 +6465,13 @@
       <c r="K3" s="32"/>
       <c r="L3" s="32"/>
       <c r="M3" s="33" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="N3" s="51"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="38" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="N4" s="51"/>
     </row>
@@ -6492,67 +6480,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="64" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="57" t="s">
+        <v>716</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>717</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>718</v>
+      </c>
+      <c r="E6" s="59" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="F6" s="55" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="G6" s="55" t="s">
+        <v>669</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>673</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>680</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>681</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>682</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>700</v>
+      </c>
+      <c r="M6" s="55" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="N6" s="71" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="79" t="s">
-        <v>723</v>
-      </c>
-      <c r="G6" s="79" t="s">
-        <v>669</v>
-      </c>
-      <c r="H6" s="79" t="s">
-        <v>673</v>
-      </c>
-      <c r="I6" s="79" t="s">
-        <v>680</v>
-      </c>
-      <c r="J6" s="79" t="s">
-        <v>681</v>
-      </c>
-      <c r="K6" s="79" t="s">
-        <v>682</v>
-      </c>
-      <c r="L6" s="79" t="s">
-        <v>700</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>724</v>
-      </c>
-      <c r="N6" s="82" t="s">
-        <v>725</v>
-      </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="83"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="72"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="89" t="s">
+      <c r="A8" s="61" t="s">
         <v>178</v>
       </c>
       <c r="B8" s="24" t="s">
@@ -6574,7 +6562,7 @@
       <c r="N8" s="26"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="67"/>
+      <c r="A9" s="62"/>
       <c r="B9" s="15" t="s">
         <v>218</v>
       </c>
@@ -6594,7 +6582,7 @@
       <c r="N9" s="14"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="67"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="18" t="s">
         <v>209</v>
       </c>
@@ -6614,7 +6602,7 @@
       <c r="N10" s="14"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="67"/>
+      <c r="A11" s="62"/>
       <c r="B11" s="18" t="s">
         <v>250</v>
       </c>
@@ -6634,7 +6622,7 @@
       <c r="N11" s="14"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="67"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="22" t="s">
         <v>229</v>
       </c>
@@ -6654,7 +6642,7 @@
       <c r="N12" s="14"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="67"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="15" t="s">
         <v>327</v>
       </c>
@@ -6674,7 +6662,7 @@
       <c r="N13" s="14"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="67"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="15" t="s">
         <v>381</v>
       </c>
@@ -6694,7 +6682,7 @@
       <c r="N14" s="14"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="67"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="15" t="s">
         <v>353</v>
       </c>
@@ -6714,7 +6702,7 @@
       <c r="N15" s="14"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="67"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="15" t="s">
         <v>351</v>
       </c>
@@ -6734,7 +6722,7 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="67"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="15" t="s">
         <v>228</v>
       </c>
@@ -6754,7 +6742,7 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="67"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="15" t="s">
         <v>430</v>
       </c>
@@ -6792,8 +6780,8 @@
       <c r="N19" s="14"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="86" t="s">
-        <v>729</v>
+      <c r="A20" s="63" t="s">
+        <v>726</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>223</v>
@@ -6814,7 +6802,7 @@
       <c r="N20" s="14"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="67"/>
+      <c r="A21" s="62"/>
       <c r="B21" s="15" t="s">
         <v>415</v>
       </c>
@@ -6834,7 +6822,7 @@
       <c r="N21" s="14"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="67"/>
+      <c r="A22" s="62"/>
       <c r="B22" s="15" t="s">
         <v>506</v>
       </c>
@@ -6854,7 +6842,7 @@
       <c r="N22" s="14"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="67"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="15" t="s">
         <v>242</v>
       </c>
@@ -6892,7 +6880,7 @@
       <c r="N24" s="14"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="86" t="s">
+      <c r="A25" s="63" t="s">
         <v>486</v>
       </c>
       <c r="B25" s="15" t="s">
@@ -6914,7 +6902,7 @@
       <c r="N25" s="14"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="86"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="15" t="s">
         <v>396</v>
       </c>
@@ -6934,7 +6922,7 @@
       <c r="N26" s="14"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="86"/>
+      <c r="A27" s="63"/>
       <c r="B27" s="15" t="s">
         <v>409</v>
       </c>
@@ -6954,7 +6942,7 @@
       <c r="N27" s="14"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="86"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="15" t="s">
         <v>514</v>
       </c>
@@ -6974,7 +6962,7 @@
       <c r="N28" s="14"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="86"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="15" t="s">
         <v>502</v>
       </c>
@@ -6994,7 +6982,7 @@
       <c r="N29" s="14"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="86"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="15" t="s">
         <v>597</v>
       </c>
@@ -7014,7 +7002,7 @@
       <c r="N30" s="14"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="86"/>
+      <c r="A31" s="63"/>
       <c r="B31" s="15" t="s">
         <v>489</v>
       </c>
@@ -7034,7 +7022,7 @@
       <c r="N31" s="14"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="86"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="15" t="s">
         <v>487</v>
       </c>
@@ -7054,7 +7042,7 @@
       <c r="N32" s="14"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="86"/>
+      <c r="A33" s="63"/>
       <c r="B33" s="15" t="s">
         <v>365</v>
       </c>
@@ -7074,7 +7062,7 @@
       <c r="N33" s="14"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="86"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="15" t="s">
         <v>380</v>
       </c>
@@ -7094,7 +7082,7 @@
       <c r="N34" s="14"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="86"/>
+      <c r="A35" s="63"/>
       <c r="B35" s="15" t="s">
         <v>448</v>
       </c>
@@ -7114,7 +7102,7 @@
       <c r="N35" s="14"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="86"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="15" t="s">
         <v>372</v>
       </c>
@@ -7134,7 +7122,7 @@
       <c r="N36" s="14"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="86"/>
+      <c r="A37" s="63"/>
       <c r="B37" s="15" t="s">
         <v>393</v>
       </c>
@@ -7154,7 +7142,7 @@
       <c r="N37" s="14"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="86"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="15" t="s">
         <v>405</v>
       </c>
@@ -7174,7 +7162,7 @@
       <c r="N38" s="14"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="86"/>
+      <c r="A39" s="63"/>
       <c r="B39" s="15" t="s">
         <v>517</v>
       </c>
@@ -7194,7 +7182,7 @@
       <c r="N39" s="14"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="86"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="15" t="s">
         <v>475</v>
       </c>
@@ -7214,7 +7202,7 @@
       <c r="N40" s="14"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="86"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="15" t="s">
         <v>529</v>
       </c>
@@ -7234,7 +7222,7 @@
       <c r="N41" s="14"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="86"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="15" t="s">
         <v>495</v>
       </c>
@@ -7254,7 +7242,7 @@
       <c r="N42" s="14"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="86"/>
+      <c r="A43" s="63"/>
       <c r="B43" s="15" t="s">
         <v>361</v>
       </c>
@@ -7274,7 +7262,7 @@
       <c r="N43" s="14"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="86"/>
+      <c r="A44" s="63"/>
       <c r="B44" s="15" t="s">
         <v>375</v>
       </c>
@@ -7294,7 +7282,7 @@
       <c r="N44" s="14"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="86"/>
+      <c r="A45" s="63"/>
       <c r="B45" s="15" t="s">
         <v>354</v>
       </c>
@@ -7314,7 +7302,7 @@
       <c r="N45" s="14"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="86"/>
+      <c r="A46" s="63"/>
       <c r="B46" s="15" t="s">
         <v>491</v>
       </c>
@@ -7334,7 +7322,7 @@
       <c r="N46" s="14"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="86"/>
+      <c r="A47" s="63"/>
       <c r="B47" s="15" t="s">
         <v>384</v>
       </c>
@@ -7354,7 +7342,7 @@
       <c r="N47" s="14"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="86"/>
+      <c r="A48" s="63"/>
       <c r="B48" s="15" t="s">
         <v>536</v>
       </c>
@@ -7374,7 +7362,7 @@
       <c r="N48" s="14"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="86"/>
+      <c r="A49" s="63"/>
       <c r="B49" s="15" t="s">
         <v>451</v>
       </c>
@@ -7394,7 +7382,7 @@
       <c r="N49" s="14"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="86"/>
+      <c r="A50" s="63"/>
       <c r="B50" s="15" t="s">
         <v>440</v>
       </c>
@@ -7432,7 +7420,7 @@
       <c r="N51" s="14"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="67" t="s">
+      <c r="A52" s="62" t="s">
         <v>526</v>
       </c>
       <c r="B52" s="15" t="s">
@@ -7454,7 +7442,7 @@
       <c r="N52" s="14"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="67"/>
+      <c r="A53" s="62"/>
       <c r="B53" s="15" t="s">
         <v>360</v>
       </c>
@@ -7474,7 +7462,7 @@
       <c r="N53" s="14"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="67"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="15" t="s">
         <v>546</v>
       </c>
@@ -7494,7 +7482,7 @@
       <c r="N54" s="14"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="67"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="15" t="s">
         <v>531</v>
       </c>
@@ -7514,7 +7502,7 @@
       <c r="N55" s="14"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="67"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="15" t="s">
         <v>522</v>
       </c>
@@ -7534,7 +7522,7 @@
       <c r="N56" s="14"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="67"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="15" t="s">
         <v>472</v>
       </c>
@@ -7554,7 +7542,7 @@
       <c r="N57" s="14"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="67" t="s">
+      <c r="A58" s="62" t="s">
         <v>520</v>
       </c>
       <c r="B58" s="15" t="s">
@@ -7576,7 +7564,7 @@
       <c r="N58" s="14"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="67"/>
+      <c r="A59" s="62"/>
       <c r="B59" s="15" t="s">
         <v>482</v>
       </c>
@@ -7596,7 +7584,7 @@
       <c r="N59" s="14"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="67"/>
+      <c r="A60" s="62"/>
       <c r="B60" s="15" t="s">
         <v>508</v>
       </c>
@@ -7616,7 +7604,7 @@
       <c r="N60" s="14"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="67"/>
+      <c r="A61" s="62"/>
       <c r="B61" s="15" t="s">
         <v>490</v>
       </c>
@@ -7636,7 +7624,7 @@
       <c r="N61" s="14"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="67"/>
+      <c r="A62" s="62"/>
       <c r="B62" s="15" t="s">
         <v>503</v>
       </c>
@@ -7656,7 +7644,7 @@
       <c r="N62" s="14"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="67"/>
+      <c r="A63" s="62"/>
       <c r="B63" s="15" t="s">
         <v>511</v>
       </c>
@@ -7676,7 +7664,7 @@
       <c r="N63" s="14"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="86" t="s">
+      <c r="A64" s="63" t="s">
         <v>109</v>
       </c>
       <c r="B64" s="30" t="s">
@@ -7698,7 +7686,7 @@
       <c r="N64" s="14"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="86"/>
+      <c r="A65" s="63"/>
       <c r="B65" s="30" t="s">
         <v>387</v>
       </c>
@@ -7718,7 +7706,7 @@
       <c r="N65" s="14"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="86"/>
+      <c r="A66" s="63"/>
       <c r="B66" s="30" t="s">
         <v>397</v>
       </c>
@@ -7738,7 +7726,7 @@
       <c r="N66" s="14"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="86"/>
+      <c r="A67" s="63"/>
       <c r="B67" s="30" t="s">
         <v>496</v>
       </c>
@@ -7758,7 +7746,7 @@
       <c r="N67" s="14"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="86" t="s">
+      <c r="A68" s="63" t="s">
         <v>109</v>
       </c>
       <c r="B68" s="30" t="s">
@@ -7780,7 +7768,7 @@
       <c r="N68" s="14"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="86"/>
+      <c r="A69" s="63"/>
       <c r="B69" s="30" t="s">
         <v>501</v>
       </c>
@@ -7800,7 +7788,7 @@
       <c r="N69" s="14"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="86"/>
+      <c r="A70" s="63"/>
       <c r="B70" s="30" t="s">
         <v>450</v>
       </c>
@@ -7820,7 +7808,7 @@
       <c r="N70" s="14"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="86"/>
+      <c r="A71" s="63"/>
       <c r="B71" s="30" t="s">
         <v>480</v>
       </c>
@@ -7840,7 +7828,7 @@
       <c r="N71" s="14"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="86" t="s">
+      <c r="A72" s="63" t="s">
         <v>41</v>
       </c>
       <c r="B72" s="30" t="s">
@@ -7862,7 +7850,7 @@
       <c r="N72" s="14"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="86"/>
+      <c r="A73" s="63"/>
       <c r="B73" s="30" t="s">
         <v>545</v>
       </c>
@@ -7882,7 +7870,7 @@
       <c r="N73" s="14"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="86"/>
+      <c r="A74" s="63"/>
       <c r="B74" s="30" t="s">
         <v>470</v>
       </c>
@@ -7902,7 +7890,7 @@
       <c r="N74" s="14"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="86" t="s">
+      <c r="A75" s="63" t="s">
         <v>41</v>
       </c>
       <c r="B75" s="30" t="s">
@@ -7924,7 +7912,7 @@
       <c r="N75" s="14"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="86"/>
+      <c r="A76" s="63"/>
       <c r="B76" s="30" t="s">
         <v>494</v>
       </c>
@@ -7944,7 +7932,7 @@
       <c r="N76" s="14"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="86"/>
+      <c r="A77" s="63"/>
       <c r="B77" s="30" t="s">
         <v>544</v>
       </c>
@@ -7964,7 +7952,7 @@
       <c r="N77" s="14"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="86"/>
+      <c r="A78" s="63"/>
       <c r="B78" s="30" t="s">
         <v>558</v>
       </c>
@@ -7984,7 +7972,7 @@
       <c r="N78" s="14"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="86"/>
+      <c r="A79" s="63"/>
       <c r="B79" s="30" t="s">
         <v>542</v>
       </c>
@@ -8004,7 +7992,7 @@
       <c r="N79" s="14"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="86"/>
+      <c r="A80" s="63"/>
       <c r="B80" s="30" t="s">
         <v>534</v>
       </c>
@@ -8024,7 +8012,7 @@
       <c r="N80" s="14"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="86"/>
+      <c r="A81" s="63"/>
       <c r="B81" s="30" t="s">
         <v>519</v>
       </c>
@@ -8044,7 +8032,7 @@
       <c r="N81" s="14"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="86"/>
+      <c r="A82" s="63"/>
       <c r="B82" s="30" t="s">
         <v>541</v>
       </c>
@@ -8082,7 +8070,7 @@
       <c r="N83" s="14"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="67" t="s">
+      <c r="A84" s="62" t="s">
         <v>605</v>
       </c>
       <c r="B84" s="15" t="s">
@@ -8104,7 +8092,7 @@
       <c r="N84" s="14"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="67"/>
+      <c r="A85" s="62"/>
       <c r="B85" s="15" t="s">
         <v>349</v>
       </c>
@@ -8124,7 +8112,7 @@
       <c r="N85" s="14"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="67"/>
+      <c r="A86" s="62"/>
       <c r="B86" s="15" t="s">
         <v>507</v>
       </c>
@@ -8144,7 +8132,7 @@
       <c r="N86" s="14"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="67"/>
+      <c r="A87" s="62"/>
       <c r="B87" s="15" t="s">
         <v>326</v>
       </c>
@@ -8164,7 +8152,7 @@
       <c r="N87" s="14"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="67"/>
+      <c r="A88" s="62"/>
       <c r="B88" s="15" t="s">
         <v>549</v>
       </c>
@@ -8184,7 +8172,7 @@
       <c r="N88" s="14"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="67"/>
+      <c r="A89" s="62"/>
       <c r="B89" s="15" t="s">
         <v>334</v>
       </c>
@@ -8204,7 +8192,7 @@
       <c r="N89" s="14"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="67"/>
+      <c r="A90" s="62"/>
       <c r="B90" s="15" t="s">
         <v>330</v>
       </c>
@@ -8224,7 +8212,7 @@
       <c r="N90" s="14"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="67"/>
+      <c r="A91" s="62"/>
       <c r="B91" s="15" t="s">
         <v>305</v>
       </c>
@@ -8262,7 +8250,7 @@
       <c r="N92" s="14"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="67" t="s">
+      <c r="A93" s="62" t="s">
         <v>504</v>
       </c>
       <c r="B93" s="15" t="s">
@@ -8284,7 +8272,7 @@
       <c r="N93" s="14"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="67"/>
+      <c r="A94" s="62"/>
       <c r="B94" s="15" t="s">
         <v>434</v>
       </c>
@@ -8304,7 +8292,7 @@
       <c r="N94" s="14"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="67"/>
+      <c r="A95" s="62"/>
       <c r="B95" s="15" t="s">
         <v>512</v>
       </c>
@@ -8324,7 +8312,7 @@
       <c r="N95" s="14"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="67"/>
+      <c r="A96" s="62"/>
       <c r="B96" s="15" t="s">
         <v>510</v>
       </c>
@@ -8344,7 +8332,7 @@
       <c r="N96" s="14"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="67"/>
+      <c r="A97" s="62"/>
       <c r="B97" s="15" t="s">
         <v>554</v>
       </c>
@@ -8364,7 +8352,7 @@
       <c r="N97" s="14"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="67"/>
+      <c r="A98" s="62"/>
       <c r="B98" s="15" t="s">
         <v>560</v>
       </c>
@@ -8384,7 +8372,7 @@
       <c r="N98" s="14"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="67"/>
+      <c r="A99" s="62"/>
       <c r="B99" s="15" t="s">
         <v>523</v>
       </c>
@@ -8404,7 +8392,7 @@
       <c r="N99" s="14"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="67"/>
+      <c r="A100" s="62"/>
       <c r="B100" s="15" t="s">
         <v>564</v>
       </c>
@@ -8424,7 +8412,7 @@
       <c r="N100" s="14"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="67"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="15" t="s">
         <v>509</v>
       </c>
@@ -8444,7 +8432,7 @@
       <c r="N101" s="14"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="67"/>
+      <c r="A102" s="62"/>
       <c r="B102" s="15" t="s">
         <v>473</v>
       </c>
@@ -8464,7 +8452,7 @@
       <c r="N102" s="14"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="67"/>
+      <c r="A103" s="62"/>
       <c r="B103" s="15" t="s">
         <v>476</v>
       </c>
@@ -8484,7 +8472,7 @@
       <c r="N103" s="14"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="67"/>
+      <c r="A104" s="62"/>
       <c r="B104" s="15" t="s">
         <v>532</v>
       </c>
@@ -8504,7 +8492,7 @@
       <c r="N104" s="14"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="67"/>
+      <c r="A105" s="62"/>
       <c r="B105" s="15" t="s">
         <v>524</v>
       </c>
@@ -8524,7 +8512,7 @@
       <c r="N105" s="14"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="67"/>
+      <c r="A106" s="62"/>
       <c r="B106" s="15" t="s">
         <v>528</v>
       </c>
@@ -8544,7 +8532,7 @@
       <c r="N106" s="14"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="67"/>
+      <c r="A107" s="62"/>
       <c r="B107" s="15" t="s">
         <v>521</v>
       </c>
@@ -8564,7 +8552,7 @@
       <c r="N107" s="14"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="67"/>
+      <c r="A108" s="62"/>
       <c r="B108" s="15" t="s">
         <v>515</v>
       </c>
@@ -8602,7 +8590,7 @@
       <c r="N109" s="14"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="86" t="s">
+      <c r="A110" s="63" t="s">
         <v>2</v>
       </c>
       <c r="B110" s="30" t="s">
@@ -8624,7 +8612,7 @@
       <c r="N110" s="14"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="86"/>
+      <c r="A111" s="63"/>
       <c r="B111" s="30" t="s">
         <v>547</v>
       </c>
@@ -8644,7 +8632,7 @@
       <c r="N111" s="14"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="86"/>
+      <c r="A112" s="63"/>
       <c r="B112" s="30" t="s">
         <v>540</v>
       </c>
@@ -8664,7 +8652,7 @@
       <c r="N112" s="14"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="86"/>
+      <c r="A113" s="63"/>
       <c r="B113" s="30" t="s">
         <v>543</v>
       </c>
@@ -8684,7 +8672,7 @@
       <c r="N113" s="14"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="86"/>
+      <c r="A114" s="63"/>
       <c r="B114" s="30" t="s">
         <v>538</v>
       </c>
@@ -8704,7 +8692,7 @@
       <c r="N114" s="14"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="86"/>
+      <c r="A115" s="63"/>
       <c r="B115" s="30" t="s">
         <v>537</v>
       </c>
@@ -8724,7 +8712,7 @@
       <c r="N115" s="14"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="86"/>
+      <c r="A116" s="63"/>
       <c r="B116" s="30" t="s">
         <v>261</v>
       </c>
@@ -8762,7 +8750,7 @@
       <c r="N117" s="14"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="67" t="s">
+      <c r="A118" s="62" t="s">
         <v>257</v>
       </c>
       <c r="B118" s="30" t="s">
@@ -8784,7 +8772,7 @@
       <c r="N118" s="14"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="67"/>
+      <c r="A119" s="62"/>
       <c r="B119" s="30" t="s">
         <v>311</v>
       </c>
@@ -8804,7 +8792,7 @@
       <c r="N119" s="14"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="67"/>
+      <c r="A120" s="62"/>
       <c r="B120" s="31" t="s">
         <v>587</v>
       </c>
@@ -8824,7 +8812,7 @@
       <c r="N120" s="14"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="67"/>
+      <c r="A121" s="62"/>
       <c r="B121" s="31" t="s">
         <v>217</v>
       </c>
@@ -8862,7 +8850,7 @@
       <c r="N122" s="14"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="67" t="s">
+      <c r="A123" s="62" t="s">
         <v>252</v>
       </c>
       <c r="B123" s="15" t="s">
@@ -8884,7 +8872,7 @@
       <c r="N123" s="14"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="67"/>
+      <c r="A124" s="62"/>
       <c r="B124" s="15" t="s">
         <v>319</v>
       </c>
@@ -8904,7 +8892,7 @@
       <c r="N124" s="14"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="67"/>
+      <c r="A125" s="62"/>
       <c r="B125" s="15" t="s">
         <v>588</v>
       </c>
@@ -8924,7 +8912,7 @@
       <c r="N125" s="14"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="67"/>
+      <c r="A126" s="62"/>
       <c r="B126" s="15" t="s">
         <v>207</v>
       </c>
@@ -8944,7 +8932,7 @@
       <c r="N126" s="14"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="67"/>
+      <c r="A127" s="62"/>
       <c r="B127" s="15" t="s">
         <v>376</v>
       </c>
@@ -8964,7 +8952,7 @@
       <c r="N127" s="14"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="67"/>
+      <c r="A128" s="62"/>
       <c r="B128" s="15" t="s">
         <v>234</v>
       </c>
@@ -8984,7 +8972,7 @@
       <c r="N128" s="14"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="67"/>
+      <c r="A129" s="62"/>
       <c r="B129" s="15" t="s">
         <v>239</v>
       </c>
@@ -9004,7 +8992,7 @@
       <c r="N129" s="14"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="67"/>
+      <c r="A130" s="62"/>
       <c r="B130" s="15" t="s">
         <v>373</v>
       </c>
@@ -9024,7 +9012,7 @@
       <c r="N130" s="14"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="67"/>
+      <c r="A131" s="62"/>
       <c r="B131" s="15" t="s">
         <v>593</v>
       </c>
@@ -9044,7 +9032,7 @@
       <c r="N131" s="14"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="67"/>
+      <c r="A132" s="62"/>
       <c r="B132" s="31" t="s">
         <v>406</v>
       </c>
@@ -9064,7 +9052,7 @@
       <c r="N132" s="14"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="67"/>
+      <c r="A133" s="62"/>
       <c r="B133" s="31" t="s">
         <v>348</v>
       </c>
@@ -9084,7 +9072,7 @@
       <c r="N133" s="14"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="67"/>
+      <c r="A134" s="62"/>
       <c r="B134" s="31" t="s">
         <v>395</v>
       </c>
@@ -9122,7 +9110,7 @@
       <c r="N135" s="14"/>
     </row>
     <row r="136" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="67" t="s">
+      <c r="A136" s="62" t="s">
         <v>603</v>
       </c>
       <c r="B136" s="15" t="s">
@@ -9144,7 +9132,7 @@
       <c r="N136" s="14"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="67"/>
+      <c r="A137" s="62"/>
       <c r="B137" s="15" t="s">
         <v>368</v>
       </c>
@@ -9164,7 +9152,7 @@
       <c r="N137" s="14"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="67"/>
+      <c r="A138" s="62"/>
       <c r="B138" s="15" t="s">
         <v>235</v>
       </c>
@@ -9184,7 +9172,7 @@
       <c r="N138" s="14"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="67"/>
+      <c r="A139" s="62"/>
       <c r="B139" s="30" t="s">
         <v>221</v>
       </c>
@@ -9204,7 +9192,7 @@
       <c r="N139" s="14"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="67"/>
+      <c r="A140" s="62"/>
       <c r="B140" s="15" t="s">
         <v>320</v>
       </c>
@@ -9224,7 +9212,7 @@
       <c r="N140" s="14"/>
     </row>
     <row r="141" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="67"/>
+      <c r="A141" s="62"/>
       <c r="B141" s="15" t="s">
         <v>236</v>
       </c>
@@ -9244,7 +9232,7 @@
       <c r="N141" s="14"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="67"/>
+      <c r="A142" s="62"/>
       <c r="B142" s="30" t="s">
         <v>251</v>
       </c>
@@ -9264,7 +9252,7 @@
       <c r="N142" s="14"/>
     </row>
     <row r="143" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="67" t="s">
+      <c r="A143" s="62" t="s">
         <v>603</v>
       </c>
       <c r="B143" s="15" t="s">
@@ -9286,7 +9274,7 @@
       <c r="N143" s="14"/>
     </row>
     <row r="144" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="67"/>
+      <c r="A144" s="62"/>
       <c r="B144" s="15" t="s">
         <v>201</v>
       </c>
@@ -9306,7 +9294,7 @@
       <c r="N144" s="14"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="67"/>
+      <c r="A145" s="62"/>
       <c r="B145" s="15" t="s">
         <v>364</v>
       </c>
@@ -9326,7 +9314,7 @@
       <c r="N145" s="14"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="67"/>
+      <c r="A146" s="62"/>
       <c r="B146" s="15" t="s">
         <v>388</v>
       </c>
@@ -9346,7 +9334,7 @@
       <c r="N146" s="14"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="67"/>
+      <c r="A147" s="62"/>
       <c r="B147" s="15" t="s">
         <v>358</v>
       </c>
@@ -9366,7 +9354,7 @@
       <c r="N147" s="14"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="67"/>
+      <c r="A148" s="62"/>
       <c r="B148" s="15" t="s">
         <v>377</v>
       </c>
@@ -9386,7 +9374,7 @@
       <c r="N148" s="14"/>
     </row>
     <row r="149" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="67"/>
+      <c r="A149" s="62"/>
       <c r="B149" s="15" t="s">
         <v>370</v>
       </c>
@@ -9406,7 +9394,7 @@
       <c r="N149" s="14"/>
     </row>
     <row r="150" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="67"/>
+      <c r="A150" s="62"/>
       <c r="B150" s="15" t="s">
         <v>199</v>
       </c>
@@ -9426,7 +9414,7 @@
       <c r="N150" s="14"/>
     </row>
     <row r="151" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="67"/>
+      <c r="A151" s="62"/>
       <c r="B151" s="15" t="s">
         <v>260</v>
       </c>
@@ -9464,7 +9452,7 @@
       <c r="N152" s="14"/>
     </row>
     <row r="153" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="67" t="s">
+      <c r="A153" s="62" t="s">
         <v>599</v>
       </c>
       <c r="B153" s="15" t="s">
@@ -9486,7 +9474,7 @@
       <c r="N153" s="14"/>
     </row>
     <row r="154" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="67"/>
+      <c r="A154" s="62"/>
       <c r="B154" s="15">
         <v>25034</v>
       </c>
@@ -9506,7 +9494,7 @@
       <c r="N154" s="14"/>
     </row>
     <row r="155" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="67"/>
+      <c r="A155" s="62"/>
       <c r="B155" s="15" t="s">
         <v>309</v>
       </c>
@@ -9548,7 +9536,7 @@
       <c r="N156" s="14"/>
     </row>
     <row r="157" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="67" t="s">
+      <c r="A157" s="62" t="s">
         <v>300</v>
       </c>
       <c r="B157" s="15" t="s">
@@ -9570,7 +9558,7 @@
       <c r="N157" s="14"/>
     </row>
     <row r="158" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="67"/>
+      <c r="A158" s="62"/>
       <c r="B158" s="30" t="s">
         <v>346</v>
       </c>
@@ -9590,7 +9578,7 @@
       <c r="N158" s="14"/>
     </row>
     <row r="159" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="67"/>
+      <c r="A159" s="62"/>
       <c r="B159" s="30" t="s">
         <v>670</v>
       </c>
@@ -9650,7 +9638,7 @@
       <c r="N161" s="14"/>
     </row>
     <row r="162" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="86" t="s">
+      <c r="A162" s="63" t="s">
         <v>59</v>
       </c>
       <c r="B162" s="15" t="s">
@@ -9672,7 +9660,7 @@
       <c r="N162" s="14"/>
     </row>
     <row r="163" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="86"/>
+      <c r="A163" s="63"/>
       <c r="B163" s="15" t="s">
         <v>347</v>
       </c>
@@ -9692,7 +9680,7 @@
       <c r="N163" s="14"/>
     </row>
     <row r="164" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="86"/>
+      <c r="A164" s="63"/>
       <c r="B164" s="15" t="s">
         <v>421</v>
       </c>
@@ -9712,7 +9700,7 @@
       <c r="N164" s="14"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="86"/>
+      <c r="A165" s="63"/>
       <c r="B165" s="15" t="s">
         <v>323</v>
       </c>
@@ -9732,7 +9720,7 @@
       <c r="N165" s="14"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="86"/>
+      <c r="A166" s="63"/>
       <c r="B166" s="15" t="s">
         <v>342</v>
       </c>
@@ -9752,7 +9740,7 @@
       <c r="N166" s="14"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="86"/>
+      <c r="A167" s="63"/>
       <c r="B167" s="15" t="s">
         <v>322</v>
       </c>
@@ -9772,7 +9760,7 @@
       <c r="N167" s="14"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="86"/>
+      <c r="A168" s="63"/>
       <c r="B168" s="15" t="s">
         <v>291</v>
       </c>
@@ -9792,7 +9780,7 @@
       <c r="N168" s="14"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="86"/>
+      <c r="A169" s="63"/>
       <c r="B169" s="15" t="s">
         <v>331</v>
       </c>
@@ -9830,7 +9818,7 @@
       <c r="N170" s="14"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="67" t="s">
+      <c r="A171" s="62" t="s">
         <v>604</v>
       </c>
       <c r="B171" s="15" t="s">
@@ -9852,7 +9840,7 @@
       <c r="N171" s="14"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="67"/>
+      <c r="A172" s="62"/>
       <c r="B172" s="15" t="s">
         <v>266</v>
       </c>
@@ -9872,7 +9860,7 @@
       <c r="N172" s="14"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="67"/>
+      <c r="A173" s="62"/>
       <c r="B173" s="15" t="s">
         <v>362</v>
       </c>
@@ -9892,7 +9880,7 @@
       <c r="N173" s="14"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="67"/>
+      <c r="A174" s="62"/>
       <c r="B174" s="15" t="s">
         <v>379</v>
       </c>
@@ -9930,7 +9918,7 @@
       <c r="N175" s="14"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="67" t="s">
+      <c r="A176" s="62" t="s">
         <v>324</v>
       </c>
       <c r="B176" s="15" t="s">
@@ -9952,7 +9940,7 @@
       <c r="N176" s="14"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="67"/>
+      <c r="A177" s="62"/>
       <c r="B177" s="15" t="s">
         <v>445</v>
       </c>
@@ -9972,14 +9960,14 @@
       <c r="N177" s="14"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A178" s="55" t="s">
+      <c r="A178" s="86" t="s">
         <v>135</v>
       </c>
-      <c r="B178" s="56"/>
-      <c r="C178" s="56"/>
-      <c r="D178" s="56"/>
-      <c r="E178" s="56"/>
-      <c r="F178" s="57"/>
+      <c r="B178" s="87"/>
+      <c r="C178" s="87"/>
+      <c r="D178" s="87"/>
+      <c r="E178" s="87"/>
+      <c r="F178" s="88"/>
       <c r="G178" s="48"/>
       <c r="H178" s="48"/>
       <c r="I178" s="48"/>
@@ -9990,14 +9978,14 @@
       <c r="N178" s="23"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A179" s="58" t="s">
+      <c r="A179" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="B179" s="59"/>
-      <c r="C179" s="59"/>
-      <c r="D179" s="59"/>
-      <c r="E179" s="59"/>
-      <c r="F179" s="60"/>
+      <c r="B179" s="90"/>
+      <c r="C179" s="90"/>
+      <c r="D179" s="90"/>
+      <c r="E179" s="90"/>
+      <c r="F179" s="91"/>
       <c r="G179" s="49"/>
       <c r="H179" s="49"/>
       <c r="I179" s="49"/>
@@ -10027,96 +10015,107 @@
       <c r="A181" s="3"/>
       <c r="B181" s="1"/>
       <c r="C181" s="5"/>
-      <c r="D181" s="71"/>
-      <c r="E181" s="72"/>
-      <c r="F181" s="72"/>
-      <c r="G181" s="63"/>
-      <c r="H181" s="63"/>
-      <c r="I181" s="63"/>
-      <c r="J181" s="64"/>
+      <c r="D181" s="82"/>
+      <c r="E181" s="83"/>
+      <c r="F181" s="83"/>
+      <c r="G181" s="75"/>
+      <c r="H181" s="75"/>
+      <c r="I181" s="75"/>
+      <c r="J181" s="76"/>
       <c r="K181" s="8"/>
       <c r="L181" s="8"/>
       <c r="M181" s="8"/>
       <c r="N181" s="8"/>
     </row>
     <row r="182" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D182" s="73" t="s">
+      <c r="D182" s="84" t="s">
+        <v>774</v>
+      </c>
+      <c r="E182" s="85"/>
+      <c r="F182" s="85"/>
+      <c r="G182" s="77"/>
+      <c r="H182" s="77"/>
+      <c r="I182" s="77"/>
+      <c r="J182" s="78"/>
+    </row>
+    <row r="183" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D183" s="66" t="s">
+        <v>775</v>
+      </c>
+      <c r="E183" s="67"/>
+      <c r="F183" s="67"/>
+      <c r="G183" s="62"/>
+      <c r="H183" s="62"/>
+      <c r="I183" s="62"/>
+      <c r="J183" s="80"/>
+    </row>
+    <row r="184" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D184" s="66" t="s">
+        <v>776</v>
+      </c>
+      <c r="E184" s="67"/>
+      <c r="F184" s="67"/>
+      <c r="G184" s="62"/>
+      <c r="H184" s="62"/>
+      <c r="I184" s="62"/>
+      <c r="J184" s="80"/>
+    </row>
+    <row r="185" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D185" s="68" t="s">
         <v>777</v>
       </c>
-      <c r="E182" s="74"/>
-      <c r="F182" s="74"/>
-      <c r="G182" s="65"/>
-      <c r="H182" s="65"/>
-      <c r="I182" s="65"/>
-      <c r="J182" s="66"/>
-    </row>
-    <row r="183" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D183" s="75" t="s">
+      <c r="E185" s="69"/>
+      <c r="F185" s="69"/>
+      <c r="G185" s="79"/>
+      <c r="H185" s="79"/>
+      <c r="I185" s="79"/>
+      <c r="J185" s="81"/>
+    </row>
+    <row r="186" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D186" s="73" t="s">
         <v>778</v>
       </c>
-      <c r="E183" s="76"/>
-      <c r="F183" s="76"/>
-      <c r="G183" s="67"/>
-      <c r="H183" s="67"/>
-      <c r="I183" s="67"/>
-      <c r="J183" s="69"/>
-    </row>
-    <row r="184" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D184" s="75" t="s">
-        <v>779</v>
-      </c>
-      <c r="E184" s="76"/>
-      <c r="F184" s="76"/>
-      <c r="G184" s="67"/>
-      <c r="H184" s="67"/>
-      <c r="I184" s="67"/>
-      <c r="J184" s="69"/>
-    </row>
-    <row r="185" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D185" s="77" t="s">
-        <v>780</v>
-      </c>
-      <c r="E185" s="78"/>
-      <c r="F185" s="78"/>
-      <c r="G185" s="68"/>
-      <c r="H185" s="68"/>
-      <c r="I185" s="68"/>
-      <c r="J185" s="70"/>
-    </row>
-    <row r="186" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D186" s="61" t="s">
-        <v>781</v>
-      </c>
-      <c r="E186" s="62"/>
-      <c r="F186" s="62"/>
-      <c r="G186" s="63"/>
-      <c r="H186" s="63"/>
-      <c r="I186" s="63"/>
-      <c r="J186" s="63"/>
+      <c r="E186" s="74"/>
+      <c r="F186" s="74"/>
+      <c r="G186" s="75"/>
+      <c r="H186" s="75"/>
+      <c r="I186" s="75"/>
+      <c r="J186" s="75"/>
     </row>
   </sheetData>
   <mergeCells count="69">
-    <mergeCell ref="A24:F24"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A8:A18"/>
-    <mergeCell ref="A20:A23"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A161:F161"/>
-    <mergeCell ref="A25:A50"/>
-    <mergeCell ref="A58:A63"/>
-    <mergeCell ref="A64:A67"/>
-    <mergeCell ref="A68:A71"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="A75:A82"/>
-    <mergeCell ref="A84:A91"/>
-    <mergeCell ref="A93:A108"/>
-    <mergeCell ref="A110:A116"/>
-    <mergeCell ref="A52:A57"/>
-    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A170:F170"/>
+    <mergeCell ref="A175:F175"/>
+    <mergeCell ref="A178:F178"/>
+    <mergeCell ref="A179:F179"/>
+    <mergeCell ref="A83:F83"/>
+    <mergeCell ref="A92:F92"/>
+    <mergeCell ref="A109:F109"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="A122:F122"/>
+    <mergeCell ref="A136:A142"/>
+    <mergeCell ref="A143:A151"/>
+    <mergeCell ref="A157:A159"/>
+    <mergeCell ref="A153:A155"/>
+    <mergeCell ref="A162:A169"/>
+    <mergeCell ref="A135:F135"/>
+    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="D186:F186"/>
+    <mergeCell ref="G181:H181"/>
+    <mergeCell ref="I181:J181"/>
+    <mergeCell ref="G182:H182"/>
+    <mergeCell ref="I182:J182"/>
+    <mergeCell ref="G183:H183"/>
+    <mergeCell ref="G184:H184"/>
+    <mergeCell ref="G185:H185"/>
+    <mergeCell ref="G186:H186"/>
+    <mergeCell ref="I183:J183"/>
+    <mergeCell ref="I184:J184"/>
+    <mergeCell ref="I185:J185"/>
+    <mergeCell ref="I186:J186"/>
+    <mergeCell ref="D181:F181"/>
+    <mergeCell ref="D182:F182"/>
+    <mergeCell ref="D183:F183"/>
     <mergeCell ref="D184:F184"/>
     <mergeCell ref="D185:F185"/>
     <mergeCell ref="L6:L7"/>
@@ -10133,47 +10132,39 @@
     <mergeCell ref="A176:A177"/>
     <mergeCell ref="A118:A121"/>
     <mergeCell ref="A123:A134"/>
-    <mergeCell ref="D186:F186"/>
-    <mergeCell ref="G181:H181"/>
-    <mergeCell ref="I181:J181"/>
-    <mergeCell ref="G182:H182"/>
-    <mergeCell ref="I182:J182"/>
-    <mergeCell ref="G183:H183"/>
-    <mergeCell ref="G184:H184"/>
-    <mergeCell ref="G185:H185"/>
-    <mergeCell ref="G186:H186"/>
-    <mergeCell ref="I183:J183"/>
-    <mergeCell ref="I184:J184"/>
-    <mergeCell ref="I185:J185"/>
-    <mergeCell ref="I186:J186"/>
-    <mergeCell ref="D181:F181"/>
-    <mergeCell ref="D182:F182"/>
-    <mergeCell ref="D183:F183"/>
-    <mergeCell ref="A170:F170"/>
-    <mergeCell ref="A175:F175"/>
-    <mergeCell ref="A178:F178"/>
-    <mergeCell ref="A179:F179"/>
-    <mergeCell ref="A83:F83"/>
-    <mergeCell ref="A92:F92"/>
-    <mergeCell ref="A109:F109"/>
-    <mergeCell ref="A117:F117"/>
-    <mergeCell ref="A122:F122"/>
-    <mergeCell ref="A136:A142"/>
-    <mergeCell ref="A143:A151"/>
-    <mergeCell ref="A157:A159"/>
-    <mergeCell ref="A153:A155"/>
-    <mergeCell ref="A162:A169"/>
-    <mergeCell ref="A135:F135"/>
-    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="A161:F161"/>
+    <mergeCell ref="A25:A50"/>
+    <mergeCell ref="A58:A63"/>
+    <mergeCell ref="A64:A67"/>
+    <mergeCell ref="A68:A71"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="A75:A82"/>
+    <mergeCell ref="A84:A91"/>
+    <mergeCell ref="A93:A108"/>
+    <mergeCell ref="A110:A116"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A8:A18"/>
+    <mergeCell ref="A20:A23"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A19:F19"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="63" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40003A12-299B-49DA-9F58-285CA1AE7CAF}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:N199"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -12646,22 +12637,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81" t="s">
-        <v>717</v>
-      </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32"/>
@@ -12677,13 +12666,13 @@
       <c r="K3" s="32"/>
       <c r="L3" s="32"/>
       <c r="M3" s="33" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="N3" s="51"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="38" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="N4" s="51"/>
     </row>
@@ -12692,68 +12681,68 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="64" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="57" t="s">
+        <v>716</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>717</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>718</v>
+      </c>
+      <c r="E6" s="59" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="F6" s="55" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="G6" s="55" t="s">
+        <v>669</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>673</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>680</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>681</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>682</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>700</v>
+      </c>
+      <c r="M6" s="55" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="N6" s="71" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="79" t="s">
-        <v>723</v>
-      </c>
-      <c r="G6" s="79" t="s">
-        <v>669</v>
-      </c>
-      <c r="H6" s="79" t="s">
-        <v>673</v>
-      </c>
-      <c r="I6" s="79" t="s">
-        <v>680</v>
-      </c>
-      <c r="J6" s="79" t="s">
-        <v>681</v>
-      </c>
-      <c r="K6" s="79" t="s">
-        <v>682</v>
-      </c>
-      <c r="L6" s="79" t="s">
-        <v>700</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>724</v>
-      </c>
-      <c r="N6" s="82" t="s">
+    </row>
+    <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="65"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="72"/>
+    </row>
+    <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="92" t="s">
         <v>725</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="83"/>
-    </row>
-    <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="96" t="s">
-        <v>728</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>418</v>
@@ -12774,7 +12763,7 @@
       <c r="N8" s="28"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="94"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="13" t="s">
         <v>410</v>
       </c>
@@ -12794,7 +12783,7 @@
       <c r="N9" s="27"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="94"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="11" t="s">
         <v>341</v>
       </c>
@@ -12814,7 +12803,7 @@
       <c r="N10" s="27"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="94"/>
+      <c r="A11" s="93"/>
       <c r="B11" s="11" t="s">
         <v>293</v>
       </c>
@@ -12834,7 +12823,7 @@
       <c r="N11" s="27"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="94"/>
+      <c r="A12" s="93"/>
       <c r="B12" s="11" t="s">
         <v>391</v>
       </c>
@@ -12854,7 +12843,7 @@
       <c r="N12" s="27"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
+      <c r="A13" s="93"/>
       <c r="B13" s="11" t="s">
         <v>420</v>
       </c>
@@ -12874,7 +12863,7 @@
       <c r="N13" s="27"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="94"/>
+      <c r="A14" s="93"/>
       <c r="B14" s="11" t="s">
         <v>426</v>
       </c>
@@ -12894,7 +12883,7 @@
       <c r="N14" s="27"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="94"/>
+      <c r="A15" s="93"/>
       <c r="B15" s="11" t="s">
         <v>424</v>
       </c>
@@ -12914,7 +12903,7 @@
       <c r="N15" s="27"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="94"/>
+      <c r="A16" s="93"/>
       <c r="B16" s="11" t="s">
         <v>290</v>
       </c>
@@ -12934,7 +12923,7 @@
       <c r="N16" s="27"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="94"/>
+      <c r="A17" s="93"/>
       <c r="B17" s="11" t="s">
         <v>497</v>
       </c>
@@ -12954,7 +12943,7 @@
       <c r="N17" s="27"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="94"/>
+      <c r="A18" s="93"/>
       <c r="B18" s="11" t="s">
         <v>425</v>
       </c>
@@ -12974,7 +12963,7 @@
       <c r="N18" s="27"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="94"/>
+      <c r="A19" s="93"/>
       <c r="B19" s="11" t="s">
         <v>703</v>
       </c>
@@ -12994,7 +12983,7 @@
       <c r="N19" s="27"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="92" t="s">
+      <c r="A20" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B20" s="53"/>
@@ -13012,8 +13001,8 @@
       <c r="N20" s="27"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="94" t="s">
-        <v>730</v>
+      <c r="A21" s="93" t="s">
+        <v>727</v>
       </c>
       <c r="B21" s="40" t="s">
         <v>460</v>
@@ -13034,7 +13023,7 @@
       <c r="N21" s="27"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="94"/>
+      <c r="A22" s="93"/>
       <c r="B22" s="41" t="s">
         <v>413</v>
       </c>
@@ -13054,7 +13043,7 @@
       <c r="N22" s="27"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="94"/>
+      <c r="A23" s="93"/>
       <c r="B23" s="40" t="s">
         <v>439</v>
       </c>
@@ -13074,7 +13063,7 @@
       <c r="N23" s="27"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="94"/>
+      <c r="A24" s="93"/>
       <c r="B24" s="40" t="s">
         <v>444</v>
       </c>
@@ -13094,7 +13083,7 @@
       <c r="N24" s="27"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="94"/>
+      <c r="A25" s="93"/>
       <c r="B25" s="40" t="s">
         <v>289</v>
       </c>
@@ -13114,7 +13103,7 @@
       <c r="N25" s="27"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="94"/>
+      <c r="A26" s="93"/>
       <c r="B26" s="40" t="s">
         <v>477</v>
       </c>
@@ -13134,7 +13123,7 @@
       <c r="N26" s="27"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="94"/>
+      <c r="A27" s="93"/>
       <c r="B27" s="40" t="s">
         <v>284</v>
       </c>
@@ -13154,9 +13143,9 @@
       <c r="N27" s="27"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="94"/>
+      <c r="A28" s="93"/>
       <c r="B28" s="40" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C28" s="10" t="s">
         <v>33</v>
@@ -13174,7 +13163,7 @@
       <c r="N28" s="27"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="92" t="s">
+      <c r="A29" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B29" s="53"/>
@@ -13192,8 +13181,8 @@
       <c r="N29" s="27"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="94" t="s">
-        <v>732</v>
+      <c r="A30" s="93" t="s">
+        <v>729</v>
       </c>
       <c r="B30" s="42" t="s">
         <v>411</v>
@@ -13214,7 +13203,7 @@
       <c r="N30" s="27"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="94"/>
+      <c r="A31" s="93"/>
       <c r="B31" s="42" t="s">
         <v>383</v>
       </c>
@@ -13234,7 +13223,7 @@
       <c r="N31" s="27"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="94"/>
+      <c r="A32" s="93"/>
       <c r="B32" s="44" t="s">
         <v>419</v>
       </c>
@@ -13254,7 +13243,7 @@
       <c r="N32" s="27"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="94"/>
+      <c r="A33" s="93"/>
       <c r="B33" s="42" t="s">
         <v>449</v>
       </c>
@@ -13274,7 +13263,7 @@
       <c r="N33" s="27"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92" t="s">
+      <c r="A34" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B34" s="53"/>
@@ -13292,8 +13281,8 @@
       <c r="N34" s="27"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="95" t="s">
-        <v>733</v>
+      <c r="A35" s="94" t="s">
+        <v>730</v>
       </c>
       <c r="B35" s="40" t="s">
         <v>474</v>
@@ -13314,7 +13303,7 @@
       <c r="N35" s="27"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="95"/>
+      <c r="A36" s="94"/>
       <c r="B36" s="41" t="s">
         <v>461</v>
       </c>
@@ -13334,7 +13323,7 @@
       <c r="N36" s="27"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="95"/>
+      <c r="A37" s="94"/>
       <c r="B37" s="40" t="s">
         <v>274</v>
       </c>
@@ -13354,7 +13343,7 @@
       <c r="N37" s="27"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="95"/>
+      <c r="A38" s="94"/>
       <c r="B38" s="40" t="s">
         <v>248</v>
       </c>
@@ -13374,7 +13363,7 @@
       <c r="N38" s="27"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="95"/>
+      <c r="A39" s="94"/>
       <c r="B39" s="40" t="s">
         <v>273</v>
       </c>
@@ -13394,7 +13383,7 @@
       <c r="N39" s="27"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="95"/>
+      <c r="A40" s="94"/>
       <c r="B40" s="40" t="s">
         <v>241</v>
       </c>
@@ -13414,7 +13403,7 @@
       <c r="N40" s="27"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="95"/>
+      <c r="A41" s="94"/>
       <c r="B41" s="40" t="s">
         <v>269</v>
       </c>
@@ -13434,7 +13423,7 @@
       <c r="N41" s="27"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="95"/>
+      <c r="A42" s="94"/>
       <c r="B42" s="40" t="s">
         <v>267</v>
       </c>
@@ -13454,7 +13443,7 @@
       <c r="N42" s="27"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="95"/>
+      <c r="A43" s="94"/>
       <c r="B43" s="40" t="s">
         <v>407</v>
       </c>
@@ -13474,7 +13463,7 @@
       <c r="N43" s="27"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="95"/>
+      <c r="A44" s="94"/>
       <c r="B44" s="40" t="s">
         <v>443</v>
       </c>
@@ -13494,7 +13483,7 @@
       <c r="N44" s="27"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="95"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="40" t="s">
         <v>249</v>
       </c>
@@ -13514,7 +13503,7 @@
       <c r="N45" s="27"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="95"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="40" t="s">
         <v>478</v>
       </c>
@@ -13534,7 +13523,7 @@
       <c r="N46" s="27"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="92" t="s">
+      <c r="A47" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B47" s="53"/>
@@ -13552,8 +13541,8 @@
       <c r="N47" s="27"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="95" t="s">
-        <v>734</v>
+      <c r="A48" s="94" t="s">
+        <v>731</v>
       </c>
       <c r="B48" s="15" t="s">
         <v>579</v>
@@ -13574,7 +13563,7 @@
       <c r="N48" s="27"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="95"/>
+      <c r="A49" s="94"/>
       <c r="B49" s="15" t="s">
         <v>592</v>
       </c>
@@ -13594,7 +13583,7 @@
       <c r="N49" s="27"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="95"/>
+      <c r="A50" s="94"/>
       <c r="B50" s="15" t="s">
         <v>591</v>
       </c>
@@ -13614,7 +13603,7 @@
       <c r="N50" s="27"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="95"/>
+      <c r="A51" s="94"/>
       <c r="B51" s="15" t="s">
         <v>586</v>
       </c>
@@ -13634,7 +13623,7 @@
       <c r="N51" s="27"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="95"/>
+      <c r="A52" s="94"/>
       <c r="B52" s="15" t="s">
         <v>562</v>
       </c>
@@ -13654,7 +13643,7 @@
       <c r="N52" s="27"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="95"/>
+      <c r="A53" s="94"/>
       <c r="B53" s="15" t="s">
         <v>563</v>
       </c>
@@ -13674,12 +13663,12 @@
       <c r="N53" s="27"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="95"/>
+      <c r="A54" s="94"/>
       <c r="B54" s="15" t="s">
         <v>567</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -13694,7 +13683,7 @@
       <c r="N54" s="27"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="95"/>
+      <c r="A55" s="94"/>
       <c r="B55" s="15" t="s">
         <v>213</v>
       </c>
@@ -13714,7 +13703,7 @@
       <c r="N55" s="27"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="95"/>
+      <c r="A56" s="94"/>
       <c r="B56" s="15" t="s">
         <v>568</v>
       </c>
@@ -13734,7 +13723,7 @@
       <c r="N56" s="27"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="94"/>
+      <c r="A57" s="93"/>
       <c r="B57" s="15" t="s">
         <v>576</v>
       </c>
@@ -13754,7 +13743,7 @@
       <c r="N57" s="27"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="94"/>
+      <c r="A58" s="93"/>
       <c r="B58" s="15" t="s">
         <v>454</v>
       </c>
@@ -13774,7 +13763,7 @@
       <c r="N58" s="27"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="92" t="s">
+      <c r="A59" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B59" s="53"/>
@@ -13792,8 +13781,8 @@
       <c r="N59" s="27"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="95" t="s">
-        <v>736</v>
+      <c r="A60" s="94" t="s">
+        <v>733</v>
       </c>
       <c r="B60" s="15" t="s">
         <v>463</v>
@@ -13814,7 +13803,7 @@
       <c r="N60" s="27"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="94"/>
+      <c r="A61" s="93"/>
       <c r="B61" s="15" t="s">
         <v>469</v>
       </c>
@@ -13834,7 +13823,7 @@
       <c r="N61" s="27"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="94"/>
+      <c r="A62" s="93"/>
       <c r="B62" s="15" t="s">
         <v>705</v>
       </c>
@@ -13854,7 +13843,7 @@
       <c r="N62" s="27"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="94"/>
+      <c r="A63" s="93"/>
       <c r="B63" s="15" t="s">
         <v>457</v>
       </c>
@@ -13874,7 +13863,7 @@
       <c r="N63" s="27"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="94"/>
+      <c r="A64" s="93"/>
       <c r="B64" s="15" t="s">
         <v>707</v>
       </c>
@@ -13894,7 +13883,7 @@
       <c r="N64" s="27"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="94"/>
+      <c r="A65" s="93"/>
       <c r="B65" s="15" t="s">
         <v>438</v>
       </c>
@@ -13914,7 +13903,7 @@
       <c r="N65" s="27"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="94"/>
+      <c r="A66" s="93"/>
       <c r="B66" s="15" t="s">
         <v>709</v>
       </c>
@@ -13934,7 +13923,7 @@
       <c r="N66" s="27"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="94"/>
+      <c r="A67" s="93"/>
       <c r="B67" s="15" t="s">
         <v>694</v>
       </c>
@@ -13954,7 +13943,7 @@
       <c r="N67" s="27"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="94"/>
+      <c r="A68" s="93"/>
       <c r="B68" s="15" t="s">
         <v>441</v>
       </c>
@@ -13974,7 +13963,7 @@
       <c r="N68" s="27"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="94"/>
+      <c r="A69" s="93"/>
       <c r="B69" s="15" t="s">
         <v>206</v>
       </c>
@@ -13994,7 +13983,7 @@
       <c r="N69" s="27"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="94"/>
+      <c r="A70" s="93"/>
       <c r="B70" s="15" t="s">
         <v>711</v>
       </c>
@@ -14014,7 +14003,7 @@
       <c r="N70" s="27"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="94"/>
+      <c r="A71" s="93"/>
       <c r="B71" s="15" t="s">
         <v>459</v>
       </c>
@@ -14034,7 +14023,7 @@
       <c r="N71" s="27"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="94"/>
+      <c r="A72" s="93"/>
       <c r="B72" s="15" t="s">
         <v>713</v>
       </c>
@@ -14054,7 +14043,7 @@
       <c r="N72" s="27"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="94"/>
+      <c r="A73" s="93"/>
       <c r="B73" s="15" t="s">
         <v>559</v>
       </c>
@@ -14074,7 +14063,7 @@
       <c r="N73" s="27"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="94"/>
+      <c r="A74" s="93"/>
       <c r="B74" s="15" t="s">
         <v>585</v>
       </c>
@@ -14094,7 +14083,7 @@
       <c r="N74" s="27"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="92" t="s">
+      <c r="A75" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B75" s="53"/>
@@ -14112,8 +14101,8 @@
       <c r="N75" s="27"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="95" t="s">
-        <v>737</v>
+      <c r="A76" s="94" t="s">
+        <v>734</v>
       </c>
       <c r="B76" s="45" t="s">
         <v>580</v>
@@ -14134,7 +14123,7 @@
       <c r="N76" s="27"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="95"/>
+      <c r="A77" s="94"/>
       <c r="B77" s="40" t="s">
         <v>570</v>
       </c>
@@ -14154,7 +14143,7 @@
       <c r="N77" s="27"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="95"/>
+      <c r="A78" s="94"/>
       <c r="B78" s="45" t="s">
         <v>594</v>
       </c>
@@ -14174,7 +14163,7 @@
       <c r="N78" s="27"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="95"/>
+      <c r="A79" s="94"/>
       <c r="B79" s="45" t="s">
         <v>231</v>
       </c>
@@ -14194,7 +14183,7 @@
       <c r="N79" s="27"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="95"/>
+      <c r="A80" s="94"/>
       <c r="B80" s="45" t="s">
         <v>219</v>
       </c>
@@ -14214,7 +14203,7 @@
       <c r="N80" s="27"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="95"/>
+      <c r="A81" s="94"/>
       <c r="B81" s="45" t="s">
         <v>237</v>
       </c>
@@ -14234,7 +14223,7 @@
       <c r="N81" s="27"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="92" t="s">
+      <c r="A82" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B82" s="53"/>
@@ -14252,8 +14241,8 @@
       <c r="N82" s="27"/>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="95" t="s">
-        <v>738</v>
+      <c r="A83" s="94" t="s">
+        <v>735</v>
       </c>
       <c r="B83" s="45" t="s">
         <v>202</v>
@@ -14274,7 +14263,7 @@
       <c r="N83" s="27"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="95"/>
+      <c r="A84" s="94"/>
       <c r="B84" s="45" t="s">
         <v>205</v>
       </c>
@@ -14294,7 +14283,7 @@
       <c r="N84" s="27"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="95"/>
+      <c r="A85" s="94"/>
       <c r="B85" s="45" t="s">
         <v>233</v>
       </c>
@@ -14314,7 +14303,7 @@
       <c r="N85" s="27"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="95"/>
+      <c r="A86" s="94"/>
       <c r="B86" s="45" t="s">
         <v>211</v>
       </c>
@@ -14334,7 +14323,7 @@
       <c r="N86" s="27"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="92" t="s">
+      <c r="A87" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B87" s="53"/>
@@ -14352,8 +14341,8 @@
       <c r="N87" s="27"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="95" t="s">
-        <v>739</v>
+      <c r="A88" s="94" t="s">
+        <v>736</v>
       </c>
       <c r="B88" s="30" t="s">
         <v>286</v>
@@ -14374,7 +14363,7 @@
       <c r="N88" s="27"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="95"/>
+      <c r="A89" s="94"/>
       <c r="B89" s="30" t="s">
         <v>275</v>
       </c>
@@ -14394,7 +14383,7 @@
       <c r="N89" s="27"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="95"/>
+      <c r="A90" s="94"/>
       <c r="B90" s="30" t="s">
         <v>389</v>
       </c>
@@ -14414,7 +14403,7 @@
       <c r="N90" s="27"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="95"/>
+      <c r="A91" s="94"/>
       <c r="B91" s="30" t="s">
         <v>313</v>
       </c>
@@ -14434,7 +14423,7 @@
       <c r="N91" s="27"/>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="95"/>
+      <c r="A92" s="94"/>
       <c r="B92" s="30" t="s">
         <v>385</v>
       </c>
@@ -14454,7 +14443,7 @@
       <c r="N92" s="27"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="95"/>
+      <c r="A93" s="94"/>
       <c r="B93" s="30" t="s">
         <v>693</v>
       </c>
@@ -14474,7 +14463,7 @@
       <c r="N93" s="27"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="92" t="s">
+      <c r="A94" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B94" s="53"/>
@@ -14492,8 +14481,8 @@
       <c r="N94" s="27"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="95" t="s">
-        <v>740</v>
+      <c r="A95" s="94" t="s">
+        <v>737</v>
       </c>
       <c r="B95" s="15" t="s">
         <v>356</v>
@@ -14514,7 +14503,7 @@
       <c r="N95" s="27"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="95"/>
+      <c r="A96" s="94"/>
       <c r="B96" s="15" t="s">
         <v>315</v>
       </c>
@@ -14534,8 +14523,8 @@
       <c r="N96" s="27"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="95" t="s">
-        <v>741</v>
+      <c r="A97" s="94" t="s">
+        <v>738</v>
       </c>
       <c r="B97" s="15" t="s">
         <v>299</v>
@@ -14556,7 +14545,7 @@
       <c r="N97" s="27"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="94"/>
+      <c r="A98" s="93"/>
       <c r="B98" s="15" t="s">
         <v>277</v>
       </c>
@@ -14576,7 +14565,7 @@
       <c r="N98" s="27"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="92" t="s">
+      <c r="A99" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B99" s="53"/>
@@ -14594,8 +14583,8 @@
       <c r="N99" s="27"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="95" t="s">
-        <v>743</v>
+      <c r="A100" s="94" t="s">
+        <v>740</v>
       </c>
       <c r="B100" s="15" t="s">
         <v>442</v>
@@ -14616,12 +14605,12 @@
       <c r="N100" s="27"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="94"/>
+      <c r="A101" s="93"/>
       <c r="B101" s="15" t="s">
         <v>467</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -14636,7 +14625,7 @@
       <c r="N101" s="27"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="94"/>
+      <c r="A102" s="93"/>
       <c r="B102" s="15" t="s">
         <v>464</v>
       </c>
@@ -14656,7 +14645,7 @@
       <c r="N102" s="27"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="94"/>
+      <c r="A103" s="93"/>
       <c r="B103" s="15" t="s">
         <v>408</v>
       </c>
@@ -14676,7 +14665,7 @@
       <c r="N103" s="27"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="94"/>
+      <c r="A104" s="93"/>
       <c r="B104" s="15" t="s">
         <v>692</v>
       </c>
@@ -14696,7 +14685,7 @@
       <c r="N104" s="27"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="94"/>
+      <c r="A105" s="93"/>
       <c r="B105" s="15" t="s">
         <v>691</v>
       </c>
@@ -14716,7 +14705,7 @@
       <c r="N105" s="27"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="94"/>
+      <c r="A106" s="93"/>
       <c r="B106" s="15" t="s">
         <v>437</v>
       </c>
@@ -14736,7 +14725,7 @@
       <c r="N106" s="27"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="94"/>
+      <c r="A107" s="93"/>
       <c r="B107" s="15" t="s">
         <v>416</v>
       </c>
@@ -14756,7 +14745,7 @@
       <c r="N107" s="27"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="94"/>
+      <c r="A108" s="93"/>
       <c r="B108" s="15" t="s">
         <v>292</v>
       </c>
@@ -14776,7 +14765,7 @@
       <c r="N108" s="27"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="94"/>
+      <c r="A109" s="93"/>
       <c r="B109" s="15" t="s">
         <v>378</v>
       </c>
@@ -14796,7 +14785,7 @@
       <c r="N109" s="27"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="94"/>
+      <c r="A110" s="93"/>
       <c r="B110" s="15" t="s">
         <v>287</v>
       </c>
@@ -14816,7 +14805,7 @@
       <c r="N110" s="27"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="94"/>
+      <c r="A111" s="93"/>
       <c r="B111" s="15" t="s">
         <v>481</v>
       </c>
@@ -14836,7 +14825,7 @@
       <c r="N111" s="27"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="94"/>
+      <c r="A112" s="93"/>
       <c r="B112" s="15" t="s">
         <v>271</v>
       </c>
@@ -14856,7 +14845,7 @@
       <c r="N112" s="27"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="94"/>
+      <c r="A113" s="93"/>
       <c r="B113" s="15" t="s">
         <v>422</v>
       </c>
@@ -14876,7 +14865,7 @@
       <c r="N113" s="27"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="94"/>
+      <c r="A114" s="93"/>
       <c r="B114" s="15" t="s">
         <v>282</v>
       </c>
@@ -14896,8 +14885,8 @@
       <c r="N114" s="27"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="95" t="s">
-        <v>744</v>
+      <c r="A115" s="94" t="s">
+        <v>741</v>
       </c>
       <c r="B115" s="15" t="s">
         <v>390</v>
@@ -14918,7 +14907,7 @@
       <c r="N115" s="27"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="94"/>
+      <c r="A116" s="93"/>
       <c r="B116" s="15" t="s">
         <v>447</v>
       </c>
@@ -14938,7 +14927,7 @@
       <c r="N116" s="27"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="94"/>
+      <c r="A117" s="93"/>
       <c r="B117" s="15" t="s">
         <v>402</v>
       </c>
@@ -14958,7 +14947,7 @@
       <c r="N117" s="27"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="94"/>
+      <c r="A118" s="93"/>
       <c r="B118" s="15" t="s">
         <v>435</v>
       </c>
@@ -14978,7 +14967,7 @@
       <c r="N118" s="27"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="94"/>
+      <c r="A119" s="93"/>
       <c r="B119" s="15" t="s">
         <v>427</v>
       </c>
@@ -14998,7 +14987,7 @@
       <c r="N119" s="27"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="94"/>
+      <c r="A120" s="93"/>
       <c r="B120" s="15" t="s">
         <v>488</v>
       </c>
@@ -15018,7 +15007,7 @@
       <c r="N120" s="27"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="94"/>
+      <c r="A121" s="93"/>
       <c r="B121" s="15" t="s">
         <v>493</v>
       </c>
@@ -15038,7 +15027,7 @@
       <c r="N121" s="27"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="94"/>
+      <c r="A122" s="93"/>
       <c r="B122" s="15" t="s">
         <v>452</v>
       </c>
@@ -15058,7 +15047,7 @@
       <c r="N122" s="27"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="94"/>
+      <c r="A123" s="93"/>
       <c r="B123" s="15" t="s">
         <v>268</v>
       </c>
@@ -15078,8 +15067,8 @@
       <c r="N123" s="27"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="95" t="s">
-        <v>745</v>
+      <c r="A124" s="94" t="s">
+        <v>742</v>
       </c>
       <c r="B124" s="15" t="s">
         <v>492</v>
@@ -15100,7 +15089,7 @@
       <c r="N124" s="27"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="94"/>
+      <c r="A125" s="93"/>
       <c r="B125" s="15" t="s">
         <v>484</v>
       </c>
@@ -15120,7 +15109,7 @@
       <c r="N125" s="27"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="94"/>
+      <c r="A126" s="93"/>
       <c r="B126" s="15" t="s">
         <v>297</v>
       </c>
@@ -15140,7 +15129,7 @@
       <c r="N126" s="27"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="94"/>
+      <c r="A127" s="93"/>
       <c r="B127" s="15" t="s">
         <v>468</v>
       </c>
@@ -15160,7 +15149,7 @@
       <c r="N127" s="27"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="94"/>
+      <c r="A128" s="93"/>
       <c r="B128" s="15" t="s">
         <v>283</v>
       </c>
@@ -15180,7 +15169,7 @@
       <c r="N128" s="27"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="94"/>
+      <c r="A129" s="93"/>
       <c r="B129" s="15" t="s">
         <v>288</v>
       </c>
@@ -15200,7 +15189,7 @@
       <c r="N129" s="27"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="94"/>
+      <c r="A130" s="93"/>
       <c r="B130" s="15" t="s">
         <v>471</v>
       </c>
@@ -15220,7 +15209,7 @@
       <c r="N130" s="27"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="94"/>
+      <c r="A131" s="93"/>
       <c r="B131" s="15" t="s">
         <v>270</v>
       </c>
@@ -15240,7 +15229,7 @@
       <c r="N131" s="27"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="94"/>
+      <c r="A132" s="93"/>
       <c r="B132" s="15" t="s">
         <v>317</v>
       </c>
@@ -15260,7 +15249,7 @@
       <c r="N132" s="27"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="94"/>
+      <c r="A133" s="93"/>
       <c r="B133" s="15" t="s">
         <v>303</v>
       </c>
@@ -15280,7 +15269,7 @@
       <c r="N133" s="27"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="94"/>
+      <c r="A134" s="93"/>
       <c r="B134" s="15" t="s">
         <v>307</v>
       </c>
@@ -15300,7 +15289,7 @@
       <c r="N134" s="27"/>
     </row>
     <row r="135" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="94"/>
+      <c r="A135" s="93"/>
       <c r="B135" s="15" t="s">
         <v>247</v>
       </c>
@@ -15320,8 +15309,8 @@
       <c r="N135" s="27"/>
     </row>
     <row r="136" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="95" t="s">
-        <v>746</v>
+      <c r="A136" s="94" t="s">
+        <v>743</v>
       </c>
       <c r="B136" s="15" t="s">
         <v>295</v>
@@ -15342,7 +15331,7 @@
       <c r="N136" s="27"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="94"/>
+      <c r="A137" s="93"/>
       <c r="B137" s="15" t="s">
         <v>246</v>
       </c>
@@ -15362,7 +15351,7 @@
       <c r="N137" s="27"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="94"/>
+      <c r="A138" s="93"/>
       <c r="B138" s="15" t="s">
         <v>343</v>
       </c>
@@ -15382,7 +15371,7 @@
       <c r="N138" s="27"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="94"/>
+      <c r="A139" s="93"/>
       <c r="B139" s="15" t="s">
         <v>329</v>
       </c>
@@ -15402,7 +15391,7 @@
       <c r="N139" s="27"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="94"/>
+      <c r="A140" s="93"/>
       <c r="B140" s="15" t="s">
         <v>279</v>
       </c>
@@ -15422,7 +15411,7 @@
       <c r="N140" s="27"/>
     </row>
     <row r="141" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="94"/>
+      <c r="A141" s="93"/>
       <c r="B141" s="15" t="s">
         <v>328</v>
       </c>
@@ -15442,7 +15431,7 @@
       <c r="N141" s="27"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="94"/>
+      <c r="A142" s="93"/>
       <c r="B142" s="15" t="s">
         <v>272</v>
       </c>
@@ -15463,7 +15452,7 @@
     </row>
     <row r="143" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="17" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="B143" s="15" t="s">
         <v>280</v>
@@ -15484,8 +15473,8 @@
       <c r="N143" s="27"/>
     </row>
     <row r="144" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="95" t="s">
-        <v>748</v>
+      <c r="A144" s="94" t="s">
+        <v>745</v>
       </c>
       <c r="B144" s="15" t="s">
         <v>433</v>
@@ -15506,7 +15495,7 @@
       <c r="N144" s="27"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="94"/>
+      <c r="A145" s="93"/>
       <c r="B145" s="15" t="s">
         <v>338</v>
       </c>
@@ -15526,7 +15515,7 @@
       <c r="N145" s="27"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="94"/>
+      <c r="A146" s="93"/>
       <c r="B146" s="15" t="s">
         <v>301</v>
       </c>
@@ -15546,7 +15535,7 @@
       <c r="N146" s="27"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="94"/>
+      <c r="A147" s="93"/>
       <c r="B147" s="15" t="s">
         <v>432</v>
       </c>
@@ -15566,7 +15555,7 @@
       <c r="N147" s="27"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="94"/>
+      <c r="A148" s="93"/>
       <c r="B148" s="15" t="s">
         <v>264</v>
       </c>
@@ -15586,7 +15575,7 @@
       <c r="N148" s="27"/>
     </row>
     <row r="149" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="92" t="s">
+      <c r="A149" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B149" s="53"/>
@@ -15604,8 +15593,8 @@
       <c r="N149" s="27"/>
     </row>
     <row r="150" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="95" t="s">
-        <v>750</v>
+      <c r="A150" s="94" t="s">
+        <v>747</v>
       </c>
       <c r="B150" s="30" t="s">
         <v>363</v>
@@ -15626,7 +15615,7 @@
       <c r="N150" s="27"/>
     </row>
     <row r="151" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="95"/>
+      <c r="A151" s="94"/>
       <c r="B151" s="30" t="s">
         <v>423</v>
       </c>
@@ -15646,7 +15635,7 @@
       <c r="N151" s="27"/>
     </row>
     <row r="152" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="95"/>
+      <c r="A152" s="94"/>
       <c r="B152" s="30" t="s">
         <v>340</v>
       </c>
@@ -15666,7 +15655,7 @@
       <c r="N152" s="27"/>
     </row>
     <row r="153" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="95"/>
+      <c r="A153" s="94"/>
       <c r="B153" s="30" t="s">
         <v>310</v>
       </c>
@@ -15686,7 +15675,7 @@
       <c r="N153" s="27"/>
     </row>
     <row r="154" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="95"/>
+      <c r="A154" s="94"/>
       <c r="B154" s="30" t="s">
         <v>276</v>
       </c>
@@ -15706,7 +15695,7 @@
       <c r="N154" s="27"/>
     </row>
     <row r="155" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="95"/>
+      <c r="A155" s="94"/>
       <c r="B155" s="30" t="s">
         <v>382</v>
       </c>
@@ -15726,8 +15715,8 @@
       <c r="N155" s="27"/>
     </row>
     <row r="156" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="95" t="s">
-        <v>751</v>
+      <c r="A156" s="94" t="s">
+        <v>748</v>
       </c>
       <c r="B156" s="30" t="s">
         <v>258</v>
@@ -15748,7 +15737,7 @@
       <c r="N156" s="27"/>
     </row>
     <row r="157" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="95"/>
+      <c r="A157" s="94"/>
       <c r="B157" s="30" t="s">
         <v>306</v>
       </c>
@@ -15768,7 +15757,7 @@
       <c r="N157" s="27"/>
     </row>
     <row r="158" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="95"/>
+      <c r="A158" s="94"/>
       <c r="B158" s="30" t="s">
         <v>278</v>
       </c>
@@ -15788,7 +15777,7 @@
       <c r="N158" s="27"/>
     </row>
     <row r="159" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="95"/>
+      <c r="A159" s="94"/>
       <c r="B159" s="30" t="s">
         <v>265</v>
       </c>
@@ -15808,7 +15797,7 @@
       <c r="N159" s="27"/>
     </row>
     <row r="160" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="95"/>
+      <c r="A160" s="94"/>
       <c r="B160" s="30" t="s">
         <v>417</v>
       </c>
@@ -15828,7 +15817,7 @@
       <c r="N160" s="27"/>
     </row>
     <row r="161" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="95"/>
+      <c r="A161" s="94"/>
       <c r="B161" s="30" t="s">
         <v>332</v>
       </c>
@@ -15848,8 +15837,8 @@
       <c r="N161" s="27"/>
     </row>
     <row r="162" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="95" t="s">
-        <v>752</v>
+      <c r="A162" s="94" t="s">
+        <v>749</v>
       </c>
       <c r="B162" s="30" t="s">
         <v>483</v>
@@ -15870,12 +15859,12 @@
       <c r="N162" s="27"/>
     </row>
     <row r="163" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="95"/>
+      <c r="A163" s="94"/>
       <c r="B163" s="30" t="s">
         <v>701</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D163" s="4"/>
       <c r="E163" s="4"/>
@@ -15890,7 +15879,7 @@
       <c r="N163" s="27"/>
     </row>
     <row r="164" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="92" t="s">
+      <c r="A164" s="95" t="s">
         <v>595</v>
       </c>
       <c r="B164" s="53"/>
@@ -15908,7 +15897,7 @@
       <c r="N164" s="27"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="94" t="s">
+      <c r="A165" s="93" t="s">
         <v>252</v>
       </c>
       <c r="B165" s="15" t="s">
@@ -15930,7 +15919,7 @@
       <c r="N165" s="27"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="94"/>
+      <c r="A166" s="93"/>
       <c r="B166" s="15" t="s">
         <v>294</v>
       </c>
@@ -15950,7 +15939,7 @@
       <c r="N166" s="27"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="94"/>
+      <c r="A167" s="93"/>
       <c r="B167" s="15" t="s">
         <v>294</v>
       </c>
@@ -15970,8 +15959,8 @@
       <c r="N167" s="27"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="94" t="s">
-        <v>768</v>
+      <c r="A168" s="93" t="s">
+        <v>765</v>
       </c>
       <c r="B168" s="15" t="s">
         <v>465</v>
@@ -15992,7 +15981,7 @@
       <c r="N168" s="27"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="94"/>
+      <c r="A169" s="93"/>
       <c r="B169" s="15" t="s">
         <v>428</v>
       </c>
@@ -16012,14 +16001,14 @@
       <c r="N169" s="27"/>
     </row>
     <row r="170" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="94" t="s">
-        <v>767</v>
+      <c r="A170" s="93" t="s">
+        <v>764</v>
       </c>
       <c r="B170" s="15" t="s">
         <v>446</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -16034,12 +16023,12 @@
       <c r="N170" s="27"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="94"/>
+      <c r="A171" s="93"/>
       <c r="B171" s="15" t="s">
         <v>412</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -16054,8 +16043,8 @@
       <c r="N171" s="27"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="94" t="s">
-        <v>766</v>
+      <c r="A172" s="93" t="s">
+        <v>763</v>
       </c>
       <c r="B172" s="15" t="s">
         <v>285</v>
@@ -16076,7 +16065,7 @@
       <c r="N172" s="27"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="94"/>
+      <c r="A173" s="93"/>
       <c r="B173" s="15" t="s">
         <v>369</v>
       </c>
@@ -16096,14 +16085,14 @@
       <c r="N173" s="27"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="94" t="s">
-        <v>765</v>
+      <c r="A174" s="93" t="s">
+        <v>762</v>
       </c>
       <c r="B174" s="15" t="s">
         <v>695</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -16118,12 +16107,12 @@
       <c r="N174" s="27"/>
     </row>
     <row r="175" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="94"/>
+      <c r="A175" s="93"/>
       <c r="B175" s="15" t="s">
         <v>696</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -16138,12 +16127,12 @@
       <c r="N175" s="27"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="94"/>
+      <c r="A176" s="93"/>
       <c r="B176" s="15" t="s">
         <v>697</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -16158,12 +16147,12 @@
       <c r="N176" s="27"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="94"/>
+      <c r="A177" s="93"/>
       <c r="B177" s="15" t="s">
         <v>698</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -16178,12 +16167,12 @@
       <c r="N177" s="27"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="94"/>
+      <c r="A178" s="93"/>
       <c r="B178" s="15" t="s">
         <v>699</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -16198,8 +16187,8 @@
       <c r="N178" s="27"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="94" t="s">
-        <v>764</v>
+      <c r="A179" s="93" t="s">
+        <v>761</v>
       </c>
       <c r="B179" s="15" t="s">
         <v>350</v>
@@ -16220,7 +16209,7 @@
       <c r="N179" s="27"/>
     </row>
     <row r="180" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="94"/>
+      <c r="A180" s="93"/>
       <c r="B180" s="15" t="s">
         <v>344</v>
       </c>
@@ -16240,14 +16229,14 @@
       <c r="N180" s="27"/>
     </row>
     <row r="181" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="94" t="s">
-        <v>763</v>
+      <c r="A181" s="93" t="s">
+        <v>760</v>
       </c>
       <c r="B181" s="15" t="s">
         <v>337</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -16262,12 +16251,12 @@
       <c r="N181" s="27"/>
     </row>
     <row r="182" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="94"/>
+      <c r="A182" s="93"/>
       <c r="B182" s="15" t="s">
         <v>296</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -16282,12 +16271,12 @@
       <c r="N182" s="27"/>
     </row>
     <row r="183" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="94"/>
+      <c r="A183" s="93"/>
       <c r="B183" s="15" t="s">
         <v>316</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -16302,7 +16291,7 @@
       <c r="N183" s="27"/>
     </row>
     <row r="184" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="92" t="s">
+      <c r="A184" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B184" s="53"/>
@@ -16320,8 +16309,8 @@
       <c r="N184" s="27"/>
     </row>
     <row r="185" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="94" t="s">
-        <v>775</v>
+      <c r="A185" s="93" t="s">
+        <v>772</v>
       </c>
       <c r="B185" s="15" t="s">
         <v>243</v>
@@ -16342,7 +16331,7 @@
       <c r="N185" s="27"/>
     </row>
     <row r="186" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="94"/>
+      <c r="A186" s="93"/>
       <c r="B186" s="15" t="s">
         <v>527</v>
       </c>
@@ -16362,8 +16351,8 @@
       <c r="N186" s="27"/>
     </row>
     <row r="187" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="94" t="s">
-        <v>776</v>
+      <c r="A187" s="93" t="s">
+        <v>773</v>
       </c>
       <c r="B187" s="15" t="s">
         <v>550</v>
@@ -16384,7 +16373,7 @@
       <c r="N187" s="27"/>
     </row>
     <row r="188" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="94"/>
+      <c r="A188" s="93"/>
       <c r="B188" s="15" t="s">
         <v>513</v>
       </c>
@@ -16404,7 +16393,7 @@
       <c r="N188" s="27"/>
     </row>
     <row r="189" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="94"/>
+      <c r="A189" s="93"/>
       <c r="B189" s="15" t="s">
         <v>518</v>
       </c>
@@ -16424,7 +16413,7 @@
       <c r="N189" s="27"/>
     </row>
     <row r="190" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="94"/>
+      <c r="A190" s="93"/>
       <c r="B190" s="15" t="s">
         <v>525</v>
       </c>
@@ -16444,7 +16433,7 @@
       <c r="N190" s="27"/>
     </row>
     <row r="191" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="94"/>
+      <c r="A191" s="93"/>
       <c r="B191" s="15" t="s">
         <v>499</v>
       </c>
@@ -16464,7 +16453,7 @@
       <c r="N191" s="27"/>
     </row>
     <row r="192" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="94"/>
+      <c r="A192" s="93"/>
       <c r="B192" s="15" t="s">
         <v>516</v>
       </c>
@@ -16484,14 +16473,14 @@
       <c r="N192" s="27"/>
     </row>
     <row r="193" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="94" t="s">
+      <c r="A193" s="93" t="s">
         <v>715</v>
       </c>
       <c r="B193" s="15" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -16506,12 +16495,12 @@
       <c r="N193" s="27"/>
     </row>
     <row r="194" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="94"/>
+      <c r="A194" s="93"/>
       <c r="B194" s="15" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -16526,12 +16515,12 @@
       <c r="N194" s="27"/>
     </row>
     <row r="195" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="94"/>
+      <c r="A195" s="93"/>
       <c r="B195" s="15" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="D195" s="4"/>
       <c r="E195" s="4"/>
@@ -16546,14 +16535,14 @@
       <c r="N195" s="27"/>
     </row>
     <row r="196" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="93" t="s">
+      <c r="A196" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="B196" s="56"/>
-      <c r="C196" s="56"/>
-      <c r="D196" s="56"/>
-      <c r="E196" s="56"/>
-      <c r="F196" s="57"/>
+      <c r="B196" s="87"/>
+      <c r="C196" s="87"/>
+      <c r="D196" s="87"/>
+      <c r="E196" s="87"/>
+      <c r="F196" s="88"/>
       <c r="G196" s="48"/>
       <c r="H196" s="48"/>
       <c r="I196" s="48"/>
@@ -16564,14 +16553,14 @@
       <c r="N196" s="29"/>
     </row>
     <row r="197" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="58" t="s">
+      <c r="A197" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="B197" s="59"/>
-      <c r="C197" s="59"/>
-      <c r="D197" s="59"/>
-      <c r="E197" s="59"/>
-      <c r="F197" s="60"/>
+      <c r="B197" s="90"/>
+      <c r="C197" s="90"/>
+      <c r="D197" s="90"/>
+      <c r="E197" s="90"/>
+      <c r="F197" s="91"/>
       <c r="G197" s="49"/>
       <c r="H197" s="49"/>
       <c r="I197" s="49"/>
@@ -16615,6 +16604,49 @@
     </row>
   </sheetData>
   <mergeCells count="59">
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A181:A183"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A48:A58"/>
+    <mergeCell ref="A60:A74"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A197:F197"/>
+    <mergeCell ref="A196:F196"/>
+    <mergeCell ref="A184:F184"/>
+    <mergeCell ref="A164:F164"/>
+    <mergeCell ref="A149:F149"/>
+    <mergeCell ref="A185:A186"/>
+    <mergeCell ref="A187:A192"/>
+    <mergeCell ref="A193:A195"/>
+    <mergeCell ref="A168:A169"/>
+    <mergeCell ref="A150:A155"/>
+    <mergeCell ref="A156:A161"/>
+    <mergeCell ref="A162:A163"/>
+    <mergeCell ref="A174:A178"/>
+    <mergeCell ref="A179:A180"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="A124:A135"/>
+    <mergeCell ref="A136:A142"/>
+    <mergeCell ref="A144:A148"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A100:A114"/>
+    <mergeCell ref="A115:A123"/>
+    <mergeCell ref="A165:A167"/>
+    <mergeCell ref="A21:A28"/>
+    <mergeCell ref="A35:A46"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A30:A33"/>
     <mergeCell ref="A8:A19"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A6:A7"/>
@@ -16631,58 +16663,18 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A21:A28"/>
-    <mergeCell ref="A35:A46"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A174:A178"/>
-    <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="A124:A135"/>
-    <mergeCell ref="A136:A142"/>
-    <mergeCell ref="A144:A148"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A100:A114"/>
-    <mergeCell ref="A115:A123"/>
-    <mergeCell ref="A48:A58"/>
-    <mergeCell ref="A60:A74"/>
-    <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A197:F197"/>
-    <mergeCell ref="A196:F196"/>
-    <mergeCell ref="A184:F184"/>
-    <mergeCell ref="A164:F164"/>
-    <mergeCell ref="A149:F149"/>
-    <mergeCell ref="A185:A186"/>
-    <mergeCell ref="A187:A192"/>
-    <mergeCell ref="A193:A195"/>
-    <mergeCell ref="A168:A169"/>
-    <mergeCell ref="A150:A155"/>
-    <mergeCell ref="A156:A161"/>
-    <mergeCell ref="A162:A163"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="A181:A183"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A47:F47"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="63" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C9DEE9D-E018-49EA-AD01-F6853D9BB462}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:N69"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -19155,22 +19147,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81" t="s">
-        <v>718</v>
-      </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32"/>
@@ -19186,13 +19176,13 @@
       <c r="K3" s="32"/>
       <c r="L3" s="32"/>
       <c r="M3" s="33" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="N3" s="51"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="38" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="N4" s="51"/>
     </row>
@@ -19201,74 +19191,74 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="64" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="57" t="s">
+        <v>716</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>717</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>718</v>
+      </c>
+      <c r="E6" s="59" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="F6" s="55" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="G6" s="55" t="s">
+        <v>669</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>673</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>680</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>681</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>682</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>700</v>
+      </c>
+      <c r="M6" s="55" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="N6" s="71" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="79" t="s">
-        <v>723</v>
-      </c>
-      <c r="G6" s="79" t="s">
-        <v>669</v>
-      </c>
-      <c r="H6" s="79" t="s">
-        <v>673</v>
-      </c>
-      <c r="I6" s="79" t="s">
-        <v>680</v>
-      </c>
-      <c r="J6" s="79" t="s">
-        <v>681</v>
-      </c>
-      <c r="K6" s="79" t="s">
-        <v>682</v>
-      </c>
-      <c r="L6" s="79" t="s">
-        <v>700</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>724</v>
-      </c>
-      <c r="N6" s="82" t="s">
-        <v>725</v>
-      </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="83"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="72"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="96" t="s">
-        <v>805</v>
+      <c r="A8" s="92" t="s">
+        <v>802</v>
       </c>
       <c r="B8" s="24">
         <v>7425</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -19283,12 +19273,12 @@
       <c r="N8" s="28"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="94"/>
+      <c r="A9" s="93"/>
       <c r="B9" s="15">
         <v>7427</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -19303,12 +19293,12 @@
       <c r="N9" s="27"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="94"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="18">
         <v>7429</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
@@ -19323,12 +19313,12 @@
       <c r="N10" s="27"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="94"/>
+      <c r="A11" s="93"/>
       <c r="B11" s="18">
         <v>7431</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
@@ -19343,12 +19333,12 @@
       <c r="N11" s="27"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="94"/>
+      <c r="A12" s="93"/>
       <c r="B12" s="18">
         <v>7433</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
@@ -19363,12 +19353,12 @@
       <c r="N12" s="27"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
+      <c r="A13" s="93"/>
       <c r="B13" s="18">
         <v>7435</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
@@ -19383,12 +19373,12 @@
       <c r="N13" s="27"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="94"/>
+      <c r="A14" s="93"/>
       <c r="B14" s="18">
         <v>7437</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
@@ -19403,12 +19393,12 @@
       <c r="N14" s="27"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="94"/>
+      <c r="A15" s="93"/>
       <c r="B15" s="18">
         <v>7439</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
@@ -19423,12 +19413,12 @@
       <c r="N15" s="27"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="94"/>
+      <c r="A16" s="93"/>
       <c r="B16" s="18">
         <v>7441</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19"/>
@@ -19443,12 +19433,12 @@
       <c r="N16" s="27"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="94"/>
+      <c r="A17" s="93"/>
       <c r="B17" s="18">
         <v>7426</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
@@ -19463,12 +19453,12 @@
       <c r="N17" s="27"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="94"/>
+      <c r="A18" s="93"/>
       <c r="B18" s="18">
         <v>7430</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
@@ -19483,12 +19473,12 @@
       <c r="N18" s="27"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="94"/>
+      <c r="A19" s="93"/>
       <c r="B19" s="18">
         <v>7432</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19"/>
@@ -19503,12 +19493,12 @@
       <c r="N19" s="27"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="94"/>
+      <c r="A20" s="93"/>
       <c r="B20" s="18">
         <v>7434</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
@@ -19523,12 +19513,12 @@
       <c r="N20" s="27"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="94"/>
+      <c r="A21" s="93"/>
       <c r="B21" s="18">
         <v>7436</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
@@ -19543,12 +19533,12 @@
       <c r="N21" s="27"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="94"/>
+      <c r="A22" s="93"/>
       <c r="B22" s="18">
         <v>7438</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -19563,12 +19553,12 @@
       <c r="N22" s="27"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="94"/>
+      <c r="A23" s="93"/>
       <c r="B23" s="18">
         <v>7440</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -19583,12 +19573,12 @@
       <c r="N23" s="27"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="94"/>
+      <c r="A24" s="93"/>
       <c r="B24" s="18">
         <v>7442</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -19603,12 +19593,12 @@
       <c r="N24" s="27"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="94"/>
+      <c r="A25" s="93"/>
       <c r="B25" s="18">
         <v>7443</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -19623,12 +19613,12 @@
       <c r="N25" s="27"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="94"/>
+      <c r="A26" s="93"/>
       <c r="B26" s="18">
         <v>7445</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
@@ -19643,12 +19633,12 @@
       <c r="N26" s="27"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="94"/>
+      <c r="A27" s="93"/>
       <c r="B27" s="18">
         <v>7444</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
@@ -19663,12 +19653,12 @@
       <c r="N27" s="27"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="94"/>
+      <c r="A28" s="93"/>
       <c r="B28" s="18">
         <v>7446</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -19683,12 +19673,12 @@
       <c r="N28" s="27"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="94"/>
+      <c r="A29" s="93"/>
       <c r="B29" s="18">
         <v>7448</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
@@ -19703,12 +19693,12 @@
       <c r="N29" s="27"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="94"/>
+      <c r="A30" s="93"/>
       <c r="B30" s="18">
         <v>7450</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
@@ -19723,7 +19713,7 @@
       <c r="N30" s="27"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="92" t="s">
+      <c r="A31" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B31" s="53"/>
@@ -19741,8 +19731,8 @@
       <c r="N31" s="27"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="94" t="s">
-        <v>806</v>
+      <c r="A32" s="93" t="s">
+        <v>803</v>
       </c>
       <c r="B32" s="15" t="s">
         <v>575</v>
@@ -19763,7 +19753,7 @@
       <c r="N32" s="27"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="94"/>
+      <c r="A33" s="93"/>
       <c r="B33" s="15" t="s">
         <v>577</v>
       </c>
@@ -19783,7 +19773,7 @@
       <c r="N33" s="27"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="94"/>
+      <c r="A34" s="93"/>
       <c r="B34" s="15" t="s">
         <v>574</v>
       </c>
@@ -19803,7 +19793,7 @@
       <c r="N34" s="27"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="94"/>
+      <c r="A35" s="93"/>
       <c r="B35" s="15" t="s">
         <v>552</v>
       </c>
@@ -19823,7 +19813,7 @@
       <c r="N35" s="27"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="94"/>
+      <c r="A36" s="93"/>
       <c r="B36" s="15" t="s">
         <v>431</v>
       </c>
@@ -19843,7 +19833,7 @@
       <c r="N36" s="27"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="94"/>
+      <c r="A37" s="93"/>
       <c r="B37" s="15" t="s">
         <v>436</v>
       </c>
@@ -19863,7 +19853,7 @@
       <c r="N37" s="27"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="94"/>
+      <c r="A38" s="93"/>
       <c r="B38" s="15" t="s">
         <v>505</v>
       </c>
@@ -19883,7 +19873,7 @@
       <c r="N38" s="27"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="94"/>
+      <c r="A39" s="93"/>
       <c r="B39" s="15" t="s">
         <v>566</v>
       </c>
@@ -19903,7 +19893,7 @@
       <c r="N39" s="27"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="92" t="s">
+      <c r="A40" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B40" s="53"/>
@@ -19921,8 +19911,8 @@
       <c r="N40" s="27"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="95" t="s">
-        <v>808</v>
+      <c r="A41" s="94" t="s">
+        <v>805</v>
       </c>
       <c r="B41" s="30" t="s">
         <v>556</v>
@@ -19943,7 +19933,7 @@
       <c r="N41" s="27"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="95"/>
+      <c r="A42" s="94"/>
       <c r="B42" s="30" t="s">
         <v>581</v>
       </c>
@@ -19963,12 +19953,12 @@
       <c r="N42" s="27"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="95"/>
+      <c r="A43" s="94"/>
       <c r="B43" s="30" t="s">
         <v>590</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -19983,7 +19973,7 @@
       <c r="N43" s="27"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="95"/>
+      <c r="A44" s="94"/>
       <c r="B44" s="30" t="s">
         <v>548</v>
       </c>
@@ -20003,7 +19993,7 @@
       <c r="N44" s="27"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="95"/>
+      <c r="A45" s="94"/>
       <c r="B45" s="30" t="s">
         <v>583</v>
       </c>
@@ -20023,7 +20013,7 @@
       <c r="N45" s="27"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="95"/>
+      <c r="A46" s="94"/>
       <c r="B46" s="30" t="s">
         <v>453</v>
       </c>
@@ -20043,7 +20033,7 @@
       <c r="N46" s="27"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="95"/>
+      <c r="A47" s="94"/>
       <c r="B47" s="30" t="s">
         <v>671</v>
       </c>
@@ -20063,7 +20053,7 @@
       <c r="N47" s="27"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="95"/>
+      <c r="A48" s="94"/>
       <c r="B48" s="30" t="s">
         <v>582</v>
       </c>
@@ -20083,7 +20073,7 @@
       <c r="N48" s="27"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="95"/>
+      <c r="A49" s="94"/>
       <c r="B49" s="30" t="s">
         <v>553</v>
       </c>
@@ -20103,7 +20093,7 @@
       <c r="N49" s="27"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="95"/>
+      <c r="A50" s="94"/>
       <c r="B50" s="30" t="s">
         <v>573</v>
       </c>
@@ -20123,7 +20113,7 @@
       <c r="N50" s="27"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="92" t="s">
+      <c r="A51" s="95" t="s">
         <v>595</v>
       </c>
       <c r="B51" s="53"/>
@@ -20141,8 +20131,8 @@
       <c r="N51" s="27"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="94" t="s">
-        <v>810</v>
+      <c r="A52" s="93" t="s">
+        <v>807</v>
       </c>
       <c r="B52" s="30" t="s">
         <v>352</v>
@@ -20163,7 +20153,7 @@
       <c r="N52" s="27"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="94"/>
+      <c r="A53" s="93"/>
       <c r="B53" s="30" t="s">
         <v>571</v>
       </c>
@@ -20183,7 +20173,7 @@
       <c r="N53" s="27"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="94"/>
+      <c r="A54" s="93"/>
       <c r="B54" s="30" t="s">
         <v>392</v>
       </c>
@@ -20203,7 +20193,7 @@
       <c r="N54" s="27"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="94"/>
+      <c r="A55" s="93"/>
       <c r="B55" s="30" t="s">
         <v>429</v>
       </c>
@@ -20223,12 +20213,12 @@
       <c r="N55" s="27"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="94"/>
+      <c r="A56" s="93"/>
       <c r="B56" s="30" t="s">
         <v>672</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -20243,7 +20233,7 @@
       <c r="N56" s="27"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="92" t="s">
+      <c r="A57" s="95" t="s">
         <v>135</v>
       </c>
       <c r="B57" s="53"/>
@@ -20261,8 +20251,8 @@
       <c r="N57" s="27"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="94" t="s">
-        <v>811</v>
+      <c r="A58" s="93" t="s">
+        <v>808</v>
       </c>
       <c r="B58" s="15" t="s">
         <v>555</v>
@@ -20283,9 +20273,9 @@
       <c r="N58" s="27"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="94"/>
+      <c r="A59" s="93"/>
       <c r="B59" s="15" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>683</v>
@@ -20303,9 +20293,9 @@
       <c r="N59" s="27"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="94"/>
+      <c r="A60" s="93"/>
       <c r="B60" s="15" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>684</v>
@@ -20323,9 +20313,9 @@
       <c r="N60" s="27"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="94"/>
+      <c r="A61" s="93"/>
       <c r="B61" s="15" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C61" s="4" t="s">
         <v>685</v>
@@ -20343,9 +20333,9 @@
       <c r="N61" s="27"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="94"/>
+      <c r="A62" s="93"/>
       <c r="B62" s="15" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>686</v>
@@ -20363,7 +20353,7 @@
       <c r="N62" s="27"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="94"/>
+      <c r="A63" s="93"/>
       <c r="B63" s="15" t="s">
         <v>676</v>
       </c>
@@ -20383,7 +20373,7 @@
       <c r="N63" s="27"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="94"/>
+      <c r="A64" s="93"/>
       <c r="B64" s="15" t="s">
         <v>677</v>
       </c>
@@ -20403,7 +20393,7 @@
       <c r="N64" s="27"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="94"/>
+      <c r="A65" s="93"/>
       <c r="B65" s="15" t="s">
         <v>679</v>
       </c>
@@ -20423,7 +20413,7 @@
       <c r="N65" s="27"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="94"/>
+      <c r="A66" s="93"/>
       <c r="B66" s="15" t="s">
         <v>678</v>
       </c>
@@ -20443,14 +20433,14 @@
       <c r="N66" s="27"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="93" t="s">
+      <c r="A67" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="B67" s="56"/>
-      <c r="C67" s="56"/>
-      <c r="D67" s="56"/>
-      <c r="E67" s="56"/>
-      <c r="F67" s="57"/>
+      <c r="B67" s="87"/>
+      <c r="C67" s="87"/>
+      <c r="D67" s="87"/>
+      <c r="E67" s="87"/>
+      <c r="F67" s="88"/>
       <c r="G67" s="48"/>
       <c r="H67" s="48"/>
       <c r="I67" s="48"/>
@@ -20461,14 +20451,14 @@
       <c r="N67" s="29"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="58" t="s">
+      <c r="A68" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="B68" s="59"/>
-      <c r="C68" s="59"/>
-      <c r="D68" s="59"/>
-      <c r="E68" s="59"/>
-      <c r="F68" s="60"/>
+      <c r="B68" s="90"/>
+      <c r="C68" s="90"/>
+      <c r="D68" s="90"/>
+      <c r="E68" s="90"/>
+      <c r="F68" s="91"/>
       <c r="G68" s="49"/>
       <c r="H68" s="49"/>
       <c r="I68" s="49"/>
@@ -20496,6 +20486,16 @@
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A51:F51"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A67:F67"/>
+    <mergeCell ref="A68:F68"/>
+    <mergeCell ref="A52:A56"/>
+    <mergeCell ref="A58:A66"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A41:A50"/>
     <mergeCell ref="A8:A30"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A6:A7"/>
@@ -20512,25 +20512,18 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A68:F68"/>
-    <mergeCell ref="A52:A56"/>
-    <mergeCell ref="A58:A66"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="A41:A50"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A67:F67"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="63" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33D46427-D453-4EA9-AC82-DC2763457A38}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:N22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
@@ -23003,22 +22996,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81" t="s">
-        <v>717</v>
-      </c>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="A2" s="70"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
+      <c r="L2" s="70"/>
+      <c r="M2" s="70"/>
+      <c r="N2" s="70"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="32"/>
@@ -23034,13 +23025,13 @@
       <c r="K3" s="32"/>
       <c r="L3" s="32"/>
       <c r="M3" s="33" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="N3" s="51"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="38" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="N4" s="51"/>
     </row>
@@ -23049,68 +23040,68 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="90" t="s">
+      <c r="A6" s="64" t="s">
         <v>462</v>
       </c>
-      <c r="B6" s="87" t="s">
+      <c r="B6" s="57" t="s">
+        <v>716</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>717</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>718</v>
+      </c>
+      <c r="E6" s="59" t="s">
         <v>719</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="F6" s="55" t="s">
         <v>720</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="G6" s="55" t="s">
+        <v>669</v>
+      </c>
+      <c r="H6" s="55" t="s">
+        <v>673</v>
+      </c>
+      <c r="I6" s="55" t="s">
+        <v>680</v>
+      </c>
+      <c r="J6" s="55" t="s">
+        <v>681</v>
+      </c>
+      <c r="K6" s="55" t="s">
+        <v>682</v>
+      </c>
+      <c r="L6" s="55" t="s">
+        <v>700</v>
+      </c>
+      <c r="M6" s="55" t="s">
         <v>721</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="N6" s="71" t="s">
         <v>722</v>
       </c>
-      <c r="F6" s="79" t="s">
-        <v>723</v>
-      </c>
-      <c r="G6" s="79" t="s">
-        <v>669</v>
-      </c>
-      <c r="H6" s="79" t="s">
-        <v>673</v>
-      </c>
-      <c r="I6" s="79" t="s">
-        <v>680</v>
-      </c>
-      <c r="J6" s="79" t="s">
-        <v>681</v>
-      </c>
-      <c r="K6" s="79" t="s">
-        <v>682</v>
-      </c>
-      <c r="L6" s="79" t="s">
-        <v>700</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>724</v>
-      </c>
-      <c r="N6" s="82" t="s">
-        <v>725</v>
-      </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="91"/>
-      <c r="B7" s="88"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="83"/>
+      <c r="A7" s="65"/>
+      <c r="B7" s="58"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="60"/>
+      <c r="E7" s="60"/>
+      <c r="F7" s="56"/>
+      <c r="G7" s="56"/>
+      <c r="H7" s="56"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="72"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="96" t="s">
-        <v>819</v>
+      <c r="A8" s="92" t="s">
+        <v>816</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>203</v>
@@ -23131,7 +23122,7 @@
       <c r="N8" s="28"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="95"/>
+      <c r="A9" s="94"/>
       <c r="B9" s="13" t="s">
         <v>584</v>
       </c>
@@ -23151,7 +23142,7 @@
       <c r="N9" s="27"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="95"/>
+      <c r="A10" s="94"/>
       <c r="B10" s="11" t="s">
         <v>215</v>
       </c>
@@ -23171,7 +23162,7 @@
       <c r="N10" s="27"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="95"/>
+      <c r="A11" s="94"/>
       <c r="B11" s="11" t="s">
         <v>578</v>
       </c>
@@ -23191,7 +23182,7 @@
       <c r="N11" s="27"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="95"/>
+      <c r="A12" s="94"/>
       <c r="B12" s="11" t="s">
         <v>220</v>
       </c>
@@ -23211,7 +23202,7 @@
       <c r="N12" s="27"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="95"/>
+      <c r="A13" s="94"/>
       <c r="B13" s="11" t="s">
         <v>455</v>
       </c>
@@ -23231,8 +23222,8 @@
       <c r="N13" s="27"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="95" t="s">
-        <v>820</v>
+      <c r="A14" s="94" t="s">
+        <v>817</v>
       </c>
       <c r="B14" s="11" t="s">
         <v>572</v>
@@ -23253,7 +23244,7 @@
       <c r="N14" s="27"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="95"/>
+      <c r="A15" s="94"/>
       <c r="B15" s="11" t="s">
         <v>226</v>
       </c>
@@ -23273,7 +23264,7 @@
       <c r="N15" s="27"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="95"/>
+      <c r="A16" s="94"/>
       <c r="B16" s="11" t="s">
         <v>210</v>
       </c>
@@ -23293,7 +23284,7 @@
       <c r="N16" s="27"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="95"/>
+      <c r="A17" s="94"/>
       <c r="B17" s="11" t="s">
         <v>204</v>
       </c>
@@ -23314,13 +23305,13 @@
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -23335,14 +23326,14 @@
       <c r="N18" s="27"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="93" t="s">
+      <c r="A19" s="96" t="s">
         <v>135</v>
       </c>
-      <c r="B19" s="56"/>
-      <c r="C19" s="56"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="56"/>
-      <c r="F19" s="57"/>
+      <c r="B19" s="87"/>
+      <c r="C19" s="87"/>
+      <c r="D19" s="87"/>
+      <c r="E19" s="87"/>
+      <c r="F19" s="88"/>
       <c r="G19" s="48"/>
       <c r="H19" s="48"/>
       <c r="I19" s="48"/>
@@ -23353,14 +23344,14 @@
       <c r="N19" s="29"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="58" t="s">
+      <c r="A20" s="89" t="s">
         <v>111</v>
       </c>
-      <c r="B20" s="59"/>
-      <c r="C20" s="59"/>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="60"/>
+      <c r="B20" s="90"/>
+      <c r="C20" s="90"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="90"/>
+      <c r="F20" s="91"/>
       <c r="G20" s="49"/>
       <c r="H20" s="49"/>
       <c r="I20" s="49"/>
@@ -23404,6 +23395,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
@@ -23418,14 +23414,9 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="63" fitToHeight="0" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/temp.xlsx
+++ b/data/temp.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A64C89F-B89F-46A1-819F-034108B60307}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB157B95-5D38-42B2-B06F-CF158A069CB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2956,7 +2956,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3119,6 +3119,99 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3134,134 +3227,32 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="28" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="13" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="19" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="20" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="32" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="14" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6247,22 +6238,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
     </row>
     <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -6295,75 +6286,75 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="58" t="s">
         <v>625</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="58" t="s">
         <v>626</v>
       </c>
-      <c r="E6" s="99" t="s">
+      <c r="E6" s="65" t="s">
         <v>727</v>
       </c>
-      <c r="F6" s="101" t="s">
+      <c r="F6" s="67" t="s">
         <v>728</v>
       </c>
-      <c r="G6" s="84" t="s">
+      <c r="G6" s="58" t="s">
         <v>627</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="54" t="s">
         <v>628</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="54" t="s">
         <v>578</v>
       </c>
-      <c r="J6" s="79" t="s">
+      <c r="J6" s="54" t="s">
         <v>582</v>
       </c>
-      <c r="K6" s="79" t="s">
+      <c r="K6" s="54" t="s">
         <v>588</v>
       </c>
-      <c r="L6" s="79" t="s">
+      <c r="L6" s="54" t="s">
         <v>589</v>
       </c>
-      <c r="M6" s="79" t="s">
+      <c r="M6" s="54" t="s">
         <v>590</v>
       </c>
-      <c r="N6" s="79" t="s">
+      <c r="N6" s="54" t="s">
         <v>608</v>
       </c>
-      <c r="O6" s="79" t="s">
+      <c r="O6" s="54" t="s">
         <v>629</v>
       </c>
-      <c r="P6" s="82" t="s">
+      <c r="P6" s="74" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="90"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="83"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="75"/>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88" t="s">
+      <c r="A8" s="60" t="s">
         <v>150</v>
       </c>
       <c r="B8" s="23" t="s">
@@ -6387,7 +6378,7 @@
       <c r="P8" s="25"/>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="60"/>
+      <c r="A9" s="61"/>
       <c r="B9" s="15" t="s">
         <v>186</v>
       </c>
@@ -6409,7 +6400,7 @@
       <c r="P9" s="14"/>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="60"/>
+      <c r="A10" s="61"/>
       <c r="B10" s="15" t="s">
         <v>284</v>
       </c>
@@ -6431,7 +6422,7 @@
       <c r="P10" s="14"/>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="60"/>
+      <c r="A11" s="61"/>
       <c r="B11" s="15" t="s">
         <v>336</v>
       </c>
@@ -6453,7 +6444,7 @@
       <c r="P11" s="14"/>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="60"/>
+      <c r="A12" s="61"/>
       <c r="B12" s="15" t="s">
         <v>308</v>
       </c>
@@ -6475,7 +6466,7 @@
       <c r="P12" s="14"/>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60"/>
+      <c r="A13" s="61"/>
       <c r="B13" s="15" t="s">
         <v>306</v>
       </c>
@@ -6497,7 +6488,7 @@
       <c r="P13" s="14"/>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="60"/>
+      <c r="A14" s="61"/>
       <c r="B14" s="15" t="s">
         <v>193</v>
       </c>
@@ -6519,7 +6510,7 @@
       <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="60"/>
+      <c r="A15" s="61"/>
       <c r="B15" s="15" t="s">
         <v>383</v>
       </c>
@@ -6561,7 +6552,7 @@
       <c r="P16" s="14"/>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="61" t="s">
+      <c r="A17" s="62" t="s">
         <v>634</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -6585,7 +6576,7 @@
       <c r="P17" s="14"/>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
+      <c r="A18" s="61"/>
       <c r="B18" s="15" t="s">
         <v>368</v>
       </c>
@@ -6607,7 +6598,7 @@
       <c r="P18" s="14"/>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60"/>
+      <c r="A19" s="61"/>
       <c r="B19" s="15" t="s">
         <v>450</v>
       </c>
@@ -6629,7 +6620,7 @@
       <c r="P19" s="14"/>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="60"/>
+      <c r="A20" s="61"/>
       <c r="B20" s="15" t="s">
         <v>205</v>
       </c>
@@ -6671,7 +6662,7 @@
       <c r="P21" s="14"/>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="61" t="s">
+      <c r="A22" s="62" t="s">
         <v>435</v>
       </c>
       <c r="B22" s="15" t="s">
@@ -6695,7 +6686,7 @@
       <c r="P22" s="14"/>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="61"/>
+      <c r="A23" s="62"/>
       <c r="B23" s="15" t="s">
         <v>350</v>
       </c>
@@ -6717,7 +6708,7 @@
       <c r="P23" s="14"/>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="61"/>
+      <c r="A24" s="62"/>
       <c r="B24" s="15" t="s">
         <v>362</v>
       </c>
@@ -6739,7 +6730,7 @@
       <c r="P24" s="14"/>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="61"/>
+      <c r="A25" s="62"/>
       <c r="B25" s="15" t="s">
         <v>508</v>
       </c>
@@ -6761,7 +6752,7 @@
       <c r="P25" s="14"/>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="61"/>
+      <c r="A26" s="62"/>
       <c r="B26" s="15" t="s">
         <v>438</v>
       </c>
@@ -6783,7 +6774,7 @@
       <c r="P26" s="14"/>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="61"/>
+      <c r="A27" s="62"/>
       <c r="B27" s="15" t="s">
         <v>436</v>
       </c>
@@ -6805,7 +6796,7 @@
       <c r="P27" s="14"/>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="61"/>
+      <c r="A28" s="62"/>
       <c r="B28" s="15" t="s">
         <v>320</v>
       </c>
@@ -6827,7 +6818,7 @@
       <c r="P28" s="14"/>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="61"/>
+      <c r="A29" s="62"/>
       <c r="B29" s="15" t="s">
         <v>335</v>
       </c>
@@ -6849,7 +6840,7 @@
       <c r="P29" s="14"/>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="61"/>
+      <c r="A30" s="62"/>
       <c r="B30" s="15" t="s">
         <v>401</v>
       </c>
@@ -6871,7 +6862,7 @@
       <c r="P30" s="14"/>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="61"/>
+      <c r="A31" s="62"/>
       <c r="B31" s="15" t="s">
         <v>327</v>
       </c>
@@ -6893,7 +6884,7 @@
       <c r="P31" s="14"/>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="61"/>
+      <c r="A32" s="62"/>
       <c r="B32" s="15" t="s">
         <v>347</v>
       </c>
@@ -6915,7 +6906,7 @@
       <c r="P32" s="14"/>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="61"/>
+      <c r="A33" s="62"/>
       <c r="B33" s="15" t="s">
         <v>358</v>
       </c>
@@ -6937,7 +6928,7 @@
       <c r="P33" s="14"/>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="61"/>
+      <c r="A34" s="62"/>
       <c r="B34" s="15" t="s">
         <v>457</v>
       </c>
@@ -6959,7 +6950,7 @@
       <c r="P34" s="14"/>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="61"/>
+      <c r="A35" s="62"/>
       <c r="B35" s="15" t="s">
         <v>426</v>
       </c>
@@ -6981,7 +6972,7 @@
       <c r="P35" s="14"/>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="61"/>
+      <c r="A36" s="62"/>
       <c r="B36" s="15" t="s">
         <v>465</v>
       </c>
@@ -7003,7 +6994,7 @@
       <c r="P36" s="14"/>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="61"/>
+      <c r="A37" s="62"/>
       <c r="B37" s="15" t="s">
         <v>443</v>
       </c>
@@ -7025,7 +7016,7 @@
       <c r="P37" s="14"/>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="61"/>
+      <c r="A38" s="62"/>
       <c r="B38" s="15" t="s">
         <v>316</v>
       </c>
@@ -7047,7 +7038,7 @@
       <c r="P38" s="14"/>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="61"/>
+      <c r="A39" s="62"/>
       <c r="B39" s="15" t="s">
         <v>330</v>
       </c>
@@ -7069,7 +7060,7 @@
       <c r="P39" s="14"/>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="61"/>
+      <c r="A40" s="62"/>
       <c r="B40" s="15" t="s">
         <v>309</v>
       </c>
@@ -7091,7 +7082,7 @@
       <c r="P40" s="14"/>
     </row>
     <row r="41" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="61"/>
+      <c r="A41" s="62"/>
       <c r="B41" s="15" t="s">
         <v>440</v>
       </c>
@@ -7113,7 +7104,7 @@
       <c r="P41" s="14"/>
     </row>
     <row r="42" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="61"/>
+      <c r="A42" s="62"/>
       <c r="B42" s="15" t="s">
         <v>339</v>
       </c>
@@ -7135,7 +7126,7 @@
       <c r="P42" s="14"/>
     </row>
     <row r="43" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="61"/>
+      <c r="A43" s="62"/>
       <c r="B43" s="15" t="s">
         <v>468</v>
       </c>
@@ -7157,7 +7148,7 @@
       <c r="P43" s="14"/>
     </row>
     <row r="44" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="61"/>
+      <c r="A44" s="62"/>
       <c r="B44" s="15" t="s">
         <v>403</v>
       </c>
@@ -7179,7 +7170,7 @@
       <c r="P44" s="14"/>
     </row>
     <row r="45" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="61"/>
+      <c r="A45" s="62"/>
       <c r="B45" s="15" t="s">
         <v>393</v>
       </c>
@@ -7221,7 +7212,7 @@
       <c r="P46" s="14"/>
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="60" t="s">
+      <c r="A47" s="61" t="s">
         <v>463</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -7245,7 +7236,7 @@
       <c r="P47" s="14"/>
     </row>
     <row r="48" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="60"/>
+      <c r="A48" s="61"/>
       <c r="B48" s="15" t="s">
         <v>315</v>
       </c>
@@ -7267,7 +7258,7 @@
       <c r="P48" s="14"/>
     </row>
     <row r="49" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="60"/>
+      <c r="A49" s="61"/>
       <c r="B49" s="15" t="s">
         <v>469</v>
       </c>
@@ -7289,7 +7280,7 @@
       <c r="P49" s="14"/>
     </row>
     <row r="50" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="60"/>
+      <c r="A50" s="61"/>
       <c r="B50" s="15" t="s">
         <v>466</v>
       </c>
@@ -7311,7 +7302,7 @@
       <c r="P50" s="14"/>
     </row>
     <row r="51" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="60"/>
+      <c r="A51" s="61"/>
       <c r="B51" s="15" t="s">
         <v>461</v>
       </c>
@@ -7333,7 +7324,7 @@
       <c r="P51" s="14"/>
     </row>
     <row r="52" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="60"/>
+      <c r="A52" s="61"/>
       <c r="B52" s="15" t="s">
         <v>423</v>
       </c>
@@ -7355,7 +7346,7 @@
       <c r="P52" s="14"/>
     </row>
     <row r="53" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="60" t="s">
+      <c r="A53" s="61" t="s">
         <v>459</v>
       </c>
       <c r="B53" s="15" t="s">
@@ -7379,7 +7370,7 @@
       <c r="P53" s="14"/>
     </row>
     <row r="54" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="60"/>
+      <c r="A54" s="61"/>
       <c r="B54" s="15" t="s">
         <v>431</v>
       </c>
@@ -7401,7 +7392,7 @@
       <c r="P54" s="14"/>
     </row>
     <row r="55" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="60"/>
+      <c r="A55" s="61"/>
       <c r="B55" s="15" t="s">
         <v>451</v>
       </c>
@@ -7423,7 +7414,7 @@
       <c r="P55" s="14"/>
     </row>
     <row r="56" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="60"/>
+      <c r="A56" s="61"/>
       <c r="B56" s="15" t="s">
         <v>439</v>
       </c>
@@ -7445,7 +7436,7 @@
       <c r="P56" s="14"/>
     </row>
     <row r="57" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="60"/>
+      <c r="A57" s="61"/>
       <c r="B57" s="15" t="s">
         <v>447</v>
       </c>
@@ -7467,7 +7458,7 @@
       <c r="P57" s="14"/>
     </row>
     <row r="58" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="60"/>
+      <c r="A58" s="61"/>
       <c r="B58" s="15" t="s">
         <v>452</v>
       </c>
@@ -7509,7 +7500,7 @@
       <c r="P59" s="14"/>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="60" t="s">
+      <c r="A60" s="61" t="s">
         <v>515</v>
       </c>
       <c r="B60" s="15" t="s">
@@ -7533,7 +7524,7 @@
       <c r="P60" s="14"/>
     </row>
     <row r="61" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="60"/>
+      <c r="A61" s="61"/>
       <c r="B61" s="15" t="s">
         <v>304</v>
       </c>
@@ -7555,7 +7546,7 @@
       <c r="P61" s="14"/>
     </row>
     <row r="62" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="60"/>
+      <c r="A62" s="61"/>
       <c r="B62" s="15" t="s">
         <v>283</v>
       </c>
@@ -7577,7 +7568,7 @@
       <c r="P62" s="14"/>
     </row>
     <row r="63" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="60"/>
+      <c r="A63" s="61"/>
       <c r="B63" s="15" t="s">
         <v>287</v>
       </c>
@@ -7619,7 +7610,7 @@
       <c r="P64" s="14"/>
     </row>
     <row r="65" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="60" t="s">
+      <c r="A65" s="61" t="s">
         <v>448</v>
       </c>
       <c r="B65" s="15" t="s">
@@ -7643,7 +7634,7 @@
       <c r="P65" s="14"/>
     </row>
     <row r="66" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="60"/>
+      <c r="A66" s="61"/>
       <c r="B66" s="15" t="s">
         <v>387</v>
       </c>
@@ -7665,7 +7656,7 @@
       <c r="P66" s="14"/>
     </row>
     <row r="67" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="60"/>
+      <c r="A67" s="61"/>
       <c r="B67" s="15" t="s">
         <v>453</v>
       </c>
@@ -7687,7 +7678,7 @@
       <c r="P67" s="14"/>
     </row>
     <row r="68" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="60"/>
+      <c r="A68" s="61"/>
       <c r="B68" s="15" t="s">
         <v>475</v>
       </c>
@@ -7709,7 +7700,7 @@
       <c r="P68" s="14"/>
     </row>
     <row r="69" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="60"/>
+      <c r="A69" s="61"/>
       <c r="B69" s="15" t="s">
         <v>481</v>
       </c>
@@ -7731,7 +7722,7 @@
       <c r="P69" s="14"/>
     </row>
     <row r="70" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="60"/>
+      <c r="A70" s="61"/>
       <c r="B70" s="15" t="s">
         <v>424</v>
       </c>
@@ -7753,7 +7744,7 @@
       <c r="P70" s="14"/>
     </row>
     <row r="71" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="60"/>
+      <c r="A71" s="61"/>
       <c r="B71" s="15" t="s">
         <v>427</v>
       </c>
@@ -7775,7 +7766,7 @@
       <c r="P71" s="14"/>
     </row>
     <row r="72" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="60"/>
+      <c r="A72" s="61"/>
       <c r="B72" s="15" t="s">
         <v>467</v>
       </c>
@@ -7797,7 +7788,7 @@
       <c r="P72" s="14"/>
     </row>
     <row r="73" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="60"/>
+      <c r="A73" s="61"/>
       <c r="B73" s="15" t="s">
         <v>460</v>
       </c>
@@ -7819,7 +7810,7 @@
       <c r="P73" s="14"/>
     </row>
     <row r="74" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="60"/>
+      <c r="A74" s="61"/>
       <c r="B74" s="15" t="s">
         <v>455</v>
       </c>
@@ -7861,7 +7852,7 @@
       <c r="P75" s="14"/>
     </row>
     <row r="76" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="60" t="s">
+      <c r="A76" s="61" t="s">
         <v>219</v>
       </c>
       <c r="B76" s="29" t="s">
@@ -7885,7 +7876,7 @@
       <c r="P76" s="14"/>
     </row>
     <row r="77" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="60"/>
+      <c r="A77" s="61"/>
       <c r="B77" s="29" t="s">
         <v>269</v>
       </c>
@@ -7927,7 +7918,7 @@
       <c r="P78" s="14"/>
     </row>
     <row r="79" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="60"/>
+      <c r="A79" s="61"/>
       <c r="B79" s="15" t="s">
         <v>277</v>
       </c>
@@ -7949,7 +7940,7 @@
       <c r="P79" s="14"/>
     </row>
     <row r="80" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="60"/>
+      <c r="A80" s="61"/>
       <c r="B80" s="15" t="s">
         <v>178</v>
       </c>
@@ -7971,7 +7962,7 @@
       <c r="P80" s="14"/>
     </row>
     <row r="81" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="60"/>
+      <c r="A81" s="61"/>
       <c r="B81" s="15" t="s">
         <v>331</v>
       </c>
@@ -7993,7 +7984,7 @@
       <c r="P81" s="14"/>
     </row>
     <row r="82" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="60"/>
+      <c r="A82" s="61"/>
       <c r="B82" s="15" t="s">
         <v>198</v>
       </c>
@@ -8015,7 +8006,7 @@
       <c r="P82" s="14"/>
     </row>
     <row r="83" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="60"/>
+      <c r="A83" s="61"/>
       <c r="B83" s="15" t="s">
         <v>328</v>
       </c>
@@ -8037,7 +8028,7 @@
       <c r="P83" s="14"/>
     </row>
     <row r="84" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="60"/>
+      <c r="A84" s="61"/>
       <c r="B84" s="30" t="s">
         <v>359</v>
       </c>
@@ -8059,7 +8050,7 @@
       <c r="P84" s="14"/>
     </row>
     <row r="85" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="60"/>
+      <c r="A85" s="61"/>
       <c r="B85" s="30" t="s">
         <v>303</v>
       </c>
@@ -8081,7 +8072,7 @@
       <c r="P85" s="14"/>
     </row>
     <row r="86" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="60"/>
+      <c r="A86" s="61"/>
       <c r="B86" s="30" t="s">
         <v>349</v>
       </c>
@@ -8123,7 +8114,7 @@
       <c r="P87" s="14"/>
     </row>
     <row r="88" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="60" t="s">
+      <c r="A88" s="61" t="s">
         <v>513</v>
       </c>
       <c r="B88" s="15" t="s">
@@ -8147,7 +8138,7 @@
       <c r="P88" s="14"/>
     </row>
     <row r="89" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="60"/>
+      <c r="A89" s="61"/>
       <c r="B89" s="15" t="s">
         <v>323</v>
       </c>
@@ -8169,7 +8160,7 @@
       <c r="P89" s="14"/>
     </row>
     <row r="90" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="60"/>
+      <c r="A90" s="61"/>
       <c r="B90" s="15" t="s">
         <v>199</v>
       </c>
@@ -8191,7 +8182,7 @@
       <c r="P90" s="14"/>
     </row>
     <row r="91" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="60"/>
+      <c r="A91" s="61"/>
       <c r="B91" s="29" t="s">
         <v>189</v>
       </c>
@@ -8213,7 +8204,7 @@
       <c r="P91" s="14"/>
     </row>
     <row r="92" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="60"/>
+      <c r="A92" s="61"/>
       <c r="B92" s="15" t="s">
         <v>278</v>
       </c>
@@ -8235,7 +8226,7 @@
       <c r="P92" s="14"/>
     </row>
     <row r="93" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="60"/>
+      <c r="A93" s="61"/>
       <c r="B93" s="15" t="s">
         <v>200</v>
       </c>
@@ -8257,7 +8248,7 @@
       <c r="P93" s="14"/>
     </row>
     <row r="94" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="60"/>
+      <c r="A94" s="61"/>
       <c r="B94" s="29" t="s">
         <v>213</v>
       </c>
@@ -8279,7 +8270,7 @@
       <c r="P94" s="14"/>
     </row>
     <row r="95" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="60" t="s">
+      <c r="A95" s="61" t="s">
         <v>513</v>
       </c>
       <c r="B95" s="15" t="s">
@@ -8303,7 +8294,7 @@
       <c r="P95" s="14"/>
     </row>
     <row r="96" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="60"/>
+      <c r="A96" s="61"/>
       <c r="B96" s="15" t="s">
         <v>172</v>
       </c>
@@ -8325,7 +8316,7 @@
       <c r="P96" s="14"/>
     </row>
     <row r="97" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="60"/>
+      <c r="A97" s="61"/>
       <c r="B97" s="15" t="s">
         <v>319</v>
       </c>
@@ -8347,7 +8338,7 @@
       <c r="P97" s="14"/>
     </row>
     <row r="98" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="60"/>
+      <c r="A98" s="61"/>
       <c r="B98" s="15" t="s">
         <v>342</v>
       </c>
@@ -8369,7 +8360,7 @@
       <c r="P98" s="14"/>
     </row>
     <row r="99" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="60"/>
+      <c r="A99" s="61"/>
       <c r="B99" s="15" t="s">
         <v>313</v>
       </c>
@@ -8391,7 +8382,7 @@
       <c r="P99" s="14"/>
     </row>
     <row r="100" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="60"/>
+      <c r="A100" s="61"/>
       <c r="B100" s="15" t="s">
         <v>332</v>
       </c>
@@ -8413,7 +8404,7 @@
       <c r="P100" s="14"/>
     </row>
     <row r="101" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="60"/>
+      <c r="A101" s="61"/>
       <c r="B101" s="15" t="s">
         <v>325</v>
       </c>
@@ -8435,7 +8426,7 @@
       <c r="P101" s="14"/>
     </row>
     <row r="102" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="60"/>
+      <c r="A102" s="61"/>
       <c r="B102" s="15" t="s">
         <v>170</v>
       </c>
@@ -8457,7 +8448,7 @@
       <c r="P102" s="14"/>
     </row>
     <row r="103" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="60"/>
+      <c r="A103" s="61"/>
       <c r="B103" s="15" t="s">
         <v>222</v>
       </c>
@@ -8547,7 +8538,7 @@
       <c r="P106" s="14"/>
     </row>
     <row r="107" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="60" t="s">
+      <c r="A107" s="61" t="s">
         <v>259</v>
       </c>
       <c r="B107" s="15" t="s">
@@ -8571,7 +8562,7 @@
       <c r="P107" s="14"/>
     </row>
     <row r="108" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="60"/>
+      <c r="A108" s="61"/>
       <c r="B108" s="29" t="s">
         <v>301</v>
       </c>
@@ -8593,7 +8584,7 @@
       <c r="P108" s="14"/>
     </row>
     <row r="109" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="60"/>
+      <c r="A109" s="61"/>
       <c r="B109" s="29" t="s">
         <v>579</v>
       </c>
@@ -8659,7 +8650,7 @@
       <c r="P111" s="14"/>
     </row>
     <row r="112" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="61" t="s">
+      <c r="A112" s="62" t="s">
         <v>49</v>
       </c>
       <c r="B112" s="15" t="s">
@@ -8683,7 +8674,7 @@
       <c r="P112" s="14"/>
     </row>
     <row r="113" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="61"/>
+      <c r="A113" s="62"/>
       <c r="B113" s="15" t="s">
         <v>302</v>
       </c>
@@ -8705,7 +8696,7 @@
       <c r="P113" s="14"/>
     </row>
     <row r="114" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="61"/>
+      <c r="A114" s="62"/>
       <c r="B114" s="15" t="s">
         <v>374</v>
       </c>
@@ -8727,7 +8718,7 @@
       <c r="P114" s="14"/>
     </row>
     <row r="115" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="61"/>
+      <c r="A115" s="62"/>
       <c r="B115" s="15" t="s">
         <v>280</v>
       </c>
@@ -8749,7 +8740,7 @@
       <c r="P115" s="14"/>
     </row>
     <row r="116" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="61"/>
+      <c r="A116" s="62"/>
       <c r="B116" s="15" t="s">
         <v>298</v>
       </c>
@@ -8771,7 +8762,7 @@
       <c r="P116" s="14"/>
     </row>
     <row r="117" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="61"/>
+      <c r="A117" s="62"/>
       <c r="B117" s="15" t="s">
         <v>279</v>
       </c>
@@ -8793,7 +8784,7 @@
       <c r="P117" s="14"/>
     </row>
     <row r="118" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="61"/>
+      <c r="A118" s="62"/>
       <c r="B118" s="15" t="s">
         <v>250</v>
       </c>
@@ -8815,7 +8806,7 @@
       <c r="P118" s="14"/>
     </row>
     <row r="119" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="61"/>
+      <c r="A119" s="62"/>
       <c r="B119" s="15" t="s">
         <v>288</v>
       </c>
@@ -8857,7 +8848,7 @@
       <c r="P120" s="14"/>
     </row>
     <row r="121" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="60" t="s">
+      <c r="A121" s="61" t="s">
         <v>514</v>
       </c>
       <c r="B121" s="15" t="s">
@@ -8881,7 +8872,7 @@
       <c r="P121" s="14"/>
     </row>
     <row r="122" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="60"/>
+      <c r="A122" s="61"/>
       <c r="B122" s="15" t="s">
         <v>226</v>
       </c>
@@ -8903,7 +8894,7 @@
       <c r="P122" s="14"/>
     </row>
     <row r="123" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="60"/>
+      <c r="A123" s="61"/>
       <c r="B123" s="15" t="s">
         <v>317</v>
       </c>
@@ -8925,7 +8916,7 @@
       <c r="P123" s="14"/>
     </row>
     <row r="124" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="60"/>
+      <c r="A124" s="61"/>
       <c r="B124" s="15" t="s">
         <v>334</v>
       </c>
@@ -8967,7 +8958,7 @@
       <c r="P125" s="14"/>
     </row>
     <row r="126" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="60" t="s">
+      <c r="A126" s="61" t="s">
         <v>281</v>
       </c>
       <c r="B126" s="15" t="s">
@@ -8991,7 +8982,7 @@
       <c r="P126" s="14"/>
     </row>
     <row r="127" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="60"/>
+      <c r="A127" s="61"/>
       <c r="B127" s="15" t="s">
         <v>398</v>
       </c>
@@ -9013,16 +9004,16 @@
       <c r="P127" s="14"/>
     </row>
     <row r="128" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="54" t="s">
+      <c r="A128" s="85" t="s">
         <v>114</v>
       </c>
-      <c r="B128" s="55"/>
-      <c r="C128" s="55"/>
-      <c r="D128" s="55"/>
-      <c r="E128" s="55"/>
-      <c r="F128" s="55"/>
-      <c r="G128" s="55"/>
-      <c r="H128" s="56"/>
+      <c r="B128" s="86"/>
+      <c r="C128" s="86"/>
+      <c r="D128" s="86"/>
+      <c r="E128" s="86"/>
+      <c r="F128" s="86"/>
+      <c r="G128" s="86"/>
+      <c r="H128" s="87"/>
       <c r="I128" s="47"/>
       <c r="J128" s="47"/>
       <c r="K128" s="47"/>
@@ -9033,16 +9024,16 @@
       <c r="P128" s="22"/>
     </row>
     <row r="129" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="57" t="s">
+      <c r="A129" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="B129" s="58"/>
-      <c r="C129" s="58"/>
-      <c r="D129" s="58"/>
-      <c r="E129" s="58"/>
-      <c r="F129" s="58"/>
-      <c r="G129" s="58"/>
-      <c r="H129" s="59"/>
+      <c r="B129" s="89"/>
+      <c r="C129" s="89"/>
+      <c r="D129" s="89"/>
+      <c r="E129" s="89"/>
+      <c r="F129" s="89"/>
+      <c r="G129" s="89"/>
+      <c r="H129" s="77"/>
       <c r="I129" s="48"/>
       <c r="J129" s="48"/>
       <c r="K129" s="48"/>
@@ -9074,104 +9065,118 @@
       <c r="A131" s="3"/>
       <c r="B131" s="1"/>
       <c r="C131" s="5"/>
-      <c r="D131" s="71"/>
-      <c r="E131" s="96"/>
-      <c r="F131" s="96"/>
-      <c r="G131" s="72"/>
-      <c r="H131" s="72"/>
-      <c r="I131" s="64"/>
-      <c r="J131" s="64"/>
-      <c r="K131" s="64"/>
-      <c r="L131" s="65"/>
+      <c r="D131" s="79"/>
+      <c r="E131" s="80"/>
+      <c r="F131" s="80"/>
+      <c r="G131" s="81"/>
+      <c r="H131" s="81"/>
+      <c r="I131" s="78"/>
+      <c r="J131" s="78"/>
+      <c r="K131" s="78"/>
+      <c r="L131" s="95"/>
       <c r="M131" s="8"/>
       <c r="N131" s="8"/>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
     </row>
     <row r="132" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D132" s="73" t="s">
+      <c r="D132" s="82" t="s">
         <v>682</v>
       </c>
-      <c r="E132" s="97"/>
-      <c r="F132" s="97"/>
-      <c r="G132" s="74"/>
-      <c r="H132" s="74"/>
-      <c r="I132" s="66"/>
-      <c r="J132" s="66"/>
-      <c r="K132" s="66"/>
-      <c r="L132" s="67"/>
+      <c r="E132" s="83"/>
+      <c r="F132" s="83"/>
+      <c r="G132" s="84"/>
+      <c r="H132" s="84"/>
+      <c r="I132" s="84"/>
+      <c r="J132" s="84"/>
+      <c r="K132" s="84"/>
+      <c r="L132" s="96"/>
     </row>
     <row r="133" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D133" s="75" t="s">
+      <c r="D133" s="68" t="s">
         <v>683</v>
       </c>
       <c r="E133" s="53"/>
       <c r="F133" s="53"/>
-      <c r="G133" s="76"/>
-      <c r="H133" s="76"/>
-      <c r="I133" s="60"/>
-      <c r="J133" s="60"/>
-      <c r="K133" s="60"/>
-      <c r="L133" s="69"/>
+      <c r="G133" s="69"/>
+      <c r="H133" s="69"/>
+      <c r="I133" s="69"/>
+      <c r="J133" s="69"/>
+      <c r="K133" s="69"/>
+      <c r="L133" s="97"/>
     </row>
     <row r="134" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D134" s="75" t="s">
+      <c r="D134" s="68" t="s">
         <v>684</v>
       </c>
       <c r="E134" s="53"/>
       <c r="F134" s="53"/>
-      <c r="G134" s="76"/>
-      <c r="H134" s="76"/>
-      <c r="I134" s="60"/>
-      <c r="J134" s="60"/>
-      <c r="K134" s="60"/>
-      <c r="L134" s="69"/>
+      <c r="G134" s="69"/>
+      <c r="H134" s="69"/>
+      <c r="I134" s="69"/>
+      <c r="J134" s="69"/>
+      <c r="K134" s="69"/>
+      <c r="L134" s="97"/>
     </row>
     <row r="135" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D135" s="77" t="s">
+      <c r="D135" s="70" t="s">
         <v>685</v>
       </c>
-      <c r="E135" s="98"/>
-      <c r="F135" s="98"/>
-      <c r="G135" s="78"/>
-      <c r="H135" s="78"/>
-      <c r="I135" s="68"/>
-      <c r="J135" s="68"/>
-      <c r="K135" s="68"/>
-      <c r="L135" s="70"/>
+      <c r="E135" s="71"/>
+      <c r="F135" s="71"/>
+      <c r="G135" s="72"/>
+      <c r="H135" s="72"/>
+      <c r="I135" s="72"/>
+      <c r="J135" s="72"/>
+      <c r="K135" s="72"/>
+      <c r="L135" s="98"/>
     </row>
     <row r="136" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D136" s="62" t="s">
+      <c r="D136" s="76" t="s">
         <v>686</v>
       </c>
-      <c r="E136" s="59"/>
-      <c r="F136" s="59"/>
-      <c r="G136" s="63"/>
-      <c r="H136" s="63"/>
-      <c r="I136" s="64"/>
-      <c r="J136" s="64"/>
-      <c r="K136" s="64"/>
-      <c r="L136" s="64"/>
+      <c r="E136" s="77"/>
+      <c r="F136" s="77"/>
+      <c r="G136" s="78"/>
+      <c r="H136" s="78"/>
+      <c r="I136" s="78"/>
+      <c r="J136" s="78"/>
+      <c r="K136" s="78"/>
+      <c r="L136" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A8:A15"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A22:A45"/>
-    <mergeCell ref="A53:A58"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="A65:A74"/>
-    <mergeCell ref="A47:A52"/>
-    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="A125:H125"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A103"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A112:A119"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="D136:H136"/>
+    <mergeCell ref="I131:J131"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="I133:J133"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="I136:J136"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="D131:H131"/>
+    <mergeCell ref="D132:H132"/>
+    <mergeCell ref="D133:H133"/>
     <mergeCell ref="D134:H134"/>
     <mergeCell ref="D135:H135"/>
     <mergeCell ref="N6:N7"/>
@@ -9188,37 +9193,23 @@
     <mergeCell ref="A126:A127"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="A79:A86"/>
-    <mergeCell ref="D136:H136"/>
-    <mergeCell ref="I131:J131"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="I133:J133"/>
-    <mergeCell ref="I134:J134"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="I136:J136"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="D131:H131"/>
-    <mergeCell ref="D132:H132"/>
-    <mergeCell ref="D133:H133"/>
-    <mergeCell ref="A120:H120"/>
-    <mergeCell ref="A125:H125"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A129:H129"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A103"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A112:A119"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A104:H104"/>
-    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="A22:A45"/>
+    <mergeCell ref="A53:A58"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A65:A74"/>
+    <mergeCell ref="A47:A52"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A8:A15"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11703,20 +11694,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -11747,67 +11738,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="58" t="s">
         <v>625</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="58" t="s">
         <v>626</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="58" t="s">
         <v>627</v>
       </c>
-      <c r="F6" s="79" t="s">
+      <c r="F6" s="54" t="s">
         <v>628</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="54" t="s">
         <v>578</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="54" t="s">
         <v>582</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="54" t="s">
         <v>588</v>
       </c>
-      <c r="J6" s="79" t="s">
+      <c r="J6" s="54" t="s">
         <v>589</v>
       </c>
-      <c r="K6" s="79" t="s">
+      <c r="K6" s="54" t="s">
         <v>590</v>
       </c>
-      <c r="L6" s="79" t="s">
+      <c r="L6" s="54" t="s">
         <v>608</v>
       </c>
-      <c r="M6" s="79" t="s">
+      <c r="M6" s="54" t="s">
         <v>629</v>
       </c>
-      <c r="N6" s="82" t="s">
+      <c r="N6" s="74" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="90"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="83"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="75"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="93" t="s">
         <v>633</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -11829,7 +11820,7 @@
       <c r="N8" s="27"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="92"/>
+      <c r="A9" s="90"/>
       <c r="B9" s="13" t="s">
         <v>363</v>
       </c>
@@ -11849,7 +11840,7 @@
       <c r="N9" s="26"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="92"/>
+      <c r="A10" s="90"/>
       <c r="B10" s="11" t="s">
         <v>297</v>
       </c>
@@ -11869,7 +11860,7 @@
       <c r="N10" s="26"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="92"/>
+      <c r="A11" s="90"/>
       <c r="B11" s="11" t="s">
         <v>252</v>
       </c>
@@ -11889,7 +11880,7 @@
       <c r="N11" s="26"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="92"/>
+      <c r="A12" s="90"/>
       <c r="B12" s="11" t="s">
         <v>345</v>
       </c>
@@ -11909,7 +11900,7 @@
       <c r="N12" s="26"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="92"/>
+      <c r="A13" s="90"/>
       <c r="B13" s="11" t="s">
         <v>373</v>
       </c>
@@ -11929,7 +11920,7 @@
       <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="92"/>
+      <c r="A14" s="90"/>
       <c r="B14" s="11" t="s">
         <v>379</v>
       </c>
@@ -11949,7 +11940,7 @@
       <c r="N14" s="26"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="92"/>
+      <c r="A15" s="90"/>
       <c r="B15" s="11" t="s">
         <v>377</v>
       </c>
@@ -11969,7 +11960,7 @@
       <c r="N15" s="26"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="92"/>
+      <c r="A16" s="90"/>
       <c r="B16" s="11" t="s">
         <v>249</v>
       </c>
@@ -11989,7 +11980,7 @@
       <c r="N16" s="26"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="92"/>
+      <c r="A17" s="90"/>
       <c r="B17" s="11" t="s">
         <v>444</v>
       </c>
@@ -12009,7 +12000,7 @@
       <c r="N17" s="26"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="92"/>
+      <c r="A18" s="90"/>
       <c r="B18" s="11" t="s">
         <v>378</v>
       </c>
@@ -12029,7 +12020,7 @@
       <c r="N18" s="26"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="92"/>
+      <c r="A19" s="90"/>
       <c r="B19" s="11" t="s">
         <v>611</v>
       </c>
@@ -12049,7 +12040,7 @@
       <c r="N19" s="26"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="93" t="s">
+      <c r="A20" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B20" s="52"/>
@@ -12067,7 +12058,7 @@
       <c r="N20" s="26"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="90" t="s">
         <v>635</v>
       </c>
       <c r="B21" s="39" t="s">
@@ -12089,7 +12080,7 @@
       <c r="N21" s="26"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="92"/>
+      <c r="A22" s="90"/>
       <c r="B22" s="40" t="s">
         <v>366</v>
       </c>
@@ -12109,7 +12100,7 @@
       <c r="N22" s="26"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="92"/>
+      <c r="A23" s="90"/>
       <c r="B23" s="39" t="s">
         <v>392</v>
       </c>
@@ -12129,7 +12120,7 @@
       <c r="N23" s="26"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="92"/>
+      <c r="A24" s="90"/>
       <c r="B24" s="39" t="s">
         <v>397</v>
       </c>
@@ -12149,7 +12140,7 @@
       <c r="N24" s="26"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="92"/>
+      <c r="A25" s="90"/>
       <c r="B25" s="39" t="s">
         <v>248</v>
       </c>
@@ -12169,7 +12160,7 @@
       <c r="N25" s="26"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="92"/>
+      <c r="A26" s="90"/>
       <c r="B26" s="39" t="s">
         <v>428</v>
       </c>
@@ -12189,7 +12180,7 @@
       <c r="N26" s="26"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="92"/>
+      <c r="A27" s="90"/>
       <c r="B27" s="39" t="s">
         <v>243</v>
       </c>
@@ -12209,7 +12200,7 @@
       <c r="N27" s="26"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="92"/>
+      <c r="A28" s="90"/>
       <c r="B28" s="39" t="s">
         <v>636</v>
       </c>
@@ -12229,7 +12220,7 @@
       <c r="N28" s="26"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="93" t="s">
+      <c r="A29" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B29" s="52"/>
@@ -12247,7 +12238,7 @@
       <c r="N29" s="26"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="92" t="s">
+      <c r="A30" s="90" t="s">
         <v>637</v>
       </c>
       <c r="B30" s="41" t="s">
@@ -12269,7 +12260,7 @@
       <c r="N30" s="26"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="92"/>
+      <c r="A31" s="90"/>
       <c r="B31" s="41" t="s">
         <v>338</v>
       </c>
@@ -12289,7 +12280,7 @@
       <c r="N31" s="26"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92"/>
+      <c r="A32" s="90"/>
       <c r="B32" s="43" t="s">
         <v>372</v>
       </c>
@@ -12309,7 +12300,7 @@
       <c r="N32" s="26"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
+      <c r="A33" s="90"/>
       <c r="B33" s="41" t="s">
         <v>402</v>
       </c>
@@ -12329,7 +12320,7 @@
       <c r="N33" s="26"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="93" t="s">
+      <c r="A34" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B34" s="52"/>
@@ -12589,7 +12580,7 @@
       <c r="N46" s="26"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="93" t="s">
+      <c r="A47" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B47" s="52"/>
@@ -12789,7 +12780,7 @@
       <c r="N56" s="26"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="92"/>
+      <c r="A57" s="90"/>
       <c r="B57" s="15" t="s">
         <v>493</v>
       </c>
@@ -12809,7 +12800,7 @@
       <c r="N57" s="26"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="92"/>
+      <c r="A58" s="90"/>
       <c r="B58" s="15" t="s">
         <v>406</v>
       </c>
@@ -12829,7 +12820,7 @@
       <c r="N58" s="26"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="93" t="s">
+      <c r="A59" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B59" s="52"/>
@@ -12869,7 +12860,7 @@
       <c r="N60" s="26"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="92"/>
+      <c r="A61" s="90"/>
       <c r="B61" s="15" t="s">
         <v>421</v>
       </c>
@@ -12889,7 +12880,7 @@
       <c r="N61" s="26"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="92"/>
+      <c r="A62" s="90"/>
       <c r="B62" s="15" t="s">
         <v>613</v>
       </c>
@@ -12909,7 +12900,7 @@
       <c r="N62" s="26"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="92"/>
+      <c r="A63" s="90"/>
       <c r="B63" s="15" t="s">
         <v>409</v>
       </c>
@@ -12929,7 +12920,7 @@
       <c r="N63" s="26"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="92"/>
+      <c r="A64" s="90"/>
       <c r="B64" s="15" t="s">
         <v>615</v>
       </c>
@@ -12949,7 +12940,7 @@
       <c r="N64" s="26"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="92"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="15" t="s">
         <v>391</v>
       </c>
@@ -12969,7 +12960,7 @@
       <c r="N65" s="26"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="92"/>
+      <c r="A66" s="90"/>
       <c r="B66" s="15" t="s">
         <v>617</v>
       </c>
@@ -12989,7 +12980,7 @@
       <c r="N66" s="26"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="92"/>
+      <c r="A67" s="90"/>
       <c r="B67" s="15" t="s">
         <v>602</v>
       </c>
@@ -13009,7 +13000,7 @@
       <c r="N67" s="26"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="92"/>
+      <c r="A68" s="90"/>
       <c r="B68" s="15" t="s">
         <v>394</v>
       </c>
@@ -13029,7 +13020,7 @@
       <c r="N68" s="26"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="92"/>
+      <c r="A69" s="90"/>
       <c r="B69" s="15" t="s">
         <v>177</v>
       </c>
@@ -13049,7 +13040,7 @@
       <c r="N69" s="26"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="92"/>
+      <c r="A70" s="90"/>
       <c r="B70" s="15" t="s">
         <v>619</v>
       </c>
@@ -13069,7 +13060,7 @@
       <c r="N70" s="26"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="92"/>
+      <c r="A71" s="90"/>
       <c r="B71" s="15" t="s">
         <v>411</v>
       </c>
@@ -13089,7 +13080,7 @@
       <c r="N71" s="26"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="92"/>
+      <c r="A72" s="90"/>
       <c r="B72" s="15" t="s">
         <v>621</v>
       </c>
@@ -13109,7 +13100,7 @@
       <c r="N72" s="26"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="92"/>
+      <c r="A73" s="90"/>
       <c r="B73" s="15" t="s">
         <v>478</v>
       </c>
@@ -13129,7 +13120,7 @@
       <c r="N73" s="26"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="92"/>
+      <c r="A74" s="90"/>
       <c r="B74" s="15" t="s">
         <v>501</v>
       </c>
@@ -13149,7 +13140,7 @@
       <c r="N74" s="26"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="93" t="s">
+      <c r="A75" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B75" s="52"/>
@@ -13289,7 +13280,7 @@
       <c r="N81" s="26"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="93" t="s">
+      <c r="A82" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B82" s="52"/>
@@ -13389,7 +13380,7 @@
       <c r="N86" s="26"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="93" t="s">
+      <c r="A87" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B87" s="52"/>
@@ -13529,7 +13520,7 @@
       <c r="N93" s="26"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="93" t="s">
+      <c r="A94" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B94" s="52"/>
@@ -13611,7 +13602,7 @@
       <c r="N97" s="26"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="92"/>
+      <c r="A98" s="90"/>
       <c r="B98" s="15" t="s">
         <v>237</v>
       </c>
@@ -13631,7 +13622,7 @@
       <c r="N98" s="26"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="93" t="s">
+      <c r="A99" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B99" s="52"/>
@@ -13671,7 +13662,7 @@
       <c r="N100" s="26"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="92"/>
+      <c r="A101" s="90"/>
       <c r="B101" s="15" t="s">
         <v>419</v>
       </c>
@@ -13691,7 +13682,7 @@
       <c r="N101" s="26"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="92"/>
+      <c r="A102" s="90"/>
       <c r="B102" s="15" t="s">
         <v>416</v>
       </c>
@@ -13711,7 +13702,7 @@
       <c r="N102" s="26"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="92"/>
+      <c r="A103" s="90"/>
       <c r="B103" s="15" t="s">
         <v>361</v>
       </c>
@@ -13731,7 +13722,7 @@
       <c r="N103" s="26"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="92"/>
+      <c r="A104" s="90"/>
       <c r="B104" s="15" t="s">
         <v>600</v>
       </c>
@@ -13751,7 +13742,7 @@
       <c r="N104" s="26"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="92"/>
+      <c r="A105" s="90"/>
       <c r="B105" s="15" t="s">
         <v>599</v>
       </c>
@@ -13771,7 +13762,7 @@
       <c r="N105" s="26"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="92"/>
+      <c r="A106" s="90"/>
       <c r="B106" s="15" t="s">
         <v>390</v>
       </c>
@@ -13791,7 +13782,7 @@
       <c r="N106" s="26"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="92"/>
+      <c r="A107" s="90"/>
       <c r="B107" s="15" t="s">
         <v>369</v>
       </c>
@@ -13811,7 +13802,7 @@
       <c r="N107" s="26"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="92"/>
+      <c r="A108" s="90"/>
       <c r="B108" s="15" t="s">
         <v>251</v>
       </c>
@@ -13831,7 +13822,7 @@
       <c r="N108" s="26"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="92"/>
+      <c r="A109" s="90"/>
       <c r="B109" s="15" t="s">
         <v>333</v>
       </c>
@@ -13851,7 +13842,7 @@
       <c r="N109" s="26"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="92"/>
+      <c r="A110" s="90"/>
       <c r="B110" s="15" t="s">
         <v>246</v>
       </c>
@@ -13871,7 +13862,7 @@
       <c r="N110" s="26"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="92"/>
+      <c r="A111" s="90"/>
       <c r="B111" s="15" t="s">
         <v>430</v>
       </c>
@@ -13891,7 +13882,7 @@
       <c r="N111" s="26"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="92"/>
+      <c r="A112" s="90"/>
       <c r="B112" s="15" t="s">
         <v>231</v>
       </c>
@@ -13911,7 +13902,7 @@
       <c r="N112" s="26"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="92"/>
+      <c r="A113" s="90"/>
       <c r="B113" s="15" t="s">
         <v>375</v>
       </c>
@@ -13931,7 +13922,7 @@
       <c r="N113" s="26"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="92"/>
+      <c r="A114" s="90"/>
       <c r="B114" s="15" t="s">
         <v>241</v>
       </c>
@@ -13973,7 +13964,7 @@
       <c r="N115" s="26"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="92"/>
+      <c r="A116" s="90"/>
       <c r="B116" s="15" t="s">
         <v>400</v>
       </c>
@@ -13993,7 +13984,7 @@
       <c r="N116" s="26"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="92"/>
+      <c r="A117" s="90"/>
       <c r="B117" s="15" t="s">
         <v>355</v>
       </c>
@@ -14013,7 +14004,7 @@
       <c r="N117" s="26"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="92"/>
+      <c r="A118" s="90"/>
       <c r="B118" s="15" t="s">
         <v>388</v>
       </c>
@@ -14033,7 +14024,7 @@
       <c r="N118" s="26"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="92"/>
+      <c r="A119" s="90"/>
       <c r="B119" s="15" t="s">
         <v>380</v>
       </c>
@@ -14053,7 +14044,7 @@
       <c r="N119" s="26"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="92"/>
+      <c r="A120" s="90"/>
       <c r="B120" s="15" t="s">
         <v>437</v>
       </c>
@@ -14073,7 +14064,7 @@
       <c r="N120" s="26"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="92"/>
+      <c r="A121" s="90"/>
       <c r="B121" s="15" t="s">
         <v>442</v>
       </c>
@@ -14093,7 +14084,7 @@
       <c r="N121" s="26"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="92"/>
+      <c r="A122" s="90"/>
       <c r="B122" s="15" t="s">
         <v>404</v>
       </c>
@@ -14113,7 +14104,7 @@
       <c r="N122" s="26"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="92"/>
+      <c r="A123" s="90"/>
       <c r="B123" s="15" t="s">
         <v>228</v>
       </c>
@@ -14155,7 +14146,7 @@
       <c r="N124" s="26"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="92"/>
+      <c r="A125" s="90"/>
       <c r="B125" s="15" t="s">
         <v>433</v>
       </c>
@@ -14175,7 +14166,7 @@
       <c r="N125" s="26"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="92"/>
+      <c r="A126" s="90"/>
       <c r="B126" s="15" t="s">
         <v>256</v>
       </c>
@@ -14195,7 +14186,7 @@
       <c r="N126" s="26"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="92"/>
+      <c r="A127" s="90"/>
       <c r="B127" s="15" t="s">
         <v>420</v>
       </c>
@@ -14215,7 +14206,7 @@
       <c r="N127" s="26"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="92"/>
+      <c r="A128" s="90"/>
       <c r="B128" s="15" t="s">
         <v>242</v>
       </c>
@@ -14235,7 +14226,7 @@
       <c r="N128" s="26"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="92"/>
+      <c r="A129" s="90"/>
       <c r="B129" s="15" t="s">
         <v>247</v>
       </c>
@@ -14255,7 +14246,7 @@
       <c r="N129" s="26"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="92"/>
+      <c r="A130" s="90"/>
       <c r="B130" s="15" t="s">
         <v>422</v>
       </c>
@@ -14275,7 +14266,7 @@
       <c r="N130" s="26"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="92"/>
+      <c r="A131" s="90"/>
       <c r="B131" s="15" t="s">
         <v>230</v>
       </c>
@@ -14295,7 +14286,7 @@
       <c r="N131" s="26"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="92"/>
+      <c r="A132" s="90"/>
       <c r="B132" s="15" t="s">
         <v>275</v>
       </c>
@@ -14315,7 +14306,7 @@
       <c r="N132" s="26"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="92"/>
+      <c r="A133" s="90"/>
       <c r="B133" s="15" t="s">
         <v>262</v>
       </c>
@@ -14335,7 +14326,7 @@
       <c r="N133" s="26"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="92"/>
+      <c r="A134" s="90"/>
       <c r="B134" s="15" t="s">
         <v>265</v>
       </c>
@@ -14355,7 +14346,7 @@
       <c r="N134" s="26"/>
     </row>
     <row r="135" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="92"/>
+      <c r="A135" s="90"/>
       <c r="B135" s="15" t="s">
         <v>210</v>
       </c>
@@ -14397,7 +14388,7 @@
       <c r="N136" s="26"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="92"/>
+      <c r="A137" s="90"/>
       <c r="B137" s="15" t="s">
         <v>209</v>
       </c>
@@ -14417,7 +14408,7 @@
       <c r="N137" s="26"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="92"/>
+      <c r="A138" s="90"/>
       <c r="B138" s="15" t="s">
         <v>299</v>
       </c>
@@ -14437,7 +14428,7 @@
       <c r="N138" s="26"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="92"/>
+      <c r="A139" s="90"/>
       <c r="B139" s="15" t="s">
         <v>286</v>
       </c>
@@ -14457,7 +14448,7 @@
       <c r="N139" s="26"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="92"/>
+      <c r="A140" s="90"/>
       <c r="B140" s="15" t="s">
         <v>239</v>
       </c>
@@ -14477,7 +14468,7 @@
       <c r="N140" s="26"/>
     </row>
     <row r="141" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="92"/>
+      <c r="A141" s="90"/>
       <c r="B141" s="15" t="s">
         <v>285</v>
       </c>
@@ -14497,7 +14488,7 @@
       <c r="N141" s="26"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="92"/>
+      <c r="A142" s="90"/>
       <c r="B142" s="15" t="s">
         <v>232</v>
       </c>
@@ -14561,7 +14552,7 @@
       <c r="N144" s="26"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="92"/>
+      <c r="A145" s="90"/>
       <c r="B145" s="15" t="s">
         <v>294</v>
       </c>
@@ -14581,7 +14572,7 @@
       <c r="N145" s="26"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="92"/>
+      <c r="A146" s="90"/>
       <c r="B146" s="15" t="s">
         <v>260</v>
       </c>
@@ -14601,7 +14592,7 @@
       <c r="N146" s="26"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="92"/>
+      <c r="A147" s="90"/>
       <c r="B147" s="15" t="s">
         <v>385</v>
       </c>
@@ -14621,7 +14612,7 @@
       <c r="N147" s="26"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="92"/>
+      <c r="A148" s="90"/>
       <c r="B148" s="15" t="s">
         <v>224</v>
       </c>
@@ -14641,7 +14632,7 @@
       <c r="N148" s="26"/>
     </row>
     <row r="149" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="93" t="s">
+      <c r="A149" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B149" s="52"/>
@@ -14945,7 +14936,7 @@
       <c r="N163" s="26"/>
     </row>
     <row r="164" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="93" t="s">
+      <c r="A164" s="92" t="s">
         <v>507</v>
       </c>
       <c r="B164" s="52"/>
@@ -14963,7 +14954,7 @@
       <c r="N164" s="26"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="92" t="s">
+      <c r="A165" s="90" t="s">
         <v>214</v>
       </c>
       <c r="B165" s="15" t="s">
@@ -14985,7 +14976,7 @@
       <c r="N165" s="26"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="92"/>
+      <c r="A166" s="90"/>
       <c r="B166" s="15" t="s">
         <v>253</v>
       </c>
@@ -15005,7 +14996,7 @@
       <c r="N166" s="26"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="92"/>
+      <c r="A167" s="90"/>
       <c r="B167" s="15" t="s">
         <v>253</v>
       </c>
@@ -15025,7 +15016,7 @@
       <c r="N167" s="26"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="92" t="s">
+      <c r="A168" s="90" t="s">
         <v>673</v>
       </c>
       <c r="B168" s="15" t="s">
@@ -15047,7 +15038,7 @@
       <c r="N168" s="26"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="92"/>
+      <c r="A169" s="90"/>
       <c r="B169" s="15" t="s">
         <v>381</v>
       </c>
@@ -15067,7 +15058,7 @@
       <c r="N169" s="26"/>
     </row>
     <row r="170" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="92" t="s">
+      <c r="A170" s="90" t="s">
         <v>672</v>
       </c>
       <c r="B170" s="15" t="s">
@@ -15089,7 +15080,7 @@
       <c r="N170" s="26"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="92"/>
+      <c r="A171" s="90"/>
       <c r="B171" s="15" t="s">
         <v>365</v>
       </c>
@@ -15109,7 +15100,7 @@
       <c r="N171" s="26"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="92" t="s">
+      <c r="A172" s="90" t="s">
         <v>671</v>
       </c>
       <c r="B172" s="15" t="s">
@@ -15131,7 +15122,7 @@
       <c r="N172" s="26"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="92"/>
+      <c r="A173" s="90"/>
       <c r="B173" s="15" t="s">
         <v>324</v>
       </c>
@@ -15151,7 +15142,7 @@
       <c r="N173" s="26"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="92" t="s">
+      <c r="A174" s="90" t="s">
         <v>670</v>
       </c>
       <c r="B174" s="15" t="s">
@@ -15173,7 +15164,7 @@
       <c r="N174" s="26"/>
     </row>
     <row r="175" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="92"/>
+      <c r="A175" s="90"/>
       <c r="B175" s="15" t="s">
         <v>604</v>
       </c>
@@ -15193,7 +15184,7 @@
       <c r="N175" s="26"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="92"/>
+      <c r="A176" s="90"/>
       <c r="B176" s="15" t="s">
         <v>605</v>
       </c>
@@ -15213,7 +15204,7 @@
       <c r="N176" s="26"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="92"/>
+      <c r="A177" s="90"/>
       <c r="B177" s="15" t="s">
         <v>606</v>
       </c>
@@ -15233,7 +15224,7 @@
       <c r="N177" s="26"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="92"/>
+      <c r="A178" s="90"/>
       <c r="B178" s="15" t="s">
         <v>607</v>
       </c>
@@ -15253,7 +15244,7 @@
       <c r="N178" s="26"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="92" t="s">
+      <c r="A179" s="90" t="s">
         <v>669</v>
       </c>
       <c r="B179" s="15" t="s">
@@ -15275,7 +15266,7 @@
       <c r="N179" s="26"/>
     </row>
     <row r="180" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="92"/>
+      <c r="A180" s="90"/>
       <c r="B180" s="15" t="s">
         <v>300</v>
       </c>
@@ -15295,7 +15286,7 @@
       <c r="N180" s="26"/>
     </row>
     <row r="181" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="92" t="s">
+      <c r="A181" s="90" t="s">
         <v>668</v>
       </c>
       <c r="B181" s="15" t="s">
@@ -15317,7 +15308,7 @@
       <c r="N181" s="26"/>
     </row>
     <row r="182" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="92"/>
+      <c r="A182" s="90"/>
       <c r="B182" s="15" t="s">
         <v>255</v>
       </c>
@@ -15337,7 +15328,7 @@
       <c r="N182" s="26"/>
     </row>
     <row r="183" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="92"/>
+      <c r="A183" s="90"/>
       <c r="B183" s="15" t="s">
         <v>274</v>
       </c>
@@ -15357,7 +15348,7 @@
       <c r="N183" s="26"/>
     </row>
     <row r="184" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="93" t="s">
+      <c r="A184" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B184" s="52"/>
@@ -15375,7 +15366,7 @@
       <c r="N184" s="26"/>
     </row>
     <row r="185" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="92" t="s">
+      <c r="A185" s="90" t="s">
         <v>680</v>
       </c>
       <c r="B185" s="15" t="s">
@@ -15397,7 +15388,7 @@
       <c r="N185" s="26"/>
     </row>
     <row r="186" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="92"/>
+      <c r="A186" s="90"/>
       <c r="B186" s="15" t="s">
         <v>464</v>
       </c>
@@ -15417,7 +15408,7 @@
       <c r="N186" s="26"/>
     </row>
     <row r="187" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="92" t="s">
+      <c r="A187" s="90" t="s">
         <v>681</v>
       </c>
       <c r="B187" s="15" t="s">
@@ -15439,7 +15430,7 @@
       <c r="N187" s="26"/>
     </row>
     <row r="188" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="92"/>
+      <c r="A188" s="90"/>
       <c r="B188" s="15" t="s">
         <v>454</v>
       </c>
@@ -15459,7 +15450,7 @@
       <c r="N188" s="26"/>
     </row>
     <row r="189" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="92"/>
+      <c r="A189" s="90"/>
       <c r="B189" s="15" t="s">
         <v>458</v>
       </c>
@@ -15479,7 +15470,7 @@
       <c r="N189" s="26"/>
     </row>
     <row r="190" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="92"/>
+      <c r="A190" s="90"/>
       <c r="B190" s="15" t="s">
         <v>462</v>
       </c>
@@ -15499,7 +15490,7 @@
       <c r="N190" s="26"/>
     </row>
     <row r="191" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="92"/>
+      <c r="A191" s="90"/>
       <c r="B191" s="15" t="s">
         <v>445</v>
       </c>
@@ -15519,7 +15510,7 @@
       <c r="N191" s="26"/>
     </row>
     <row r="192" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="92"/>
+      <c r="A192" s="90"/>
       <c r="B192" s="15" t="s">
         <v>456</v>
       </c>
@@ -15539,7 +15530,7 @@
       <c r="N192" s="26"/>
     </row>
     <row r="193" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="92" t="s">
+      <c r="A193" s="90" t="s">
         <v>623</v>
       </c>
       <c r="B193" s="15" t="s">
@@ -15561,7 +15552,7 @@
       <c r="N193" s="26"/>
     </row>
     <row r="194" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="92"/>
+      <c r="A194" s="90"/>
       <c r="B194" s="15" t="s">
         <v>676</v>
       </c>
@@ -15581,7 +15572,7 @@
       <c r="N194" s="26"/>
     </row>
     <row r="195" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="92"/>
+      <c r="A195" s="90"/>
       <c r="B195" s="15" t="s">
         <v>678</v>
       </c>
@@ -15604,11 +15595,11 @@
       <c r="A196" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B196" s="55"/>
-      <c r="C196" s="55"/>
-      <c r="D196" s="55"/>
-      <c r="E196" s="55"/>
-      <c r="F196" s="56"/>
+      <c r="B196" s="86"/>
+      <c r="C196" s="86"/>
+      <c r="D196" s="86"/>
+      <c r="E196" s="86"/>
+      <c r="F196" s="87"/>
       <c r="G196" s="47"/>
       <c r="H196" s="47"/>
       <c r="I196" s="47"/>
@@ -15619,14 +15610,14 @@
       <c r="N196" s="28"/>
     </row>
     <row r="197" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A197" s="57" t="s">
+      <c r="A197" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="B197" s="58"/>
-      <c r="C197" s="58"/>
-      <c r="D197" s="58"/>
-      <c r="E197" s="58"/>
-      <c r="F197" s="59"/>
+      <c r="B197" s="89"/>
+      <c r="C197" s="89"/>
+      <c r="D197" s="89"/>
+      <c r="E197" s="89"/>
+      <c r="F197" s="77"/>
       <c r="G197" s="48"/>
       <c r="H197" s="48"/>
       <c r="I197" s="48"/>
@@ -15670,27 +15661,28 @@
     </row>
   </sheetData>
   <mergeCells count="59">
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A21:A28"/>
-    <mergeCell ref="A35:A46"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A48:A58"/>
+    <mergeCell ref="A60:A74"/>
+    <mergeCell ref="A76:A81"/>
+    <mergeCell ref="A83:A86"/>
+    <mergeCell ref="A88:A93"/>
+    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="A124:A135"/>
+    <mergeCell ref="A136:A142"/>
+    <mergeCell ref="A144:A148"/>
+    <mergeCell ref="A115:A123"/>
+    <mergeCell ref="A100:A114"/>
+    <mergeCell ref="A94:F94"/>
+    <mergeCell ref="A95:A96"/>
+    <mergeCell ref="A97:A98"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A181:A183"/>
+    <mergeCell ref="A170:A171"/>
+    <mergeCell ref="A172:A173"/>
+    <mergeCell ref="A87:F87"/>
+    <mergeCell ref="A165:A167"/>
     <mergeCell ref="A8:A19"/>
     <mergeCell ref="A47:F47"/>
     <mergeCell ref="A197:F197"/>
@@ -15707,28 +15699,27 @@
     <mergeCell ref="A162:A163"/>
     <mergeCell ref="A174:A178"/>
     <mergeCell ref="A179:A180"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A181:A183"/>
-    <mergeCell ref="A170:A171"/>
-    <mergeCell ref="A172:A173"/>
-    <mergeCell ref="A87:F87"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A124:A135"/>
-    <mergeCell ref="A136:A142"/>
-    <mergeCell ref="A144:A148"/>
-    <mergeCell ref="A115:A123"/>
-    <mergeCell ref="A165:A167"/>
-    <mergeCell ref="A100:A114"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A48:A58"/>
-    <mergeCell ref="A60:A74"/>
-    <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A75:F75"/>
+    <mergeCell ref="A21:A28"/>
+    <mergeCell ref="A35:A46"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18213,22 +18204,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
+      <c r="O2" s="73"/>
+      <c r="P2" s="73"/>
     </row>
     <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -18261,75 +18252,75 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="58" t="s">
         <v>625</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="58" t="s">
         <v>626</v>
       </c>
-      <c r="E6" s="99" t="s">
+      <c r="E6" s="65" t="s">
         <v>727</v>
       </c>
-      <c r="F6" s="101" t="s">
+      <c r="F6" s="67" t="s">
         <v>728</v>
       </c>
-      <c r="G6" s="84" t="s">
+      <c r="G6" s="58" t="s">
         <v>627</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="54" t="s">
         <v>628</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="54" t="s">
         <v>578</v>
       </c>
-      <c r="J6" s="79" t="s">
+      <c r="J6" s="54" t="s">
         <v>582</v>
       </c>
-      <c r="K6" s="79" t="s">
+      <c r="K6" s="54" t="s">
         <v>588</v>
       </c>
-      <c r="L6" s="79" t="s">
+      <c r="L6" s="54" t="s">
         <v>589</v>
       </c>
-      <c r="M6" s="79" t="s">
+      <c r="M6" s="54" t="s">
         <v>590</v>
       </c>
-      <c r="N6" s="79" t="s">
+      <c r="N6" s="54" t="s">
         <v>608</v>
       </c>
-      <c r="O6" s="79" t="s">
+      <c r="O6" s="54" t="s">
         <v>629</v>
       </c>
-      <c r="P6" s="82" t="s">
+      <c r="P6" s="74" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="90"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="100"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="83"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="66"/>
+      <c r="F7" s="66"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="55"/>
+      <c r="O7" s="55"/>
+      <c r="P7" s="75"/>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="93" t="s">
         <v>710</v>
       </c>
       <c r="B8" s="23">
@@ -18353,7 +18344,7 @@
       <c r="P8" s="27"/>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="92"/>
+      <c r="A9" s="90"/>
       <c r="B9" s="15">
         <v>7427</v>
       </c>
@@ -18375,7 +18366,7 @@
       <c r="P9" s="26"/>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="92"/>
+      <c r="A10" s="90"/>
       <c r="B10" s="18">
         <v>7429</v>
       </c>
@@ -18397,7 +18388,7 @@
       <c r="P10" s="26"/>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="92"/>
+      <c r="A11" s="90"/>
       <c r="B11" s="18">
         <v>7431</v>
       </c>
@@ -18419,7 +18410,7 @@
       <c r="P11" s="26"/>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="92"/>
+      <c r="A12" s="90"/>
       <c r="B12" s="18">
         <v>7433</v>
       </c>
@@ -18441,7 +18432,7 @@
       <c r="P12" s="26"/>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="92"/>
+      <c r="A13" s="90"/>
       <c r="B13" s="18">
         <v>7435</v>
       </c>
@@ -18463,7 +18454,7 @@
       <c r="P13" s="26"/>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="92"/>
+      <c r="A14" s="90"/>
       <c r="B14" s="18">
         <v>7437</v>
       </c>
@@ -18485,7 +18476,7 @@
       <c r="P14" s="26"/>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="92"/>
+      <c r="A15" s="90"/>
       <c r="B15" s="18">
         <v>7439</v>
       </c>
@@ -18507,7 +18498,7 @@
       <c r="P15" s="26"/>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="92"/>
+      <c r="A16" s="90"/>
       <c r="B16" s="18">
         <v>7441</v>
       </c>
@@ -18529,7 +18520,7 @@
       <c r="P16" s="26"/>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="92"/>
+      <c r="A17" s="90"/>
       <c r="B17" s="18">
         <v>7426</v>
       </c>
@@ -18551,7 +18542,7 @@
       <c r="P17" s="26"/>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="92"/>
+      <c r="A18" s="90"/>
       <c r="B18" s="18">
         <v>7430</v>
       </c>
@@ -18573,7 +18564,7 @@
       <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="92"/>
+      <c r="A19" s="90"/>
       <c r="B19" s="18">
         <v>7432</v>
       </c>
@@ -18595,7 +18586,7 @@
       <c r="P19" s="26"/>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="92"/>
+      <c r="A20" s="90"/>
       <c r="B20" s="18">
         <v>7434</v>
       </c>
@@ -18617,7 +18608,7 @@
       <c r="P20" s="26"/>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="92"/>
+      <c r="A21" s="90"/>
       <c r="B21" s="18">
         <v>7436</v>
       </c>
@@ -18639,7 +18630,7 @@
       <c r="P21" s="26"/>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="92"/>
+      <c r="A22" s="90"/>
       <c r="B22" s="18">
         <v>7438</v>
       </c>
@@ -18661,7 +18652,7 @@
       <c r="P22" s="26"/>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="92"/>
+      <c r="A23" s="90"/>
       <c r="B23" s="18">
         <v>7440</v>
       </c>
@@ -18683,7 +18674,7 @@
       <c r="P23" s="26"/>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="92"/>
+      <c r="A24" s="90"/>
       <c r="B24" s="18">
         <v>7442</v>
       </c>
@@ -18705,7 +18696,7 @@
       <c r="P24" s="26"/>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="92"/>
+      <c r="A25" s="90"/>
       <c r="B25" s="18">
         <v>7443</v>
       </c>
@@ -18727,7 +18718,7 @@
       <c r="P25" s="26"/>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="92"/>
+      <c r="A26" s="90"/>
       <c r="B26" s="18">
         <v>7445</v>
       </c>
@@ -18749,7 +18740,7 @@
       <c r="P26" s="26"/>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="92"/>
+      <c r="A27" s="90"/>
       <c r="B27" s="18">
         <v>7444</v>
       </c>
@@ -18771,7 +18762,7 @@
       <c r="P27" s="26"/>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="92"/>
+      <c r="A28" s="90"/>
       <c r="B28" s="18">
         <v>7446</v>
       </c>
@@ -18793,7 +18784,7 @@
       <c r="P28" s="26"/>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="92"/>
+      <c r="A29" s="90"/>
       <c r="B29" s="18">
         <v>7448</v>
       </c>
@@ -18815,7 +18806,7 @@
       <c r="P29" s="26"/>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="92"/>
+      <c r="A30" s="90"/>
       <c r="B30" s="18">
         <v>7450</v>
       </c>
@@ -18837,7 +18828,7 @@
       <c r="P30" s="26"/>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="93" t="s">
+      <c r="A31" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B31" s="52"/>
@@ -18857,7 +18848,7 @@
       <c r="P31" s="26"/>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="92" t="s">
+      <c r="A32" s="90" t="s">
         <v>711</v>
       </c>
       <c r="B32" s="15" t="s">
@@ -18881,7 +18872,7 @@
       <c r="P32" s="26"/>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="92"/>
+      <c r="A33" s="90"/>
       <c r="B33" s="15" t="s">
         <v>494</v>
       </c>
@@ -18903,7 +18894,7 @@
       <c r="P33" s="26"/>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="92"/>
+      <c r="A34" s="90"/>
       <c r="B34" s="15" t="s">
         <v>491</v>
       </c>
@@ -18925,7 +18916,7 @@
       <c r="P34" s="26"/>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="92"/>
+      <c r="A35" s="90"/>
       <c r="B35" s="15" t="s">
         <v>473</v>
       </c>
@@ -18947,7 +18938,7 @@
       <c r="P35" s="26"/>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="92"/>
+      <c r="A36" s="90"/>
       <c r="B36" s="15" t="s">
         <v>384</v>
       </c>
@@ -18969,7 +18960,7 @@
       <c r="P36" s="26"/>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="92"/>
+      <c r="A37" s="90"/>
       <c r="B37" s="15" t="s">
         <v>389</v>
       </c>
@@ -18991,7 +18982,7 @@
       <c r="P37" s="26"/>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="92"/>
+      <c r="A38" s="90"/>
       <c r="B38" s="15" t="s">
         <v>449</v>
       </c>
@@ -19013,7 +19004,7 @@
       <c r="P38" s="26"/>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="92"/>
+      <c r="A39" s="90"/>
       <c r="B39" s="15" t="s">
         <v>483</v>
       </c>
@@ -19035,7 +19026,7 @@
       <c r="P39" s="26"/>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="93" t="s">
+      <c r="A40" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B40" s="52"/>
@@ -19255,7 +19246,7 @@
       <c r="P49" s="26"/>
     </row>
     <row r="50" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="93" t="s">
+      <c r="A50" s="92" t="s">
         <v>507</v>
       </c>
       <c r="B50" s="52"/>
@@ -19275,7 +19266,7 @@
       <c r="P50" s="26"/>
     </row>
     <row r="51" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="92" t="s">
+      <c r="A51" s="90" t="s">
         <v>715</v>
       </c>
       <c r="B51" s="29" t="s">
@@ -19299,7 +19290,7 @@
       <c r="P51" s="26"/>
     </row>
     <row r="52" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="92"/>
+      <c r="A52" s="90"/>
       <c r="B52" s="29" t="s">
         <v>488</v>
       </c>
@@ -19321,7 +19312,7 @@
       <c r="P52" s="26"/>
     </row>
     <row r="53" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="92"/>
+      <c r="A53" s="90"/>
       <c r="B53" s="29" t="s">
         <v>346</v>
       </c>
@@ -19343,7 +19334,7 @@
       <c r="P53" s="26"/>
     </row>
     <row r="54" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="92"/>
+      <c r="A54" s="90"/>
       <c r="B54" s="29" t="s">
         <v>382</v>
       </c>
@@ -19365,7 +19356,7 @@
       <c r="P54" s="26"/>
     </row>
     <row r="55" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="92"/>
+      <c r="A55" s="90"/>
       <c r="B55" s="29" t="s">
         <v>581</v>
       </c>
@@ -19387,7 +19378,7 @@
       <c r="P55" s="26"/>
     </row>
     <row r="56" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="93" t="s">
+      <c r="A56" s="92" t="s">
         <v>114</v>
       </c>
       <c r="B56" s="52"/>
@@ -19407,7 +19398,7 @@
       <c r="P56" s="26"/>
     </row>
     <row r="57" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="92" t="s">
+      <c r="A57" s="90" t="s">
         <v>716</v>
       </c>
       <c r="B57" s="15" t="s">
@@ -19431,7 +19422,7 @@
       <c r="P57" s="26"/>
     </row>
     <row r="58" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="92"/>
+      <c r="A58" s="90"/>
       <c r="B58" s="15" t="s">
         <v>717</v>
       </c>
@@ -19453,7 +19444,7 @@
       <c r="P58" s="26"/>
     </row>
     <row r="59" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="92"/>
+      <c r="A59" s="90"/>
       <c r="B59" s="15" t="s">
         <v>718</v>
       </c>
@@ -19475,7 +19466,7 @@
       <c r="P59" s="26"/>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="92"/>
+      <c r="A60" s="90"/>
       <c r="B60" s="15" t="s">
         <v>719</v>
       </c>
@@ -19497,7 +19488,7 @@
       <c r="P60" s="26"/>
     </row>
     <row r="61" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="92"/>
+      <c r="A61" s="90"/>
       <c r="B61" s="15" t="s">
         <v>720</v>
       </c>
@@ -19519,7 +19510,7 @@
       <c r="P61" s="26"/>
     </row>
     <row r="62" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="92"/>
+      <c r="A62" s="90"/>
       <c r="B62" s="15" t="s">
         <v>584</v>
       </c>
@@ -19541,7 +19532,7 @@
       <c r="P62" s="26"/>
     </row>
     <row r="63" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="92"/>
+      <c r="A63" s="90"/>
       <c r="B63" s="15" t="s">
         <v>585</v>
       </c>
@@ -19563,7 +19554,7 @@
       <c r="P63" s="26"/>
     </row>
     <row r="64" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="92"/>
+      <c r="A64" s="90"/>
       <c r="B64" s="15" t="s">
         <v>587</v>
       </c>
@@ -19585,7 +19576,7 @@
       <c r="P64" s="26"/>
     </row>
     <row r="65" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="92"/>
+      <c r="A65" s="90"/>
       <c r="B65" s="15" t="s">
         <v>586</v>
       </c>
@@ -19610,13 +19601,13 @@
       <c r="A66" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B66" s="55"/>
-      <c r="C66" s="55"/>
-      <c r="D66" s="55"/>
-      <c r="E66" s="55"/>
-      <c r="F66" s="55"/>
-      <c r="G66" s="55"/>
-      <c r="H66" s="56"/>
+      <c r="B66" s="86"/>
+      <c r="C66" s="86"/>
+      <c r="D66" s="86"/>
+      <c r="E66" s="86"/>
+      <c r="F66" s="86"/>
+      <c r="G66" s="86"/>
+      <c r="H66" s="87"/>
       <c r="I66" s="47"/>
       <c r="J66" s="47"/>
       <c r="K66" s="47"/>
@@ -19627,16 +19618,16 @@
       <c r="P66" s="28"/>
     </row>
     <row r="67" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="57" t="s">
+      <c r="A67" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="B67" s="58"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="59"/>
+      <c r="B67" s="89"/>
+      <c r="C67" s="89"/>
+      <c r="D67" s="89"/>
+      <c r="E67" s="89"/>
+      <c r="F67" s="89"/>
+      <c r="G67" s="89"/>
+      <c r="H67" s="77"/>
       <c r="I67" s="48"/>
       <c r="J67" s="48"/>
       <c r="K67" s="48"/>
@@ -19666,6 +19657,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="A57:A65"/>
+    <mergeCell ref="A8:A30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A41:A49"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A6:A7"/>
@@ -19682,18 +19685,6 @@
     <mergeCell ref="N6:N7"/>
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="A57:A65"/>
-    <mergeCell ref="A8:A30"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="A41:A49"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22178,20 +22169,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="A2" s="73"/>
+      <c r="B2" s="73"/>
+      <c r="C2" s="73"/>
+      <c r="D2" s="73"/>
+      <c r="E2" s="73"/>
+      <c r="F2" s="73"/>
+      <c r="G2" s="73"/>
+      <c r="H2" s="73"/>
+      <c r="I2" s="73"/>
+      <c r="J2" s="73"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="73"/>
+      <c r="N2" s="73"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -22222,67 +22213,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
+      <c r="A6" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="B6" s="86" t="s">
+      <c r="B6" s="56" t="s">
         <v>624</v>
       </c>
-      <c r="C6" s="84" t="s">
+      <c r="C6" s="58" t="s">
         <v>625</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="58" t="s">
         <v>626</v>
       </c>
-      <c r="E6" s="84" t="s">
+      <c r="E6" s="58" t="s">
         <v>627</v>
       </c>
-      <c r="F6" s="79" t="s">
+      <c r="F6" s="54" t="s">
         <v>628</v>
       </c>
-      <c r="G6" s="79" t="s">
+      <c r="G6" s="54" t="s">
         <v>578</v>
       </c>
-      <c r="H6" s="79" t="s">
+      <c r="H6" s="54" t="s">
         <v>582</v>
       </c>
-      <c r="I6" s="79" t="s">
+      <c r="I6" s="54" t="s">
         <v>588</v>
       </c>
-      <c r="J6" s="79" t="s">
+      <c r="J6" s="54" t="s">
         <v>589</v>
       </c>
-      <c r="K6" s="79" t="s">
+      <c r="K6" s="54" t="s">
         <v>590</v>
       </c>
-      <c r="L6" s="79" t="s">
+      <c r="L6" s="54" t="s">
         <v>608</v>
       </c>
-      <c r="M6" s="79" t="s">
+      <c r="M6" s="54" t="s">
         <v>629</v>
       </c>
-      <c r="N6" s="82" t="s">
+      <c r="N6" s="74" t="s">
         <v>630</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="90"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="83"/>
+      <c r="A7" s="64"/>
+      <c r="B7" s="57"/>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="55"/>
+      <c r="G7" s="55"/>
+      <c r="H7" s="55"/>
+      <c r="I7" s="55"/>
+      <c r="J7" s="55"/>
+      <c r="K7" s="55"/>
+      <c r="L7" s="55"/>
+      <c r="M7" s="55"/>
+      <c r="N7" s="75"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="95" t="s">
+      <c r="A8" s="93" t="s">
         <v>724</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -22511,11 +22502,11 @@
       <c r="A19" s="94" t="s">
         <v>114</v>
       </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="56"/>
+      <c r="B19" s="86"/>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="87"/>
       <c r="G19" s="47"/>
       <c r="H19" s="47"/>
       <c r="I19" s="47"/>
@@ -22526,14 +22517,14 @@
       <c r="N19" s="28"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="88" t="s">
         <v>94</v>
       </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="59"/>
+      <c r="B20" s="89"/>
+      <c r="C20" s="89"/>
+      <c r="D20" s="89"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="77"/>
       <c r="G20" s="48"/>
       <c r="H20" s="48"/>
       <c r="I20" s="48"/>
@@ -22577,6 +22568,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
@@ -22591,11 +22587,6 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/temp.xlsx
+++ b/data/temp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD928607-0204-43BB-B01D-BBEEF224235D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C913B2F4-FB1C-4804-A9C0-88EE6EECE02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19200" yWindow="0" windowWidth="19200" windowHeight="15600" tabRatio="613" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="완제품 임가공" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="849" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="725">
   <si>
     <t xml:space="preserve"> APBL2-AL22 G</t>
   </si>
@@ -215,9 +215,6 @@
     <t>(SET)DC 48V ASS`Y</t>
   </si>
   <si>
-    <t>DC 30V(COIL)ASS`Y</t>
-  </si>
-  <si>
     <t>BR2 2A2B 하부+홀다 앗세이</t>
   </si>
   <si>
@@ -681,9 +678,6 @@
     <t>016532</t>
   </si>
   <si>
-    <t>T.T.R</t>
-  </si>
-  <si>
     <t>6P(일체형)</t>
   </si>
   <si>
@@ -777,9 +771,6 @@
     <t>022706</t>
   </si>
   <si>
-    <t>024018</t>
-  </si>
-  <si>
     <t>017284</t>
   </si>
   <si>
@@ -939,9 +930,6 @@
     <t>019846</t>
   </si>
   <si>
-    <t>021738</t>
-  </si>
-  <si>
     <t>014906</t>
   </si>
   <si>
@@ -1072,9 +1060,6 @@
   </si>
   <si>
     <t>008118</t>
-  </si>
-  <si>
-    <t>023181</t>
   </si>
   <si>
     <t>022509</t>
@@ -1660,9 +1645,6 @@
     <t>(RE SET)AC 220V ASS`Y</t>
   </si>
   <si>
-    <t xml:space="preserve"> V형 M S/W 유동접점콕킹 ASS'Y</t>
-  </si>
-  <si>
     <t>YSSK MY-2S(RY08A-C6)</t>
   </si>
   <si>
@@ -1754,9 +1736,6 @@
   </si>
   <si>
     <t>BPL용LEDAC110V PCB앗세이</t>
-  </si>
-  <si>
-    <t>신형 캠 10A 하부 A'SSY(흑색하부)(볼트체결)</t>
   </si>
   <si>
     <t>AC 110V_60HZ(COIL)ASS`Y(2중권선)</t>
@@ -1862,21 +1841,6 @@
   </si>
   <si>
     <t>028585</t>
-  </si>
-  <si>
-    <t>028758</t>
-  </si>
-  <si>
-    <t>028759</t>
-  </si>
-  <si>
-    <t>028760</t>
-  </si>
-  <si>
-    <t>028761</t>
-  </si>
-  <si>
-    <t>028762</t>
   </si>
   <si>
     <t>11&amp;12차
@@ -2085,21 +2049,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>소형 리미트 고정점점콕킹 ASSY(단-좌)</t>
-  </si>
-  <si>
-    <t>소형 리미트 고정점점콕킹 ASSY(단-우)</t>
-  </si>
-  <si>
-    <t>소형 리미트 고정점점콕킹 ASSY(장-좌)</t>
-  </si>
-  <si>
-    <t>소형 리미트 고정점점콕킹 ASSY(장-우)</t>
-  </si>
-  <si>
-    <t>소형 리미트 유동접점 콕킹 ASS`Y</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Z형 M S/W 1번고정접점콕킹 ASS'Y</t>
   </si>
   <si>
@@ -2372,6 +2321,14 @@
   </si>
   <si>
     <t>BPBL 25@ 홀다 ASS'Y G</t>
+  </si>
+  <si>
+    <t>NPBL 고정접점(NC) ASS`Y A</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>NPBL 고정접점(NC) ASS`Y B</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2478,7 +2435,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="37">
+  <borders count="38">
     <border>
       <left/>
       <right/>
@@ -2978,6 +2935,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2996,7 +2964,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3150,7 +3118,52 @@
     <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3159,14 +3172,8 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3177,11 +3184,50 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3196,12 +3242,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3225,80 +3265,20 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6284,22 +6264,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
     </row>
     <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -6317,13 +6297,13 @@
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
       <c r="O3" s="32" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="P3" s="50"/>
     </row>
     <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O4" s="37" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="P4" s="50"/>
     </row>
@@ -6332,82 +6312,82 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="86" t="s">
-        <v>624</v>
-      </c>
-      <c r="C6" s="84" t="s">
-        <v>625</v>
-      </c>
-      <c r="D6" s="84" t="s">
-        <v>626</v>
-      </c>
-      <c r="E6" s="91" t="s">
-        <v>727</v>
-      </c>
-      <c r="F6" s="93" t="s">
-        <v>728</v>
-      </c>
-      <c r="G6" s="84" t="s">
-        <v>627</v>
-      </c>
-      <c r="H6" s="79" t="s">
-        <v>628</v>
-      </c>
-      <c r="I6" s="79" t="s">
-        <v>578</v>
-      </c>
-      <c r="J6" s="79" t="s">
+      <c r="A6" s="56" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>612</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>614</v>
+      </c>
+      <c r="E6" s="80" t="s">
+        <v>710</v>
+      </c>
+      <c r="F6" s="82" t="s">
+        <v>711</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>615</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>616</v>
+      </c>
+      <c r="I6" s="62" t="s">
+        <v>571</v>
+      </c>
+      <c r="J6" s="62" t="s">
+        <v>575</v>
+      </c>
+      <c r="K6" s="62" t="s">
+        <v>581</v>
+      </c>
+      <c r="L6" s="62" t="s">
         <v>582</v>
       </c>
-      <c r="K6" s="79" t="s">
-        <v>588</v>
-      </c>
-      <c r="L6" s="79" t="s">
-        <v>589</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>590</v>
-      </c>
-      <c r="N6" s="79" t="s">
-        <v>608</v>
-      </c>
-      <c r="O6" s="79" t="s">
-        <v>629</v>
-      </c>
-      <c r="P6" s="82" t="s">
-        <v>630</v>
+      <c r="M6" s="62" t="s">
+        <v>583</v>
+      </c>
+      <c r="N6" s="62" t="s">
+        <v>596</v>
+      </c>
+      <c r="O6" s="62" t="s">
+        <v>617</v>
+      </c>
+      <c r="P6" s="64" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="90"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="83"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="65"/>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="88" t="s">
-        <v>150</v>
+      <c r="A8" s="77" t="s">
+        <v>149</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -6424,12 +6404,12 @@
       <c r="P8" s="25"/>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="60"/>
+      <c r="A9" s="78"/>
       <c r="B9" s="15" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -6446,12 +6426,12 @@
       <c r="P9" s="14"/>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="60"/>
+      <c r="A10" s="78"/>
       <c r="B10" s="15" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
@@ -6468,12 +6448,12 @@
       <c r="P10" s="14"/>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="60"/>
+      <c r="A11" s="78"/>
       <c r="B11" s="15" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
@@ -6490,12 +6470,12 @@
       <c r="P11" s="14"/>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="60"/>
+      <c r="A12" s="78"/>
       <c r="B12" s="15" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -6512,12 +6492,12 @@
       <c r="P12" s="14"/>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60"/>
+      <c r="A13" s="78"/>
       <c r="B13" s="15" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -6534,12 +6514,12 @@
       <c r="P13" s="14"/>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="60"/>
+      <c r="A14" s="78"/>
       <c r="B14" s="15" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -6556,12 +6536,12 @@
       <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="60"/>
+      <c r="A15" s="78"/>
       <c r="B15" s="15" t="s">
-        <v>383</v>
+        <v>378</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -6578,16 +6558,16 @@
       <c r="P15" s="14"/>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" s="52"/>
-      <c r="C16" s="52"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="52"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="52"/>
-      <c r="H16" s="53"/>
+      <c r="A16" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B16" s="67"/>
+      <c r="C16" s="67"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="67"/>
+      <c r="G16" s="67"/>
+      <c r="H16" s="68"/>
       <c r="I16" s="38"/>
       <c r="J16" s="38"/>
       <c r="K16" s="38"/>
@@ -6598,14 +6578,14 @@
       <c r="P16" s="14"/>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="61" t="s">
-        <v>634</v>
+      <c r="A17" s="79" t="s">
+        <v>622</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -6622,12 +6602,12 @@
       <c r="P17" s="14"/>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="60"/>
+      <c r="A18" s="78"/>
       <c r="B18" s="15" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -6644,12 +6624,12 @@
       <c r="P18" s="14"/>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="60"/>
+      <c r="A19" s="78"/>
       <c r="B19" s="15" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -6666,12 +6646,12 @@
       <c r="P19" s="14"/>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="60"/>
+      <c r="A20" s="78"/>
       <c r="B20" s="15" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
@@ -6688,16 +6668,16 @@
       <c r="P20" s="14"/>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" s="52"/>
-      <c r="C21" s="52"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="52"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="52"/>
-      <c r="H21" s="53"/>
+      <c r="A21" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="67"/>
+      <c r="C21" s="67"/>
+      <c r="D21" s="67"/>
+      <c r="E21" s="67"/>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="68"/>
       <c r="I21" s="38"/>
       <c r="J21" s="38"/>
       <c r="K21" s="38"/>
@@ -6708,14 +6688,14 @@
       <c r="P21" s="14"/>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="61" t="s">
-        <v>435</v>
+      <c r="A22" s="79" t="s">
+        <v>430</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -6732,12 +6712,12 @@
       <c r="P22" s="14"/>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="61"/>
+      <c r="A23" s="79"/>
       <c r="B23" s="15" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -6754,12 +6734,12 @@
       <c r="P23" s="14"/>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="61"/>
+      <c r="A24" s="79"/>
       <c r="B24" s="15" t="s">
-        <v>362</v>
+        <v>357</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -6776,12 +6756,12 @@
       <c r="P24" s="14"/>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="61"/>
+      <c r="A25" s="79"/>
       <c r="B25" s="15" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -6798,12 +6778,12 @@
       <c r="P25" s="14"/>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="61"/>
+      <c r="A26" s="79"/>
       <c r="B26" s="15" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -6820,12 +6800,12 @@
       <c r="P26" s="14"/>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="61"/>
+      <c r="A27" s="79"/>
       <c r="B27" s="15" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -6842,12 +6822,12 @@
       <c r="P27" s="14"/>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="61"/>
+      <c r="A28" s="79"/>
       <c r="B28" s="15" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -6864,12 +6844,12 @@
       <c r="P28" s="14"/>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="61"/>
+      <c r="A29" s="79"/>
       <c r="B29" s="15" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
@@ -6886,12 +6866,12 @@
       <c r="P29" s="14"/>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="61"/>
+      <c r="A30" s="79"/>
       <c r="B30" s="15" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -6908,12 +6888,12 @@
       <c r="P30" s="14"/>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="61"/>
+      <c r="A31" s="79"/>
       <c r="B31" s="15" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -6930,12 +6910,12 @@
       <c r="P31" s="14"/>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="61"/>
+      <c r="A32" s="79"/>
       <c r="B32" s="15" t="s">
-        <v>347</v>
+        <v>342</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -6952,12 +6932,12 @@
       <c r="P32" s="14"/>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="61"/>
+      <c r="A33" s="79"/>
       <c r="B33" s="15" t="s">
-        <v>358</v>
+        <v>353</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -6974,12 +6954,12 @@
       <c r="P33" s="14"/>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="61"/>
+      <c r="A34" s="79"/>
       <c r="B34" s="15" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -6996,12 +6976,12 @@
       <c r="P34" s="14"/>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="61"/>
+      <c r="A35" s="79"/>
       <c r="B35" s="15" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -7018,12 +6998,12 @@
       <c r="P35" s="14"/>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="61"/>
+      <c r="A36" s="79"/>
       <c r="B36" s="15" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -7040,12 +7020,12 @@
       <c r="P36" s="14"/>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="61"/>
+      <c r="A37" s="79"/>
       <c r="B37" s="15" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -7062,12 +7042,12 @@
       <c r="P37" s="14"/>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="61"/>
+      <c r="A38" s="79"/>
       <c r="B38" s="15" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -7084,12 +7064,12 @@
       <c r="P38" s="14"/>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="61"/>
+      <c r="A39" s="79"/>
       <c r="B39" s="15" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -7106,12 +7086,12 @@
       <c r="P39" s="14"/>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="61"/>
+      <c r="A40" s="79"/>
       <c r="B40" s="15" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -7128,12 +7108,12 @@
       <c r="P40" s="14"/>
     </row>
     <row r="41" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="61"/>
+      <c r="A41" s="79"/>
       <c r="B41" s="15" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -7150,12 +7130,12 @@
       <c r="P41" s="14"/>
     </row>
     <row r="42" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="61"/>
+      <c r="A42" s="79"/>
       <c r="B42" s="15" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -7172,12 +7152,12 @@
       <c r="P42" s="14"/>
     </row>
     <row r="43" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="61"/>
+      <c r="A43" s="79"/>
       <c r="B43" s="15" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -7194,12 +7174,12 @@
       <c r="P43" s="14"/>
     </row>
     <row r="44" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="61"/>
+      <c r="A44" s="79"/>
       <c r="B44" s="15" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -7216,12 +7196,12 @@
       <c r="P44" s="14"/>
     </row>
     <row r="45" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="61"/>
+      <c r="A45" s="79"/>
       <c r="B45" s="15" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -7238,16 +7218,16 @@
       <c r="P45" s="14"/>
     </row>
     <row r="46" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B46" s="52"/>
-      <c r="C46" s="52"/>
-      <c r="D46" s="52"/>
-      <c r="E46" s="52"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="52"/>
-      <c r="H46" s="53"/>
+      <c r="A46" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="67"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="67"/>
+      <c r="G46" s="67"/>
+      <c r="H46" s="68"/>
       <c r="I46" s="38"/>
       <c r="J46" s="38"/>
       <c r="K46" s="38"/>
@@ -7258,11 +7238,11 @@
       <c r="P46" s="14"/>
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="60" t="s">
-        <v>463</v>
+      <c r="A47" s="78" t="s">
+        <v>458</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>51</v>
@@ -7282,9 +7262,9 @@
       <c r="P47" s="14"/>
     </row>
     <row r="48" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="60"/>
+      <c r="A48" s="78"/>
       <c r="B48" s="15" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>48</v>
@@ -7304,9 +7284,9 @@
       <c r="P48" s="14"/>
     </row>
     <row r="49" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="60"/>
+      <c r="A49" s="78"/>
       <c r="B49" s="15" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>45</v>
@@ -7326,9 +7306,9 @@
       <c r="P49" s="14"/>
     </row>
     <row r="50" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="60"/>
+      <c r="A50" s="78"/>
       <c r="B50" s="15" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>34</v>
@@ -7348,9 +7328,9 @@
       <c r="P50" s="14"/>
     </row>
     <row r="51" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="60"/>
+      <c r="A51" s="78"/>
       <c r="B51" s="15" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>44</v>
@@ -7370,9 +7350,9 @@
       <c r="P51" s="14"/>
     </row>
     <row r="52" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="60"/>
+      <c r="A52" s="78"/>
       <c r="B52" s="15" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>53</v>
@@ -7392,11 +7372,11 @@
       <c r="P52" s="14"/>
     </row>
     <row r="53" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="60" t="s">
-        <v>459</v>
+      <c r="A53" s="78" t="s">
+        <v>454</v>
       </c>
       <c r="B53" s="15" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>54</v>
@@ -7416,9 +7396,9 @@
       <c r="P53" s="14"/>
     </row>
     <row r="54" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="60"/>
+      <c r="A54" s="78"/>
       <c r="B54" s="15" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>0</v>
@@ -7438,9 +7418,9 @@
       <c r="P54" s="14"/>
     </row>
     <row r="55" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="60"/>
+      <c r="A55" s="78"/>
       <c r="B55" s="15" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>39</v>
@@ -7460,9 +7440,9 @@
       <c r="P55" s="14"/>
     </row>
     <row r="56" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="60"/>
+      <c r="A56" s="78"/>
       <c r="B56" s="15" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>23</v>
@@ -7482,9 +7462,9 @@
       <c r="P56" s="14"/>
     </row>
     <row r="57" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="60"/>
+      <c r="A57" s="78"/>
       <c r="B57" s="15" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>17</v>
@@ -7504,9 +7484,9 @@
       <c r="P57" s="14"/>
     </row>
     <row r="58" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="60"/>
+      <c r="A58" s="78"/>
       <c r="B58" s="15" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>50</v>
@@ -7526,16 +7506,16 @@
       <c r="P58" s="14"/>
     </row>
     <row r="59" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59" s="52"/>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="52"/>
-      <c r="H59" s="53"/>
+      <c r="A59" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B59" s="67"/>
+      <c r="C59" s="67"/>
+      <c r="D59" s="67"/>
+      <c r="E59" s="67"/>
+      <c r="F59" s="67"/>
+      <c r="G59" s="67"/>
+      <c r="H59" s="68"/>
       <c r="I59" s="38"/>
       <c r="J59" s="38"/>
       <c r="K59" s="38"/>
@@ -7546,11 +7526,11 @@
       <c r="P59" s="14"/>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="60" t="s">
-        <v>515</v>
+      <c r="A60" s="78" t="s">
+        <v>510</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="C60" s="4" t="s">
         <v>7</v>
@@ -7570,12 +7550,12 @@
       <c r="P60" s="14"/>
     </row>
     <row r="61" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="60"/>
+      <c r="A61" s="78"/>
       <c r="B61" s="15" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -7592,12 +7572,12 @@
       <c r="P61" s="14"/>
     </row>
     <row r="62" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="60"/>
+      <c r="A62" s="78"/>
       <c r="B62" s="15" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -7614,9 +7594,9 @@
       <c r="P62" s="14"/>
     </row>
     <row r="63" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="60"/>
+      <c r="A63" s="78"/>
       <c r="B63" s="15" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>22</v>
@@ -7636,16 +7616,16 @@
       <c r="P63" s="14"/>
     </row>
     <row r="64" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B64" s="52"/>
-      <c r="C64" s="52"/>
-      <c r="D64" s="52"/>
-      <c r="E64" s="52"/>
-      <c r="F64" s="52"/>
-      <c r="G64" s="52"/>
-      <c r="H64" s="53"/>
+      <c r="A64" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B64" s="67"/>
+      <c r="C64" s="67"/>
+      <c r="D64" s="67"/>
+      <c r="E64" s="67"/>
+      <c r="F64" s="67"/>
+      <c r="G64" s="67"/>
+      <c r="H64" s="68"/>
       <c r="I64" s="38"/>
       <c r="J64" s="38"/>
       <c r="K64" s="38"/>
@@ -7656,14 +7636,14 @@
       <c r="P64" s="14"/>
     </row>
     <row r="65" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="60" t="s">
-        <v>448</v>
+      <c r="A65" s="78" t="s">
+        <v>443</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>367</v>
+        <v>362</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -7680,12 +7660,12 @@
       <c r="P65" s="14"/>
     </row>
     <row r="66" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="60"/>
+      <c r="A66" s="78"/>
       <c r="B66" s="15" t="s">
-        <v>387</v>
+        <v>382</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -7702,12 +7682,12 @@
       <c r="P66" s="14"/>
     </row>
     <row r="67" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="60"/>
+      <c r="A67" s="78"/>
       <c r="B67" s="15" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -7724,12 +7704,12 @@
       <c r="P67" s="14"/>
     </row>
     <row r="68" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="60"/>
+      <c r="A68" s="78"/>
       <c r="B68" s="15" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -7746,12 +7726,12 @@
       <c r="P68" s="14"/>
     </row>
     <row r="69" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="60"/>
+      <c r="A69" s="78"/>
       <c r="B69" s="15" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -7768,12 +7748,12 @@
       <c r="P69" s="14"/>
     </row>
     <row r="70" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="60"/>
+      <c r="A70" s="78"/>
       <c r="B70" s="15" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -7790,12 +7770,12 @@
       <c r="P70" s="14"/>
     </row>
     <row r="71" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="60"/>
+      <c r="A71" s="78"/>
       <c r="B71" s="15" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -7812,12 +7792,12 @@
       <c r="P71" s="14"/>
     </row>
     <row r="72" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="60"/>
+      <c r="A72" s="78"/>
       <c r="B72" s="15" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -7834,12 +7814,12 @@
       <c r="P72" s="14"/>
     </row>
     <row r="73" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="60"/>
+      <c r="A73" s="78"/>
       <c r="B73" s="15" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -7856,12 +7836,12 @@
       <c r="P73" s="14"/>
     </row>
     <row r="74" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="60"/>
+      <c r="A74" s="78"/>
       <c r="B74" s="15" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D74" s="4"/>
       <c r="E74" s="4"/>
@@ -7878,16 +7858,16 @@
       <c r="P74" s="14"/>
     </row>
     <row r="75" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="52"/>
-      <c r="H75" s="53"/>
+      <c r="A75" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B75" s="67"/>
+      <c r="C75" s="67"/>
+      <c r="D75" s="67"/>
+      <c r="E75" s="67"/>
+      <c r="F75" s="67"/>
+      <c r="G75" s="67"/>
+      <c r="H75" s="68"/>
       <c r="I75" s="38"/>
       <c r="J75" s="38"/>
       <c r="K75" s="38"/>
@@ -7898,11 +7878,11 @@
       <c r="P75" s="14"/>
     </row>
     <row r="76" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="60" t="s">
-        <v>219</v>
+      <c r="A76" s="78" t="s">
+        <v>217</v>
       </c>
       <c r="B76" s="29" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C76" s="4" t="s">
         <v>13</v>
@@ -7922,9 +7902,9 @@
       <c r="P76" s="14"/>
     </row>
     <row r="77" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="60"/>
+      <c r="A77" s="78"/>
       <c r="B77" s="29" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C77" s="4" t="s">
         <v>52</v>
@@ -7944,16 +7924,16 @@
       <c r="P77" s="14"/>
     </row>
     <row r="78" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B78" s="52"/>
-      <c r="C78" s="52"/>
-      <c r="D78" s="52"/>
-      <c r="E78" s="52"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="52"/>
-      <c r="H78" s="53"/>
+      <c r="A78" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B78" s="67"/>
+      <c r="C78" s="67"/>
+      <c r="D78" s="67"/>
+      <c r="E78" s="67"/>
+      <c r="F78" s="67"/>
+      <c r="G78" s="67"/>
+      <c r="H78" s="68"/>
       <c r="I78" s="38"/>
       <c r="J78" s="38"/>
       <c r="K78" s="38"/>
@@ -7964,12 +7944,12 @@
       <c r="P78" s="14"/>
     </row>
     <row r="79" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="60"/>
+      <c r="A79" s="78"/>
       <c r="B79" s="15" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -7986,12 +7966,12 @@
       <c r="P79" s="14"/>
     </row>
     <row r="80" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="60"/>
+      <c r="A80" s="78"/>
       <c r="B80" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -8008,12 +7988,12 @@
       <c r="P80" s="14"/>
     </row>
     <row r="81" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="60"/>
+      <c r="A81" s="78"/>
       <c r="B81" s="15" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="4"/>
@@ -8030,12 +8010,12 @@
       <c r="P81" s="14"/>
     </row>
     <row r="82" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="60"/>
+      <c r="A82" s="78"/>
       <c r="B82" s="15" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="4"/>
@@ -8052,12 +8032,12 @@
       <c r="P82" s="14"/>
     </row>
     <row r="83" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="60"/>
+      <c r="A83" s="78"/>
       <c r="B83" s="15" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -8074,12 +8054,12 @@
       <c r="P83" s="14"/>
     </row>
     <row r="84" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="60"/>
+      <c r="A84" s="78"/>
       <c r="B84" s="30" t="s">
-        <v>359</v>
+        <v>354</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -8096,12 +8076,12 @@
       <c r="P84" s="14"/>
     </row>
     <row r="85" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="60"/>
+      <c r="A85" s="78"/>
       <c r="B85" s="30" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -8118,12 +8098,12 @@
       <c r="P85" s="14"/>
     </row>
     <row r="86" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="60"/>
+      <c r="A86" s="78"/>
       <c r="B86" s="30" t="s">
-        <v>349</v>
+        <v>344</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D86" s="4"/>
       <c r="E86" s="4"/>
@@ -8140,16 +8120,16 @@
       <c r="P86" s="14"/>
     </row>
     <row r="87" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="52"/>
-      <c r="H87" s="53"/>
+      <c r="A87" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B87" s="67"/>
+      <c r="C87" s="67"/>
+      <c r="D87" s="67"/>
+      <c r="E87" s="67"/>
+      <c r="F87" s="67"/>
+      <c r="G87" s="67"/>
+      <c r="H87" s="68"/>
       <c r="I87" s="38"/>
       <c r="J87" s="38"/>
       <c r="K87" s="38"/>
@@ -8160,14 +8140,14 @@
       <c r="P87" s="14"/>
     </row>
     <row r="88" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="60" t="s">
-        <v>513</v>
+      <c r="A88" s="78" t="s">
+        <v>508</v>
       </c>
       <c r="B88" s="15" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -8184,12 +8164,12 @@
       <c r="P88" s="14"/>
     </row>
     <row r="89" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="60"/>
+      <c r="A89" s="78"/>
       <c r="B89" s="15" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -8206,12 +8186,12 @@
       <c r="P89" s="14"/>
     </row>
     <row r="90" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="60"/>
+      <c r="A90" s="78"/>
       <c r="B90" s="15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -8228,12 +8208,12 @@
       <c r="P90" s="14"/>
     </row>
     <row r="91" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="60"/>
+      <c r="A91" s="78"/>
       <c r="B91" s="29" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -8250,12 +8230,12 @@
       <c r="P91" s="14"/>
     </row>
     <row r="92" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="60"/>
+      <c r="A92" s="78"/>
       <c r="B92" s="15" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -8272,12 +8252,12 @@
       <c r="P92" s="14"/>
     </row>
     <row r="93" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="60"/>
+      <c r="A93" s="78"/>
       <c r="B93" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -8294,12 +8274,12 @@
       <c r="P93" s="14"/>
     </row>
     <row r="94" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="60"/>
+      <c r="A94" s="78"/>
       <c r="B94" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>215</v>
       </c>
       <c r="D94" s="4"/>
       <c r="E94" s="4"/>
@@ -8316,14 +8296,14 @@
       <c r="P94" s="14"/>
     </row>
     <row r="95" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="60" t="s">
-        <v>513</v>
+      <c r="A95" s="78" t="s">
+        <v>508</v>
       </c>
       <c r="B95" s="15" t="s">
-        <v>357</v>
+        <v>352</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -8340,12 +8320,12 @@
       <c r="P95" s="14"/>
     </row>
     <row r="96" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="60"/>
+      <c r="A96" s="78"/>
       <c r="B96" s="15" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -8362,12 +8342,12 @@
       <c r="P96" s="14"/>
     </row>
     <row r="97" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="60"/>
+      <c r="A97" s="78"/>
       <c r="B97" s="15" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -8384,12 +8364,12 @@
       <c r="P97" s="14"/>
     </row>
     <row r="98" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="60"/>
+      <c r="A98" s="78"/>
       <c r="B98" s="15" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="4"/>
@@ -8406,12 +8386,12 @@
       <c r="P98" s="14"/>
     </row>
     <row r="99" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="60"/>
+      <c r="A99" s="78"/>
       <c r="B99" s="15" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -8428,12 +8408,12 @@
       <c r="P99" s="14"/>
     </row>
     <row r="100" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="60"/>
+      <c r="A100" s="78"/>
       <c r="B100" s="15" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -8450,12 +8430,12 @@
       <c r="P100" s="14"/>
     </row>
     <row r="101" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="60"/>
+      <c r="A101" s="78"/>
       <c r="B101" s="15" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -8472,12 +8452,12 @@
       <c r="P101" s="14"/>
     </row>
     <row r="102" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="60"/>
+      <c r="A102" s="78"/>
       <c r="B102" s="15" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -8494,12 +8474,12 @@
       <c r="P102" s="14"/>
     </row>
     <row r="103" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="60"/>
+      <c r="A103" s="78"/>
       <c r="B103" s="15" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -8516,16 +8496,16 @@
       <c r="P103" s="14"/>
     </row>
     <row r="104" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B104" s="52"/>
-      <c r="C104" s="52"/>
-      <c r="D104" s="52"/>
-      <c r="E104" s="52"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="52"/>
-      <c r="H104" s="53"/>
+      <c r="A104" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B104" s="67"/>
+      <c r="C104" s="67"/>
+      <c r="D104" s="67"/>
+      <c r="E104" s="67"/>
+      <c r="F104" s="67"/>
+      <c r="G104" s="67"/>
+      <c r="H104" s="68"/>
       <c r="I104" s="38"/>
       <c r="J104" s="38"/>
       <c r="K104" s="38"/>
@@ -8537,13 +8517,13 @@
     </row>
     <row r="105" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="14" t="s">
-        <v>726</v>
+        <v>709</v>
       </c>
       <c r="B105" s="15" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -8561,13 +8541,13 @@
     </row>
     <row r="106" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="14" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B106" s="15" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -8584,11 +8564,11 @@
       <c r="P106" s="14"/>
     </row>
     <row r="107" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="60" t="s">
-        <v>259</v>
+      <c r="A107" s="78" t="s">
+        <v>256</v>
       </c>
       <c r="B107" s="15" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C107" s="4" t="s">
         <v>4</v>
@@ -8608,12 +8588,12 @@
       <c r="P107" s="14"/>
     </row>
     <row r="108" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="60"/>
+      <c r="A108" s="78"/>
       <c r="B108" s="29" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -8630,12 +8610,12 @@
       <c r="P108" s="14"/>
     </row>
     <row r="109" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="60"/>
+      <c r="A109" s="78"/>
       <c r="B109" s="29" t="s">
-        <v>579</v>
+        <v>572</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
@@ -8653,10 +8633,10 @@
     </row>
     <row r="110" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B110" s="15" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C110" s="4" t="s">
         <v>2</v>
@@ -8676,16 +8656,16 @@
       <c r="P110" s="14"/>
     </row>
     <row r="111" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B111" s="52"/>
-      <c r="C111" s="52"/>
-      <c r="D111" s="52"/>
-      <c r="E111" s="52"/>
-      <c r="F111" s="52"/>
-      <c r="G111" s="52"/>
-      <c r="H111" s="53"/>
+      <c r="A111" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B111" s="67"/>
+      <c r="C111" s="67"/>
+      <c r="D111" s="67"/>
+      <c r="E111" s="67"/>
+      <c r="F111" s="67"/>
+      <c r="G111" s="67"/>
+      <c r="H111" s="68"/>
       <c r="I111" s="38"/>
       <c r="J111" s="38"/>
       <c r="K111" s="38"/>
@@ -8696,14 +8676,14 @@
       <c r="P111" s="14"/>
     </row>
     <row r="112" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="61" t="s">
+      <c r="A112" s="79" t="s">
         <v>49</v>
       </c>
       <c r="B112" s="15" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
@@ -8720,12 +8700,12 @@
       <c r="P112" s="14"/>
     </row>
     <row r="113" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="61"/>
+      <c r="A113" s="79"/>
       <c r="B113" s="15" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -8742,12 +8722,12 @@
       <c r="P113" s="14"/>
     </row>
     <row r="114" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="61"/>
+      <c r="A114" s="79"/>
       <c r="B114" s="15" t="s">
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -8764,12 +8744,12 @@
       <c r="P114" s="14"/>
     </row>
     <row r="115" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="61"/>
+      <c r="A115" s="79"/>
       <c r="B115" s="15" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -8786,12 +8766,12 @@
       <c r="P115" s="14"/>
     </row>
     <row r="116" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="61"/>
+      <c r="A116" s="79"/>
       <c r="B116" s="15" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -8808,12 +8788,12 @@
       <c r="P116" s="14"/>
     </row>
     <row r="117" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="61"/>
+      <c r="A117" s="79"/>
       <c r="B117" s="15" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -8830,12 +8810,12 @@
       <c r="P117" s="14"/>
     </row>
     <row r="118" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="61"/>
+      <c r="A118" s="79"/>
       <c r="B118" s="15" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -8852,12 +8832,12 @@
       <c r="P118" s="14"/>
     </row>
     <row r="119" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="61"/>
+      <c r="A119" s="79"/>
       <c r="B119" s="15" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -8874,16 +8854,16 @@
       <c r="P119" s="14"/>
     </row>
     <row r="120" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B120" s="52"/>
-      <c r="C120" s="52"/>
-      <c r="D120" s="52"/>
-      <c r="E120" s="52"/>
-      <c r="F120" s="52"/>
-      <c r="G120" s="52"/>
-      <c r="H120" s="53"/>
+      <c r="A120" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B120" s="67"/>
+      <c r="C120" s="67"/>
+      <c r="D120" s="67"/>
+      <c r="E120" s="67"/>
+      <c r="F120" s="67"/>
+      <c r="G120" s="67"/>
+      <c r="H120" s="68"/>
       <c r="I120" s="38"/>
       <c r="J120" s="38"/>
       <c r="K120" s="38"/>
@@ -8894,14 +8874,14 @@
       <c r="P120" s="14"/>
     </row>
     <row r="121" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="60" t="s">
-        <v>514</v>
+      <c r="A121" s="78" t="s">
+        <v>509</v>
       </c>
       <c r="B121" s="15" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
@@ -8918,12 +8898,12 @@
       <c r="P121" s="14"/>
     </row>
     <row r="122" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="60"/>
+      <c r="A122" s="78"/>
       <c r="B122" s="15" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
@@ -8940,12 +8920,12 @@
       <c r="P122" s="14"/>
     </row>
     <row r="123" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="60"/>
+      <c r="A123" s="78"/>
       <c r="B123" s="15" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
@@ -8962,12 +8942,12 @@
       <c r="P123" s="14"/>
     </row>
     <row r="124" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="60"/>
+      <c r="A124" s="78"/>
       <c r="B124" s="15" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -8984,16 +8964,16 @@
       <c r="P124" s="14"/>
     </row>
     <row r="125" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B125" s="52"/>
-      <c r="C125" s="52"/>
-      <c r="D125" s="52"/>
-      <c r="E125" s="52"/>
-      <c r="F125" s="52"/>
-      <c r="G125" s="52"/>
-      <c r="H125" s="53"/>
+      <c r="A125" s="76" t="s">
+        <v>113</v>
+      </c>
+      <c r="B125" s="67"/>
+      <c r="C125" s="67"/>
+      <c r="D125" s="67"/>
+      <c r="E125" s="67"/>
+      <c r="F125" s="67"/>
+      <c r="G125" s="67"/>
+      <c r="H125" s="68"/>
       <c r="I125" s="38"/>
       <c r="J125" s="38"/>
       <c r="K125" s="38"/>
@@ -9004,11 +8984,11 @@
       <c r="P125" s="14"/>
     </row>
     <row r="126" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="60" t="s">
-        <v>281</v>
+      <c r="A126" s="78" t="s">
+        <v>278</v>
       </c>
       <c r="B126" s="15" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C126" s="4" t="s">
         <v>18</v>
@@ -9028,12 +9008,12 @@
       <c r="P126" s="14"/>
     </row>
     <row r="127" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="60"/>
+      <c r="A127" s="78"/>
       <c r="B127" s="15" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -9050,16 +9030,16 @@
       <c r="P127" s="14"/>
     </row>
     <row r="128" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="54" t="s">
-        <v>114</v>
-      </c>
-      <c r="B128" s="55"/>
-      <c r="C128" s="55"/>
-      <c r="D128" s="55"/>
-      <c r="E128" s="55"/>
-      <c r="F128" s="55"/>
-      <c r="G128" s="55"/>
-      <c r="H128" s="56"/>
+      <c r="A128" s="100" t="s">
+        <v>113</v>
+      </c>
+      <c r="B128" s="74"/>
+      <c r="C128" s="74"/>
+      <c r="D128" s="74"/>
+      <c r="E128" s="74"/>
+      <c r="F128" s="74"/>
+      <c r="G128" s="74"/>
+      <c r="H128" s="75"/>
       <c r="I128" s="47"/>
       <c r="J128" s="47"/>
       <c r="K128" s="47"/>
@@ -9070,16 +9050,16 @@
       <c r="P128" s="22"/>
     </row>
     <row r="129" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B129" s="58"/>
-      <c r="C129" s="58"/>
-      <c r="D129" s="58"/>
-      <c r="E129" s="58"/>
-      <c r="F129" s="58"/>
-      <c r="G129" s="58"/>
-      <c r="H129" s="59"/>
+      <c r="A129" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="B129" s="71"/>
+      <c r="C129" s="71"/>
+      <c r="D129" s="71"/>
+      <c r="E129" s="71"/>
+      <c r="F129" s="71"/>
+      <c r="G129" s="71"/>
+      <c r="H129" s="72"/>
       <c r="I129" s="48"/>
       <c r="J129" s="48"/>
       <c r="K129" s="48"/>
@@ -9111,104 +9091,118 @@
       <c r="A131" s="3"/>
       <c r="B131" s="1"/>
       <c r="C131" s="5"/>
-      <c r="D131" s="71"/>
-      <c r="E131" s="72"/>
-      <c r="F131" s="72"/>
-      <c r="G131" s="73"/>
-      <c r="H131" s="73"/>
-      <c r="I131" s="63"/>
-      <c r="J131" s="63"/>
-      <c r="K131" s="63"/>
-      <c r="L131" s="64"/>
+      <c r="D131" s="95"/>
+      <c r="E131" s="96"/>
+      <c r="F131" s="96"/>
+      <c r="G131" s="97"/>
+      <c r="H131" s="97"/>
+      <c r="I131" s="89"/>
+      <c r="J131" s="89"/>
+      <c r="K131" s="89"/>
+      <c r="L131" s="90"/>
       <c r="M131" s="8"/>
       <c r="N131" s="8"/>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
     </row>
     <row r="132" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D132" s="74" t="s">
-        <v>682</v>
-      </c>
-      <c r="E132" s="75"/>
-      <c r="F132" s="75"/>
-      <c r="G132" s="65"/>
-      <c r="H132" s="65"/>
-      <c r="I132" s="65"/>
-      <c r="J132" s="65"/>
-      <c r="K132" s="65"/>
-      <c r="L132" s="66"/>
+      <c r="D132" s="98" t="s">
+        <v>665</v>
+      </c>
+      <c r="E132" s="99"/>
+      <c r="F132" s="99"/>
+      <c r="G132" s="91"/>
+      <c r="H132" s="91"/>
+      <c r="I132" s="91"/>
+      <c r="J132" s="91"/>
+      <c r="K132" s="91"/>
+      <c r="L132" s="92"/>
     </row>
     <row r="133" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D133" s="76" t="s">
-        <v>683</v>
-      </c>
-      <c r="E133" s="53"/>
-      <c r="F133" s="53"/>
-      <c r="G133" s="67"/>
-      <c r="H133" s="67"/>
-      <c r="I133" s="67"/>
-      <c r="J133" s="67"/>
-      <c r="K133" s="67"/>
-      <c r="L133" s="69"/>
+      <c r="D133" s="83" t="s">
+        <v>666</v>
+      </c>
+      <c r="E133" s="68"/>
+      <c r="F133" s="68"/>
+      <c r="G133" s="84"/>
+      <c r="H133" s="84"/>
+      <c r="I133" s="84"/>
+      <c r="J133" s="84"/>
+      <c r="K133" s="84"/>
+      <c r="L133" s="93"/>
     </row>
     <row r="134" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D134" s="76" t="s">
-        <v>684</v>
-      </c>
-      <c r="E134" s="53"/>
-      <c r="F134" s="53"/>
-      <c r="G134" s="67"/>
-      <c r="H134" s="67"/>
-      <c r="I134" s="67"/>
-      <c r="J134" s="67"/>
-      <c r="K134" s="67"/>
-      <c r="L134" s="69"/>
+      <c r="D134" s="83" t="s">
+        <v>667</v>
+      </c>
+      <c r="E134" s="68"/>
+      <c r="F134" s="68"/>
+      <c r="G134" s="84"/>
+      <c r="H134" s="84"/>
+      <c r="I134" s="84"/>
+      <c r="J134" s="84"/>
+      <c r="K134" s="84"/>
+      <c r="L134" s="93"/>
     </row>
     <row r="135" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D135" s="77" t="s">
-        <v>685</v>
-      </c>
-      <c r="E135" s="78"/>
-      <c r="F135" s="78"/>
-      <c r="G135" s="68"/>
-      <c r="H135" s="68"/>
-      <c r="I135" s="68"/>
-      <c r="J135" s="68"/>
-      <c r="K135" s="68"/>
-      <c r="L135" s="70"/>
+      <c r="D135" s="85" t="s">
+        <v>668</v>
+      </c>
+      <c r="E135" s="86"/>
+      <c r="F135" s="86"/>
+      <c r="G135" s="87"/>
+      <c r="H135" s="87"/>
+      <c r="I135" s="87"/>
+      <c r="J135" s="87"/>
+      <c r="K135" s="87"/>
+      <c r="L135" s="94"/>
     </row>
     <row r="136" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D136" s="62" t="s">
-        <v>686</v>
-      </c>
-      <c r="E136" s="59"/>
-      <c r="F136" s="59"/>
-      <c r="G136" s="63"/>
-      <c r="H136" s="63"/>
-      <c r="I136" s="63"/>
-      <c r="J136" s="63"/>
-      <c r="K136" s="63"/>
-      <c r="L136" s="63"/>
+      <c r="D136" s="88" t="s">
+        <v>669</v>
+      </c>
+      <c r="E136" s="72"/>
+      <c r="F136" s="72"/>
+      <c r="G136" s="89"/>
+      <c r="H136" s="89"/>
+      <c r="I136" s="89"/>
+      <c r="J136" s="89"/>
+      <c r="K136" s="89"/>
+      <c r="L136" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A8:A15"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A22:A45"/>
-    <mergeCell ref="A53:A58"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="A65:A74"/>
-    <mergeCell ref="A47:A52"/>
-    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="A125:H125"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A103"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A112:A119"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="D136:H136"/>
+    <mergeCell ref="I131:J131"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="I132:J132"/>
+    <mergeCell ref="K132:L132"/>
+    <mergeCell ref="I133:J133"/>
+    <mergeCell ref="I134:J134"/>
+    <mergeCell ref="I135:J135"/>
+    <mergeCell ref="I136:J136"/>
+    <mergeCell ref="K133:L133"/>
+    <mergeCell ref="K134:L134"/>
+    <mergeCell ref="K135:L135"/>
+    <mergeCell ref="K136:L136"/>
+    <mergeCell ref="D131:H131"/>
+    <mergeCell ref="D132:H132"/>
+    <mergeCell ref="D133:H133"/>
     <mergeCell ref="D134:H134"/>
     <mergeCell ref="D135:H135"/>
     <mergeCell ref="N6:N7"/>
@@ -9225,37 +9219,23 @@
     <mergeCell ref="A126:A127"/>
     <mergeCell ref="A76:A77"/>
     <mergeCell ref="A79:A86"/>
-    <mergeCell ref="D136:H136"/>
-    <mergeCell ref="I131:J131"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="I132:J132"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="I133:J133"/>
-    <mergeCell ref="I134:J134"/>
-    <mergeCell ref="I135:J135"/>
-    <mergeCell ref="I136:J136"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="D131:H131"/>
-    <mergeCell ref="D132:H132"/>
-    <mergeCell ref="D133:H133"/>
-    <mergeCell ref="A120:H120"/>
-    <mergeCell ref="A125:H125"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A129:H129"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A103"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A112:A119"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A104:H104"/>
-    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="A22:A45"/>
+    <mergeCell ref="A53:A58"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A65:A74"/>
+    <mergeCell ref="A47:A52"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A8:A15"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9268,7 +9248,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:N204"/>
+  <dimension ref="A2:N198"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.625" style="34" customWidth="1"/>
@@ -11740,20 +11720,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -11769,13 +11749,13 @@
       <c r="K3" s="31"/>
       <c r="L3" s="31"/>
       <c r="M3" s="32" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="N3" s="50"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="37" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="N4" s="50"/>
     </row>
@@ -11784,74 +11764,74 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="86" t="s">
-        <v>624</v>
-      </c>
-      <c r="C6" s="84" t="s">
-        <v>625</v>
-      </c>
-      <c r="D6" s="84" t="s">
-        <v>626</v>
-      </c>
-      <c r="E6" s="84" t="s">
-        <v>627</v>
-      </c>
-      <c r="F6" s="79" t="s">
-        <v>628</v>
-      </c>
-      <c r="G6" s="79" t="s">
-        <v>578</v>
-      </c>
-      <c r="H6" s="79" t="s">
+      <c r="A6" s="56" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>612</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>614</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>615</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>616</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>571</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>575</v>
+      </c>
+      <c r="I6" s="62" t="s">
+        <v>581</v>
+      </c>
+      <c r="J6" s="62" t="s">
         <v>582</v>
       </c>
-      <c r="I6" s="79" t="s">
-        <v>588</v>
-      </c>
-      <c r="J6" s="79" t="s">
-        <v>589</v>
-      </c>
-      <c r="K6" s="79" t="s">
-        <v>590</v>
-      </c>
-      <c r="L6" s="79" t="s">
-        <v>608</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>629</v>
-      </c>
-      <c r="N6" s="82" t="s">
-        <v>630</v>
+      <c r="K6" s="62" t="s">
+        <v>583</v>
+      </c>
+      <c r="L6" s="62" t="s">
+        <v>596</v>
+      </c>
+      <c r="M6" s="62" t="s">
+        <v>617</v>
+      </c>
+      <c r="N6" s="64" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="90"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="83"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="65"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="97" t="s">
-        <v>633</v>
+      <c r="A8" s="69" t="s">
+        <v>621</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>371</v>
+        <v>366</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -11866,12 +11846,12 @@
       <c r="N8" s="27"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="95"/>
+      <c r="A9" s="54"/>
       <c r="B9" s="13" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -11886,12 +11866,12 @@
       <c r="N9" s="26"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="95"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="11" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>575</v>
+        <v>568</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
@@ -11906,12 +11886,12 @@
       <c r="N10" s="26"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="95"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="11" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>577</v>
+        <v>570</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
@@ -11926,32 +11906,32 @@
       <c r="N11" s="26"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="95"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="11" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>572</v>
-      </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="20"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="21"/>
-      <c r="L12" s="21"/>
-      <c r="M12" s="21"/>
+        <v>38</v>
+      </c>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
+      <c r="L12" s="14"/>
+      <c r="M12" s="14"/>
       <c r="N12" s="26"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="95"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="11" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>38</v>
+        <v>166</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -11966,12 +11946,12 @@
       <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="95"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="11" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>167</v>
+        <v>559</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -11986,12 +11966,12 @@
       <c r="N14" s="26"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="95"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="11" t="s">
-        <v>377</v>
+        <v>246</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>565</v>
+        <v>544</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -12006,12 +11986,12 @@
       <c r="N15" s="26"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="95"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="11" t="s">
-        <v>249</v>
+        <v>439</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -12026,12 +12006,12 @@
       <c r="N16" s="26"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="95"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="11" t="s">
-        <v>444</v>
+        <v>373</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>535</v>
+        <v>47</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -12046,12 +12026,12 @@
       <c r="N17" s="26"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="95"/>
+      <c r="A18" s="54"/>
       <c r="B18" s="11" t="s">
-        <v>378</v>
+        <v>599</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>47</v>
+        <v>600</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -12066,52 +12046,52 @@
       <c r="N18" s="26"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="95"/>
-      <c r="B19" s="11" t="s">
-        <v>611</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>612</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
+      <c r="A19" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="67"/>
+      <c r="C19" s="67"/>
+      <c r="D19" s="67"/>
+      <c r="E19" s="67"/>
+      <c r="F19" s="68"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
+      <c r="M19" s="38"/>
       <c r="N19" s="26"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="53"/>
-      <c r="G20" s="38"/>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="38"/>
-      <c r="L20" s="38"/>
-      <c r="M20" s="38"/>
+      <c r="A20" s="54" t="s">
+        <v>623</v>
+      </c>
+      <c r="B20" s="39" t="s">
+        <v>407</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
       <c r="N20" s="26"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="95" t="s">
-        <v>635</v>
-      </c>
-      <c r="B21" s="39" t="s">
-        <v>412</v>
+      <c r="A21" s="54"/>
+      <c r="B21" s="40" t="s">
+        <v>361</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>141</v>
+        <v>35</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -12126,12 +12106,12 @@
       <c r="N21" s="26"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="95"/>
-      <c r="B22" s="40" t="s">
-        <v>366</v>
+      <c r="A22" s="54"/>
+      <c r="B22" s="39" t="s">
+        <v>387</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>35</v>
+        <v>405</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -12146,12 +12126,12 @@
       <c r="N22" s="26"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="95"/>
+      <c r="A23" s="54"/>
       <c r="B23" s="39" t="s">
         <v>392</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
@@ -12166,12 +12146,12 @@
       <c r="N23" s="26"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="95"/>
+      <c r="A24" s="54"/>
       <c r="B24" s="39" t="s">
-        <v>397</v>
+        <v>245</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>408</v>
+        <v>101</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -12186,12 +12166,12 @@
       <c r="N24" s="26"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="95"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="39" t="s">
-        <v>248</v>
+        <v>423</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
@@ -12206,12 +12186,12 @@
       <c r="N25" s="26"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="95"/>
+      <c r="A26" s="54"/>
       <c r="B26" s="39" t="s">
-        <v>428</v>
+        <v>241</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
@@ -12226,12 +12206,12 @@
       <c r="N26" s="26"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="95"/>
+      <c r="A27" s="54"/>
       <c r="B27" s="39" t="s">
-        <v>243</v>
+        <v>624</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -12246,52 +12226,52 @@
       <c r="N27" s="26"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="95"/>
-      <c r="B28" s="39" t="s">
-        <v>636</v>
-      </c>
-      <c r="C28" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
+      <c r="A28" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B28" s="67"/>
+      <c r="C28" s="67"/>
+      <c r="D28" s="67"/>
+      <c r="E28" s="67"/>
+      <c r="F28" s="68"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="38"/>
+      <c r="I28" s="38"/>
+      <c r="J28" s="38"/>
+      <c r="K28" s="38"/>
+      <c r="L28" s="38"/>
+      <c r="M28" s="38"/>
       <c r="N28" s="26"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B29" s="52"/>
-      <c r="C29" s="52"/>
-      <c r="D29" s="52"/>
-      <c r="E29" s="52"/>
-      <c r="F29" s="53"/>
+      <c r="A29" s="54" t="s">
+        <v>625</v>
+      </c>
+      <c r="B29" s="41" t="s">
+        <v>359</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>523</v>
+      </c>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="16"/>
       <c r="G29" s="38"/>
       <c r="H29" s="38"/>
       <c r="I29" s="38"/>
       <c r="J29" s="38"/>
       <c r="K29" s="38"/>
       <c r="L29" s="38"/>
-      <c r="M29" s="38"/>
+      <c r="M29" s="14"/>
       <c r="N29" s="26"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="95" t="s">
-        <v>637</v>
-      </c>
+      <c r="A30" s="54"/>
       <c r="B30" s="41" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="C30" s="42" t="s">
-        <v>528</v>
+        <v>521</v>
       </c>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
@@ -12306,12 +12286,12 @@
       <c r="N30" s="26"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="95"/>
-      <c r="B31" s="41" t="s">
-        <v>338</v>
+      <c r="A31" s="54"/>
+      <c r="B31" s="43" t="s">
+        <v>367</v>
       </c>
       <c r="C31" s="42" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
@@ -12326,12 +12306,12 @@
       <c r="N31" s="26"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="95"/>
-      <c r="B32" s="43" t="s">
-        <v>372</v>
+      <c r="A32" s="54"/>
+      <c r="B32" s="41" t="s">
+        <v>397</v>
       </c>
       <c r="C32" s="42" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
@@ -12346,52 +12326,52 @@
       <c r="N32" s="26"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="95"/>
-      <c r="B33" s="41" t="s">
-        <v>402</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>569</v>
-      </c>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="16"/>
+      <c r="A33" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B33" s="67"/>
+      <c r="C33" s="67"/>
+      <c r="D33" s="67"/>
+      <c r="E33" s="67"/>
+      <c r="F33" s="68"/>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
       <c r="I33" s="38"/>
       <c r="J33" s="38"/>
       <c r="K33" s="38"/>
       <c r="L33" s="38"/>
-      <c r="M33" s="14"/>
+      <c r="M33" s="38"/>
       <c r="N33" s="26"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" s="52"/>
-      <c r="C34" s="52"/>
-      <c r="D34" s="52"/>
-      <c r="E34" s="52"/>
-      <c r="F34" s="53"/>
-      <c r="G34" s="38"/>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="38"/>
-      <c r="K34" s="38"/>
-      <c r="L34" s="38"/>
-      <c r="M34" s="38"/>
+      <c r="A34" s="53" t="s">
+        <v>626</v>
+      </c>
+      <c r="B34" s="39" t="s">
+        <v>420</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
       <c r="N34" s="26"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="94" t="s">
-        <v>638</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>425</v>
+      <c r="A35" s="53"/>
+      <c r="B35" s="40" t="s">
+        <v>408</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>65</v>
+        <v>102</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -12406,12 +12386,12 @@
       <c r="N35" s="26"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="94"/>
-      <c r="B36" s="40" t="s">
-        <v>413</v>
+      <c r="A36" s="53"/>
+      <c r="B36" s="39" t="s">
+        <v>232</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>103</v>
+        <v>59</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -12426,16 +12406,16 @@
       <c r="N36" s="26"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="94"/>
+      <c r="A37" s="53"/>
       <c r="B37" s="39" t="s">
-        <v>234</v>
+        <v>210</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
-      <c r="F37" s="16"/>
+      <c r="F37" s="20"/>
       <c r="G37" s="14"/>
       <c r="H37" s="14"/>
       <c r="I37" s="14"/>
@@ -12446,12 +12426,12 @@
       <c r="N37" s="26"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="94"/>
+      <c r="A38" s="53"/>
       <c r="B38" s="39" t="s">
-        <v>211</v>
+        <v>231</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -12466,16 +12446,16 @@
       <c r="N38" s="26"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="94"/>
+      <c r="A39" s="53"/>
       <c r="B39" s="39" t="s">
-        <v>233</v>
+        <v>203</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>62</v>
+        <v>107</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
-      <c r="F39" s="20"/>
+      <c r="F39" s="16"/>
       <c r="G39" s="14"/>
       <c r="H39" s="14"/>
       <c r="I39" s="14"/>
@@ -12486,12 +12466,12 @@
       <c r="N39" s="26"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="94"/>
+      <c r="A40" s="53"/>
       <c r="B40" s="39" t="s">
-        <v>204</v>
+        <v>227</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>108</v>
+        <v>91</v>
       </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
@@ -12506,12 +12486,12 @@
       <c r="N40" s="26"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="94"/>
+      <c r="A41" s="53"/>
       <c r="B41" s="39" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -12526,12 +12506,12 @@
       <c r="N41" s="26"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="94"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="39" t="s">
-        <v>227</v>
+        <v>355</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>101</v>
+        <v>37</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -12546,12 +12526,12 @@
       <c r="N42" s="26"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="94"/>
+      <c r="A43" s="53"/>
       <c r="B43" s="39" t="s">
-        <v>360</v>
+        <v>391</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -12566,12 +12546,12 @@
       <c r="N43" s="26"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="94"/>
+      <c r="A44" s="53"/>
       <c r="B44" s="39" t="s">
-        <v>396</v>
+        <v>211</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -12586,12 +12566,12 @@
       <c r="N44" s="26"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="94"/>
+      <c r="A45" s="53"/>
       <c r="B45" s="39" t="s">
-        <v>212</v>
+        <v>424</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>8</v>
+        <v>63</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -12606,52 +12586,52 @@
       <c r="N45" s="26"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="94"/>
-      <c r="B46" s="39" t="s">
-        <v>429</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
+      <c r="A46" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B46" s="67"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
+      <c r="F46" s="68"/>
+      <c r="G46" s="38"/>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="38"/>
+      <c r="K46" s="38"/>
+      <c r="L46" s="38"/>
+      <c r="M46" s="38"/>
       <c r="N46" s="26"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" s="52"/>
-      <c r="C47" s="52"/>
-      <c r="D47" s="52"/>
-      <c r="E47" s="52"/>
-      <c r="F47" s="53"/>
-      <c r="G47" s="38"/>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
-      <c r="K47" s="38"/>
-      <c r="L47" s="38"/>
-      <c r="M47" s="38"/>
+      <c r="A47" s="53" t="s">
+        <v>627</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>491</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>518</v>
+      </c>
+      <c r="D47" s="4"/>
+      <c r="E47" s="4"/>
+      <c r="F47" s="16"/>
+      <c r="G47" s="14"/>
+      <c r="H47" s="14"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="14"/>
       <c r="N47" s="26"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="94" t="s">
-        <v>639</v>
-      </c>
+      <c r="A48" s="53"/>
       <c r="B48" s="15" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -12666,12 +12646,12 @@
       <c r="N48" s="26"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="94"/>
+      <c r="A49" s="53"/>
       <c r="B49" s="15" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -12686,12 +12666,12 @@
       <c r="N49" s="26"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="94"/>
+      <c r="A50" s="53"/>
       <c r="B50" s="15" t="s">
-        <v>504</v>
+        <v>497</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>534</v>
+        <v>85</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
@@ -12706,12 +12686,12 @@
       <c r="N50" s="26"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="94"/>
+      <c r="A51" s="53"/>
       <c r="B51" s="15" t="s">
-        <v>502</v>
+        <v>474</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>86</v>
+        <v>547</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -12726,12 +12706,12 @@
       <c r="N51" s="26"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="94"/>
+      <c r="A52" s="53"/>
       <c r="B52" s="15" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>553</v>
+        <v>549</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -12746,12 +12726,12 @@
       <c r="N52" s="26"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="94"/>
+      <c r="A53" s="53"/>
       <c r="B53" s="15" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>555</v>
+        <v>628</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -12766,12 +12746,12 @@
       <c r="N53" s="26"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="94"/>
+      <c r="A54" s="53"/>
       <c r="B54" s="15" t="s">
-        <v>484</v>
+        <v>181</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>640</v>
+        <v>520</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -12786,9 +12766,9 @@
       <c r="N54" s="26"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="94"/>
+      <c r="A55" s="53"/>
       <c r="B55" s="15" t="s">
-        <v>182</v>
+        <v>480</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>525</v>
@@ -12806,12 +12786,12 @@
       <c r="N55" s="26"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="94"/>
+      <c r="A56" s="54"/>
       <c r="B56" s="15" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="D56" s="4"/>
       <c r="E56" s="4"/>
@@ -12826,12 +12806,12 @@
       <c r="N56" s="26"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="95"/>
+      <c r="A57" s="54"/>
       <c r="B57" s="15" t="s">
-        <v>493</v>
+        <v>401</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>529</v>
+        <v>65</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -12846,52 +12826,52 @@
       <c r="N57" s="26"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="95"/>
-      <c r="B58" s="15" t="s">
-        <v>406</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="D58" s="4"/>
-      <c r="E58" s="4"/>
-      <c r="F58" s="16"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
+      <c r="A58" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" s="67"/>
+      <c r="C58" s="67"/>
+      <c r="D58" s="67"/>
+      <c r="E58" s="67"/>
+      <c r="F58" s="68"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38"/>
+      <c r="K58" s="38"/>
+      <c r="L58" s="38"/>
+      <c r="M58" s="38"/>
       <c r="N58" s="26"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59" s="52"/>
-      <c r="C59" s="52"/>
-      <c r="D59" s="52"/>
-      <c r="E59" s="52"/>
-      <c r="F59" s="53"/>
-      <c r="G59" s="38"/>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="38"/>
-      <c r="K59" s="38"/>
-      <c r="L59" s="38"/>
-      <c r="M59" s="38"/>
+      <c r="A59" s="53" t="s">
+        <v>629</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>410</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D59" s="4"/>
+      <c r="E59" s="4"/>
+      <c r="F59" s="16"/>
+      <c r="G59" s="14"/>
+      <c r="H59" s="14"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="94" t="s">
-        <v>641</v>
-      </c>
+      <c r="A60" s="54"/>
       <c r="B60" s="15" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>73</v>
+        <v>565</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -12906,12 +12886,12 @@
       <c r="N60" s="26"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="95"/>
+      <c r="A61" s="54"/>
       <c r="B61" s="15" t="s">
-        <v>421</v>
+        <v>601</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>571</v>
+        <v>602</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -12926,12 +12906,12 @@
       <c r="N61" s="26"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="95"/>
+      <c r="A62" s="54"/>
       <c r="B62" s="15" t="s">
-        <v>613</v>
+        <v>404</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>614</v>
+        <v>554</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -12946,12 +12926,12 @@
       <c r="N62" s="26"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="95"/>
+      <c r="A63" s="54"/>
       <c r="B63" s="15" t="s">
-        <v>409</v>
+        <v>603</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>560</v>
+        <v>604</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -12966,12 +12946,12 @@
       <c r="N63" s="26"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="95"/>
+      <c r="A64" s="54"/>
       <c r="B64" s="15" t="s">
-        <v>615</v>
+        <v>386</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>616</v>
+        <v>562</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -12986,12 +12966,12 @@
       <c r="N64" s="26"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="95"/>
+      <c r="A65" s="54"/>
       <c r="B65" s="15" t="s">
-        <v>391</v>
+        <v>605</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>568</v>
+        <v>606</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -13006,12 +12986,12 @@
       <c r="N65" s="26"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="95"/>
+      <c r="A66" s="54"/>
       <c r="B66" s="15" t="s">
-        <v>617</v>
+        <v>595</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>618</v>
+        <v>576</v>
       </c>
       <c r="D66" s="4"/>
       <c r="E66" s="4"/>
@@ -13026,12 +13006,12 @@
       <c r="N66" s="26"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="95"/>
+      <c r="A67" s="54"/>
       <c r="B67" s="15" t="s">
-        <v>602</v>
+        <v>389</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>583</v>
+        <v>73</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="4"/>
@@ -13046,12 +13026,12 @@
       <c r="N67" s="26"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="95"/>
+      <c r="A68" s="54"/>
       <c r="B68" s="15" t="s">
-        <v>394</v>
+        <v>176</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>74</v>
+        <v>550</v>
       </c>
       <c r="D68" s="4"/>
       <c r="E68" s="4"/>
@@ -13066,12 +13046,12 @@
       <c r="N68" s="26"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="95"/>
+      <c r="A69" s="54"/>
       <c r="B69" s="15" t="s">
-        <v>177</v>
+        <v>607</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>556</v>
+        <v>608</v>
       </c>
       <c r="D69" s="4"/>
       <c r="E69" s="4"/>
@@ -13086,12 +13066,12 @@
       <c r="N69" s="26"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="95"/>
+      <c r="A70" s="54"/>
       <c r="B70" s="15" t="s">
-        <v>619</v>
+        <v>406</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>620</v>
+        <v>557</v>
       </c>
       <c r="D70" s="4"/>
       <c r="E70" s="4"/>
@@ -13106,12 +13086,12 @@
       <c r="N70" s="26"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="95"/>
+      <c r="A71" s="54"/>
       <c r="B71" s="15" t="s">
-        <v>411</v>
+        <v>609</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>563</v>
+        <v>610</v>
       </c>
       <c r="D71" s="4"/>
       <c r="E71" s="4"/>
@@ -13126,12 +13106,12 @@
       <c r="N71" s="26"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="95"/>
+      <c r="A72" s="54"/>
       <c r="B72" s="15" t="s">
-        <v>621</v>
+        <v>473</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>622</v>
+        <v>538</v>
       </c>
       <c r="D72" s="4"/>
       <c r="E72" s="4"/>
@@ -13146,12 +13126,12 @@
       <c r="N72" s="26"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="95"/>
+      <c r="A73" s="54"/>
       <c r="B73" s="15" t="s">
-        <v>478</v>
+        <v>496</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D73" s="4"/>
       <c r="E73" s="4"/>
@@ -13166,52 +13146,52 @@
       <c r="N73" s="26"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="95"/>
-      <c r="B74" s="15" t="s">
-        <v>501</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>547</v>
-      </c>
-      <c r="D74" s="4"/>
-      <c r="E74" s="4"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-      <c r="M74" s="14"/>
+      <c r="A74" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B74" s="67"/>
+      <c r="C74" s="67"/>
+      <c r="D74" s="67"/>
+      <c r="E74" s="67"/>
+      <c r="F74" s="68"/>
+      <c r="G74" s="38"/>
+      <c r="H74" s="38"/>
+      <c r="I74" s="38"/>
+      <c r="J74" s="38"/>
+      <c r="K74" s="38"/>
+      <c r="L74" s="38"/>
+      <c r="M74" s="38"/>
       <c r="N74" s="26"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B75" s="52"/>
-      <c r="C75" s="52"/>
-      <c r="D75" s="52"/>
-      <c r="E75" s="52"/>
-      <c r="F75" s="53"/>
-      <c r="G75" s="38"/>
-      <c r="H75" s="38"/>
-      <c r="I75" s="38"/>
-      <c r="J75" s="38"/>
-      <c r="K75" s="38"/>
-      <c r="L75" s="38"/>
-      <c r="M75" s="38"/>
+      <c r="A75" s="53" t="s">
+        <v>630</v>
+      </c>
+      <c r="B75" s="44" t="s">
+        <v>492</v>
+      </c>
+      <c r="C75" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="D75" s="4"/>
+      <c r="E75" s="4"/>
+      <c r="F75" s="16"/>
+      <c r="G75" s="14"/>
+      <c r="H75" s="14"/>
+      <c r="I75" s="14"/>
+      <c r="J75" s="14"/>
+      <c r="K75" s="14"/>
+      <c r="L75" s="14"/>
+      <c r="M75" s="14"/>
       <c r="N75" s="26"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="94" t="s">
-        <v>642</v>
-      </c>
-      <c r="B76" s="44" t="s">
-        <v>497</v>
-      </c>
-      <c r="C76" s="45" t="s">
-        <v>14</v>
+      <c r="A76" s="53"/>
+      <c r="B76" s="39" t="s">
+        <v>482</v>
+      </c>
+      <c r="C76" s="46" t="s">
+        <v>533</v>
       </c>
       <c r="D76" s="4"/>
       <c r="E76" s="4"/>
@@ -13226,12 +13206,12 @@
       <c r="N76" s="26"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="94"/>
-      <c r="B77" s="39" t="s">
-        <v>487</v>
-      </c>
-      <c r="C77" s="46" t="s">
-        <v>538</v>
+      <c r="A77" s="53"/>
+      <c r="B77" s="44" t="s">
+        <v>501</v>
+      </c>
+      <c r="C77" s="45" t="s">
+        <v>43</v>
       </c>
       <c r="D77" s="4"/>
       <c r="E77" s="4"/>
@@ -13246,12 +13226,12 @@
       <c r="N77" s="26"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="94"/>
+      <c r="A78" s="53"/>
       <c r="B78" s="44" t="s">
-        <v>506</v>
+        <v>194</v>
       </c>
       <c r="C78" s="45" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="D78" s="4"/>
       <c r="E78" s="4"/>
@@ -13266,12 +13246,12 @@
       <c r="N78" s="26"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="94"/>
+      <c r="A79" s="53"/>
       <c r="B79" s="44" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="C79" s="45" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D79" s="4"/>
       <c r="E79" s="4"/>
@@ -13286,12 +13266,12 @@
       <c r="N79" s="26"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="94"/>
+      <c r="A80" s="53"/>
       <c r="B80" s="44" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="C80" s="45" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="4"/>
@@ -13306,52 +13286,52 @@
       <c r="N80" s="26"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="94"/>
-      <c r="B81" s="44" t="s">
-        <v>201</v>
-      </c>
-      <c r="C81" s="45" t="s">
-        <v>36</v>
-      </c>
-      <c r="D81" s="4"/>
-      <c r="E81" s="4"/>
-      <c r="F81" s="16"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="14"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
+      <c r="A81" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B81" s="67"/>
+      <c r="C81" s="67"/>
+      <c r="D81" s="67"/>
+      <c r="E81" s="67"/>
+      <c r="F81" s="68"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="38"/>
+      <c r="I81" s="38"/>
+      <c r="J81" s="38"/>
+      <c r="K81" s="38"/>
+      <c r="L81" s="38"/>
+      <c r="M81" s="38"/>
       <c r="N81" s="26"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B82" s="52"/>
-      <c r="C82" s="52"/>
-      <c r="D82" s="52"/>
-      <c r="E82" s="52"/>
-      <c r="F82" s="53"/>
-      <c r="G82" s="38"/>
-      <c r="H82" s="38"/>
-      <c r="I82" s="38"/>
-      <c r="J82" s="38"/>
-      <c r="K82" s="38"/>
-      <c r="L82" s="38"/>
-      <c r="M82" s="38"/>
+      <c r="A82" s="53" t="s">
+        <v>631</v>
+      </c>
+      <c r="B82" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="C82" s="45" t="s">
+        <v>561</v>
+      </c>
+      <c r="D82" s="4"/>
+      <c r="E82" s="4"/>
+      <c r="F82" s="16"/>
+      <c r="G82" s="14"/>
+      <c r="H82" s="14"/>
+      <c r="I82" s="14"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
+      <c r="M82" s="14"/>
       <c r="N82" s="26"/>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="94" t="s">
-        <v>643</v>
-      </c>
+      <c r="A83" s="53"/>
       <c r="B83" s="44" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C83" s="45" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="D83" s="4"/>
       <c r="E83" s="4"/>
@@ -13366,12 +13346,12 @@
       <c r="N83" s="26"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="94"/>
+      <c r="A84" s="53"/>
       <c r="B84" s="44" t="s">
-        <v>176</v>
+        <v>196</v>
       </c>
       <c r="C84" s="45" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="D84" s="4"/>
       <c r="E84" s="4"/>
@@ -13386,12 +13366,12 @@
       <c r="N84" s="26"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="94"/>
+      <c r="A85" s="53"/>
       <c r="B85" s="44" t="s">
-        <v>197</v>
+        <v>179</v>
       </c>
       <c r="C85" s="45" t="s">
-        <v>552</v>
+        <v>531</v>
       </c>
       <c r="D85" s="4"/>
       <c r="E85" s="4"/>
@@ -13406,52 +13386,52 @@
       <c r="N85" s="26"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="94"/>
-      <c r="B86" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="C86" s="45" t="s">
-        <v>536</v>
-      </c>
-      <c r="D86" s="4"/>
-      <c r="E86" s="4"/>
-      <c r="F86" s="16"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="14"/>
-      <c r="J86" s="14"/>
-      <c r="K86" s="14"/>
-      <c r="L86" s="14"/>
-      <c r="M86" s="14"/>
+      <c r="A86" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B86" s="67"/>
+      <c r="C86" s="67"/>
+      <c r="D86" s="67"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="68"/>
+      <c r="G86" s="38"/>
+      <c r="H86" s="38"/>
+      <c r="I86" s="38"/>
+      <c r="J86" s="38"/>
+      <c r="K86" s="38"/>
+      <c r="L86" s="38"/>
+      <c r="M86" s="38"/>
       <c r="N86" s="26"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B87" s="52"/>
-      <c r="C87" s="52"/>
-      <c r="D87" s="52"/>
-      <c r="E87" s="52"/>
-      <c r="F87" s="53"/>
-      <c r="G87" s="38"/>
-      <c r="H87" s="38"/>
-      <c r="I87" s="38"/>
-      <c r="J87" s="38"/>
-      <c r="K87" s="38"/>
-      <c r="L87" s="38"/>
-      <c r="M87" s="38"/>
+      <c r="A87" s="53" t="s">
+        <v>632</v>
+      </c>
+      <c r="B87" s="29" t="s">
+        <v>243</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="16"/>
+      <c r="G87" s="14"/>
+      <c r="H87" s="14"/>
+      <c r="I87" s="14"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="14"/>
+      <c r="L87" s="14"/>
+      <c r="M87" s="14"/>
       <c r="N87" s="26"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="94" t="s">
-        <v>644</v>
-      </c>
+      <c r="A88" s="53"/>
       <c r="B88" s="29" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>11</v>
+        <v>98</v>
       </c>
       <c r="D88" s="4"/>
       <c r="E88" s="4"/>
@@ -13466,12 +13446,12 @@
       <c r="N88" s="26"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="94"/>
+      <c r="A89" s="53"/>
       <c r="B89" s="29" t="s">
-        <v>235</v>
+        <v>339</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>99</v>
+        <v>144</v>
       </c>
       <c r="D89" s="4"/>
       <c r="E89" s="4"/>
@@ -13486,12 +13466,12 @@
       <c r="N89" s="26"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="94"/>
+      <c r="A90" s="53"/>
       <c r="B90" s="29" t="s">
-        <v>343</v>
+        <v>268</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>145</v>
+        <v>9</v>
       </c>
       <c r="D90" s="4"/>
       <c r="E90" s="4"/>
@@ -13506,12 +13486,12 @@
       <c r="N90" s="26"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="94"/>
+      <c r="A91" s="53"/>
       <c r="B91" s="29" t="s">
-        <v>271</v>
+        <v>336</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D91" s="4"/>
       <c r="E91" s="4"/>
@@ -13526,12 +13506,12 @@
       <c r="N91" s="26"/>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="94"/>
+      <c r="A92" s="53"/>
       <c r="B92" s="29" t="s">
-        <v>340</v>
+        <v>594</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -13546,52 +13526,52 @@
       <c r="N92" s="26"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="94"/>
-      <c r="B93" s="29" t="s">
-        <v>601</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D93" s="4"/>
-      <c r="E93" s="4"/>
-      <c r="F93" s="16"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="14"/>
-      <c r="K93" s="14"/>
-      <c r="L93" s="14"/>
-      <c r="M93" s="14"/>
+      <c r="A93" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B93" s="67"/>
+      <c r="C93" s="67"/>
+      <c r="D93" s="67"/>
+      <c r="E93" s="67"/>
+      <c r="F93" s="68"/>
+      <c r="G93" s="38"/>
+      <c r="H93" s="38"/>
+      <c r="I93" s="38"/>
+      <c r="J93" s="38"/>
+      <c r="K93" s="38"/>
+      <c r="L93" s="38"/>
+      <c r="M93" s="38"/>
       <c r="N93" s="26"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B94" s="52"/>
-      <c r="C94" s="52"/>
-      <c r="D94" s="52"/>
-      <c r="E94" s="52"/>
-      <c r="F94" s="53"/>
-      <c r="G94" s="38"/>
-      <c r="H94" s="38"/>
-      <c r="I94" s="38"/>
-      <c r="J94" s="38"/>
-      <c r="K94" s="38"/>
-      <c r="L94" s="38"/>
-      <c r="M94" s="38"/>
+      <c r="A94" s="53" t="s">
+        <v>633</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="D94" s="4"/>
+      <c r="E94" s="4"/>
+      <c r="F94" s="16"/>
+      <c r="G94" s="14"/>
+      <c r="H94" s="14"/>
+      <c r="I94" s="14"/>
+      <c r="J94" s="14"/>
+      <c r="K94" s="14"/>
+      <c r="L94" s="14"/>
+      <c r="M94" s="14"/>
       <c r="N94" s="26"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="94" t="s">
-        <v>645</v>
-      </c>
+      <c r="A95" s="53"/>
       <c r="B95" s="15" t="s">
-        <v>311</v>
+        <v>270</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="4"/>
@@ -13606,12 +13586,14 @@
       <c r="N95" s="26"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="94"/>
+      <c r="A96" s="53" t="s">
+        <v>634</v>
+      </c>
       <c r="B96" s="15" t="s">
-        <v>273</v>
+        <v>255</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>110</v>
+        <v>92</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="4"/>
@@ -13626,14 +13608,12 @@
       <c r="N96" s="26"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="94" t="s">
-        <v>646</v>
-      </c>
+      <c r="A97" s="54"/>
       <c r="B97" s="15" t="s">
-        <v>258</v>
+        <v>235</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>93</v>
+        <v>109</v>
       </c>
       <c r="D97" s="4"/>
       <c r="E97" s="4"/>
@@ -13648,52 +13628,52 @@
       <c r="N97" s="26"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="95"/>
-      <c r="B98" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D98" s="4"/>
-      <c r="E98" s="4"/>
-      <c r="F98" s="16"/>
-      <c r="G98" s="14"/>
-      <c r="H98" s="14"/>
-      <c r="I98" s="14"/>
-      <c r="J98" s="14"/>
-      <c r="K98" s="14"/>
-      <c r="L98" s="14"/>
-      <c r="M98" s="14"/>
+      <c r="A98" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B98" s="67"/>
+      <c r="C98" s="67"/>
+      <c r="D98" s="67"/>
+      <c r="E98" s="67"/>
+      <c r="F98" s="68"/>
+      <c r="G98" s="38"/>
+      <c r="H98" s="38"/>
+      <c r="I98" s="38"/>
+      <c r="J98" s="38"/>
+      <c r="K98" s="38"/>
+      <c r="L98" s="38"/>
+      <c r="M98" s="38"/>
       <c r="N98" s="26"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B99" s="52"/>
-      <c r="C99" s="52"/>
-      <c r="D99" s="52"/>
-      <c r="E99" s="52"/>
-      <c r="F99" s="53"/>
-      <c r="G99" s="38"/>
-      <c r="H99" s="38"/>
-      <c r="I99" s="38"/>
-      <c r="J99" s="38"/>
-      <c r="K99" s="38"/>
-      <c r="L99" s="38"/>
-      <c r="M99" s="38"/>
+      <c r="A99" s="53" t="s">
+        <v>636</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>390</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="D99" s="4"/>
+      <c r="E99" s="4"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="14"/>
+      <c r="H99" s="14"/>
+      <c r="I99" s="14"/>
+      <c r="J99" s="14"/>
+      <c r="K99" s="14"/>
+      <c r="L99" s="14"/>
+      <c r="M99" s="14"/>
       <c r="N99" s="26"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="94" t="s">
-        <v>648</v>
-      </c>
+      <c r="A100" s="54"/>
       <c r="B100" s="15" t="s">
-        <v>395</v>
+        <v>414</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>574</v>
+        <v>635</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="4"/>
@@ -13708,12 +13688,12 @@
       <c r="N100" s="26"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="95"/>
+      <c r="A101" s="54"/>
       <c r="B101" s="15" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>647</v>
+        <v>515</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -13728,12 +13708,12 @@
       <c r="N101" s="26"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="95"/>
+      <c r="A102" s="54"/>
       <c r="B102" s="15" t="s">
-        <v>416</v>
+        <v>356</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>520</v>
+        <v>566</v>
       </c>
       <c r="D102" s="4"/>
       <c r="E102" s="4"/>
@@ -13748,12 +13728,12 @@
       <c r="N102" s="26"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="95"/>
+      <c r="A103" s="54"/>
       <c r="B103" s="15" t="s">
-        <v>361</v>
+        <v>593</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>573</v>
+        <v>516</v>
       </c>
       <c r="D103" s="4"/>
       <c r="E103" s="4"/>
@@ -13768,12 +13748,12 @@
       <c r="N103" s="26"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="95"/>
+      <c r="A104" s="54"/>
       <c r="B104" s="15" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>521</v>
+        <v>569</v>
       </c>
       <c r="D104" s="4"/>
       <c r="E104" s="4"/>
@@ -13788,12 +13768,12 @@
       <c r="N104" s="26"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="95"/>
+      <c r="A105" s="54"/>
       <c r="B105" s="15" t="s">
-        <v>599</v>
+        <v>385</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>576</v>
+        <v>558</v>
       </c>
       <c r="D105" s="4"/>
       <c r="E105" s="4"/>
@@ -13808,12 +13788,12 @@
       <c r="N105" s="26"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="95"/>
+      <c r="A106" s="54"/>
       <c r="B106" s="15" t="s">
-        <v>390</v>
+        <v>364</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="D106" s="4"/>
       <c r="E106" s="4"/>
@@ -13828,12 +13808,12 @@
       <c r="N106" s="26"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="95"/>
+      <c r="A107" s="54"/>
       <c r="B107" s="15" t="s">
-        <v>369</v>
+        <v>248</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D107" s="4"/>
       <c r="E107" s="4"/>
@@ -13848,12 +13828,12 @@
       <c r="N107" s="26"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="95"/>
+      <c r="A108" s="54"/>
       <c r="B108" s="15" t="s">
-        <v>251</v>
+        <v>329</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>558</v>
+        <v>79</v>
       </c>
       <c r="D108" s="4"/>
       <c r="E108" s="4"/>
@@ -13868,12 +13848,12 @@
       <c r="N108" s="26"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="95"/>
+      <c r="A109" s="54"/>
       <c r="B109" s="15" t="s">
-        <v>333</v>
+        <v>425</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D109" s="4"/>
       <c r="E109" s="4"/>
@@ -13888,12 +13868,12 @@
       <c r="N109" s="26"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="95"/>
+      <c r="A110" s="54"/>
       <c r="B110" s="15" t="s">
-        <v>246</v>
+        <v>229</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>59</v>
+        <v>167</v>
       </c>
       <c r="D110" s="4"/>
       <c r="E110" s="4"/>
@@ -13908,12 +13888,12 @@
       <c r="N110" s="26"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="95"/>
+      <c r="A111" s="54"/>
       <c r="B111" s="15" t="s">
-        <v>430</v>
+        <v>370</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D111" s="4"/>
       <c r="E111" s="4"/>
@@ -13928,12 +13908,12 @@
       <c r="N111" s="26"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="95"/>
+      <c r="A112" s="54"/>
       <c r="B112" s="15" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="D112" s="4"/>
       <c r="E112" s="4"/>
@@ -13948,12 +13928,14 @@
       <c r="N112" s="26"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="95"/>
+      <c r="A113" s="53" t="s">
+        <v>637</v>
+      </c>
       <c r="B113" s="15" t="s">
-        <v>375</v>
+        <v>340</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="D113" s="4"/>
       <c r="E113" s="4"/>
@@ -13968,12 +13950,12 @@
       <c r="N113" s="26"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="95"/>
+      <c r="A114" s="54"/>
       <c r="B114" s="15" t="s">
-        <v>241</v>
+        <v>395</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="D114" s="4"/>
       <c r="E114" s="4"/>
@@ -13988,14 +13970,12 @@
       <c r="N114" s="26"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="94" t="s">
-        <v>649</v>
-      </c>
+      <c r="A115" s="54"/>
       <c r="B115" s="15" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="4"/>
@@ -14010,12 +13990,12 @@
       <c r="N115" s="26"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="95"/>
+      <c r="A116" s="54"/>
       <c r="B116" s="15" t="s">
-        <v>400</v>
+        <v>383</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="D116" s="4"/>
       <c r="E116" s="4"/>
@@ -14030,12 +14010,12 @@
       <c r="N116" s="26"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="95"/>
+      <c r="A117" s="54"/>
       <c r="B117" s="15" t="s">
-        <v>355</v>
+        <v>375</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="D117" s="4"/>
       <c r="E117" s="4"/>
@@ -14050,12 +14030,12 @@
       <c r="N117" s="26"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="95"/>
+      <c r="A118" s="54"/>
       <c r="B118" s="15" t="s">
-        <v>388</v>
+        <v>432</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>79</v>
+        <v>522</v>
       </c>
       <c r="D118" s="4"/>
       <c r="E118" s="4"/>
@@ -14070,12 +14050,12 @@
       <c r="N118" s="26"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="95"/>
+      <c r="A119" s="54"/>
       <c r="B119" s="15" t="s">
-        <v>380</v>
+        <v>437</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>75</v>
+        <v>167</v>
       </c>
       <c r="D119" s="4"/>
       <c r="E119" s="4"/>
@@ -14090,12 +14070,12 @@
       <c r="N119" s="26"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="95"/>
+      <c r="A120" s="54"/>
       <c r="B120" s="15" t="s">
-        <v>437</v>
+        <v>399</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>527</v>
+        <v>68</v>
       </c>
       <c r="D120" s="4"/>
       <c r="E120" s="4"/>
@@ -14110,12 +14090,12 @@
       <c r="N120" s="26"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="95"/>
+      <c r="A121" s="54"/>
       <c r="B121" s="15" t="s">
-        <v>442</v>
+        <v>226</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="D121" s="4"/>
       <c r="E121" s="4"/>
@@ -14130,12 +14110,14 @@
       <c r="N121" s="26"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="95"/>
+      <c r="A122" s="53" t="s">
+        <v>638</v>
+      </c>
       <c r="B122" s="15" t="s">
-        <v>404</v>
+        <v>436</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="D122" s="4"/>
       <c r="E122" s="4"/>
@@ -14150,12 +14132,12 @@
       <c r="N122" s="26"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="95"/>
+      <c r="A123" s="54"/>
       <c r="B123" s="15" t="s">
-        <v>228</v>
+        <v>428</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>72</v>
+        <v>540</v>
       </c>
       <c r="D123" s="4"/>
       <c r="E123" s="4"/>
@@ -14170,14 +14152,12 @@
       <c r="N123" s="26"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="94" t="s">
-        <v>650</v>
-      </c>
+      <c r="A124" s="54"/>
       <c r="B124" s="15" t="s">
-        <v>441</v>
+        <v>253</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="D124" s="4"/>
       <c r="E124" s="4"/>
@@ -14192,12 +14172,12 @@
       <c r="N124" s="26"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="95"/>
+      <c r="A125" s="54"/>
       <c r="B125" s="15" t="s">
-        <v>433</v>
+        <v>415</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>546</v>
+        <v>534</v>
       </c>
       <c r="D125" s="4"/>
       <c r="E125" s="4"/>
@@ -14212,12 +14192,12 @@
       <c r="N125" s="26"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="95"/>
+      <c r="A126" s="54"/>
       <c r="B126" s="15" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D126" s="4"/>
       <c r="E126" s="4"/>
@@ -14232,12 +14212,12 @@
       <c r="N126" s="26"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="95"/>
+      <c r="A127" s="54"/>
       <c r="B127" s="15" t="s">
-        <v>420</v>
+        <v>244</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="D127" s="4"/>
       <c r="E127" s="4"/>
@@ -14252,12 +14232,12 @@
       <c r="N127" s="26"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="95"/>
+      <c r="A128" s="54"/>
       <c r="B128" s="15" t="s">
-        <v>242</v>
+        <v>417</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="4"/>
@@ -14272,12 +14252,12 @@
       <c r="N128" s="26"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="95"/>
+      <c r="A129" s="54"/>
       <c r="B129" s="15" t="s">
-        <v>247</v>
+        <v>228</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>557</v>
+        <v>539</v>
       </c>
       <c r="D129" s="4"/>
       <c r="E129" s="4"/>
@@ -14292,12 +14272,12 @@
       <c r="N129" s="26"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="95"/>
+      <c r="A130" s="54"/>
       <c r="B130" s="15" t="s">
-        <v>422</v>
+        <v>272</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -14312,12 +14292,12 @@
       <c r="N130" s="26"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="95"/>
+      <c r="A131" s="54"/>
       <c r="B131" s="15" t="s">
-        <v>230</v>
+        <v>259</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>545</v>
+        <v>528</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="4"/>
@@ -14332,12 +14312,12 @@
       <c r="N131" s="26"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="95"/>
+      <c r="A132" s="54"/>
       <c r="B132" s="15" t="s">
-        <v>275</v>
+        <v>262</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="D132" s="4"/>
       <c r="E132" s="4"/>
@@ -14352,12 +14332,12 @@
       <c r="N132" s="26"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="95"/>
+      <c r="A133" s="54"/>
       <c r="B133" s="15" t="s">
-        <v>262</v>
+        <v>209</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="4"/>
@@ -14372,12 +14352,14 @@
       <c r="N133" s="26"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="95"/>
+      <c r="A134" s="53" t="s">
+        <v>639</v>
+      </c>
       <c r="B134" s="15" t="s">
-        <v>265</v>
+        <v>251</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D134" s="4"/>
       <c r="E134" s="4"/>
@@ -14392,12 +14374,12 @@
       <c r="N134" s="26"/>
     </row>
     <row r="135" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="95"/>
+      <c r="A135" s="54"/>
       <c r="B135" s="15" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>542</v>
+        <v>77</v>
       </c>
       <c r="D135" s="4"/>
       <c r="E135" s="4"/>
@@ -14412,14 +14394,12 @@
       <c r="N135" s="26"/>
     </row>
     <row r="136" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="94" t="s">
-        <v>651</v>
-      </c>
+      <c r="A136" s="54"/>
       <c r="B136" s="15" t="s">
-        <v>254</v>
+        <v>296</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="4"/>
@@ -14434,12 +14414,12 @@
       <c r="N136" s="26"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="95"/>
+      <c r="A137" s="54"/>
       <c r="B137" s="15" t="s">
-        <v>209</v>
+        <v>283</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D137" s="4"/>
       <c r="E137" s="4"/>
@@ -14454,12 +14434,12 @@
       <c r="N137" s="26"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="95"/>
+      <c r="A138" s="54"/>
       <c r="B138" s="15" t="s">
-        <v>299</v>
+        <v>237</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D138" s="4"/>
       <c r="E138" s="4"/>
@@ -14474,12 +14454,12 @@
       <c r="N138" s="26"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="95"/>
+      <c r="A139" s="54"/>
       <c r="B139" s="15" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="4"/>
@@ -14494,12 +14474,12 @@
       <c r="N139" s="26"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="95"/>
+      <c r="A140" s="54"/>
       <c r="B140" s="15" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D140" s="4"/>
       <c r="E140" s="4"/>
@@ -14514,12 +14494,14 @@
       <c r="N140" s="26"/>
     </row>
     <row r="141" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A141" s="95"/>
+      <c r="A141" s="17" t="s">
+        <v>640</v>
+      </c>
       <c r="B141" s="15" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D141" s="4"/>
       <c r="E141" s="4"/>
@@ -14534,12 +14516,14 @@
       <c r="N141" s="26"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="95"/>
+      <c r="A142" s="53" t="s">
+        <v>641</v>
+      </c>
       <c r="B142" s="15" t="s">
-        <v>232</v>
+        <v>381</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4"/>
@@ -14554,14 +14538,12 @@
       <c r="N142" s="26"/>
     </row>
     <row r="143" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="17" t="s">
-        <v>652</v>
-      </c>
+      <c r="A143" s="54"/>
       <c r="B143" s="15" t="s">
-        <v>240</v>
+        <v>291</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="D143" s="4"/>
       <c r="E143" s="4"/>
@@ -14576,14 +14558,12 @@
       <c r="N143" s="26"/>
     </row>
     <row r="144" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="94" t="s">
-        <v>653</v>
-      </c>
+      <c r="A144" s="54"/>
       <c r="B144" s="15" t="s">
-        <v>386</v>
+        <v>257</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D144" s="4"/>
       <c r="E144" s="4"/>
@@ -14598,12 +14578,12 @@
       <c r="N144" s="26"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="95"/>
+      <c r="A145" s="54"/>
       <c r="B145" s="15" t="s">
-        <v>294</v>
+        <v>380</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D145" s="4"/>
       <c r="E145" s="4"/>
@@ -14618,12 +14598,12 @@
       <c r="N145" s="26"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="95"/>
+      <c r="A146" s="54"/>
       <c r="B146" s="15" t="s">
-        <v>260</v>
+        <v>222</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="D146" s="4"/>
       <c r="E146" s="4"/>
@@ -14638,36 +14618,36 @@
       <c r="N146" s="26"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="95"/>
-      <c r="B147" s="15" t="s">
-        <v>385</v>
-      </c>
-      <c r="C147" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="D147" s="4"/>
-      <c r="E147" s="4"/>
-      <c r="F147" s="16"/>
-      <c r="G147" s="14"/>
-      <c r="H147" s="14"/>
-      <c r="I147" s="14"/>
-      <c r="J147" s="14"/>
-      <c r="K147" s="14"/>
-      <c r="L147" s="14"/>
-      <c r="M147" s="14"/>
+      <c r="A147" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B147" s="67"/>
+      <c r="C147" s="67"/>
+      <c r="D147" s="67"/>
+      <c r="E147" s="67"/>
+      <c r="F147" s="68"/>
+      <c r="G147" s="38"/>
+      <c r="H147" s="38"/>
+      <c r="I147" s="38"/>
+      <c r="J147" s="38"/>
+      <c r="K147" s="38"/>
+      <c r="L147" s="38"/>
+      <c r="M147" s="38"/>
       <c r="N147" s="26"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="95"/>
-      <c r="B148" s="15" t="s">
-        <v>224</v>
+      <c r="A148" s="53" t="s">
+        <v>643</v>
+      </c>
+      <c r="B148" s="29" t="s">
+        <v>314</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>69</v>
+        <v>30</v>
       </c>
       <c r="D148" s="4"/>
       <c r="E148" s="4"/>
-      <c r="F148" s="16"/>
+      <c r="F148" s="20"/>
       <c r="G148" s="14"/>
       <c r="H148" s="14"/>
       <c r="I148" s="14"/>
@@ -14678,32 +14658,32 @@
       <c r="N148" s="26"/>
     </row>
     <row r="149" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B149" s="52"/>
-      <c r="C149" s="52"/>
-      <c r="D149" s="52"/>
-      <c r="E149" s="52"/>
-      <c r="F149" s="53"/>
-      <c r="G149" s="38"/>
-      <c r="H149" s="38"/>
-      <c r="I149" s="38"/>
-      <c r="J149" s="38"/>
-      <c r="K149" s="38"/>
-      <c r="L149" s="38"/>
-      <c r="M149" s="38"/>
+      <c r="A149" s="53"/>
+      <c r="B149" s="29" t="s">
+        <v>371</v>
+      </c>
+      <c r="C149" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="D149" s="4"/>
+      <c r="E149" s="4"/>
+      <c r="F149" s="20"/>
+      <c r="G149" s="14"/>
+      <c r="H149" s="14"/>
+      <c r="I149" s="14"/>
+      <c r="J149" s="14"/>
+      <c r="K149" s="14"/>
+      <c r="L149" s="14"/>
+      <c r="M149" s="14"/>
       <c r="N149" s="26"/>
     </row>
     <row r="150" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="94" t="s">
-        <v>655</v>
-      </c>
+      <c r="A150" s="53"/>
       <c r="B150" s="29" t="s">
-        <v>318</v>
+        <v>293</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="D150" s="4"/>
       <c r="E150" s="4"/>
@@ -14718,12 +14698,12 @@
       <c r="N150" s="26"/>
     </row>
     <row r="151" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="94"/>
+      <c r="A151" s="53"/>
       <c r="B151" s="29" t="s">
-        <v>376</v>
+        <v>712</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>42</v>
+        <v>713</v>
       </c>
       <c r="D151" s="4"/>
       <c r="E151" s="4"/>
@@ -14738,12 +14718,12 @@
       <c r="N151" s="26"/>
     </row>
     <row r="152" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="94"/>
+      <c r="A152" s="53"/>
       <c r="B152" s="29" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -14758,12 +14738,12 @@
       <c r="N152" s="26"/>
     </row>
     <row r="153" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="94"/>
+      <c r="A153" s="53"/>
       <c r="B153" s="29" t="s">
-        <v>729</v>
+        <v>234</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>730</v>
+        <v>5</v>
       </c>
       <c r="D153" s="4"/>
       <c r="E153" s="4"/>
@@ -14778,12 +14758,12 @@
       <c r="N153" s="26"/>
     </row>
     <row r="154" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="94"/>
+      <c r="A154" s="53"/>
       <c r="B154" s="29" t="s">
-        <v>268</v>
+        <v>333</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="D154" s="4"/>
       <c r="E154" s="4"/>
@@ -14798,12 +14778,14 @@
       <c r="N154" s="26"/>
     </row>
     <row r="155" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="94"/>
+      <c r="A155" s="53" t="s">
+        <v>644</v>
+      </c>
       <c r="B155" s="29" t="s">
-        <v>236</v>
+        <v>218</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="4"/>
@@ -14818,12 +14800,12 @@
       <c r="N155" s="26"/>
     </row>
     <row r="156" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="94"/>
+      <c r="A156" s="53"/>
       <c r="B156" s="29" t="s">
-        <v>337</v>
+        <v>261</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="4"/>
@@ -14838,14 +14820,12 @@
       <c r="N156" s="26"/>
     </row>
     <row r="157" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="94" t="s">
-        <v>656</v>
-      </c>
+      <c r="A157" s="53"/>
       <c r="B157" s="29" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="D157" s="4"/>
       <c r="E157" s="4"/>
@@ -14860,12 +14840,12 @@
       <c r="N157" s="26"/>
     </row>
     <row r="158" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="94"/>
+      <c r="A158" s="53"/>
       <c r="B158" s="29" t="s">
-        <v>264</v>
+        <v>223</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D158" s="4"/>
       <c r="E158" s="4"/>
@@ -14880,12 +14860,12 @@
       <c r="N158" s="26"/>
     </row>
     <row r="159" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="94"/>
+      <c r="A159" s="53"/>
       <c r="B159" s="29" t="s">
-        <v>238</v>
+        <v>365</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="D159" s="4"/>
       <c r="E159" s="4"/>
@@ -14900,12 +14880,12 @@
       <c r="N159" s="26"/>
     </row>
     <row r="160" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="94"/>
+      <c r="A160" s="53"/>
       <c r="B160" s="29" t="s">
-        <v>225</v>
+        <v>286</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="4"/>
@@ -14920,12 +14900,14 @@
       <c r="N160" s="26"/>
     </row>
     <row r="161" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="94"/>
+      <c r="A161" s="53" t="s">
+        <v>645</v>
+      </c>
       <c r="B161" s="29" t="s">
-        <v>370</v>
+        <v>427</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>55</v>
+        <v>519</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="4"/>
@@ -14940,12 +14922,12 @@
       <c r="N161" s="26"/>
     </row>
     <row r="162" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="94"/>
+      <c r="A162" s="53"/>
       <c r="B162" s="29" t="s">
-        <v>289</v>
+        <v>597</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>20</v>
+        <v>642</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="4"/>
@@ -14960,38 +14942,36 @@
       <c r="N162" s="26"/>
     </row>
     <row r="163" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="94" t="s">
-        <v>657</v>
-      </c>
-      <c r="B163" s="29" t="s">
-        <v>432</v>
-      </c>
-      <c r="C163" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="D163" s="4"/>
-      <c r="E163" s="4"/>
-      <c r="F163" s="20"/>
-      <c r="G163" s="14"/>
-      <c r="H163" s="14"/>
-      <c r="I163" s="14"/>
-      <c r="J163" s="14"/>
-      <c r="K163" s="14"/>
-      <c r="L163" s="14"/>
-      <c r="M163" s="14"/>
+      <c r="A163" s="66" t="s">
+        <v>502</v>
+      </c>
+      <c r="B163" s="67"/>
+      <c r="C163" s="67"/>
+      <c r="D163" s="67"/>
+      <c r="E163" s="67"/>
+      <c r="F163" s="68"/>
+      <c r="G163" s="38"/>
+      <c r="H163" s="38"/>
+      <c r="I163" s="38"/>
+      <c r="J163" s="38"/>
+      <c r="K163" s="38"/>
+      <c r="L163" s="38"/>
+      <c r="M163" s="38"/>
       <c r="N163" s="26"/>
     </row>
     <row r="164" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="94"/>
-      <c r="B164" s="29" t="s">
-        <v>609</v>
+      <c r="A164" s="103" t="s">
+        <v>656</v>
+      </c>
+      <c r="B164" s="15" t="s">
+        <v>263</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>654</v>
+        <v>134</v>
       </c>
       <c r="D164" s="4"/>
       <c r="E164" s="4"/>
-      <c r="F164" s="20"/>
+      <c r="F164" s="16"/>
       <c r="G164" s="14"/>
       <c r="H164" s="14"/>
       <c r="I164" s="14"/>
@@ -15002,32 +14982,32 @@
       <c r="N164" s="26"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="96" t="s">
-        <v>507</v>
-      </c>
-      <c r="B165" s="52"/>
-      <c r="C165" s="52"/>
-      <c r="D165" s="52"/>
-      <c r="E165" s="52"/>
-      <c r="F165" s="53"/>
-      <c r="G165" s="38"/>
-      <c r="H165" s="38"/>
-      <c r="I165" s="38"/>
-      <c r="J165" s="38"/>
-      <c r="K165" s="38"/>
-      <c r="L165" s="38"/>
-      <c r="M165" s="38"/>
+      <c r="A165" s="104"/>
+      <c r="B165" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="C165" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="D165" s="4"/>
+      <c r="E165" s="4"/>
+      <c r="F165" s="16"/>
+      <c r="G165" s="14"/>
+      <c r="H165" s="14"/>
+      <c r="I165" s="14"/>
+      <c r="J165" s="14"/>
+      <c r="K165" s="14"/>
+      <c r="L165" s="14"/>
+      <c r="M165" s="14"/>
       <c r="N165" s="26"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="95" t="s">
-        <v>214</v>
-      </c>
+      <c r="A166" s="104"/>
       <c r="B166" s="15" t="s">
-        <v>266</v>
+        <v>250</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>135</v>
+        <v>526</v>
       </c>
       <c r="D166" s="4"/>
       <c r="E166" s="4"/>
@@ -15042,12 +15022,10 @@
       <c r="N166" s="26"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="95"/>
-      <c r="B167" s="15" t="s">
-        <v>253</v>
-      </c>
+      <c r="A167" s="104"/>
+      <c r="B167" s="15"/>
       <c r="C167" s="4" t="s">
-        <v>570</v>
+        <v>723</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="4"/>
@@ -15062,12 +15040,10 @@
       <c r="N167" s="26"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="95"/>
-      <c r="B168" s="15" t="s">
-        <v>253</v>
-      </c>
+      <c r="A168" s="69"/>
+      <c r="B168" s="15"/>
       <c r="C168" s="4" t="s">
-        <v>531</v>
+        <v>724</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="4"/>
@@ -15082,14 +15058,14 @@
       <c r="N168" s="26"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="95" t="s">
-        <v>673</v>
+      <c r="A169" s="101" t="s">
+        <v>655</v>
       </c>
       <c r="B169" s="15" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="4"/>
@@ -15104,12 +15080,12 @@
       <c r="N169" s="26"/>
     </row>
     <row r="170" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="95"/>
+      <c r="A170" s="102"/>
       <c r="B170" s="15" t="s">
-        <v>381</v>
+        <v>376</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D170" s="4"/>
       <c r="E170" s="4"/>
@@ -15124,14 +15100,14 @@
       <c r="N170" s="26"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="95" t="s">
-        <v>672</v>
+      <c r="A171" s="54" t="s">
+        <v>654</v>
       </c>
       <c r="B171" s="15" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>666</v>
+        <v>649</v>
       </c>
       <c r="D171" s="4"/>
       <c r="E171" s="4"/>
@@ -15146,12 +15122,12 @@
       <c r="N171" s="26"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="95"/>
+      <c r="A172" s="54"/>
       <c r="B172" s="15" t="s">
-        <v>365</v>
+        <v>360</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>667</v>
+        <v>650</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="4"/>
@@ -15166,14 +15142,14 @@
       <c r="N172" s="26"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="95" t="s">
-        <v>671</v>
+      <c r="A173" s="54" t="s">
+        <v>653</v>
       </c>
       <c r="B173" s="15" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D173" s="4"/>
       <c r="E173" s="4"/>
@@ -15188,12 +15164,12 @@
       <c r="N173" s="26"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="95"/>
+      <c r="A174" s="54"/>
       <c r="B174" s="15" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>610</v>
+        <v>598</v>
       </c>
       <c r="D174" s="4"/>
       <c r="E174" s="4"/>
@@ -15208,14 +15184,14 @@
       <c r="N174" s="26"/>
     </row>
     <row r="175" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A175" s="95" t="s">
-        <v>670</v>
+      <c r="A175" s="17" t="s">
+        <v>652</v>
       </c>
       <c r="B175" s="15" t="s">
-        <v>603</v>
+        <v>301</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>658</v>
+        <v>83</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="4"/>
@@ -15230,12 +15206,14 @@
       <c r="N175" s="26"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="95"/>
+      <c r="A176" s="54" t="s">
+        <v>651</v>
+      </c>
       <c r="B176" s="15" t="s">
-        <v>604</v>
+        <v>290</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>659</v>
+        <v>646</v>
       </c>
       <c r="D176" s="4"/>
       <c r="E176" s="4"/>
@@ -15250,12 +15228,12 @@
       <c r="N176" s="26"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="95"/>
+      <c r="A177" s="54"/>
       <c r="B177" s="15" t="s">
-        <v>605</v>
+        <v>252</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>660</v>
+        <v>647</v>
       </c>
       <c r="D177" s="4"/>
       <c r="E177" s="4"/>
@@ -15270,12 +15248,12 @@
       <c r="N177" s="26"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="95"/>
+      <c r="A178" s="54"/>
       <c r="B178" s="15" t="s">
-        <v>606</v>
+        <v>271</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>661</v>
+        <v>648</v>
       </c>
       <c r="D178" s="4"/>
       <c r="E178" s="4"/>
@@ -15290,34 +15268,32 @@
       <c r="N178" s="26"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="95"/>
-      <c r="B179" s="15" t="s">
-        <v>607</v>
-      </c>
-      <c r="C179" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="D179" s="4"/>
-      <c r="E179" s="4"/>
-      <c r="F179" s="16"/>
-      <c r="G179" s="14"/>
-      <c r="H179" s="14"/>
-      <c r="I179" s="14"/>
-      <c r="J179" s="14"/>
-      <c r="K179" s="14"/>
-      <c r="L179" s="14"/>
-      <c r="M179" s="14"/>
+      <c r="A179" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B179" s="67"/>
+      <c r="C179" s="67"/>
+      <c r="D179" s="67"/>
+      <c r="E179" s="67"/>
+      <c r="F179" s="68"/>
+      <c r="G179" s="38"/>
+      <c r="H179" s="38"/>
+      <c r="I179" s="38"/>
+      <c r="J179" s="38"/>
+      <c r="K179" s="38"/>
+      <c r="L179" s="38"/>
+      <c r="M179" s="38"/>
       <c r="N179" s="26"/>
     </row>
     <row r="180" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="95" t="s">
-        <v>669</v>
+      <c r="A180" s="54" t="s">
+        <v>663</v>
       </c>
       <c r="B180" s="15" t="s">
-        <v>305</v>
+        <v>205</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>84</v>
+        <v>214</v>
       </c>
       <c r="D180" s="4"/>
       <c r="E180" s="4"/>
@@ -15332,12 +15308,12 @@
       <c r="N180" s="26"/>
     </row>
     <row r="181" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="95"/>
+      <c r="A181" s="54"/>
       <c r="B181" s="15" t="s">
-        <v>300</v>
+        <v>459</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>540</v>
+        <v>441</v>
       </c>
       <c r="D181" s="4"/>
       <c r="E181" s="4"/>
@@ -15352,14 +15328,14 @@
       <c r="N181" s="26"/>
     </row>
     <row r="182" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="95" t="s">
-        <v>668</v>
+      <c r="A182" s="54" t="s">
+        <v>664</v>
       </c>
       <c r="B182" s="15" t="s">
-        <v>293</v>
+        <v>466</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>663</v>
+        <v>46</v>
       </c>
       <c r="D182" s="4"/>
       <c r="E182" s="4"/>
@@ -15374,12 +15350,12 @@
       <c r="N182" s="26"/>
     </row>
     <row r="183" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="95"/>
+      <c r="A183" s="54"/>
       <c r="B183" s="15" t="s">
-        <v>255</v>
+        <v>449</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>664</v>
+        <v>27</v>
       </c>
       <c r="D183" s="4"/>
       <c r="E183" s="4"/>
@@ -15394,12 +15370,12 @@
       <c r="N183" s="26"/>
     </row>
     <row r="184" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="95"/>
+      <c r="A184" s="54"/>
       <c r="B184" s="15" t="s">
-        <v>274</v>
+        <v>453</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>665</v>
+        <v>24</v>
       </c>
       <c r="D184" s="4"/>
       <c r="E184" s="4"/>
@@ -15414,32 +15390,32 @@
       <c r="N184" s="26"/>
     </row>
     <row r="185" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B185" s="52"/>
-      <c r="C185" s="52"/>
-      <c r="D185" s="52"/>
-      <c r="E185" s="52"/>
-      <c r="F185" s="53"/>
-      <c r="G185" s="38"/>
-      <c r="H185" s="38"/>
-      <c r="I185" s="38"/>
-      <c r="J185" s="38"/>
-      <c r="K185" s="38"/>
-      <c r="L185" s="38"/>
-      <c r="M185" s="38"/>
+      <c r="A185" s="54"/>
+      <c r="B185" s="15" t="s">
+        <v>457</v>
+      </c>
+      <c r="C185" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="4"/>
+      <c r="E185" s="4"/>
+      <c r="F185" s="16"/>
+      <c r="G185" s="14"/>
+      <c r="H185" s="14"/>
+      <c r="I185" s="14"/>
+      <c r="J185" s="14"/>
+      <c r="K185" s="14"/>
+      <c r="L185" s="14"/>
+      <c r="M185" s="14"/>
       <c r="N185" s="26"/>
     </row>
     <row r="186" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="95" t="s">
-        <v>680</v>
-      </c>
+      <c r="A186" s="54"/>
       <c r="B186" s="15" t="s">
-        <v>206</v>
+        <v>440</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>216</v>
+        <v>1</v>
       </c>
       <c r="D186" s="4"/>
       <c r="E186" s="4"/>
@@ -15454,12 +15430,12 @@
       <c r="N186" s="26"/>
     </row>
     <row r="187" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="95"/>
+      <c r="A187" s="54"/>
       <c r="B187" s="15" t="s">
-        <v>464</v>
+        <v>451</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>446</v>
+        <v>6</v>
       </c>
       <c r="D187" s="4"/>
       <c r="E187" s="4"/>
@@ -15474,14 +15450,14 @@
       <c r="N187" s="26"/>
     </row>
     <row r="188" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="95" t="s">
-        <v>681</v>
+      <c r="A188" s="54" t="s">
+        <v>611</v>
       </c>
       <c r="B188" s="15" t="s">
-        <v>471</v>
+        <v>657</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>46</v>
+        <v>658</v>
       </c>
       <c r="D188" s="4"/>
       <c r="E188" s="4"/>
@@ -15496,12 +15472,12 @@
       <c r="N188" s="26"/>
     </row>
     <row r="189" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="95"/>
+      <c r="A189" s="54"/>
       <c r="B189" s="15" t="s">
-        <v>454</v>
+        <v>659</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>27</v>
+        <v>660</v>
       </c>
       <c r="D189" s="4"/>
       <c r="E189" s="4"/>
@@ -15516,12 +15492,12 @@
       <c r="N189" s="26"/>
     </row>
     <row r="190" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="95"/>
+      <c r="A190" s="54"/>
       <c r="B190" s="15" t="s">
-        <v>458</v>
+        <v>661</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>24</v>
+        <v>662</v>
       </c>
       <c r="D190" s="4"/>
       <c r="E190" s="4"/>
@@ -15536,12 +15512,14 @@
       <c r="N190" s="26"/>
     </row>
     <row r="191" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="95"/>
+      <c r="A191" s="53" t="s">
+        <v>714</v>
+      </c>
       <c r="B191" s="15" t="s">
-        <v>462</v>
+        <v>715</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>3</v>
+        <v>719</v>
       </c>
       <c r="D191" s="4"/>
       <c r="E191" s="4"/>
@@ -15553,15 +15531,15 @@
       <c r="K191" s="14"/>
       <c r="L191" s="14"/>
       <c r="M191" s="14"/>
-      <c r="N191" s="26"/>
+      <c r="N191" s="28"/>
     </row>
     <row r="192" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="95"/>
+      <c r="A192" s="54"/>
       <c r="B192" s="15" t="s">
-        <v>445</v>
+        <v>716</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>1</v>
+        <v>720</v>
       </c>
       <c r="D192" s="4"/>
       <c r="E192" s="4"/>
@@ -15573,15 +15551,15 @@
       <c r="K192" s="14"/>
       <c r="L192" s="14"/>
       <c r="M192" s="14"/>
-      <c r="N192" s="26"/>
+      <c r="N192" s="28"/>
     </row>
     <row r="193" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="95"/>
+      <c r="A193" s="54"/>
       <c r="B193" s="15" t="s">
-        <v>456</v>
+        <v>717</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>6</v>
+        <v>721</v>
       </c>
       <c r="D193" s="4"/>
       <c r="E193" s="4"/>
@@ -15593,17 +15571,15 @@
       <c r="K193" s="14"/>
       <c r="L193" s="14"/>
       <c r="M193" s="14"/>
-      <c r="N193" s="26"/>
+      <c r="N193" s="28"/>
     </row>
     <row r="194" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="95" t="s">
-        <v>623</v>
-      </c>
+      <c r="A194" s="54"/>
       <c r="B194" s="15" t="s">
-        <v>674</v>
+        <v>718</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>675</v>
+        <v>722</v>
       </c>
       <c r="D194" s="4"/>
       <c r="E194" s="4"/>
@@ -15615,201 +15591,121 @@
       <c r="K194" s="14"/>
       <c r="L194" s="14"/>
       <c r="M194" s="14"/>
-      <c r="N194" s="26"/>
-    </row>
-    <row r="195" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="95"/>
-      <c r="B195" s="15" t="s">
-        <v>676</v>
-      </c>
-      <c r="C195" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="D195" s="4"/>
-      <c r="E195" s="4"/>
-      <c r="F195" s="16"/>
-      <c r="G195" s="14"/>
-      <c r="H195" s="14"/>
-      <c r="I195" s="14"/>
-      <c r="J195" s="14"/>
-      <c r="K195" s="14"/>
-      <c r="L195" s="14"/>
-      <c r="M195" s="14"/>
-      <c r="N195" s="26"/>
-    </row>
-    <row r="196" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A196" s="95"/>
-      <c r="B196" s="15" t="s">
-        <v>678</v>
-      </c>
-      <c r="C196" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="D196" s="4"/>
-      <c r="E196" s="4"/>
-      <c r="F196" s="16"/>
-      <c r="G196" s="14"/>
-      <c r="H196" s="14"/>
-      <c r="I196" s="14"/>
-      <c r="J196" s="14"/>
-      <c r="K196" s="14"/>
-      <c r="L196" s="14"/>
-      <c r="M196" s="14"/>
-      <c r="N196" s="26"/>
+      <c r="N194" s="28"/>
+    </row>
+    <row r="195" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A195" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="B195" s="74"/>
+      <c r="C195" s="74"/>
+      <c r="D195" s="74"/>
+      <c r="E195" s="74"/>
+      <c r="F195" s="75"/>
+      <c r="G195" s="51"/>
+      <c r="H195" s="51"/>
+      <c r="I195" s="51"/>
+      <c r="J195" s="51"/>
+      <c r="K195" s="51"/>
+      <c r="L195" s="51"/>
+      <c r="M195" s="51"/>
+      <c r="N195" s="52"/>
+    </row>
+    <row r="196" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A196" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="B196" s="71"/>
+      <c r="C196" s="71"/>
+      <c r="D196" s="71"/>
+      <c r="E196" s="71"/>
+      <c r="F196" s="72"/>
+      <c r="G196" s="48"/>
+      <c r="H196" s="48"/>
+      <c r="I196" s="48"/>
+      <c r="J196" s="48"/>
+      <c r="K196" s="48"/>
+      <c r="L196" s="48"/>
+      <c r="M196" s="48"/>
+      <c r="N196" s="49"/>
     </row>
     <row r="197" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="94" t="s">
-        <v>731</v>
-      </c>
-      <c r="B197" s="15" t="s">
-        <v>732</v>
-      </c>
-      <c r="C197" s="4" t="s">
-        <v>736</v>
-      </c>
-      <c r="D197" s="4"/>
-      <c r="E197" s="4"/>
-      <c r="F197" s="16"/>
-      <c r="G197" s="14"/>
-      <c r="H197" s="14"/>
-      <c r="I197" s="14"/>
-      <c r="J197" s="14"/>
-      <c r="K197" s="14"/>
-      <c r="L197" s="14"/>
-      <c r="M197" s="14"/>
-      <c r="N197" s="28"/>
+      <c r="A197" s="3"/>
+      <c r="B197" s="1"/>
+      <c r="C197" s="5"/>
+      <c r="D197" s="5"/>
+      <c r="E197" s="5"/>
+      <c r="F197" s="7"/>
+      <c r="G197" s="3"/>
+      <c r="H197" s="8"/>
+      <c r="I197" s="8"/>
+      <c r="J197" s="8"/>
+      <c r="K197" s="8"/>
+      <c r="L197" s="8"/>
+      <c r="M197" s="8"/>
+      <c r="N197" s="8"/>
     </row>
     <row r="198" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A198" s="95"/>
-      <c r="B198" s="15" t="s">
-        <v>733</v>
-      </c>
-      <c r="C198" s="4" t="s">
-        <v>737</v>
-      </c>
-      <c r="D198" s="4"/>
-      <c r="E198" s="4"/>
-      <c r="F198" s="16"/>
-      <c r="G198" s="14"/>
-      <c r="H198" s="14"/>
-      <c r="I198" s="14"/>
-      <c r="J198" s="14"/>
-      <c r="K198" s="14"/>
-      <c r="L198" s="14"/>
-      <c r="M198" s="14"/>
-      <c r="N198" s="28"/>
-    </row>
-    <row r="199" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A199" s="95"/>
-      <c r="B199" s="15" t="s">
-        <v>734</v>
-      </c>
-      <c r="C199" s="4" t="s">
-        <v>738</v>
-      </c>
-      <c r="D199" s="4"/>
-      <c r="E199" s="4"/>
-      <c r="F199" s="16"/>
-      <c r="G199" s="14"/>
-      <c r="H199" s="14"/>
-      <c r="I199" s="14"/>
-      <c r="J199" s="14"/>
-      <c r="K199" s="14"/>
-      <c r="L199" s="14"/>
-      <c r="M199" s="14"/>
-      <c r="N199" s="28"/>
-    </row>
-    <row r="200" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="95"/>
-      <c r="B200" s="15" t="s">
-        <v>735</v>
-      </c>
-      <c r="C200" s="4" t="s">
-        <v>739</v>
-      </c>
-      <c r="D200" s="4"/>
-      <c r="E200" s="4"/>
-      <c r="F200" s="16"/>
-      <c r="G200" s="14"/>
-      <c r="H200" s="14"/>
-      <c r="I200" s="14"/>
-      <c r="J200" s="14"/>
-      <c r="K200" s="14"/>
-      <c r="L200" s="14"/>
-      <c r="M200" s="14"/>
-      <c r="N200" s="28"/>
-    </row>
-    <row r="201" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A201" s="98" t="s">
-        <v>114</v>
-      </c>
-      <c r="B201" s="55"/>
-      <c r="C201" s="55"/>
-      <c r="D201" s="55"/>
-      <c r="E201" s="55"/>
-      <c r="F201" s="56"/>
-      <c r="G201" s="99"/>
-      <c r="H201" s="99"/>
-      <c r="I201" s="99"/>
-      <c r="J201" s="99"/>
-      <c r="K201" s="99"/>
-      <c r="L201" s="99"/>
-      <c r="M201" s="99"/>
-      <c r="N201" s="100"/>
-    </row>
-    <row r="202" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A202" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B202" s="58"/>
-      <c r="C202" s="58"/>
-      <c r="D202" s="58"/>
-      <c r="E202" s="58"/>
-      <c r="F202" s="59"/>
-      <c r="G202" s="48"/>
-      <c r="H202" s="48"/>
-      <c r="I202" s="48"/>
-      <c r="J202" s="48"/>
-      <c r="K202" s="48"/>
-      <c r="L202" s="48"/>
-      <c r="M202" s="48"/>
-      <c r="N202" s="49"/>
-    </row>
-    <row r="203" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A203" s="3"/>
-      <c r="B203" s="1"/>
-      <c r="C203" s="5"/>
-      <c r="D203" s="5"/>
-      <c r="E203" s="5"/>
-      <c r="F203" s="7"/>
-      <c r="G203" s="3"/>
-      <c r="H203" s="8"/>
-      <c r="I203" s="8"/>
-      <c r="J203" s="8"/>
-      <c r="K203" s="8"/>
-      <c r="L203" s="8"/>
-      <c r="M203" s="8"/>
-      <c r="N203" s="8"/>
-    </row>
-    <row r="204" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A204" s="3"/>
-      <c r="B204" s="1"/>
-      <c r="C204" s="5"/>
-      <c r="D204" s="5"/>
-      <c r="E204" s="5"/>
-      <c r="F204" s="7"/>
-      <c r="G204" s="3"/>
-      <c r="H204" s="8"/>
-      <c r="I204" s="8"/>
-      <c r="J204" s="8"/>
-      <c r="K204" s="8"/>
-      <c r="L204" s="8"/>
-      <c r="M204" s="8"/>
-      <c r="N204" s="8"/>
+      <c r="A198" s="3"/>
+      <c r="B198" s="1"/>
+      <c r="C198" s="5"/>
+      <c r="D198" s="5"/>
+      <c r="E198" s="5"/>
+      <c r="F198" s="7"/>
+      <c r="G198" s="3"/>
+      <c r="H198" s="8"/>
+      <c r="I198" s="8"/>
+      <c r="J198" s="8"/>
+      <c r="K198" s="8"/>
+      <c r="L198" s="8"/>
+      <c r="M198" s="8"/>
+      <c r="N198" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="A197:A200"/>
+  <mergeCells count="58">
+    <mergeCell ref="A47:A57"/>
+    <mergeCell ref="A59:A73"/>
+    <mergeCell ref="A75:A80"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A87:A92"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A86:F86"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A173:A174"/>
+    <mergeCell ref="A122:A133"/>
+    <mergeCell ref="A134:A140"/>
+    <mergeCell ref="A142:A146"/>
+    <mergeCell ref="A113:A121"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="A164:A168"/>
+    <mergeCell ref="A8:A18"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="A196:F196"/>
+    <mergeCell ref="A195:F195"/>
+    <mergeCell ref="A179:F179"/>
+    <mergeCell ref="A163:F163"/>
+    <mergeCell ref="A147:F147"/>
+    <mergeCell ref="A180:A181"/>
+    <mergeCell ref="A182:A187"/>
+    <mergeCell ref="A188:A190"/>
+    <mergeCell ref="A169:A170"/>
+    <mergeCell ref="A148:A154"/>
+    <mergeCell ref="A155:A160"/>
+    <mergeCell ref="A161:A162"/>
+    <mergeCell ref="A20:A27"/>
+    <mergeCell ref="A34:A45"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A191:A194"/>
     <mergeCell ref="A2:N2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
@@ -15825,50 +15721,6 @@
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A21:A28"/>
-    <mergeCell ref="A35:A46"/>
-    <mergeCell ref="A34:F34"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A30:A33"/>
-    <mergeCell ref="A8:A19"/>
-    <mergeCell ref="A47:F47"/>
-    <mergeCell ref="A202:F202"/>
-    <mergeCell ref="A201:F201"/>
-    <mergeCell ref="A185:F185"/>
-    <mergeCell ref="A165:F165"/>
-    <mergeCell ref="A149:F149"/>
-    <mergeCell ref="A186:A187"/>
-    <mergeCell ref="A188:A193"/>
-    <mergeCell ref="A194:A196"/>
-    <mergeCell ref="A169:A170"/>
-    <mergeCell ref="A150:A156"/>
-    <mergeCell ref="A157:A162"/>
-    <mergeCell ref="A163:A164"/>
-    <mergeCell ref="A175:A179"/>
-    <mergeCell ref="A180:A181"/>
-    <mergeCell ref="A94:F94"/>
-    <mergeCell ref="A95:A96"/>
-    <mergeCell ref="A97:A98"/>
-    <mergeCell ref="A99:F99"/>
-    <mergeCell ref="A182:A184"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="A173:A174"/>
-    <mergeCell ref="A166:A168"/>
-    <mergeCell ref="A124:A135"/>
-    <mergeCell ref="A136:A142"/>
-    <mergeCell ref="A144:A148"/>
-    <mergeCell ref="A115:A123"/>
-    <mergeCell ref="A100:A114"/>
-    <mergeCell ref="A48:A58"/>
-    <mergeCell ref="A60:A74"/>
-    <mergeCell ref="A76:A81"/>
-    <mergeCell ref="A83:A86"/>
-    <mergeCell ref="A88:A93"/>
-    <mergeCell ref="A59:F59"/>
-    <mergeCell ref="A75:F75"/>
-    <mergeCell ref="A82:F82"/>
-    <mergeCell ref="A87:F87"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18353,22 +18205,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="81"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
+      <c r="O2" s="55"/>
+      <c r="P2" s="55"/>
     </row>
     <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -18386,13 +18238,13 @@
       <c r="M3" s="31"/>
       <c r="N3" s="31"/>
       <c r="O3" s="32" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="P3" s="50"/>
     </row>
     <row r="4" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="O4" s="37" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="P4" s="50"/>
     </row>
@@ -18401,82 +18253,82 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="86" t="s">
-        <v>624</v>
-      </c>
-      <c r="C6" s="84" t="s">
-        <v>625</v>
-      </c>
-      <c r="D6" s="84" t="s">
-        <v>626</v>
-      </c>
-      <c r="E6" s="91" t="s">
-        <v>727</v>
-      </c>
-      <c r="F6" s="93" t="s">
-        <v>728</v>
-      </c>
-      <c r="G6" s="84" t="s">
-        <v>627</v>
-      </c>
-      <c r="H6" s="79" t="s">
-        <v>628</v>
-      </c>
-      <c r="I6" s="79" t="s">
-        <v>578</v>
-      </c>
-      <c r="J6" s="79" t="s">
+      <c r="A6" s="56" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>612</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>614</v>
+      </c>
+      <c r="E6" s="80" t="s">
+        <v>710</v>
+      </c>
+      <c r="F6" s="82" t="s">
+        <v>711</v>
+      </c>
+      <c r="G6" s="60" t="s">
+        <v>615</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>616</v>
+      </c>
+      <c r="I6" s="62" t="s">
+        <v>571</v>
+      </c>
+      <c r="J6" s="62" t="s">
+        <v>575</v>
+      </c>
+      <c r="K6" s="62" t="s">
+        <v>581</v>
+      </c>
+      <c r="L6" s="62" t="s">
         <v>582</v>
       </c>
-      <c r="K6" s="79" t="s">
-        <v>588</v>
-      </c>
-      <c r="L6" s="79" t="s">
-        <v>589</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>590</v>
-      </c>
-      <c r="N6" s="79" t="s">
-        <v>608</v>
-      </c>
-      <c r="O6" s="79" t="s">
-        <v>629</v>
-      </c>
-      <c r="P6" s="82" t="s">
-        <v>630</v>
+      <c r="M6" s="62" t="s">
+        <v>583</v>
+      </c>
+      <c r="N6" s="62" t="s">
+        <v>596</v>
+      </c>
+      <c r="O6" s="62" t="s">
+        <v>617</v>
+      </c>
+      <c r="P6" s="64" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="90"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="85"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="80"/>
-      <c r="O7" s="80"/>
-      <c r="P7" s="83"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="81"/>
+      <c r="F7" s="81"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="63"/>
+      <c r="O7" s="63"/>
+      <c r="P7" s="65"/>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="97" t="s">
-        <v>710</v>
+      <c r="A8" s="69" t="s">
+        <v>693</v>
       </c>
       <c r="B8" s="23">
         <v>7425</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>687</v>
+        <v>670</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -18493,12 +18345,12 @@
       <c r="P8" s="27"/>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="95"/>
+      <c r="A9" s="54"/>
       <c r="B9" s="15">
         <v>7427</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>688</v>
+        <v>671</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -18515,12 +18367,12 @@
       <c r="P9" s="26"/>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="95"/>
+      <c r="A10" s="54"/>
       <c r="B10" s="18">
         <v>7429</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>689</v>
+        <v>672</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
@@ -18537,12 +18389,12 @@
       <c r="P10" s="26"/>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="95"/>
+      <c r="A11" s="54"/>
       <c r="B11" s="18">
         <v>7431</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>690</v>
+        <v>673</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
@@ -18559,12 +18411,12 @@
       <c r="P11" s="26"/>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="95"/>
+      <c r="A12" s="54"/>
       <c r="B12" s="18">
         <v>7433</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>691</v>
+        <v>674</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
@@ -18581,12 +18433,12 @@
       <c r="P12" s="26"/>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="95"/>
+      <c r="A13" s="54"/>
       <c r="B13" s="18">
         <v>7435</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>692</v>
+        <v>675</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="19"/>
@@ -18603,12 +18455,12 @@
       <c r="P13" s="26"/>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="95"/>
+      <c r="A14" s="54"/>
       <c r="B14" s="18">
         <v>7437</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>693</v>
+        <v>676</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="19"/>
@@ -18625,12 +18477,12 @@
       <c r="P14" s="26"/>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="95"/>
+      <c r="A15" s="54"/>
       <c r="B15" s="18">
         <v>7439</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>694</v>
+        <v>677</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
@@ -18647,12 +18499,12 @@
       <c r="P15" s="26"/>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="95"/>
+      <c r="A16" s="54"/>
       <c r="B16" s="18">
         <v>7441</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>695</v>
+        <v>678</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="19"/>
@@ -18669,12 +18521,12 @@
       <c r="P16" s="26"/>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="95"/>
+      <c r="A17" s="54"/>
       <c r="B17" s="18">
         <v>7426</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>696</v>
+        <v>679</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="19"/>
@@ -18691,12 +18543,12 @@
       <c r="P17" s="26"/>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="95"/>
+      <c r="A18" s="54"/>
       <c r="B18" s="18">
         <v>7430</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>697</v>
+        <v>680</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19"/>
@@ -18713,12 +18565,12 @@
       <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="95"/>
+      <c r="A19" s="54"/>
       <c r="B19" s="18">
         <v>7432</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>698</v>
+        <v>681</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="19"/>
@@ -18735,12 +18587,12 @@
       <c r="P19" s="26"/>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="95"/>
+      <c r="A20" s="54"/>
       <c r="B20" s="18">
         <v>7434</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>699</v>
+        <v>682</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19"/>
@@ -18757,12 +18609,12 @@
       <c r="P20" s="26"/>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="95"/>
+      <c r="A21" s="54"/>
       <c r="B21" s="18">
         <v>7436</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>700</v>
+        <v>683</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="19"/>
@@ -18779,12 +18631,12 @@
       <c r="P21" s="26"/>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="95"/>
+      <c r="A22" s="54"/>
       <c r="B22" s="18">
         <v>7438</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>701</v>
+        <v>684</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="19"/>
@@ -18801,12 +18653,12 @@
       <c r="P22" s="26"/>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="95"/>
+      <c r="A23" s="54"/>
       <c r="B23" s="18">
         <v>7440</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>702</v>
+        <v>685</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="19"/>
@@ -18823,12 +18675,12 @@
       <c r="P23" s="26"/>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="95"/>
+      <c r="A24" s="54"/>
       <c r="B24" s="18">
         <v>7442</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>703</v>
+        <v>686</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -18845,12 +18697,12 @@
       <c r="P24" s="26"/>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="95"/>
+      <c r="A25" s="54"/>
       <c r="B25" s="18">
         <v>7443</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>704</v>
+        <v>687</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -18867,12 +18719,12 @@
       <c r="P25" s="26"/>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="95"/>
+      <c r="A26" s="54"/>
       <c r="B26" s="18">
         <v>7445</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>705</v>
+        <v>688</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="19"/>
@@ -18889,12 +18741,12 @@
       <c r="P26" s="26"/>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="95"/>
+      <c r="A27" s="54"/>
       <c r="B27" s="18">
         <v>7444</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>706</v>
+        <v>689</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19"/>
@@ -18911,12 +18763,12 @@
       <c r="P27" s="26"/>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="95"/>
+      <c r="A28" s="54"/>
       <c r="B28" s="18">
         <v>7446</v>
       </c>
       <c r="C28" s="19" t="s">
-        <v>707</v>
+        <v>690</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19"/>
@@ -18933,12 +18785,12 @@
       <c r="P28" s="26"/>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="95"/>
+      <c r="A29" s="54"/>
       <c r="B29" s="18">
         <v>7448</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>708</v>
+        <v>691</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="19"/>
@@ -18955,12 +18807,12 @@
       <c r="P29" s="26"/>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="95"/>
+      <c r="A30" s="54"/>
       <c r="B30" s="18">
         <v>7450</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>709</v>
+        <v>692</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="19"/>
@@ -18977,16 +18829,16 @@
       <c r="P30" s="26"/>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B31" s="52"/>
-      <c r="C31" s="52"/>
-      <c r="D31" s="52"/>
-      <c r="E31" s="52"/>
-      <c r="F31" s="52"/>
-      <c r="G31" s="52"/>
-      <c r="H31" s="53"/>
+      <c r="A31" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="68"/>
       <c r="I31" s="38"/>
       <c r="J31" s="38"/>
       <c r="K31" s="38"/>
@@ -18997,14 +18849,14 @@
       <c r="P31" s="26"/>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="95" t="s">
-        <v>711</v>
+      <c r="A32" s="54" t="s">
+        <v>694</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
@@ -19021,12 +18873,12 @@
       <c r="P32" s="26"/>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="95"/>
+      <c r="A33" s="54"/>
       <c r="B33" s="15" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -19043,12 +18895,12 @@
       <c r="P33" s="26"/>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="95"/>
+      <c r="A34" s="54"/>
       <c r="B34" s="15" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
@@ -19065,12 +18917,12 @@
       <c r="P34" s="26"/>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="95"/>
+      <c r="A35" s="54"/>
       <c r="B35" s="15" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
@@ -19087,12 +18939,12 @@
       <c r="P35" s="26"/>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="95"/>
+      <c r="A36" s="54"/>
       <c r="B36" s="15" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -19109,12 +18961,12 @@
       <c r="P36" s="26"/>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="95"/>
+      <c r="A37" s="54"/>
       <c r="B37" s="15" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -19131,12 +18983,12 @@
       <c r="P37" s="26"/>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="95"/>
+      <c r="A38" s="54"/>
       <c r="B38" s="15" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -19153,12 +19005,12 @@
       <c r="P38" s="26"/>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="95"/>
+      <c r="A39" s="54"/>
       <c r="B39" s="15" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
@@ -19175,16 +19027,16 @@
       <c r="P39" s="26"/>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B40" s="52"/>
-      <c r="C40" s="52"/>
-      <c r="D40" s="52"/>
-      <c r="E40" s="52"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="52"/>
-      <c r="H40" s="53"/>
+      <c r="A40" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
+      <c r="E40" s="67"/>
+      <c r="F40" s="67"/>
+      <c r="G40" s="67"/>
+      <c r="H40" s="68"/>
       <c r="I40" s="38"/>
       <c r="J40" s="38"/>
       <c r="K40" s="38"/>
@@ -19195,14 +19047,14 @@
       <c r="P40" s="26"/>
     </row>
     <row r="41" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="94" t="s">
-        <v>713</v>
+      <c r="A41" s="53" t="s">
+        <v>696</v>
       </c>
       <c r="B41" s="29" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
@@ -19219,12 +19071,12 @@
       <c r="P41" s="26"/>
     </row>
     <row r="42" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="94"/>
+      <c r="A42" s="53"/>
       <c r="B42" s="29" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
@@ -19241,12 +19093,12 @@
       <c r="P42" s="26"/>
     </row>
     <row r="43" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="94"/>
+      <c r="A43" s="53"/>
       <c r="B43" s="29" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>712</v>
+        <v>695</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
@@ -19263,12 +19115,12 @@
       <c r="P43" s="26"/>
     </row>
     <row r="44" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="94"/>
+      <c r="A44" s="53"/>
       <c r="B44" s="29" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
@@ -19285,12 +19137,12 @@
       <c r="P44" s="26"/>
     </row>
     <row r="45" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="94"/>
+      <c r="A45" s="53"/>
       <c r="B45" s="29" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
@@ -19307,12 +19159,12 @@
       <c r="P45" s="26"/>
     </row>
     <row r="46" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="94"/>
+      <c r="A46" s="53"/>
       <c r="B46" s="29" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
@@ -19329,12 +19181,12 @@
       <c r="P46" s="26"/>
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="94"/>
+      <c r="A47" s="53"/>
       <c r="B47" s="29" t="s">
-        <v>580</v>
+        <v>573</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
@@ -19351,12 +19203,12 @@
       <c r="P47" s="26"/>
     </row>
     <row r="48" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="94"/>
+      <c r="A48" s="53"/>
       <c r="B48" s="29" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
@@ -19373,12 +19225,12 @@
       <c r="P48" s="26"/>
     </row>
     <row r="49" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="94"/>
+      <c r="A49" s="53"/>
       <c r="B49" s="29" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
@@ -19395,16 +19247,16 @@
       <c r="P49" s="26"/>
     </row>
     <row r="50" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="96" t="s">
-        <v>507</v>
-      </c>
-      <c r="B50" s="52"/>
-      <c r="C50" s="52"/>
-      <c r="D50" s="52"/>
-      <c r="E50" s="52"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="52"/>
-      <c r="H50" s="53"/>
+      <c r="A50" s="66" t="s">
+        <v>502</v>
+      </c>
+      <c r="B50" s="67"/>
+      <c r="C50" s="67"/>
+      <c r="D50" s="67"/>
+      <c r="E50" s="67"/>
+      <c r="F50" s="67"/>
+      <c r="G50" s="67"/>
+      <c r="H50" s="68"/>
       <c r="I50" s="38"/>
       <c r="J50" s="38"/>
       <c r="K50" s="38"/>
@@ -19415,14 +19267,14 @@
       <c r="P50" s="26"/>
     </row>
     <row r="51" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="95" t="s">
-        <v>715</v>
+      <c r="A51" s="54" t="s">
+        <v>698</v>
       </c>
       <c r="B51" s="29" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
@@ -19439,12 +19291,12 @@
       <c r="P51" s="26"/>
     </row>
     <row r="52" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="95"/>
+      <c r="A52" s="54"/>
       <c r="B52" s="29" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D52" s="4"/>
       <c r="E52" s="4"/>
@@ -19461,12 +19313,12 @@
       <c r="P52" s="26"/>
     </row>
     <row r="53" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="95"/>
+      <c r="A53" s="54"/>
       <c r="B53" s="29" t="s">
-        <v>346</v>
+        <v>341</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D53" s="4"/>
       <c r="E53" s="4"/>
@@ -19483,12 +19335,12 @@
       <c r="P53" s="26"/>
     </row>
     <row r="54" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="95"/>
+      <c r="A54" s="54"/>
       <c r="B54" s="29" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="4"/>
@@ -19505,12 +19357,12 @@
       <c r="P54" s="26"/>
     </row>
     <row r="55" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="95"/>
+      <c r="A55" s="54"/>
       <c r="B55" s="29" t="s">
-        <v>581</v>
+        <v>574</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>714</v>
+        <v>697</v>
       </c>
       <c r="D55" s="4"/>
       <c r="E55" s="4"/>
@@ -19527,16 +19379,16 @@
       <c r="P55" s="26"/>
     </row>
     <row r="56" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="96" t="s">
-        <v>114</v>
-      </c>
-      <c r="B56" s="52"/>
-      <c r="C56" s="52"/>
-      <c r="D56" s="52"/>
-      <c r="E56" s="52"/>
-      <c r="F56" s="52"/>
-      <c r="G56" s="52"/>
-      <c r="H56" s="53"/>
+      <c r="A56" s="66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B56" s="67"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="67"/>
+      <c r="E56" s="67"/>
+      <c r="F56" s="67"/>
+      <c r="G56" s="67"/>
+      <c r="H56" s="68"/>
       <c r="I56" s="38"/>
       <c r="J56" s="38"/>
       <c r="K56" s="38"/>
@@ -19547,14 +19399,14 @@
       <c r="P56" s="26"/>
     </row>
     <row r="57" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="95" t="s">
-        <v>716</v>
+      <c r="A57" s="54" t="s">
+        <v>699</v>
       </c>
       <c r="B57" s="15" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D57" s="4"/>
       <c r="E57" s="4"/>
@@ -19571,12 +19423,12 @@
       <c r="P57" s="26"/>
     </row>
     <row r="58" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="95"/>
+      <c r="A58" s="54"/>
       <c r="B58" s="15" t="s">
-        <v>717</v>
+        <v>700</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>591</v>
+        <v>584</v>
       </c>
       <c r="D58" s="4"/>
       <c r="E58" s="4"/>
@@ -19593,12 +19445,12 @@
       <c r="P58" s="26"/>
     </row>
     <row r="59" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="95"/>
+      <c r="A59" s="54"/>
       <c r="B59" s="15" t="s">
-        <v>718</v>
+        <v>701</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>592</v>
+        <v>585</v>
       </c>
       <c r="D59" s="4"/>
       <c r="E59" s="4"/>
@@ -19615,12 +19467,12 @@
       <c r="P59" s="26"/>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="95"/>
+      <c r="A60" s="54"/>
       <c r="B60" s="15" t="s">
-        <v>719</v>
+        <v>702</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>593</v>
+        <v>586</v>
       </c>
       <c r="D60" s="4"/>
       <c r="E60" s="4"/>
@@ -19637,12 +19489,12 @@
       <c r="P60" s="26"/>
     </row>
     <row r="61" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="95"/>
+      <c r="A61" s="54"/>
       <c r="B61" s="15" t="s">
-        <v>720</v>
+        <v>703</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>594</v>
+        <v>587</v>
       </c>
       <c r="D61" s="4"/>
       <c r="E61" s="4"/>
@@ -19659,12 +19511,12 @@
       <c r="P61" s="26"/>
     </row>
     <row r="62" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="95"/>
+      <c r="A62" s="54"/>
       <c r="B62" s="15" t="s">
-        <v>584</v>
+        <v>577</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>595</v>
+        <v>588</v>
       </c>
       <c r="D62" s="4"/>
       <c r="E62" s="4"/>
@@ -19681,12 +19533,12 @@
       <c r="P62" s="26"/>
     </row>
     <row r="63" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="95"/>
+      <c r="A63" s="54"/>
       <c r="B63" s="15" t="s">
-        <v>585</v>
+        <v>578</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>596</v>
+        <v>589</v>
       </c>
       <c r="D63" s="4"/>
       <c r="E63" s="4"/>
@@ -19703,12 +19555,12 @@
       <c r="P63" s="26"/>
     </row>
     <row r="64" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="95"/>
+      <c r="A64" s="54"/>
       <c r="B64" s="15" t="s">
-        <v>587</v>
+        <v>580</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>597</v>
+        <v>590</v>
       </c>
       <c r="D64" s="4"/>
       <c r="E64" s="4"/>
@@ -19725,12 +19577,12 @@
       <c r="P64" s="26"/>
     </row>
     <row r="65" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="95"/>
+      <c r="A65" s="54"/>
       <c r="B65" s="15" t="s">
-        <v>586</v>
+        <v>579</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>598</v>
+        <v>591</v>
       </c>
       <c r="D65" s="4"/>
       <c r="E65" s="4"/>
@@ -19747,16 +19599,16 @@
       <c r="P65" s="26"/>
     </row>
     <row r="66" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="98" t="s">
-        <v>114</v>
-      </c>
-      <c r="B66" s="55"/>
-      <c r="C66" s="55"/>
-      <c r="D66" s="55"/>
-      <c r="E66" s="55"/>
-      <c r="F66" s="55"/>
-      <c r="G66" s="55"/>
-      <c r="H66" s="56"/>
+      <c r="A66" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" s="74"/>
+      <c r="C66" s="74"/>
+      <c r="D66" s="74"/>
+      <c r="E66" s="74"/>
+      <c r="F66" s="74"/>
+      <c r="G66" s="74"/>
+      <c r="H66" s="75"/>
       <c r="I66" s="47"/>
       <c r="J66" s="47"/>
       <c r="K66" s="47"/>
@@ -19767,16 +19619,16 @@
       <c r="P66" s="28"/>
     </row>
     <row r="67" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="58"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="59"/>
+      <c r="A67" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="B67" s="71"/>
+      <c r="C67" s="71"/>
+      <c r="D67" s="71"/>
+      <c r="E67" s="71"/>
+      <c r="F67" s="71"/>
+      <c r="G67" s="71"/>
+      <c r="H67" s="72"/>
       <c r="I67" s="48"/>
       <c r="J67" s="48"/>
       <c r="K67" s="48"/>
@@ -19806,6 +19658,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A41:A49"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="A57:A65"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
@@ -19822,18 +19686,6 @@
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="E6:E7"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="A57:A65"/>
-    <mergeCell ref="A8:A30"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="A41:A49"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22318,20 +22170,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="81"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="81"/>
-      <c r="L2" s="81"/>
-      <c r="M2" s="81"/>
-      <c r="N2" s="81"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="55"/>
+      <c r="L2" s="55"/>
+      <c r="M2" s="55"/>
+      <c r="N2" s="55"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -22347,13 +22199,13 @@
       <c r="K3" s="31"/>
       <c r="L3" s="31"/>
       <c r="M3" s="32" t="s">
-        <v>631</v>
+        <v>619</v>
       </c>
       <c r="N3" s="50"/>
     </row>
     <row r="4" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="37" t="s">
-        <v>632</v>
+        <v>620</v>
       </c>
       <c r="N4" s="50"/>
     </row>
@@ -22362,74 +22214,74 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="89" t="s">
-        <v>414</v>
-      </c>
-      <c r="B6" s="86" t="s">
-        <v>624</v>
-      </c>
-      <c r="C6" s="84" t="s">
-        <v>625</v>
-      </c>
-      <c r="D6" s="84" t="s">
-        <v>626</v>
-      </c>
-      <c r="E6" s="84" t="s">
-        <v>627</v>
-      </c>
-      <c r="F6" s="79" t="s">
-        <v>628</v>
-      </c>
-      <c r="G6" s="79" t="s">
-        <v>578</v>
-      </c>
-      <c r="H6" s="79" t="s">
+      <c r="A6" s="56" t="s">
+        <v>409</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>612</v>
+      </c>
+      <c r="C6" s="60" t="s">
+        <v>613</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>614</v>
+      </c>
+      <c r="E6" s="60" t="s">
+        <v>615</v>
+      </c>
+      <c r="F6" s="62" t="s">
+        <v>616</v>
+      </c>
+      <c r="G6" s="62" t="s">
+        <v>571</v>
+      </c>
+      <c r="H6" s="62" t="s">
+        <v>575</v>
+      </c>
+      <c r="I6" s="62" t="s">
+        <v>581</v>
+      </c>
+      <c r="J6" s="62" t="s">
         <v>582</v>
       </c>
-      <c r="I6" s="79" t="s">
-        <v>588</v>
-      </c>
-      <c r="J6" s="79" t="s">
-        <v>589</v>
-      </c>
-      <c r="K6" s="79" t="s">
-        <v>590</v>
-      </c>
-      <c r="L6" s="79" t="s">
-        <v>608</v>
-      </c>
-      <c r="M6" s="79" t="s">
-        <v>629</v>
-      </c>
-      <c r="N6" s="82" t="s">
-        <v>630</v>
+      <c r="K6" s="62" t="s">
+        <v>583</v>
+      </c>
+      <c r="L6" s="62" t="s">
+        <v>596</v>
+      </c>
+      <c r="M6" s="62" t="s">
+        <v>617</v>
+      </c>
+      <c r="N6" s="64" t="s">
+        <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="90"/>
-      <c r="B7" s="87"/>
-      <c r="C7" s="85"/>
-      <c r="D7" s="85"/>
-      <c r="E7" s="85"/>
-      <c r="F7" s="80"/>
-      <c r="G7" s="80"/>
-      <c r="H7" s="80"/>
-      <c r="I7" s="80"/>
-      <c r="J7" s="80"/>
-      <c r="K7" s="80"/>
-      <c r="L7" s="80"/>
-      <c r="M7" s="80"/>
-      <c r="N7" s="83"/>
+      <c r="A7" s="57"/>
+      <c r="B7" s="59"/>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="63"/>
+      <c r="G7" s="63"/>
+      <c r="H7" s="63"/>
+      <c r="I7" s="63"/>
+      <c r="J7" s="63"/>
+      <c r="K7" s="63"/>
+      <c r="L7" s="63"/>
+      <c r="M7" s="63"/>
+      <c r="N7" s="65"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="97" t="s">
-        <v>724</v>
+      <c r="A8" s="69" t="s">
+        <v>707</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -22444,12 +22296,12 @@
       <c r="N8" s="27"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="94"/>
+      <c r="A9" s="53"/>
       <c r="B9" s="13" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -22464,12 +22316,12 @@
       <c r="N9" s="26"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="94"/>
+      <c r="A10" s="53"/>
       <c r="B10" s="11" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="19"/>
@@ -22484,12 +22336,12 @@
       <c r="N10" s="26"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="94"/>
+      <c r="A11" s="53"/>
       <c r="B11" s="11" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
@@ -22504,12 +22356,12 @@
       <c r="N11" s="26"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="94"/>
+      <c r="A12" s="53"/>
       <c r="B12" s="11" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19"/>
@@ -22524,12 +22376,12 @@
       <c r="N12" s="26"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="94"/>
+      <c r="A13" s="53"/>
       <c r="B13" s="11" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -22544,14 +22396,14 @@
       <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="94" t="s">
-        <v>725</v>
+      <c r="A14" s="53" t="s">
+        <v>708</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
@@ -22566,12 +22418,12 @@
       <c r="N14" s="26"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="94"/>
+      <c r="A15" s="53"/>
       <c r="B15" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -22586,12 +22438,12 @@
       <c r="N15" s="26"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="94"/>
+      <c r="A16" s="53"/>
       <c r="B16" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
@@ -22606,12 +22458,12 @@
       <c r="N16" s="26"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="94"/>
+      <c r="A17" s="53"/>
       <c r="B17" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -22627,13 +22479,13 @@
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="17" t="s">
-        <v>723</v>
+        <v>706</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>721</v>
+        <v>704</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>722</v>
+        <v>705</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -22648,14 +22500,14 @@
       <c r="N18" s="26"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="98" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" s="55"/>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="56"/>
+      <c r="A19" s="73" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" s="74"/>
+      <c r="C19" s="74"/>
+      <c r="D19" s="74"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="75"/>
       <c r="G19" s="47"/>
       <c r="H19" s="47"/>
       <c r="I19" s="47"/>
@@ -22666,14 +22518,14 @@
       <c r="N19" s="28"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="59"/>
+      <c r="A20" s="70" t="s">
+        <v>93</v>
+      </c>
+      <c r="B20" s="71"/>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="71"/>
+      <c r="F20" s="72"/>
       <c r="G20" s="48"/>
       <c r="H20" s="48"/>
       <c r="I20" s="48"/>
@@ -22717,6 +22569,11 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
@@ -22731,11 +22588,6 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/temp.xlsx
+++ b/data/temp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\최봉수\Desktop\계획수립\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C913B2F4-FB1C-4804-A9C0-88EE6EECE02F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66938B77-5F9F-47E1-8F4C-321ED5AB627A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15840" tabRatio="613" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="45" yWindow="660" windowWidth="38355" windowHeight="15540" tabRatio="613" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="완제품 임가공" sheetId="1" r:id="rId1"/>
@@ -3124,46 +3124,7 @@
     <xf numFmtId="41" fontId="2" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3172,8 +3133,14 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="23" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="27" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3184,50 +3151,11 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="29" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="21" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="15" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3242,6 +3170,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3265,7 +3199,79 @@
     <xf numFmtId="41" fontId="3" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="24" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="34" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="2" fillId="2" borderId="18" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="31" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="30" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3273,12 +3279,6 @@
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6264,22 +6264,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
     </row>
     <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -6312,75 +6312,75 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="91" t="s">
         <v>409</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="88" t="s">
         <v>612</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="86" t="s">
         <v>613</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="86" t="s">
         <v>614</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="93" t="s">
         <v>710</v>
       </c>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="95" t="s">
         <v>711</v>
       </c>
-      <c r="G6" s="60" t="s">
+      <c r="G6" s="86" t="s">
         <v>615</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="81" t="s">
         <v>616</v>
       </c>
-      <c r="I6" s="62" t="s">
+      <c r="I6" s="81" t="s">
         <v>571</v>
       </c>
-      <c r="J6" s="62" t="s">
+      <c r="J6" s="81" t="s">
         <v>575</v>
       </c>
-      <c r="K6" s="62" t="s">
+      <c r="K6" s="81" t="s">
         <v>581</v>
       </c>
-      <c r="L6" s="62" t="s">
+      <c r="L6" s="81" t="s">
         <v>582</v>
       </c>
-      <c r="M6" s="62" t="s">
+      <c r="M6" s="81" t="s">
         <v>583</v>
       </c>
-      <c r="N6" s="62" t="s">
+      <c r="N6" s="81" t="s">
         <v>596</v>
       </c>
-      <c r="O6" s="62" t="s">
+      <c r="O6" s="81" t="s">
         <v>617</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="84" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="57"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="63"/>
-      <c r="O7" s="63"/>
-      <c r="P7" s="65"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="82"/>
+      <c r="O7" s="82"/>
+      <c r="P7" s="85"/>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="90" t="s">
         <v>149</v>
       </c>
       <c r="B8" s="23" t="s">
@@ -6404,7 +6404,7 @@
       <c r="P8" s="25"/>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="78"/>
+      <c r="A9" s="62"/>
       <c r="B9" s="15" t="s">
         <v>185</v>
       </c>
@@ -6426,7 +6426,7 @@
       <c r="P9" s="14"/>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="78"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="15" t="s">
         <v>281</v>
       </c>
@@ -6448,7 +6448,7 @@
       <c r="P10" s="14"/>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="78"/>
+      <c r="A11" s="62"/>
       <c r="B11" s="15" t="s">
         <v>332</v>
       </c>
@@ -6470,7 +6470,7 @@
       <c r="P11" s="14"/>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="78"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="15" t="s">
         <v>304</v>
       </c>
@@ -6492,7 +6492,7 @@
       <c r="P12" s="14"/>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="78"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="15" t="s">
         <v>302</v>
       </c>
@@ -6514,7 +6514,7 @@
       <c r="P13" s="14"/>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="78"/>
+      <c r="A14" s="62"/>
       <c r="B14" s="15" t="s">
         <v>192</v>
       </c>
@@ -6536,7 +6536,7 @@
       <c r="P14" s="14"/>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="78"/>
+      <c r="A15" s="62"/>
       <c r="B15" s="15" t="s">
         <v>378</v>
       </c>
@@ -6558,16 +6558,16 @@
       <c r="P15" s="14"/>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="76" t="s">
+      <c r="A16" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B16" s="67"/>
-      <c r="C16" s="67"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="67"/>
-      <c r="G16" s="67"/>
-      <c r="H16" s="68"/>
+      <c r="B16" s="54"/>
+      <c r="C16" s="54"/>
+      <c r="D16" s="54"/>
+      <c r="E16" s="54"/>
+      <c r="F16" s="54"/>
+      <c r="G16" s="54"/>
+      <c r="H16" s="55"/>
       <c r="I16" s="38"/>
       <c r="J16" s="38"/>
       <c r="K16" s="38"/>
@@ -6578,7 +6578,7 @@
       <c r="P16" s="14"/>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="79" t="s">
+      <c r="A17" s="63" t="s">
         <v>622</v>
       </c>
       <c r="B17" s="15" t="s">
@@ -6602,7 +6602,7 @@
       <c r="P17" s="14"/>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="78"/>
+      <c r="A18" s="62"/>
       <c r="B18" s="15" t="s">
         <v>363</v>
       </c>
@@ -6624,7 +6624,7 @@
       <c r="P18" s="14"/>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="78"/>
+      <c r="A19" s="62"/>
       <c r="B19" s="15" t="s">
         <v>445</v>
       </c>
@@ -6646,7 +6646,7 @@
       <c r="P19" s="14"/>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="78"/>
+      <c r="A20" s="62"/>
       <c r="B20" s="15" t="s">
         <v>204</v>
       </c>
@@ -6668,16 +6668,16 @@
       <c r="P20" s="14"/>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="76" t="s">
+      <c r="A21" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B21" s="67"/>
-      <c r="C21" s="67"/>
-      <c r="D21" s="67"/>
-      <c r="E21" s="67"/>
-      <c r="F21" s="67"/>
-      <c r="G21" s="67"/>
-      <c r="H21" s="68"/>
+      <c r="B21" s="54"/>
+      <c r="C21" s="54"/>
+      <c r="D21" s="54"/>
+      <c r="E21" s="54"/>
+      <c r="F21" s="54"/>
+      <c r="G21" s="54"/>
+      <c r="H21" s="55"/>
       <c r="I21" s="38"/>
       <c r="J21" s="38"/>
       <c r="K21" s="38"/>
@@ -6688,7 +6688,7 @@
       <c r="P21" s="14"/>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="79" t="s">
+      <c r="A22" s="63" t="s">
         <v>430</v>
       </c>
       <c r="B22" s="15" t="s">
@@ -6712,7 +6712,7 @@
       <c r="P22" s="14"/>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="79"/>
+      <c r="A23" s="63"/>
       <c r="B23" s="15" t="s">
         <v>345</v>
       </c>
@@ -6734,7 +6734,7 @@
       <c r="P23" s="14"/>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="79"/>
+      <c r="A24" s="63"/>
       <c r="B24" s="15" t="s">
         <v>357</v>
       </c>
@@ -6756,7 +6756,7 @@
       <c r="P24" s="14"/>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="79"/>
+      <c r="A25" s="63"/>
       <c r="B25" s="15" t="s">
         <v>503</v>
       </c>
@@ -6778,7 +6778,7 @@
       <c r="P25" s="14"/>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="79"/>
+      <c r="A26" s="63"/>
       <c r="B26" s="15" t="s">
         <v>433</v>
       </c>
@@ -6800,7 +6800,7 @@
       <c r="P26" s="14"/>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="79"/>
+      <c r="A27" s="63"/>
       <c r="B27" s="15" t="s">
         <v>431</v>
       </c>
@@ -6822,7 +6822,7 @@
       <c r="P27" s="14"/>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="79"/>
+      <c r="A28" s="63"/>
       <c r="B28" s="15" t="s">
         <v>316</v>
       </c>
@@ -6844,7 +6844,7 @@
       <c r="P28" s="14"/>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="79"/>
+      <c r="A29" s="63"/>
       <c r="B29" s="15" t="s">
         <v>331</v>
       </c>
@@ -6866,7 +6866,7 @@
       <c r="P29" s="14"/>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="79"/>
+      <c r="A30" s="63"/>
       <c r="B30" s="15" t="s">
         <v>396</v>
       </c>
@@ -6888,7 +6888,7 @@
       <c r="P30" s="14"/>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="79"/>
+      <c r="A31" s="63"/>
       <c r="B31" s="15" t="s">
         <v>323</v>
       </c>
@@ -6910,7 +6910,7 @@
       <c r="P31" s="14"/>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="79"/>
+      <c r="A32" s="63"/>
       <c r="B32" s="15" t="s">
         <v>342</v>
       </c>
@@ -6932,7 +6932,7 @@
       <c r="P32" s="14"/>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="79"/>
+      <c r="A33" s="63"/>
       <c r="B33" s="15" t="s">
         <v>353</v>
       </c>
@@ -6954,7 +6954,7 @@
       <c r="P33" s="14"/>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="79"/>
+      <c r="A34" s="63"/>
       <c r="B34" s="15" t="s">
         <v>452</v>
       </c>
@@ -6976,7 +6976,7 @@
       <c r="P34" s="14"/>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="79"/>
+      <c r="A35" s="63"/>
       <c r="B35" s="15" t="s">
         <v>421</v>
       </c>
@@ -6998,7 +6998,7 @@
       <c r="P35" s="14"/>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="79"/>
+      <c r="A36" s="63"/>
       <c r="B36" s="15" t="s">
         <v>460</v>
       </c>
@@ -7020,7 +7020,7 @@
       <c r="P36" s="14"/>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="79"/>
+      <c r="A37" s="63"/>
       <c r="B37" s="15" t="s">
         <v>438</v>
       </c>
@@ -7042,7 +7042,7 @@
       <c r="P37" s="14"/>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="79"/>
+      <c r="A38" s="63"/>
       <c r="B38" s="15" t="s">
         <v>312</v>
       </c>
@@ -7064,7 +7064,7 @@
       <c r="P38" s="14"/>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="79"/>
+      <c r="A39" s="63"/>
       <c r="B39" s="15" t="s">
         <v>326</v>
       </c>
@@ -7086,7 +7086,7 @@
       <c r="P39" s="14"/>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="79"/>
+      <c r="A40" s="63"/>
       <c r="B40" s="15" t="s">
         <v>305</v>
       </c>
@@ -7108,7 +7108,7 @@
       <c r="P40" s="14"/>
     </row>
     <row r="41" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="79"/>
+      <c r="A41" s="63"/>
       <c r="B41" s="15" t="s">
         <v>435</v>
       </c>
@@ -7130,7 +7130,7 @@
       <c r="P41" s="14"/>
     </row>
     <row r="42" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="79"/>
+      <c r="A42" s="63"/>
       <c r="B42" s="15" t="s">
         <v>335</v>
       </c>
@@ -7152,7 +7152,7 @@
       <c r="P42" s="14"/>
     </row>
     <row r="43" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="79"/>
+      <c r="A43" s="63"/>
       <c r="B43" s="15" t="s">
         <v>463</v>
       </c>
@@ -7174,7 +7174,7 @@
       <c r="P43" s="14"/>
     </row>
     <row r="44" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="79"/>
+      <c r="A44" s="63"/>
       <c r="B44" s="15" t="s">
         <v>398</v>
       </c>
@@ -7196,7 +7196,7 @@
       <c r="P44" s="14"/>
     </row>
     <row r="45" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="79"/>
+      <c r="A45" s="63"/>
       <c r="B45" s="15" t="s">
         <v>388</v>
       </c>
@@ -7218,16 +7218,16 @@
       <c r="P45" s="14"/>
     </row>
     <row r="46" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="76" t="s">
+      <c r="A46" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B46" s="67"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="67"/>
-      <c r="G46" s="67"/>
-      <c r="H46" s="68"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="54"/>
+      <c r="H46" s="55"/>
       <c r="I46" s="38"/>
       <c r="J46" s="38"/>
       <c r="K46" s="38"/>
@@ -7238,7 +7238,7 @@
       <c r="P46" s="14"/>
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="78" t="s">
+      <c r="A47" s="62" t="s">
         <v>458</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -7262,7 +7262,7 @@
       <c r="P47" s="14"/>
     </row>
     <row r="48" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="78"/>
+      <c r="A48" s="62"/>
       <c r="B48" s="15" t="s">
         <v>311</v>
       </c>
@@ -7284,7 +7284,7 @@
       <c r="P48" s="14"/>
     </row>
     <row r="49" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="78"/>
+      <c r="A49" s="62"/>
       <c r="B49" s="15" t="s">
         <v>464</v>
       </c>
@@ -7306,7 +7306,7 @@
       <c r="P49" s="14"/>
     </row>
     <row r="50" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="78"/>
+      <c r="A50" s="62"/>
       <c r="B50" s="15" t="s">
         <v>461</v>
       </c>
@@ -7328,7 +7328,7 @@
       <c r="P50" s="14"/>
     </row>
     <row r="51" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="78"/>
+      <c r="A51" s="62"/>
       <c r="B51" s="15" t="s">
         <v>456</v>
       </c>
@@ -7350,7 +7350,7 @@
       <c r="P51" s="14"/>
     </row>
     <row r="52" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="78"/>
+      <c r="A52" s="62"/>
       <c r="B52" s="15" t="s">
         <v>418</v>
       </c>
@@ -7372,7 +7372,7 @@
       <c r="P52" s="14"/>
     </row>
     <row r="53" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="78" t="s">
+      <c r="A53" s="62" t="s">
         <v>454</v>
       </c>
       <c r="B53" s="15" t="s">
@@ -7396,7 +7396,7 @@
       <c r="P53" s="14"/>
     </row>
     <row r="54" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="78"/>
+      <c r="A54" s="62"/>
       <c r="B54" s="15" t="s">
         <v>426</v>
       </c>
@@ -7418,7 +7418,7 @@
       <c r="P54" s="14"/>
     </row>
     <row r="55" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="78"/>
+      <c r="A55" s="62"/>
       <c r="B55" s="15" t="s">
         <v>446</v>
       </c>
@@ -7440,7 +7440,7 @@
       <c r="P55" s="14"/>
     </row>
     <row r="56" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="78"/>
+      <c r="A56" s="62"/>
       <c r="B56" s="15" t="s">
         <v>434</v>
       </c>
@@ -7462,7 +7462,7 @@
       <c r="P56" s="14"/>
     </row>
     <row r="57" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="78"/>
+      <c r="A57" s="62"/>
       <c r="B57" s="15" t="s">
         <v>442</v>
       </c>
@@ -7484,7 +7484,7 @@
       <c r="P57" s="14"/>
     </row>
     <row r="58" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="78"/>
+      <c r="A58" s="62"/>
       <c r="B58" s="15" t="s">
         <v>447</v>
       </c>
@@ -7506,16 +7506,16 @@
       <c r="P58" s="14"/>
     </row>
     <row r="59" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="76" t="s">
+      <c r="A59" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B59" s="67"/>
-      <c r="C59" s="67"/>
-      <c r="D59" s="67"/>
-      <c r="E59" s="67"/>
-      <c r="F59" s="67"/>
-      <c r="G59" s="67"/>
-      <c r="H59" s="68"/>
+      <c r="B59" s="54"/>
+      <c r="C59" s="54"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="54"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="54"/>
+      <c r="H59" s="55"/>
       <c r="I59" s="38"/>
       <c r="J59" s="38"/>
       <c r="K59" s="38"/>
@@ -7526,7 +7526,7 @@
       <c r="P59" s="14"/>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="78" t="s">
+      <c r="A60" s="62" t="s">
         <v>510</v>
       </c>
       <c r="B60" s="15" t="s">
@@ -7550,7 +7550,7 @@
       <c r="P60" s="14"/>
     </row>
     <row r="61" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="78"/>
+      <c r="A61" s="62"/>
       <c r="B61" s="15" t="s">
         <v>300</v>
       </c>
@@ -7572,7 +7572,7 @@
       <c r="P61" s="14"/>
     </row>
     <row r="62" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="78"/>
+      <c r="A62" s="62"/>
       <c r="B62" s="15" t="s">
         <v>280</v>
       </c>
@@ -7594,7 +7594,7 @@
       <c r="P62" s="14"/>
     </row>
     <row r="63" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="78"/>
+      <c r="A63" s="62"/>
       <c r="B63" s="15" t="s">
         <v>284</v>
       </c>
@@ -7616,16 +7616,16 @@
       <c r="P63" s="14"/>
     </row>
     <row r="64" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="76" t="s">
+      <c r="A64" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B64" s="67"/>
-      <c r="C64" s="67"/>
-      <c r="D64" s="67"/>
-      <c r="E64" s="67"/>
-      <c r="F64" s="67"/>
-      <c r="G64" s="67"/>
-      <c r="H64" s="68"/>
+      <c r="B64" s="54"/>
+      <c r="C64" s="54"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="55"/>
       <c r="I64" s="38"/>
       <c r="J64" s="38"/>
       <c r="K64" s="38"/>
@@ -7636,7 +7636,7 @@
       <c r="P64" s="14"/>
     </row>
     <row r="65" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="78" t="s">
+      <c r="A65" s="62" t="s">
         <v>443</v>
       </c>
       <c r="B65" s="15" t="s">
@@ -7660,7 +7660,7 @@
       <c r="P65" s="14"/>
     </row>
     <row r="66" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="78"/>
+      <c r="A66" s="62"/>
       <c r="B66" s="15" t="s">
         <v>382</v>
       </c>
@@ -7682,7 +7682,7 @@
       <c r="P66" s="14"/>
     </row>
     <row r="67" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="78"/>
+      <c r="A67" s="62"/>
       <c r="B67" s="15" t="s">
         <v>448</v>
       </c>
@@ -7704,7 +7704,7 @@
       <c r="P67" s="14"/>
     </row>
     <row r="68" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="78"/>
+      <c r="A68" s="62"/>
       <c r="B68" s="15" t="s">
         <v>470</v>
       </c>
@@ -7726,7 +7726,7 @@
       <c r="P68" s="14"/>
     </row>
     <row r="69" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="78"/>
+      <c r="A69" s="62"/>
       <c r="B69" s="15" t="s">
         <v>476</v>
       </c>
@@ -7748,7 +7748,7 @@
       <c r="P69" s="14"/>
     </row>
     <row r="70" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="78"/>
+      <c r="A70" s="62"/>
       <c r="B70" s="15" t="s">
         <v>419</v>
       </c>
@@ -7770,7 +7770,7 @@
       <c r="P70" s="14"/>
     </row>
     <row r="71" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="78"/>
+      <c r="A71" s="62"/>
       <c r="B71" s="15" t="s">
         <v>422</v>
       </c>
@@ -7792,7 +7792,7 @@
       <c r="P71" s="14"/>
     </row>
     <row r="72" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="78"/>
+      <c r="A72" s="62"/>
       <c r="B72" s="15" t="s">
         <v>462</v>
       </c>
@@ -7814,7 +7814,7 @@
       <c r="P72" s="14"/>
     </row>
     <row r="73" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="78"/>
+      <c r="A73" s="62"/>
       <c r="B73" s="15" t="s">
         <v>455</v>
       </c>
@@ -7836,7 +7836,7 @@
       <c r="P73" s="14"/>
     </row>
     <row r="74" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="78"/>
+      <c r="A74" s="62"/>
       <c r="B74" s="15" t="s">
         <v>450</v>
       </c>
@@ -7858,16 +7858,16 @@
       <c r="P74" s="14"/>
     </row>
     <row r="75" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="76" t="s">
+      <c r="A75" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B75" s="67"/>
-      <c r="C75" s="67"/>
-      <c r="D75" s="67"/>
-      <c r="E75" s="67"/>
-      <c r="F75" s="67"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="68"/>
+      <c r="B75" s="54"/>
+      <c r="C75" s="54"/>
+      <c r="D75" s="54"/>
+      <c r="E75" s="54"/>
+      <c r="F75" s="54"/>
+      <c r="G75" s="54"/>
+      <c r="H75" s="55"/>
       <c r="I75" s="38"/>
       <c r="J75" s="38"/>
       <c r="K75" s="38"/>
@@ -7878,7 +7878,7 @@
       <c r="P75" s="14"/>
     </row>
     <row r="76" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="78" t="s">
+      <c r="A76" s="62" t="s">
         <v>217</v>
       </c>
       <c r="B76" s="29" t="s">
@@ -7902,7 +7902,7 @@
       <c r="P76" s="14"/>
     </row>
     <row r="77" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="78"/>
+      <c r="A77" s="62"/>
       <c r="B77" s="29" t="s">
         <v>266</v>
       </c>
@@ -7924,16 +7924,16 @@
       <c r="P77" s="14"/>
     </row>
     <row r="78" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="76" t="s">
+      <c r="A78" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B78" s="67"/>
-      <c r="C78" s="67"/>
-      <c r="D78" s="67"/>
-      <c r="E78" s="67"/>
-      <c r="F78" s="67"/>
-      <c r="G78" s="67"/>
-      <c r="H78" s="68"/>
+      <c r="B78" s="54"/>
+      <c r="C78" s="54"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="54"/>
+      <c r="F78" s="54"/>
+      <c r="G78" s="54"/>
+      <c r="H78" s="55"/>
       <c r="I78" s="38"/>
       <c r="J78" s="38"/>
       <c r="K78" s="38"/>
@@ -7944,7 +7944,7 @@
       <c r="P78" s="14"/>
     </row>
     <row r="79" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="78"/>
+      <c r="A79" s="62"/>
       <c r="B79" s="15" t="s">
         <v>274</v>
       </c>
@@ -7966,7 +7966,7 @@
       <c r="P79" s="14"/>
     </row>
     <row r="80" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="78"/>
+      <c r="A80" s="62"/>
       <c r="B80" s="15" t="s">
         <v>177</v>
       </c>
@@ -7988,7 +7988,7 @@
       <c r="P80" s="14"/>
     </row>
     <row r="81" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="78"/>
+      <c r="A81" s="62"/>
       <c r="B81" s="15" t="s">
         <v>327</v>
       </c>
@@ -8010,7 +8010,7 @@
       <c r="P81" s="14"/>
     </row>
     <row r="82" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="78"/>
+      <c r="A82" s="62"/>
       <c r="B82" s="15" t="s">
         <v>197</v>
       </c>
@@ -8032,7 +8032,7 @@
       <c r="P82" s="14"/>
     </row>
     <row r="83" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="78"/>
+      <c r="A83" s="62"/>
       <c r="B83" s="15" t="s">
         <v>324</v>
       </c>
@@ -8054,7 +8054,7 @@
       <c r="P83" s="14"/>
     </row>
     <row r="84" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="78"/>
+      <c r="A84" s="62"/>
       <c r="B84" s="30" t="s">
         <v>354</v>
       </c>
@@ -8076,7 +8076,7 @@
       <c r="P84" s="14"/>
     </row>
     <row r="85" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="78"/>
+      <c r="A85" s="62"/>
       <c r="B85" s="30" t="s">
         <v>299</v>
       </c>
@@ -8098,7 +8098,7 @@
       <c r="P85" s="14"/>
     </row>
     <row r="86" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="78"/>
+      <c r="A86" s="62"/>
       <c r="B86" s="30" t="s">
         <v>344</v>
       </c>
@@ -8120,16 +8120,16 @@
       <c r="P86" s="14"/>
     </row>
     <row r="87" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="76" t="s">
+      <c r="A87" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B87" s="67"/>
-      <c r="C87" s="67"/>
-      <c r="D87" s="67"/>
-      <c r="E87" s="67"/>
-      <c r="F87" s="67"/>
-      <c r="G87" s="67"/>
-      <c r="H87" s="68"/>
+      <c r="B87" s="54"/>
+      <c r="C87" s="54"/>
+      <c r="D87" s="54"/>
+      <c r="E87" s="54"/>
+      <c r="F87" s="54"/>
+      <c r="G87" s="54"/>
+      <c r="H87" s="55"/>
       <c r="I87" s="38"/>
       <c r="J87" s="38"/>
       <c r="K87" s="38"/>
@@ -8140,7 +8140,7 @@
       <c r="P87" s="14"/>
     </row>
     <row r="88" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="78" t="s">
+      <c r="A88" s="62" t="s">
         <v>508</v>
       </c>
       <c r="B88" s="15" t="s">
@@ -8164,7 +8164,7 @@
       <c r="P88" s="14"/>
     </row>
     <row r="89" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="78"/>
+      <c r="A89" s="62"/>
       <c r="B89" s="15" t="s">
         <v>319</v>
       </c>
@@ -8186,7 +8186,7 @@
       <c r="P89" s="14"/>
     </row>
     <row r="90" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="78"/>
+      <c r="A90" s="62"/>
       <c r="B90" s="15" t="s">
         <v>198</v>
       </c>
@@ -8208,7 +8208,7 @@
       <c r="P90" s="14"/>
     </row>
     <row r="91" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="78"/>
+      <c r="A91" s="62"/>
       <c r="B91" s="29" t="s">
         <v>188</v>
       </c>
@@ -8230,7 +8230,7 @@
       <c r="P91" s="14"/>
     </row>
     <row r="92" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="78"/>
+      <c r="A92" s="62"/>
       <c r="B92" s="15" t="s">
         <v>275</v>
       </c>
@@ -8252,7 +8252,7 @@
       <c r="P92" s="14"/>
     </row>
     <row r="93" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="78"/>
+      <c r="A93" s="62"/>
       <c r="B93" s="15" t="s">
         <v>199</v>
       </c>
@@ -8274,7 +8274,7 @@
       <c r="P93" s="14"/>
     </row>
     <row r="94" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="78"/>
+      <c r="A94" s="62"/>
       <c r="B94" s="29" t="s">
         <v>212</v>
       </c>
@@ -8296,7 +8296,7 @@
       <c r="P94" s="14"/>
     </row>
     <row r="95" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="78" t="s">
+      <c r="A95" s="62" t="s">
         <v>508</v>
       </c>
       <c r="B95" s="15" t="s">
@@ -8320,7 +8320,7 @@
       <c r="P95" s="14"/>
     </row>
     <row r="96" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="78"/>
+      <c r="A96" s="62"/>
       <c r="B96" s="15" t="s">
         <v>171</v>
       </c>
@@ -8342,7 +8342,7 @@
       <c r="P96" s="14"/>
     </row>
     <row r="97" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="78"/>
+      <c r="A97" s="62"/>
       <c r="B97" s="15" t="s">
         <v>315</v>
       </c>
@@ -8364,7 +8364,7 @@
       <c r="P97" s="14"/>
     </row>
     <row r="98" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="78"/>
+      <c r="A98" s="62"/>
       <c r="B98" s="15" t="s">
         <v>338</v>
       </c>
@@ -8386,7 +8386,7 @@
       <c r="P98" s="14"/>
     </row>
     <row r="99" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="78"/>
+      <c r="A99" s="62"/>
       <c r="B99" s="15" t="s">
         <v>309</v>
       </c>
@@ -8408,7 +8408,7 @@
       <c r="P99" s="14"/>
     </row>
     <row r="100" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="78"/>
+      <c r="A100" s="62"/>
       <c r="B100" s="15" t="s">
         <v>328</v>
       </c>
@@ -8430,7 +8430,7 @@
       <c r="P100" s="14"/>
     </row>
     <row r="101" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="78"/>
+      <c r="A101" s="62"/>
       <c r="B101" s="15" t="s">
         <v>321</v>
       </c>
@@ -8452,7 +8452,7 @@
       <c r="P101" s="14"/>
     </row>
     <row r="102" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="78"/>
+      <c r="A102" s="62"/>
       <c r="B102" s="15" t="s">
         <v>169</v>
       </c>
@@ -8474,7 +8474,7 @@
       <c r="P102" s="14"/>
     </row>
     <row r="103" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="78"/>
+      <c r="A103" s="62"/>
       <c r="B103" s="15" t="s">
         <v>220</v>
       </c>
@@ -8496,16 +8496,16 @@
       <c r="P103" s="14"/>
     </row>
     <row r="104" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="76" t="s">
+      <c r="A104" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B104" s="67"/>
-      <c r="C104" s="67"/>
-      <c r="D104" s="67"/>
-      <c r="E104" s="67"/>
-      <c r="F104" s="67"/>
-      <c r="G104" s="67"/>
-      <c r="H104" s="68"/>
+      <c r="B104" s="54"/>
+      <c r="C104" s="54"/>
+      <c r="D104" s="54"/>
+      <c r="E104" s="54"/>
+      <c r="F104" s="54"/>
+      <c r="G104" s="54"/>
+      <c r="H104" s="55"/>
       <c r="I104" s="38"/>
       <c r="J104" s="38"/>
       <c r="K104" s="38"/>
@@ -8564,7 +8564,7 @@
       <c r="P106" s="14"/>
     </row>
     <row r="107" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="78" t="s">
+      <c r="A107" s="62" t="s">
         <v>256</v>
       </c>
       <c r="B107" s="15" t="s">
@@ -8588,7 +8588,7 @@
       <c r="P107" s="14"/>
     </row>
     <row r="108" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="78"/>
+      <c r="A108" s="62"/>
       <c r="B108" s="29" t="s">
         <v>297</v>
       </c>
@@ -8610,7 +8610,7 @@
       <c r="P108" s="14"/>
     </row>
     <row r="109" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="78"/>
+      <c r="A109" s="62"/>
       <c r="B109" s="29" t="s">
         <v>572</v>
       </c>
@@ -8656,16 +8656,16 @@
       <c r="P110" s="14"/>
     </row>
     <row r="111" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="76" t="s">
+      <c r="A111" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B111" s="67"/>
-      <c r="C111" s="67"/>
-      <c r="D111" s="67"/>
-      <c r="E111" s="67"/>
-      <c r="F111" s="67"/>
-      <c r="G111" s="67"/>
-      <c r="H111" s="68"/>
+      <c r="B111" s="54"/>
+      <c r="C111" s="54"/>
+      <c r="D111" s="54"/>
+      <c r="E111" s="54"/>
+      <c r="F111" s="54"/>
+      <c r="G111" s="54"/>
+      <c r="H111" s="55"/>
       <c r="I111" s="38"/>
       <c r="J111" s="38"/>
       <c r="K111" s="38"/>
@@ -8676,7 +8676,7 @@
       <c r="P111" s="14"/>
     </row>
     <row r="112" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="79" t="s">
+      <c r="A112" s="63" t="s">
         <v>49</v>
       </c>
       <c r="B112" s="15" t="s">
@@ -8700,7 +8700,7 @@
       <c r="P112" s="14"/>
     </row>
     <row r="113" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="79"/>
+      <c r="A113" s="63"/>
       <c r="B113" s="15" t="s">
         <v>298</v>
       </c>
@@ -8722,7 +8722,7 @@
       <c r="P113" s="14"/>
     </row>
     <row r="114" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="79"/>
+      <c r="A114" s="63"/>
       <c r="B114" s="15" t="s">
         <v>369</v>
       </c>
@@ -8744,7 +8744,7 @@
       <c r="P114" s="14"/>
     </row>
     <row r="115" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="79"/>
+      <c r="A115" s="63"/>
       <c r="B115" s="15" t="s">
         <v>277</v>
       </c>
@@ -8766,7 +8766,7 @@
       <c r="P115" s="14"/>
     </row>
     <row r="116" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="79"/>
+      <c r="A116" s="63"/>
       <c r="B116" s="15" t="s">
         <v>295</v>
       </c>
@@ -8788,7 +8788,7 @@
       <c r="P116" s="14"/>
     </row>
     <row r="117" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="79"/>
+      <c r="A117" s="63"/>
       <c r="B117" s="15" t="s">
         <v>276</v>
       </c>
@@ -8810,7 +8810,7 @@
       <c r="P117" s="14"/>
     </row>
     <row r="118" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="79"/>
+      <c r="A118" s="63"/>
       <c r="B118" s="15" t="s">
         <v>247</v>
       </c>
@@ -8832,7 +8832,7 @@
       <c r="P118" s="14"/>
     </row>
     <row r="119" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="79"/>
+      <c r="A119" s="63"/>
       <c r="B119" s="15" t="s">
         <v>285</v>
       </c>
@@ -8854,16 +8854,16 @@
       <c r="P119" s="14"/>
     </row>
     <row r="120" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="76" t="s">
+      <c r="A120" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B120" s="67"/>
-      <c r="C120" s="67"/>
-      <c r="D120" s="67"/>
-      <c r="E120" s="67"/>
-      <c r="F120" s="67"/>
-      <c r="G120" s="67"/>
-      <c r="H120" s="68"/>
+      <c r="B120" s="54"/>
+      <c r="C120" s="54"/>
+      <c r="D120" s="54"/>
+      <c r="E120" s="54"/>
+      <c r="F120" s="54"/>
+      <c r="G120" s="54"/>
+      <c r="H120" s="55"/>
       <c r="I120" s="38"/>
       <c r="J120" s="38"/>
       <c r="K120" s="38"/>
@@ -8874,7 +8874,7 @@
       <c r="P120" s="14"/>
     </row>
     <row r="121" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="78" t="s">
+      <c r="A121" s="62" t="s">
         <v>509</v>
       </c>
       <c r="B121" s="15" t="s">
@@ -8898,7 +8898,7 @@
       <c r="P121" s="14"/>
     </row>
     <row r="122" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="78"/>
+      <c r="A122" s="62"/>
       <c r="B122" s="15" t="s">
         <v>224</v>
       </c>
@@ -8920,7 +8920,7 @@
       <c r="P122" s="14"/>
     </row>
     <row r="123" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="78"/>
+      <c r="A123" s="62"/>
       <c r="B123" s="15" t="s">
         <v>313</v>
       </c>
@@ -8942,7 +8942,7 @@
       <c r="P123" s="14"/>
     </row>
     <row r="124" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="78"/>
+      <c r="A124" s="62"/>
       <c r="B124" s="15" t="s">
         <v>330</v>
       </c>
@@ -8964,16 +8964,16 @@
       <c r="P124" s="14"/>
     </row>
     <row r="125" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="76" t="s">
+      <c r="A125" s="53" t="s">
         <v>113</v>
       </c>
-      <c r="B125" s="67"/>
-      <c r="C125" s="67"/>
-      <c r="D125" s="67"/>
-      <c r="E125" s="67"/>
-      <c r="F125" s="67"/>
-      <c r="G125" s="67"/>
-      <c r="H125" s="68"/>
+      <c r="B125" s="54"/>
+      <c r="C125" s="54"/>
+      <c r="D125" s="54"/>
+      <c r="E125" s="54"/>
+      <c r="F125" s="54"/>
+      <c r="G125" s="54"/>
+      <c r="H125" s="55"/>
       <c r="I125" s="38"/>
       <c r="J125" s="38"/>
       <c r="K125" s="38"/>
@@ -8984,7 +8984,7 @@
       <c r="P125" s="14"/>
     </row>
     <row r="126" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="78" t="s">
+      <c r="A126" s="62" t="s">
         <v>278</v>
       </c>
       <c r="B126" s="15" t="s">
@@ -9008,7 +9008,7 @@
       <c r="P126" s="14"/>
     </row>
     <row r="127" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="78"/>
+      <c r="A127" s="62"/>
       <c r="B127" s="15" t="s">
         <v>393</v>
       </c>
@@ -9030,16 +9030,16 @@
       <c r="P127" s="14"/>
     </row>
     <row r="128" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="100" t="s">
+      <c r="A128" s="56" t="s">
         <v>113</v>
       </c>
-      <c r="B128" s="74"/>
-      <c r="C128" s="74"/>
-      <c r="D128" s="74"/>
-      <c r="E128" s="74"/>
-      <c r="F128" s="74"/>
-      <c r="G128" s="74"/>
-      <c r="H128" s="75"/>
+      <c r="B128" s="57"/>
+      <c r="C128" s="57"/>
+      <c r="D128" s="57"/>
+      <c r="E128" s="57"/>
+      <c r="F128" s="57"/>
+      <c r="G128" s="57"/>
+      <c r="H128" s="58"/>
       <c r="I128" s="47"/>
       <c r="J128" s="47"/>
       <c r="K128" s="47"/>
@@ -9050,16 +9050,16 @@
       <c r="P128" s="22"/>
     </row>
     <row r="129" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A129" s="70" t="s">
+      <c r="A129" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="B129" s="71"/>
-      <c r="C129" s="71"/>
-      <c r="D129" s="71"/>
-      <c r="E129" s="71"/>
-      <c r="F129" s="71"/>
-      <c r="G129" s="71"/>
-      <c r="H129" s="72"/>
+      <c r="B129" s="60"/>
+      <c r="C129" s="60"/>
+      <c r="D129" s="60"/>
+      <c r="E129" s="60"/>
+      <c r="F129" s="60"/>
+      <c r="G129" s="60"/>
+      <c r="H129" s="61"/>
       <c r="I129" s="48"/>
       <c r="J129" s="48"/>
       <c r="K129" s="48"/>
@@ -9091,102 +9091,120 @@
       <c r="A131" s="3"/>
       <c r="B131" s="1"/>
       <c r="C131" s="5"/>
-      <c r="D131" s="95"/>
-      <c r="E131" s="96"/>
-      <c r="F131" s="96"/>
-      <c r="G131" s="97"/>
-      <c r="H131" s="97"/>
-      <c r="I131" s="89"/>
-      <c r="J131" s="89"/>
-      <c r="K131" s="89"/>
-      <c r="L131" s="90"/>
+      <c r="D131" s="73"/>
+      <c r="E131" s="74"/>
+      <c r="F131" s="74"/>
+      <c r="G131" s="75"/>
+      <c r="H131" s="75"/>
+      <c r="I131" s="65"/>
+      <c r="J131" s="65"/>
+      <c r="K131" s="65"/>
+      <c r="L131" s="66"/>
       <c r="M131" s="8"/>
       <c r="N131" s="8"/>
       <c r="O131" s="8"/>
       <c r="P131" s="8"/>
     </row>
     <row r="132" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D132" s="98" t="s">
+      <c r="D132" s="76" t="s">
         <v>665</v>
       </c>
-      <c r="E132" s="99"/>
-      <c r="F132" s="99"/>
-      <c r="G132" s="91"/>
-      <c r="H132" s="91"/>
-      <c r="I132" s="91"/>
-      <c r="J132" s="91"/>
-      <c r="K132" s="91"/>
-      <c r="L132" s="92"/>
+      <c r="E132" s="77"/>
+      <c r="F132" s="77"/>
+      <c r="G132" s="67"/>
+      <c r="H132" s="67"/>
+      <c r="I132" s="67"/>
+      <c r="J132" s="67"/>
+      <c r="K132" s="67"/>
+      <c r="L132" s="68"/>
     </row>
     <row r="133" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D133" s="83" t="s">
+      <c r="D133" s="78" t="s">
         <v>666</v>
       </c>
-      <c r="E133" s="68"/>
-      <c r="F133" s="68"/>
-      <c r="G133" s="84"/>
-      <c r="H133" s="84"/>
-      <c r="I133" s="84"/>
-      <c r="J133" s="84"/>
-      <c r="K133" s="84"/>
-      <c r="L133" s="93"/>
+      <c r="E133" s="55"/>
+      <c r="F133" s="55"/>
+      <c r="G133" s="69"/>
+      <c r="H133" s="69"/>
+      <c r="I133" s="69"/>
+      <c r="J133" s="69"/>
+      <c r="K133" s="69"/>
+      <c r="L133" s="71"/>
     </row>
     <row r="134" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D134" s="83" t="s">
+      <c r="D134" s="78" t="s">
         <v>667</v>
       </c>
-      <c r="E134" s="68"/>
-      <c r="F134" s="68"/>
-      <c r="G134" s="84"/>
-      <c r="H134" s="84"/>
-      <c r="I134" s="84"/>
-      <c r="J134" s="84"/>
-      <c r="K134" s="84"/>
-      <c r="L134" s="93"/>
+      <c r="E134" s="55"/>
+      <c r="F134" s="55"/>
+      <c r="G134" s="69"/>
+      <c r="H134" s="69"/>
+      <c r="I134" s="69"/>
+      <c r="J134" s="69"/>
+      <c r="K134" s="69"/>
+      <c r="L134" s="71"/>
     </row>
     <row r="135" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D135" s="85" t="s">
+      <c r="D135" s="79" t="s">
         <v>668</v>
       </c>
-      <c r="E135" s="86"/>
-      <c r="F135" s="86"/>
-      <c r="G135" s="87"/>
-      <c r="H135" s="87"/>
-      <c r="I135" s="87"/>
-      <c r="J135" s="87"/>
-      <c r="K135" s="87"/>
-      <c r="L135" s="94"/>
+      <c r="E135" s="80"/>
+      <c r="F135" s="80"/>
+      <c r="G135" s="70"/>
+      <c r="H135" s="70"/>
+      <c r="I135" s="70"/>
+      <c r="J135" s="70"/>
+      <c r="K135" s="70"/>
+      <c r="L135" s="72"/>
     </row>
     <row r="136" spans="1:16" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D136" s="88" t="s">
+      <c r="D136" s="64" t="s">
         <v>669</v>
       </c>
-      <c r="E136" s="72"/>
-      <c r="F136" s="72"/>
-      <c r="G136" s="89"/>
-      <c r="H136" s="89"/>
-      <c r="I136" s="89"/>
-      <c r="J136" s="89"/>
-      <c r="K136" s="89"/>
-      <c r="L136" s="89"/>
+      <c r="E136" s="61"/>
+      <c r="F136" s="61"/>
+      <c r="G136" s="65"/>
+      <c r="H136" s="65"/>
+      <c r="I136" s="65"/>
+      <c r="J136" s="65"/>
+      <c r="K136" s="65"/>
+      <c r="L136" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="64">
-    <mergeCell ref="A120:H120"/>
-    <mergeCell ref="A125:H125"/>
-    <mergeCell ref="A128:H128"/>
-    <mergeCell ref="A129:H129"/>
-    <mergeCell ref="A59:H59"/>
-    <mergeCell ref="A64:H64"/>
-    <mergeCell ref="A75:H75"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A88:A94"/>
-    <mergeCell ref="A95:A103"/>
-    <mergeCell ref="A107:A109"/>
-    <mergeCell ref="A112:A119"/>
-    <mergeCell ref="A87:H87"/>
-    <mergeCell ref="A104:H104"/>
-    <mergeCell ref="A111:H111"/>
+    <mergeCell ref="A21:H21"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="A8:A15"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A22:A45"/>
+    <mergeCell ref="A53:A58"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="A65:A74"/>
+    <mergeCell ref="A47:A52"/>
+    <mergeCell ref="A46:H46"/>
+    <mergeCell ref="D134:H134"/>
+    <mergeCell ref="D135:H135"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="P6:P7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="A121:A124"/>
+    <mergeCell ref="A126:A127"/>
+    <mergeCell ref="A76:A77"/>
+    <mergeCell ref="A79:A86"/>
     <mergeCell ref="D136:H136"/>
     <mergeCell ref="I131:J131"/>
     <mergeCell ref="K131:L131"/>
@@ -9203,39 +9221,21 @@
     <mergeCell ref="D131:H131"/>
     <mergeCell ref="D132:H132"/>
     <mergeCell ref="D133:H133"/>
-    <mergeCell ref="D134:H134"/>
-    <mergeCell ref="D135:H135"/>
-    <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A2:P2"/>
-    <mergeCell ref="O6:O7"/>
-    <mergeCell ref="P6:P7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="A121:A124"/>
-    <mergeCell ref="A126:A127"/>
-    <mergeCell ref="A76:A77"/>
-    <mergeCell ref="A79:A86"/>
-    <mergeCell ref="A22:A45"/>
-    <mergeCell ref="A53:A58"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="A65:A74"/>
-    <mergeCell ref="A47:A52"/>
-    <mergeCell ref="A46:H46"/>
-    <mergeCell ref="A21:H21"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="A8:A15"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A120:H120"/>
+    <mergeCell ref="A125:H125"/>
+    <mergeCell ref="A128:H128"/>
+    <mergeCell ref="A129:H129"/>
+    <mergeCell ref="A59:H59"/>
+    <mergeCell ref="A64:H64"/>
+    <mergeCell ref="A75:H75"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A88:A94"/>
+    <mergeCell ref="A95:A103"/>
+    <mergeCell ref="A107:A109"/>
+    <mergeCell ref="A112:A119"/>
+    <mergeCell ref="A87:H87"/>
+    <mergeCell ref="A104:H104"/>
+    <mergeCell ref="A111:H111"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11720,20 +11720,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -11764,67 +11764,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="91" t="s">
         <v>409</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="88" t="s">
         <v>612</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="86" t="s">
         <v>613</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="86" t="s">
         <v>614</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="86" t="s">
         <v>615</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="81" t="s">
         <v>616</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="81" t="s">
         <v>571</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="81" t="s">
         <v>575</v>
       </c>
-      <c r="I6" s="62" t="s">
+      <c r="I6" s="81" t="s">
         <v>581</v>
       </c>
-      <c r="J6" s="62" t="s">
+      <c r="J6" s="81" t="s">
         <v>582</v>
       </c>
-      <c r="K6" s="62" t="s">
+      <c r="K6" s="81" t="s">
         <v>583</v>
       </c>
-      <c r="L6" s="62" t="s">
+      <c r="L6" s="81" t="s">
         <v>596</v>
       </c>
-      <c r="M6" s="62" t="s">
+      <c r="M6" s="81" t="s">
         <v>617</v>
       </c>
-      <c r="N6" s="64" t="s">
+      <c r="N6" s="84" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="57"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="65"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="85"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="101" t="s">
         <v>621</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -11846,7 +11846,7 @@
       <c r="N8" s="27"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="54"/>
+      <c r="A9" s="97"/>
       <c r="B9" s="13" t="s">
         <v>358</v>
       </c>
@@ -11866,7 +11866,7 @@
       <c r="N9" s="26"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54"/>
+      <c r="A10" s="97"/>
       <c r="B10" s="11" t="s">
         <v>294</v>
       </c>
@@ -11886,7 +11886,7 @@
       <c r="N10" s="26"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
+      <c r="A11" s="97"/>
       <c r="B11" s="11" t="s">
         <v>249</v>
       </c>
@@ -11906,7 +11906,7 @@
       <c r="N11" s="26"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="11" t="s">
         <v>368</v>
       </c>
@@ -11926,7 +11926,7 @@
       <c r="N12" s="26"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="11" t="s">
         <v>374</v>
       </c>
@@ -11946,7 +11946,7 @@
       <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="54"/>
+      <c r="A14" s="97"/>
       <c r="B14" s="11" t="s">
         <v>372</v>
       </c>
@@ -11966,7 +11966,7 @@
       <c r="N14" s="26"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="11" t="s">
         <v>246</v>
       </c>
@@ -11986,7 +11986,7 @@
       <c r="N15" s="26"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54"/>
+      <c r="A16" s="97"/>
       <c r="B16" s="11" t="s">
         <v>439</v>
       </c>
@@ -12006,7 +12006,7 @@
       <c r="N16" s="26"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="11" t="s">
         <v>373</v>
       </c>
@@ -12026,7 +12026,7 @@
       <c r="N17" s="26"/>
     </row>
     <row r="18" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="54"/>
+      <c r="A18" s="97"/>
       <c r="B18" s="11" t="s">
         <v>599</v>
       </c>
@@ -12046,14 +12046,14 @@
       <c r="N18" s="26"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="67"/>
-      <c r="C19" s="67"/>
-      <c r="D19" s="67"/>
-      <c r="E19" s="67"/>
-      <c r="F19" s="68"/>
+      <c r="B19" s="54"/>
+      <c r="C19" s="54"/>
+      <c r="D19" s="54"/>
+      <c r="E19" s="54"/>
+      <c r="F19" s="55"/>
       <c r="G19" s="38"/>
       <c r="H19" s="38"/>
       <c r="I19" s="38"/>
@@ -12064,7 +12064,7 @@
       <c r="N19" s="26"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="54" t="s">
+      <c r="A20" s="97" t="s">
         <v>623</v>
       </c>
       <c r="B20" s="39" t="s">
@@ -12086,7 +12086,7 @@
       <c r="N20" s="26"/>
     </row>
     <row r="21" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="54"/>
+      <c r="A21" s="97"/>
       <c r="B21" s="40" t="s">
         <v>361</v>
       </c>
@@ -12106,7 +12106,7 @@
       <c r="N21" s="26"/>
     </row>
     <row r="22" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="54"/>
+      <c r="A22" s="97"/>
       <c r="B22" s="39" t="s">
         <v>387</v>
       </c>
@@ -12126,7 +12126,7 @@
       <c r="N22" s="26"/>
     </row>
     <row r="23" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="54"/>
+      <c r="A23" s="97"/>
       <c r="B23" s="39" t="s">
         <v>392</v>
       </c>
@@ -12146,7 +12146,7 @@
       <c r="N23" s="26"/>
     </row>
     <row r="24" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="54"/>
+      <c r="A24" s="97"/>
       <c r="B24" s="39" t="s">
         <v>245</v>
       </c>
@@ -12166,7 +12166,7 @@
       <c r="N24" s="26"/>
     </row>
     <row r="25" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="54"/>
+      <c r="A25" s="97"/>
       <c r="B25" s="39" t="s">
         <v>423</v>
       </c>
@@ -12186,7 +12186,7 @@
       <c r="N25" s="26"/>
     </row>
     <row r="26" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="54"/>
+      <c r="A26" s="97"/>
       <c r="B26" s="39" t="s">
         <v>241</v>
       </c>
@@ -12206,7 +12206,7 @@
       <c r="N26" s="26"/>
     </row>
     <row r="27" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="54"/>
+      <c r="A27" s="97"/>
       <c r="B27" s="39" t="s">
         <v>624</v>
       </c>
@@ -12226,14 +12226,14 @@
       <c r="N27" s="26"/>
     </row>
     <row r="28" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="66" t="s">
+      <c r="A28" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="68"/>
+      <c r="B28" s="54"/>
+      <c r="C28" s="54"/>
+      <c r="D28" s="54"/>
+      <c r="E28" s="54"/>
+      <c r="F28" s="55"/>
       <c r="G28" s="38"/>
       <c r="H28" s="38"/>
       <c r="I28" s="38"/>
@@ -12244,7 +12244,7 @@
       <c r="N28" s="26"/>
     </row>
     <row r="29" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="54" t="s">
+      <c r="A29" s="97" t="s">
         <v>625</v>
       </c>
       <c r="B29" s="41" t="s">
@@ -12266,7 +12266,7 @@
       <c r="N29" s="26"/>
     </row>
     <row r="30" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="54"/>
+      <c r="A30" s="97"/>
       <c r="B30" s="41" t="s">
         <v>334</v>
       </c>
@@ -12286,7 +12286,7 @@
       <c r="N30" s="26"/>
     </row>
     <row r="31" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="54"/>
+      <c r="A31" s="97"/>
       <c r="B31" s="43" t="s">
         <v>367</v>
       </c>
@@ -12306,7 +12306,7 @@
       <c r="N31" s="26"/>
     </row>
     <row r="32" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="54"/>
+      <c r="A32" s="97"/>
       <c r="B32" s="41" t="s">
         <v>397</v>
       </c>
@@ -12326,14 +12326,14 @@
       <c r="N32" s="26"/>
     </row>
     <row r="33" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="66" t="s">
+      <c r="A33" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B33" s="67"/>
-      <c r="C33" s="67"/>
-      <c r="D33" s="67"/>
-      <c r="E33" s="67"/>
-      <c r="F33" s="68"/>
+      <c r="B33" s="54"/>
+      <c r="C33" s="54"/>
+      <c r="D33" s="54"/>
+      <c r="E33" s="54"/>
+      <c r="F33" s="55"/>
       <c r="G33" s="38"/>
       <c r="H33" s="38"/>
       <c r="I33" s="38"/>
@@ -12344,7 +12344,7 @@
       <c r="N33" s="26"/>
     </row>
     <row r="34" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="53" t="s">
+      <c r="A34" s="96" t="s">
         <v>626</v>
       </c>
       <c r="B34" s="39" t="s">
@@ -12366,7 +12366,7 @@
       <c r="N34" s="26"/>
     </row>
     <row r="35" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="53"/>
+      <c r="A35" s="96"/>
       <c r="B35" s="40" t="s">
         <v>408</v>
       </c>
@@ -12386,7 +12386,7 @@
       <c r="N35" s="26"/>
     </row>
     <row r="36" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="53"/>
+      <c r="A36" s="96"/>
       <c r="B36" s="39" t="s">
         <v>232</v>
       </c>
@@ -12406,7 +12406,7 @@
       <c r="N36" s="26"/>
     </row>
     <row r="37" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="53"/>
+      <c r="A37" s="96"/>
       <c r="B37" s="39" t="s">
         <v>210</v>
       </c>
@@ -12426,7 +12426,7 @@
       <c r="N37" s="26"/>
     </row>
     <row r="38" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="53"/>
+      <c r="A38" s="96"/>
       <c r="B38" s="39" t="s">
         <v>231</v>
       </c>
@@ -12446,7 +12446,7 @@
       <c r="N38" s="26"/>
     </row>
     <row r="39" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="53"/>
+      <c r="A39" s="96"/>
       <c r="B39" s="39" t="s">
         <v>203</v>
       </c>
@@ -12466,7 +12466,7 @@
       <c r="N39" s="26"/>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="53"/>
+      <c r="A40" s="96"/>
       <c r="B40" s="39" t="s">
         <v>227</v>
       </c>
@@ -12486,7 +12486,7 @@
       <c r="N40" s="26"/>
     </row>
     <row r="41" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="53"/>
+      <c r="A41" s="96"/>
       <c r="B41" s="39" t="s">
         <v>225</v>
       </c>
@@ -12506,7 +12506,7 @@
       <c r="N41" s="26"/>
     </row>
     <row r="42" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="53"/>
+      <c r="A42" s="96"/>
       <c r="B42" s="39" t="s">
         <v>355</v>
       </c>
@@ -12526,7 +12526,7 @@
       <c r="N42" s="26"/>
     </row>
     <row r="43" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="53"/>
+      <c r="A43" s="96"/>
       <c r="B43" s="39" t="s">
         <v>391</v>
       </c>
@@ -12546,7 +12546,7 @@
       <c r="N43" s="26"/>
     </row>
     <row r="44" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="53"/>
+      <c r="A44" s="96"/>
       <c r="B44" s="39" t="s">
         <v>211</v>
       </c>
@@ -12566,7 +12566,7 @@
       <c r="N44" s="26"/>
     </row>
     <row r="45" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="53"/>
+      <c r="A45" s="96"/>
       <c r="B45" s="39" t="s">
         <v>424</v>
       </c>
@@ -12586,14 +12586,14 @@
       <c r="N45" s="26"/>
     </row>
     <row r="46" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="66" t="s">
+      <c r="A46" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B46" s="67"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
-      <c r="F46" s="68"/>
+      <c r="B46" s="54"/>
+      <c r="C46" s="54"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="54"/>
+      <c r="F46" s="55"/>
       <c r="G46" s="38"/>
       <c r="H46" s="38"/>
       <c r="I46" s="38"/>
@@ -12604,7 +12604,7 @@
       <c r="N46" s="26"/>
     </row>
     <row r="47" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="53" t="s">
+      <c r="A47" s="96" t="s">
         <v>627</v>
       </c>
       <c r="B47" s="15" t="s">
@@ -12626,7 +12626,7 @@
       <c r="N47" s="26"/>
     </row>
     <row r="48" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="53"/>
+      <c r="A48" s="96"/>
       <c r="B48" s="15" t="s">
         <v>500</v>
       </c>
@@ -12646,7 +12646,7 @@
       <c r="N48" s="26"/>
     </row>
     <row r="49" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="53"/>
+      <c r="A49" s="96"/>
       <c r="B49" s="15" t="s">
         <v>499</v>
       </c>
@@ -12666,7 +12666,7 @@
       <c r="N49" s="26"/>
     </row>
     <row r="50" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="53"/>
+      <c r="A50" s="96"/>
       <c r="B50" s="15" t="s">
         <v>497</v>
       </c>
@@ -12686,7 +12686,7 @@
       <c r="N50" s="26"/>
     </row>
     <row r="51" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="53"/>
+      <c r="A51" s="96"/>
       <c r="B51" s="15" t="s">
         <v>474</v>
       </c>
@@ -12706,7 +12706,7 @@
       <c r="N51" s="26"/>
     </row>
     <row r="52" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="53"/>
+      <c r="A52" s="96"/>
       <c r="B52" s="15" t="s">
         <v>475</v>
       </c>
@@ -12726,7 +12726,7 @@
       <c r="N52" s="26"/>
     </row>
     <row r="53" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="53"/>
+      <c r="A53" s="96"/>
       <c r="B53" s="15" t="s">
         <v>479</v>
       </c>
@@ -12746,7 +12746,7 @@
       <c r="N53" s="26"/>
     </row>
     <row r="54" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="53"/>
+      <c r="A54" s="96"/>
       <c r="B54" s="15" t="s">
         <v>181</v>
       </c>
@@ -12766,7 +12766,7 @@
       <c r="N54" s="26"/>
     </row>
     <row r="55" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="53"/>
+      <c r="A55" s="96"/>
       <c r="B55" s="15" t="s">
         <v>480</v>
       </c>
@@ -12786,7 +12786,7 @@
       <c r="N55" s="26"/>
     </row>
     <row r="56" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="54"/>
+      <c r="A56" s="97"/>
       <c r="B56" s="15" t="s">
         <v>488</v>
       </c>
@@ -12806,7 +12806,7 @@
       <c r="N56" s="26"/>
     </row>
     <row r="57" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="54"/>
+      <c r="A57" s="97"/>
       <c r="B57" s="15" t="s">
         <v>401</v>
       </c>
@@ -12826,14 +12826,14 @@
       <c r="N57" s="26"/>
     </row>
     <row r="58" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="66" t="s">
+      <c r="A58" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B58" s="67"/>
-      <c r="C58" s="67"/>
-      <c r="D58" s="67"/>
-      <c r="E58" s="67"/>
-      <c r="F58" s="68"/>
+      <c r="B58" s="54"/>
+      <c r="C58" s="54"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="54"/>
+      <c r="F58" s="55"/>
       <c r="G58" s="38"/>
       <c r="H58" s="38"/>
       <c r="I58" s="38"/>
@@ -12844,7 +12844,7 @@
       <c r="N58" s="26"/>
     </row>
     <row r="59" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="53" t="s">
+      <c r="A59" s="96" t="s">
         <v>629</v>
       </c>
       <c r="B59" s="15" t="s">
@@ -12866,7 +12866,7 @@
       <c r="N59" s="26"/>
     </row>
     <row r="60" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="54"/>
+      <c r="A60" s="97"/>
       <c r="B60" s="15" t="s">
         <v>416</v>
       </c>
@@ -12886,7 +12886,7 @@
       <c r="N60" s="26"/>
     </row>
     <row r="61" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="54"/>
+      <c r="A61" s="97"/>
       <c r="B61" s="15" t="s">
         <v>601</v>
       </c>
@@ -12906,7 +12906,7 @@
       <c r="N61" s="26"/>
     </row>
     <row r="62" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="54"/>
+      <c r="A62" s="97"/>
       <c r="B62" s="15" t="s">
         <v>404</v>
       </c>
@@ -12926,7 +12926,7 @@
       <c r="N62" s="26"/>
     </row>
     <row r="63" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="54"/>
+      <c r="A63" s="97"/>
       <c r="B63" s="15" t="s">
         <v>603</v>
       </c>
@@ -12946,7 +12946,7 @@
       <c r="N63" s="26"/>
     </row>
     <row r="64" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="54"/>
+      <c r="A64" s="97"/>
       <c r="B64" s="15" t="s">
         <v>386</v>
       </c>
@@ -12966,7 +12966,7 @@
       <c r="N64" s="26"/>
     </row>
     <row r="65" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="54"/>
+      <c r="A65" s="97"/>
       <c r="B65" s="15" t="s">
         <v>605</v>
       </c>
@@ -12986,7 +12986,7 @@
       <c r="N65" s="26"/>
     </row>
     <row r="66" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="54"/>
+      <c r="A66" s="97"/>
       <c r="B66" s="15" t="s">
         <v>595</v>
       </c>
@@ -13006,7 +13006,7 @@
       <c r="N66" s="26"/>
     </row>
     <row r="67" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="54"/>
+      <c r="A67" s="97"/>
       <c r="B67" s="15" t="s">
         <v>389</v>
       </c>
@@ -13026,7 +13026,7 @@
       <c r="N67" s="26"/>
     </row>
     <row r="68" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A68" s="54"/>
+      <c r="A68" s="97"/>
       <c r="B68" s="15" t="s">
         <v>176</v>
       </c>
@@ -13046,7 +13046,7 @@
       <c r="N68" s="26"/>
     </row>
     <row r="69" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="54"/>
+      <c r="A69" s="97"/>
       <c r="B69" s="15" t="s">
         <v>607</v>
       </c>
@@ -13066,7 +13066,7 @@
       <c r="N69" s="26"/>
     </row>
     <row r="70" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="54"/>
+      <c r="A70" s="97"/>
       <c r="B70" s="15" t="s">
         <v>406</v>
       </c>
@@ -13086,7 +13086,7 @@
       <c r="N70" s="26"/>
     </row>
     <row r="71" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="54"/>
+      <c r="A71" s="97"/>
       <c r="B71" s="15" t="s">
         <v>609</v>
       </c>
@@ -13106,7 +13106,7 @@
       <c r="N71" s="26"/>
     </row>
     <row r="72" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="54"/>
+      <c r="A72" s="97"/>
       <c r="B72" s="15" t="s">
         <v>473</v>
       </c>
@@ -13126,7 +13126,7 @@
       <c r="N72" s="26"/>
     </row>
     <row r="73" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="54"/>
+      <c r="A73" s="97"/>
       <c r="B73" s="15" t="s">
         <v>496</v>
       </c>
@@ -13146,14 +13146,14 @@
       <c r="N73" s="26"/>
     </row>
     <row r="74" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="66" t="s">
+      <c r="A74" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B74" s="67"/>
-      <c r="C74" s="67"/>
-      <c r="D74" s="67"/>
-      <c r="E74" s="67"/>
-      <c r="F74" s="68"/>
+      <c r="B74" s="54"/>
+      <c r="C74" s="54"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="54"/>
+      <c r="F74" s="55"/>
       <c r="G74" s="38"/>
       <c r="H74" s="38"/>
       <c r="I74" s="38"/>
@@ -13164,7 +13164,7 @@
       <c r="N74" s="26"/>
     </row>
     <row r="75" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="53" t="s">
+      <c r="A75" s="96" t="s">
         <v>630</v>
       </c>
       <c r="B75" s="44" t="s">
@@ -13186,7 +13186,7 @@
       <c r="N75" s="26"/>
     </row>
     <row r="76" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A76" s="53"/>
+      <c r="A76" s="96"/>
       <c r="B76" s="39" t="s">
         <v>482</v>
       </c>
@@ -13206,7 +13206,7 @@
       <c r="N76" s="26"/>
     </row>
     <row r="77" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="53"/>
+      <c r="A77" s="96"/>
       <c r="B77" s="44" t="s">
         <v>501</v>
       </c>
@@ -13226,7 +13226,7 @@
       <c r="N77" s="26"/>
     </row>
     <row r="78" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="53"/>
+      <c r="A78" s="96"/>
       <c r="B78" s="44" t="s">
         <v>194</v>
       </c>
@@ -13246,7 +13246,7 @@
       <c r="N78" s="26"/>
     </row>
     <row r="79" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="53"/>
+      <c r="A79" s="96"/>
       <c r="B79" s="44" t="s">
         <v>186</v>
       </c>
@@ -13266,7 +13266,7 @@
       <c r="N79" s="26"/>
     </row>
     <row r="80" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A80" s="53"/>
+      <c r="A80" s="96"/>
       <c r="B80" s="44" t="s">
         <v>200</v>
       </c>
@@ -13286,14 +13286,14 @@
       <c r="N80" s="26"/>
     </row>
     <row r="81" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A81" s="66" t="s">
+      <c r="A81" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B81" s="67"/>
-      <c r="C81" s="67"/>
-      <c r="D81" s="67"/>
-      <c r="E81" s="67"/>
-      <c r="F81" s="68"/>
+      <c r="B81" s="54"/>
+      <c r="C81" s="54"/>
+      <c r="D81" s="54"/>
+      <c r="E81" s="54"/>
+      <c r="F81" s="55"/>
       <c r="G81" s="38"/>
       <c r="H81" s="38"/>
       <c r="I81" s="38"/>
@@ -13304,7 +13304,7 @@
       <c r="N81" s="26"/>
     </row>
     <row r="82" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="53" t="s">
+      <c r="A82" s="96" t="s">
         <v>631</v>
       </c>
       <c r="B82" s="44" t="s">
@@ -13326,7 +13326,7 @@
       <c r="N82" s="26"/>
     </row>
     <row r="83" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="53"/>
+      <c r="A83" s="96"/>
       <c r="B83" s="44" t="s">
         <v>175</v>
       </c>
@@ -13346,7 +13346,7 @@
       <c r="N83" s="26"/>
     </row>
     <row r="84" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="53"/>
+      <c r="A84" s="96"/>
       <c r="B84" s="44" t="s">
         <v>196</v>
       </c>
@@ -13366,7 +13366,7 @@
       <c r="N84" s="26"/>
     </row>
     <row r="85" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A85" s="53"/>
+      <c r="A85" s="96"/>
       <c r="B85" s="44" t="s">
         <v>179</v>
       </c>
@@ -13386,14 +13386,14 @@
       <c r="N85" s="26"/>
     </row>
     <row r="86" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="66" t="s">
+      <c r="A86" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B86" s="67"/>
-      <c r="C86" s="67"/>
-      <c r="D86" s="67"/>
-      <c r="E86" s="67"/>
-      <c r="F86" s="68"/>
+      <c r="B86" s="54"/>
+      <c r="C86" s="54"/>
+      <c r="D86" s="54"/>
+      <c r="E86" s="54"/>
+      <c r="F86" s="55"/>
       <c r="G86" s="38"/>
       <c r="H86" s="38"/>
       <c r="I86" s="38"/>
@@ -13404,7 +13404,7 @@
       <c r="N86" s="26"/>
     </row>
     <row r="87" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="53" t="s">
+      <c r="A87" s="96" t="s">
         <v>632</v>
       </c>
       <c r="B87" s="29" t="s">
@@ -13426,7 +13426,7 @@
       <c r="N87" s="26"/>
     </row>
     <row r="88" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="53"/>
+      <c r="A88" s="96"/>
       <c r="B88" s="29" t="s">
         <v>233</v>
       </c>
@@ -13446,7 +13446,7 @@
       <c r="N88" s="26"/>
     </row>
     <row r="89" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="53"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="29" t="s">
         <v>339</v>
       </c>
@@ -13466,7 +13466,7 @@
       <c r="N89" s="26"/>
     </row>
     <row r="90" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="53"/>
+      <c r="A90" s="96"/>
       <c r="B90" s="29" t="s">
         <v>268</v>
       </c>
@@ -13486,7 +13486,7 @@
       <c r="N90" s="26"/>
     </row>
     <row r="91" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="53"/>
+      <c r="A91" s="96"/>
       <c r="B91" s="29" t="s">
         <v>336</v>
       </c>
@@ -13506,7 +13506,7 @@
       <c r="N91" s="26"/>
     </row>
     <row r="92" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A92" s="53"/>
+      <c r="A92" s="96"/>
       <c r="B92" s="29" t="s">
         <v>594</v>
       </c>
@@ -13526,14 +13526,14 @@
       <c r="N92" s="26"/>
     </row>
     <row r="93" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="66" t="s">
+      <c r="A93" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B93" s="67"/>
-      <c r="C93" s="67"/>
-      <c r="D93" s="67"/>
-      <c r="E93" s="67"/>
-      <c r="F93" s="68"/>
+      <c r="B93" s="54"/>
+      <c r="C93" s="54"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="54"/>
+      <c r="F93" s="55"/>
       <c r="G93" s="38"/>
       <c r="H93" s="38"/>
       <c r="I93" s="38"/>
@@ -13544,7 +13544,7 @@
       <c r="N93" s="26"/>
     </row>
     <row r="94" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="53" t="s">
+      <c r="A94" s="96" t="s">
         <v>633</v>
       </c>
       <c r="B94" s="15" t="s">
@@ -13566,7 +13566,7 @@
       <c r="N94" s="26"/>
     </row>
     <row r="95" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A95" s="53"/>
+      <c r="A95" s="96"/>
       <c r="B95" s="15" t="s">
         <v>270</v>
       </c>
@@ -13586,7 +13586,7 @@
       <c r="N95" s="26"/>
     </row>
     <row r="96" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="53" t="s">
+      <c r="A96" s="96" t="s">
         <v>634</v>
       </c>
       <c r="B96" s="15" t="s">
@@ -13608,7 +13608,7 @@
       <c r="N96" s="26"/>
     </row>
     <row r="97" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="54"/>
+      <c r="A97" s="97"/>
       <c r="B97" s="15" t="s">
         <v>235</v>
       </c>
@@ -13628,14 +13628,14 @@
       <c r="N97" s="26"/>
     </row>
     <row r="98" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="66" t="s">
+      <c r="A98" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B98" s="67"/>
-      <c r="C98" s="67"/>
-      <c r="D98" s="67"/>
-      <c r="E98" s="67"/>
-      <c r="F98" s="68"/>
+      <c r="B98" s="54"/>
+      <c r="C98" s="54"/>
+      <c r="D98" s="54"/>
+      <c r="E98" s="54"/>
+      <c r="F98" s="55"/>
       <c r="G98" s="38"/>
       <c r="H98" s="38"/>
       <c r="I98" s="38"/>
@@ -13646,7 +13646,7 @@
       <c r="N98" s="26"/>
     </row>
     <row r="99" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="53" t="s">
+      <c r="A99" s="96" t="s">
         <v>636</v>
       </c>
       <c r="B99" s="15" t="s">
@@ -13668,7 +13668,7 @@
       <c r="N99" s="26"/>
     </row>
     <row r="100" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="54"/>
+      <c r="A100" s="97"/>
       <c r="B100" s="15" t="s">
         <v>414</v>
       </c>
@@ -13688,7 +13688,7 @@
       <c r="N100" s="26"/>
     </row>
     <row r="101" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="54"/>
+      <c r="A101" s="97"/>
       <c r="B101" s="15" t="s">
         <v>411</v>
       </c>
@@ -13708,7 +13708,7 @@
       <c r="N101" s="26"/>
     </row>
     <row r="102" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="54"/>
+      <c r="A102" s="97"/>
       <c r="B102" s="15" t="s">
         <v>356</v>
       </c>
@@ -13728,7 +13728,7 @@
       <c r="N102" s="26"/>
     </row>
     <row r="103" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="54"/>
+      <c r="A103" s="97"/>
       <c r="B103" s="15" t="s">
         <v>593</v>
       </c>
@@ -13748,7 +13748,7 @@
       <c r="N103" s="26"/>
     </row>
     <row r="104" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="54"/>
+      <c r="A104" s="97"/>
       <c r="B104" s="15" t="s">
         <v>592</v>
       </c>
@@ -13768,7 +13768,7 @@
       <c r="N104" s="26"/>
     </row>
     <row r="105" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="54"/>
+      <c r="A105" s="97"/>
       <c r="B105" s="15" t="s">
         <v>385</v>
       </c>
@@ -13788,7 +13788,7 @@
       <c r="N105" s="26"/>
     </row>
     <row r="106" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="54"/>
+      <c r="A106" s="97"/>
       <c r="B106" s="15" t="s">
         <v>364</v>
       </c>
@@ -13808,7 +13808,7 @@
       <c r="N106" s="26"/>
     </row>
     <row r="107" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="54"/>
+      <c r="A107" s="97"/>
       <c r="B107" s="15" t="s">
         <v>248</v>
       </c>
@@ -13828,7 +13828,7 @@
       <c r="N107" s="26"/>
     </row>
     <row r="108" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="54"/>
+      <c r="A108" s="97"/>
       <c r="B108" s="15" t="s">
         <v>329</v>
       </c>
@@ -13848,7 +13848,7 @@
       <c r="N108" s="26"/>
     </row>
     <row r="109" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A109" s="54"/>
+      <c r="A109" s="97"/>
       <c r="B109" s="15" t="s">
         <v>425</v>
       </c>
@@ -13868,7 +13868,7 @@
       <c r="N109" s="26"/>
     </row>
     <row r="110" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="54"/>
+      <c r="A110" s="97"/>
       <c r="B110" s="15" t="s">
         <v>229</v>
       </c>
@@ -13888,7 +13888,7 @@
       <c r="N110" s="26"/>
     </row>
     <row r="111" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="54"/>
+      <c r="A111" s="97"/>
       <c r="B111" s="15" t="s">
         <v>370</v>
       </c>
@@ -13908,7 +13908,7 @@
       <c r="N111" s="26"/>
     </row>
     <row r="112" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="54"/>
+      <c r="A112" s="97"/>
       <c r="B112" s="15" t="s">
         <v>239</v>
       </c>
@@ -13928,7 +13928,7 @@
       <c r="N112" s="26"/>
     </row>
     <row r="113" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="53" t="s">
+      <c r="A113" s="96" t="s">
         <v>637</v>
       </c>
       <c r="B113" s="15" t="s">
@@ -13950,7 +13950,7 @@
       <c r="N113" s="26"/>
     </row>
     <row r="114" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="54"/>
+      <c r="A114" s="97"/>
       <c r="B114" s="15" t="s">
         <v>395</v>
       </c>
@@ -13970,7 +13970,7 @@
       <c r="N114" s="26"/>
     </row>
     <row r="115" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="54"/>
+      <c r="A115" s="97"/>
       <c r="B115" s="15" t="s">
         <v>350</v>
       </c>
@@ -13990,7 +13990,7 @@
       <c r="N115" s="26"/>
     </row>
     <row r="116" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="54"/>
+      <c r="A116" s="97"/>
       <c r="B116" s="15" t="s">
         <v>383</v>
       </c>
@@ -14010,7 +14010,7 @@
       <c r="N116" s="26"/>
     </row>
     <row r="117" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A117" s="54"/>
+      <c r="A117" s="97"/>
       <c r="B117" s="15" t="s">
         <v>375</v>
       </c>
@@ -14030,7 +14030,7 @@
       <c r="N117" s="26"/>
     </row>
     <row r="118" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="54"/>
+      <c r="A118" s="97"/>
       <c r="B118" s="15" t="s">
         <v>432</v>
       </c>
@@ -14050,7 +14050,7 @@
       <c r="N118" s="26"/>
     </row>
     <row r="119" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="54"/>
+      <c r="A119" s="97"/>
       <c r="B119" s="15" t="s">
         <v>437</v>
       </c>
@@ -14070,7 +14070,7 @@
       <c r="N119" s="26"/>
     </row>
     <row r="120" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="54"/>
+      <c r="A120" s="97"/>
       <c r="B120" s="15" t="s">
         <v>399</v>
       </c>
@@ -14090,7 +14090,7 @@
       <c r="N120" s="26"/>
     </row>
     <row r="121" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="54"/>
+      <c r="A121" s="97"/>
       <c r="B121" s="15" t="s">
         <v>226</v>
       </c>
@@ -14110,7 +14110,7 @@
       <c r="N121" s="26"/>
     </row>
     <row r="122" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="53" t="s">
+      <c r="A122" s="96" t="s">
         <v>638</v>
       </c>
       <c r="B122" s="15" t="s">
@@ -14132,7 +14132,7 @@
       <c r="N122" s="26"/>
     </row>
     <row r="123" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="54"/>
+      <c r="A123" s="97"/>
       <c r="B123" s="15" t="s">
         <v>428</v>
       </c>
@@ -14152,7 +14152,7 @@
       <c r="N123" s="26"/>
     </row>
     <row r="124" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A124" s="54"/>
+      <c r="A124" s="97"/>
       <c r="B124" s="15" t="s">
         <v>253</v>
       </c>
@@ -14172,7 +14172,7 @@
       <c r="N124" s="26"/>
     </row>
     <row r="125" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A125" s="54"/>
+      <c r="A125" s="97"/>
       <c r="B125" s="15" t="s">
         <v>415</v>
       </c>
@@ -14192,7 +14192,7 @@
       <c r="N125" s="26"/>
     </row>
     <row r="126" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A126" s="54"/>
+      <c r="A126" s="97"/>
       <c r="B126" s="15" t="s">
         <v>240</v>
       </c>
@@ -14212,7 +14212,7 @@
       <c r="N126" s="26"/>
     </row>
     <row r="127" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A127" s="54"/>
+      <c r="A127" s="97"/>
       <c r="B127" s="15" t="s">
         <v>244</v>
       </c>
@@ -14232,7 +14232,7 @@
       <c r="N127" s="26"/>
     </row>
     <row r="128" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A128" s="54"/>
+      <c r="A128" s="97"/>
       <c r="B128" s="15" t="s">
         <v>417</v>
       </c>
@@ -14252,7 +14252,7 @@
       <c r="N128" s="26"/>
     </row>
     <row r="129" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A129" s="54"/>
+      <c r="A129" s="97"/>
       <c r="B129" s="15" t="s">
         <v>228</v>
       </c>
@@ -14272,7 +14272,7 @@
       <c r="N129" s="26"/>
     </row>
     <row r="130" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="54"/>
+      <c r="A130" s="97"/>
       <c r="B130" s="15" t="s">
         <v>272</v>
       </c>
@@ -14292,7 +14292,7 @@
       <c r="N130" s="26"/>
     </row>
     <row r="131" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A131" s="54"/>
+      <c r="A131" s="97"/>
       <c r="B131" s="15" t="s">
         <v>259</v>
       </c>
@@ -14312,7 +14312,7 @@
       <c r="N131" s="26"/>
     </row>
     <row r="132" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A132" s="54"/>
+      <c r="A132" s="97"/>
       <c r="B132" s="15" t="s">
         <v>262</v>
       </c>
@@ -14332,7 +14332,7 @@
       <c r="N132" s="26"/>
     </row>
     <row r="133" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A133" s="54"/>
+      <c r="A133" s="97"/>
       <c r="B133" s="15" t="s">
         <v>209</v>
       </c>
@@ -14352,7 +14352,7 @@
       <c r="N133" s="26"/>
     </row>
     <row r="134" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A134" s="53" t="s">
+      <c r="A134" s="96" t="s">
         <v>639</v>
       </c>
       <c r="B134" s="15" t="s">
@@ -14374,7 +14374,7 @@
       <c r="N134" s="26"/>
     </row>
     <row r="135" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A135" s="54"/>
+      <c r="A135" s="97"/>
       <c r="B135" s="15" t="s">
         <v>208</v>
       </c>
@@ -14394,7 +14394,7 @@
       <c r="N135" s="26"/>
     </row>
     <row r="136" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A136" s="54"/>
+      <c r="A136" s="97"/>
       <c r="B136" s="15" t="s">
         <v>296</v>
       </c>
@@ -14414,7 +14414,7 @@
       <c r="N136" s="26"/>
     </row>
     <row r="137" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="54"/>
+      <c r="A137" s="97"/>
       <c r="B137" s="15" t="s">
         <v>283</v>
       </c>
@@ -14434,7 +14434,7 @@
       <c r="N137" s="26"/>
     </row>
     <row r="138" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A138" s="54"/>
+      <c r="A138" s="97"/>
       <c r="B138" s="15" t="s">
         <v>237</v>
       </c>
@@ -14454,7 +14454,7 @@
       <c r="N138" s="26"/>
     </row>
     <row r="139" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="54"/>
+      <c r="A139" s="97"/>
       <c r="B139" s="15" t="s">
         <v>282</v>
       </c>
@@ -14474,7 +14474,7 @@
       <c r="N139" s="26"/>
     </row>
     <row r="140" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A140" s="54"/>
+      <c r="A140" s="97"/>
       <c r="B140" s="15" t="s">
         <v>230</v>
       </c>
@@ -14516,7 +14516,7 @@
       <c r="N141" s="26"/>
     </row>
     <row r="142" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A142" s="53" t="s">
+      <c r="A142" s="96" t="s">
         <v>641</v>
       </c>
       <c r="B142" s="15" t="s">
@@ -14538,7 +14538,7 @@
       <c r="N142" s="26"/>
     </row>
     <row r="143" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A143" s="54"/>
+      <c r="A143" s="97"/>
       <c r="B143" s="15" t="s">
         <v>291</v>
       </c>
@@ -14558,7 +14558,7 @@
       <c r="N143" s="26"/>
     </row>
     <row r="144" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A144" s="54"/>
+      <c r="A144" s="97"/>
       <c r="B144" s="15" t="s">
         <v>257</v>
       </c>
@@ -14578,7 +14578,7 @@
       <c r="N144" s="26"/>
     </row>
     <row r="145" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="54"/>
+      <c r="A145" s="97"/>
       <c r="B145" s="15" t="s">
         <v>380</v>
       </c>
@@ -14598,7 +14598,7 @@
       <c r="N145" s="26"/>
     </row>
     <row r="146" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A146" s="54"/>
+      <c r="A146" s="97"/>
       <c r="B146" s="15" t="s">
         <v>222</v>
       </c>
@@ -14618,14 +14618,14 @@
       <c r="N146" s="26"/>
     </row>
     <row r="147" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="66" t="s">
+      <c r="A147" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B147" s="67"/>
-      <c r="C147" s="67"/>
-      <c r="D147" s="67"/>
-      <c r="E147" s="67"/>
-      <c r="F147" s="68"/>
+      <c r="B147" s="54"/>
+      <c r="C147" s="54"/>
+      <c r="D147" s="54"/>
+      <c r="E147" s="54"/>
+      <c r="F147" s="55"/>
       <c r="G147" s="38"/>
       <c r="H147" s="38"/>
       <c r="I147" s="38"/>
@@ -14636,7 +14636,7 @@
       <c r="N147" s="26"/>
     </row>
     <row r="148" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A148" s="53" t="s">
+      <c r="A148" s="96" t="s">
         <v>643</v>
       </c>
       <c r="B148" s="29" t="s">
@@ -14658,7 +14658,7 @@
       <c r="N148" s="26"/>
     </row>
     <row r="149" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A149" s="53"/>
+      <c r="A149" s="96"/>
       <c r="B149" s="29" t="s">
         <v>371</v>
       </c>
@@ -14678,7 +14678,7 @@
       <c r="N149" s="26"/>
     </row>
     <row r="150" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A150" s="53"/>
+      <c r="A150" s="96"/>
       <c r="B150" s="29" t="s">
         <v>293</v>
       </c>
@@ -14698,7 +14698,7 @@
       <c r="N150" s="26"/>
     </row>
     <row r="151" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A151" s="53"/>
+      <c r="A151" s="96"/>
       <c r="B151" s="29" t="s">
         <v>712</v>
       </c>
@@ -14718,7 +14718,7 @@
       <c r="N151" s="26"/>
     </row>
     <row r="152" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A152" s="53"/>
+      <c r="A152" s="96"/>
       <c r="B152" s="29" t="s">
         <v>265</v>
       </c>
@@ -14738,7 +14738,7 @@
       <c r="N152" s="26"/>
     </row>
     <row r="153" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A153" s="53"/>
+      <c r="A153" s="96"/>
       <c r="B153" s="29" t="s">
         <v>234</v>
       </c>
@@ -14758,7 +14758,7 @@
       <c r="N153" s="26"/>
     </row>
     <row r="154" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A154" s="53"/>
+      <c r="A154" s="96"/>
       <c r="B154" s="29" t="s">
         <v>333</v>
       </c>
@@ -14778,7 +14778,7 @@
       <c r="N154" s="26"/>
     </row>
     <row r="155" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="53" t="s">
+      <c r="A155" s="96" t="s">
         <v>644</v>
       </c>
       <c r="B155" s="29" t="s">
@@ -14800,7 +14800,7 @@
       <c r="N155" s="26"/>
     </row>
     <row r="156" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A156" s="53"/>
+      <c r="A156" s="96"/>
       <c r="B156" s="29" t="s">
         <v>261</v>
       </c>
@@ -14820,7 +14820,7 @@
       <c r="N156" s="26"/>
     </row>
     <row r="157" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A157" s="53"/>
+      <c r="A157" s="96"/>
       <c r="B157" s="29" t="s">
         <v>236</v>
       </c>
@@ -14840,7 +14840,7 @@
       <c r="N157" s="26"/>
     </row>
     <row r="158" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A158" s="53"/>
+      <c r="A158" s="96"/>
       <c r="B158" s="29" t="s">
         <v>223</v>
       </c>
@@ -14860,7 +14860,7 @@
       <c r="N158" s="26"/>
     </row>
     <row r="159" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A159" s="53"/>
+      <c r="A159" s="96"/>
       <c r="B159" s="29" t="s">
         <v>365</v>
       </c>
@@ -14880,7 +14880,7 @@
       <c r="N159" s="26"/>
     </row>
     <row r="160" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A160" s="53"/>
+      <c r="A160" s="96"/>
       <c r="B160" s="29" t="s">
         <v>286</v>
       </c>
@@ -14900,7 +14900,7 @@
       <c r="N160" s="26"/>
     </row>
     <row r="161" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A161" s="53" t="s">
+      <c r="A161" s="96" t="s">
         <v>645</v>
       </c>
       <c r="B161" s="29" t="s">
@@ -14922,7 +14922,7 @@
       <c r="N161" s="26"/>
     </row>
     <row r="162" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A162" s="53"/>
+      <c r="A162" s="96"/>
       <c r="B162" s="29" t="s">
         <v>597</v>
       </c>
@@ -14942,14 +14942,14 @@
       <c r="N162" s="26"/>
     </row>
     <row r="163" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A163" s="66" t="s">
+      <c r="A163" s="98" t="s">
         <v>502</v>
       </c>
-      <c r="B163" s="67"/>
-      <c r="C163" s="67"/>
-      <c r="D163" s="67"/>
-      <c r="E163" s="67"/>
-      <c r="F163" s="68"/>
+      <c r="B163" s="54"/>
+      <c r="C163" s="54"/>
+      <c r="D163" s="54"/>
+      <c r="E163" s="54"/>
+      <c r="F163" s="55"/>
       <c r="G163" s="38"/>
       <c r="H163" s="38"/>
       <c r="I163" s="38"/>
@@ -14960,7 +14960,7 @@
       <c r="N163" s="26"/>
     </row>
     <row r="164" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A164" s="103" t="s">
+      <c r="A164" s="99" t="s">
         <v>656</v>
       </c>
       <c r="B164" s="15" t="s">
@@ -14982,7 +14982,7 @@
       <c r="N164" s="26"/>
     </row>
     <row r="165" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A165" s="104"/>
+      <c r="A165" s="100"/>
       <c r="B165" s="15" t="s">
         <v>250</v>
       </c>
@@ -15002,7 +15002,7 @@
       <c r="N165" s="26"/>
     </row>
     <row r="166" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A166" s="104"/>
+      <c r="A166" s="100"/>
       <c r="B166" s="15" t="s">
         <v>250</v>
       </c>
@@ -15022,8 +15022,10 @@
       <c r="N166" s="26"/>
     </row>
     <row r="167" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A167" s="104"/>
-      <c r="B167" s="15"/>
+      <c r="A167" s="100"/>
+      <c r="B167" s="15">
+        <v>444444</v>
+      </c>
       <c r="C167" s="4" t="s">
         <v>723</v>
       </c>
@@ -15040,8 +15042,10 @@
       <c r="N167" s="26"/>
     </row>
     <row r="168" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A168" s="69"/>
-      <c r="B168" s="15"/>
+      <c r="A168" s="101"/>
+      <c r="B168" s="15">
+        <v>444444</v>
+      </c>
       <c r="C168" s="4" t="s">
         <v>724</v>
       </c>
@@ -15058,7 +15062,7 @@
       <c r="N168" s="26"/>
     </row>
     <row r="169" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A169" s="101" t="s">
+      <c r="A169" s="103" t="s">
         <v>655</v>
       </c>
       <c r="B169" s="15" t="s">
@@ -15080,7 +15084,7 @@
       <c r="N169" s="26"/>
     </row>
     <row r="170" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A170" s="102"/>
+      <c r="A170" s="104"/>
       <c r="B170" s="15" t="s">
         <v>376</v>
       </c>
@@ -15100,7 +15104,7 @@
       <c r="N170" s="26"/>
     </row>
     <row r="171" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A171" s="54" t="s">
+      <c r="A171" s="97" t="s">
         <v>654</v>
       </c>
       <c r="B171" s="15" t="s">
@@ -15122,7 +15126,7 @@
       <c r="N171" s="26"/>
     </row>
     <row r="172" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A172" s="54"/>
+      <c r="A172" s="97"/>
       <c r="B172" s="15" t="s">
         <v>360</v>
       </c>
@@ -15142,7 +15146,7 @@
       <c r="N172" s="26"/>
     </row>
     <row r="173" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A173" s="54" t="s">
+      <c r="A173" s="97" t="s">
         <v>653</v>
       </c>
       <c r="B173" s="15" t="s">
@@ -15164,7 +15168,7 @@
       <c r="N173" s="26"/>
     </row>
     <row r="174" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A174" s="54"/>
+      <c r="A174" s="97"/>
       <c r="B174" s="15" t="s">
         <v>320</v>
       </c>
@@ -15206,7 +15210,7 @@
       <c r="N175" s="26"/>
     </row>
     <row r="176" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A176" s="54" t="s">
+      <c r="A176" s="97" t="s">
         <v>651</v>
       </c>
       <c r="B176" s="15" t="s">
@@ -15228,7 +15232,7 @@
       <c r="N176" s="26"/>
     </row>
     <row r="177" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A177" s="54"/>
+      <c r="A177" s="97"/>
       <c r="B177" s="15" t="s">
         <v>252</v>
       </c>
@@ -15248,7 +15252,7 @@
       <c r="N177" s="26"/>
     </row>
     <row r="178" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A178" s="54"/>
+      <c r="A178" s="97"/>
       <c r="B178" s="15" t="s">
         <v>271</v>
       </c>
@@ -15268,14 +15272,14 @@
       <c r="N178" s="26"/>
     </row>
     <row r="179" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A179" s="66" t="s">
+      <c r="A179" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B179" s="67"/>
-      <c r="C179" s="67"/>
-      <c r="D179" s="67"/>
-      <c r="E179" s="67"/>
-      <c r="F179" s="68"/>
+      <c r="B179" s="54"/>
+      <c r="C179" s="54"/>
+      <c r="D179" s="54"/>
+      <c r="E179" s="54"/>
+      <c r="F179" s="55"/>
       <c r="G179" s="38"/>
       <c r="H179" s="38"/>
       <c r="I179" s="38"/>
@@ -15286,7 +15290,7 @@
       <c r="N179" s="26"/>
     </row>
     <row r="180" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A180" s="54" t="s">
+      <c r="A180" s="97" t="s">
         <v>663</v>
       </c>
       <c r="B180" s="15" t="s">
@@ -15308,7 +15312,7 @@
       <c r="N180" s="26"/>
     </row>
     <row r="181" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A181" s="54"/>
+      <c r="A181" s="97"/>
       <c r="B181" s="15" t="s">
         <v>459</v>
       </c>
@@ -15328,7 +15332,7 @@
       <c r="N181" s="26"/>
     </row>
     <row r="182" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A182" s="54" t="s">
+      <c r="A182" s="97" t="s">
         <v>664</v>
       </c>
       <c r="B182" s="15" t="s">
@@ -15350,7 +15354,7 @@
       <c r="N182" s="26"/>
     </row>
     <row r="183" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="54"/>
+      <c r="A183" s="97"/>
       <c r="B183" s="15" t="s">
         <v>449</v>
       </c>
@@ -15370,7 +15374,7 @@
       <c r="N183" s="26"/>
     </row>
     <row r="184" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A184" s="54"/>
+      <c r="A184" s="97"/>
       <c r="B184" s="15" t="s">
         <v>453</v>
       </c>
@@ -15390,7 +15394,7 @@
       <c r="N184" s="26"/>
     </row>
     <row r="185" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A185" s="54"/>
+      <c r="A185" s="97"/>
       <c r="B185" s="15" t="s">
         <v>457</v>
       </c>
@@ -15410,7 +15414,7 @@
       <c r="N185" s="26"/>
     </row>
     <row r="186" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A186" s="54"/>
+      <c r="A186" s="97"/>
       <c r="B186" s="15" t="s">
         <v>440</v>
       </c>
@@ -15430,7 +15434,7 @@
       <c r="N186" s="26"/>
     </row>
     <row r="187" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A187" s="54"/>
+      <c r="A187" s="97"/>
       <c r="B187" s="15" t="s">
         <v>451</v>
       </c>
@@ -15450,7 +15454,7 @@
       <c r="N187" s="26"/>
     </row>
     <row r="188" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A188" s="54" t="s">
+      <c r="A188" s="97" t="s">
         <v>611</v>
       </c>
       <c r="B188" s="15" t="s">
@@ -15472,7 +15476,7 @@
       <c r="N188" s="26"/>
     </row>
     <row r="189" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A189" s="54"/>
+      <c r="A189" s="97"/>
       <c r="B189" s="15" t="s">
         <v>659</v>
       </c>
@@ -15492,7 +15496,7 @@
       <c r="N189" s="26"/>
     </row>
     <row r="190" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A190" s="54"/>
+      <c r="A190" s="97"/>
       <c r="B190" s="15" t="s">
         <v>661</v>
       </c>
@@ -15512,7 +15516,7 @@
       <c r="N190" s="26"/>
     </row>
     <row r="191" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A191" s="53" t="s">
+      <c r="A191" s="96" t="s">
         <v>714</v>
       </c>
       <c r="B191" s="15" t="s">
@@ -15534,7 +15538,7 @@
       <c r="N191" s="28"/>
     </row>
     <row r="192" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A192" s="54"/>
+      <c r="A192" s="97"/>
       <c r="B192" s="15" t="s">
         <v>716</v>
       </c>
@@ -15554,7 +15558,7 @@
       <c r="N192" s="28"/>
     </row>
     <row r="193" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A193" s="54"/>
+      <c r="A193" s="97"/>
       <c r="B193" s="15" t="s">
         <v>717</v>
       </c>
@@ -15574,7 +15578,7 @@
       <c r="N193" s="28"/>
     </row>
     <row r="194" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A194" s="54"/>
+      <c r="A194" s="97"/>
       <c r="B194" s="15" t="s">
         <v>718</v>
       </c>
@@ -15594,14 +15598,14 @@
       <c r="N194" s="28"/>
     </row>
     <row r="195" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A195" s="73" t="s">
+      <c r="A195" s="102" t="s">
         <v>113</v>
       </c>
-      <c r="B195" s="74"/>
-      <c r="C195" s="74"/>
-      <c r="D195" s="74"/>
-      <c r="E195" s="74"/>
-      <c r="F195" s="75"/>
+      <c r="B195" s="57"/>
+      <c r="C195" s="57"/>
+      <c r="D195" s="57"/>
+      <c r="E195" s="57"/>
+      <c r="F195" s="58"/>
       <c r="G195" s="51"/>
       <c r="H195" s="51"/>
       <c r="I195" s="51"/>
@@ -15612,14 +15616,14 @@
       <c r="N195" s="52"/>
     </row>
     <row r="196" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A196" s="70" t="s">
+      <c r="A196" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="B196" s="71"/>
-      <c r="C196" s="71"/>
-      <c r="D196" s="71"/>
-      <c r="E196" s="71"/>
-      <c r="F196" s="72"/>
+      <c r="B196" s="60"/>
+      <c r="C196" s="60"/>
+      <c r="D196" s="60"/>
+      <c r="E196" s="60"/>
+      <c r="F196" s="61"/>
       <c r="G196" s="48"/>
       <c r="H196" s="48"/>
       <c r="I196" s="48"/>
@@ -15663,28 +15667,26 @@
     </row>
   </sheetData>
   <mergeCells count="58">
-    <mergeCell ref="A47:A57"/>
-    <mergeCell ref="A59:A73"/>
-    <mergeCell ref="A75:A80"/>
-    <mergeCell ref="A82:A85"/>
-    <mergeCell ref="A87:A92"/>
-    <mergeCell ref="A58:F58"/>
-    <mergeCell ref="A74:F74"/>
-    <mergeCell ref="A81:F81"/>
-    <mergeCell ref="A86:F86"/>
-    <mergeCell ref="A93:F93"/>
-    <mergeCell ref="A94:A95"/>
-    <mergeCell ref="A96:A97"/>
-    <mergeCell ref="A98:F98"/>
-    <mergeCell ref="A176:A178"/>
-    <mergeCell ref="A171:A172"/>
-    <mergeCell ref="A173:A174"/>
-    <mergeCell ref="A122:A133"/>
-    <mergeCell ref="A134:A140"/>
-    <mergeCell ref="A142:A146"/>
-    <mergeCell ref="A113:A121"/>
-    <mergeCell ref="A99:A112"/>
-    <mergeCell ref="A164:A168"/>
+    <mergeCell ref="A2:N2"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H7"/>
+    <mergeCell ref="I6:I7"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="K6:K7"/>
+    <mergeCell ref="L6:L7"/>
+    <mergeCell ref="M6:M7"/>
+    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A29:A32"/>
+    <mergeCell ref="A191:A194"/>
     <mergeCell ref="A8:A18"/>
     <mergeCell ref="A46:F46"/>
     <mergeCell ref="A196:F196"/>
@@ -15701,26 +15703,28 @@
     <mergeCell ref="A161:A162"/>
     <mergeCell ref="A20:A27"/>
     <mergeCell ref="A34:A45"/>
-    <mergeCell ref="A33:F33"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A29:A32"/>
-    <mergeCell ref="A191:A194"/>
-    <mergeCell ref="A2:N2"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H7"/>
-    <mergeCell ref="I6:I7"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="K6:K7"/>
-    <mergeCell ref="L6:L7"/>
-    <mergeCell ref="M6:M7"/>
-    <mergeCell ref="N6:N7"/>
+    <mergeCell ref="A93:F93"/>
+    <mergeCell ref="A94:A95"/>
+    <mergeCell ref="A96:A97"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="A176:A178"/>
+    <mergeCell ref="A171:A172"/>
+    <mergeCell ref="A173:A174"/>
+    <mergeCell ref="A122:A133"/>
+    <mergeCell ref="A134:A140"/>
+    <mergeCell ref="A142:A146"/>
+    <mergeCell ref="A113:A121"/>
+    <mergeCell ref="A99:A112"/>
+    <mergeCell ref="A164:A168"/>
+    <mergeCell ref="A47:A57"/>
+    <mergeCell ref="A59:A73"/>
+    <mergeCell ref="A75:A80"/>
+    <mergeCell ref="A82:A85"/>
+    <mergeCell ref="A87:A92"/>
+    <mergeCell ref="A58:F58"/>
+    <mergeCell ref="A74:F74"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A86:F86"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18205,22 +18209,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:16" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
-      <c r="O2" s="55"/>
-      <c r="P2" s="55"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
+      <c r="O2" s="83"/>
+      <c r="P2" s="83"/>
     </row>
     <row r="3" spans="1:16" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -18253,75 +18257,75 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="91" t="s">
         <v>409</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="88" t="s">
         <v>612</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="86" t="s">
         <v>613</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="86" t="s">
         <v>614</v>
       </c>
-      <c r="E6" s="80" t="s">
+      <c r="E6" s="93" t="s">
         <v>710</v>
       </c>
-      <c r="F6" s="82" t="s">
+      <c r="F6" s="95" t="s">
         <v>711</v>
       </c>
-      <c r="G6" s="60" t="s">
+      <c r="G6" s="86" t="s">
         <v>615</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="81" t="s">
         <v>616</v>
       </c>
-      <c r="I6" s="62" t="s">
+      <c r="I6" s="81" t="s">
         <v>571</v>
       </c>
-      <c r="J6" s="62" t="s">
+      <c r="J6" s="81" t="s">
         <v>575</v>
       </c>
-      <c r="K6" s="62" t="s">
+      <c r="K6" s="81" t="s">
         <v>581</v>
       </c>
-      <c r="L6" s="62" t="s">
+      <c r="L6" s="81" t="s">
         <v>582</v>
       </c>
-      <c r="M6" s="62" t="s">
+      <c r="M6" s="81" t="s">
         <v>583</v>
       </c>
-      <c r="N6" s="62" t="s">
+      <c r="N6" s="81" t="s">
         <v>596</v>
       </c>
-      <c r="O6" s="62" t="s">
+      <c r="O6" s="81" t="s">
         <v>617</v>
       </c>
-      <c r="P6" s="64" t="s">
+      <c r="P6" s="84" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="57"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="81"/>
-      <c r="F7" s="81"/>
-      <c r="G7" s="61"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="63"/>
-      <c r="O7" s="63"/>
-      <c r="P7" s="65"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="87"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="82"/>
+      <c r="O7" s="82"/>
+      <c r="P7" s="85"/>
     </row>
     <row r="8" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="101" t="s">
         <v>693</v>
       </c>
       <c r="B8" s="23">
@@ -18345,7 +18349,7 @@
       <c r="P8" s="27"/>
     </row>
     <row r="9" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="54"/>
+      <c r="A9" s="97"/>
       <c r="B9" s="15">
         <v>7427</v>
       </c>
@@ -18367,7 +18371,7 @@
       <c r="P9" s="26"/>
     </row>
     <row r="10" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="54"/>
+      <c r="A10" s="97"/>
       <c r="B10" s="18">
         <v>7429</v>
       </c>
@@ -18389,7 +18393,7 @@
       <c r="P10" s="26"/>
     </row>
     <row r="11" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="54"/>
+      <c r="A11" s="97"/>
       <c r="B11" s="18">
         <v>7431</v>
       </c>
@@ -18411,7 +18415,7 @@
       <c r="P11" s="26"/>
     </row>
     <row r="12" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="54"/>
+      <c r="A12" s="97"/>
       <c r="B12" s="18">
         <v>7433</v>
       </c>
@@ -18433,7 +18437,7 @@
       <c r="P12" s="26"/>
     </row>
     <row r="13" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="54"/>
+      <c r="A13" s="97"/>
       <c r="B13" s="18">
         <v>7435</v>
       </c>
@@ -18455,7 +18459,7 @@
       <c r="P13" s="26"/>
     </row>
     <row r="14" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="54"/>
+      <c r="A14" s="97"/>
       <c r="B14" s="18">
         <v>7437</v>
       </c>
@@ -18477,7 +18481,7 @@
       <c r="P14" s="26"/>
     </row>
     <row r="15" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="54"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="18">
         <v>7439</v>
       </c>
@@ -18499,7 +18503,7 @@
       <c r="P15" s="26"/>
     </row>
     <row r="16" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="54"/>
+      <c r="A16" s="97"/>
       <c r="B16" s="18">
         <v>7441</v>
       </c>
@@ -18521,7 +18525,7 @@
       <c r="P16" s="26"/>
     </row>
     <row r="17" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="54"/>
+      <c r="A17" s="97"/>
       <c r="B17" s="18">
         <v>7426</v>
       </c>
@@ -18543,7 +18547,7 @@
       <c r="P17" s="26"/>
     </row>
     <row r="18" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="54"/>
+      <c r="A18" s="97"/>
       <c r="B18" s="18">
         <v>7430</v>
       </c>
@@ -18565,7 +18569,7 @@
       <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="54"/>
+      <c r="A19" s="97"/>
       <c r="B19" s="18">
         <v>7432</v>
       </c>
@@ -18587,7 +18591,7 @@
       <c r="P19" s="26"/>
     </row>
     <row r="20" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="54"/>
+      <c r="A20" s="97"/>
       <c r="B20" s="18">
         <v>7434</v>
       </c>
@@ -18609,7 +18613,7 @@
       <c r="P20" s="26"/>
     </row>
     <row r="21" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="54"/>
+      <c r="A21" s="97"/>
       <c r="B21" s="18">
         <v>7436</v>
       </c>
@@ -18631,7 +18635,7 @@
       <c r="P21" s="26"/>
     </row>
     <row r="22" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="54"/>
+      <c r="A22" s="97"/>
       <c r="B22" s="18">
         <v>7438</v>
       </c>
@@ -18653,7 +18657,7 @@
       <c r="P22" s="26"/>
     </row>
     <row r="23" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="54"/>
+      <c r="A23" s="97"/>
       <c r="B23" s="18">
         <v>7440</v>
       </c>
@@ -18675,7 +18679,7 @@
       <c r="P23" s="26"/>
     </row>
     <row r="24" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="54"/>
+      <c r="A24" s="97"/>
       <c r="B24" s="18">
         <v>7442</v>
       </c>
@@ -18697,7 +18701,7 @@
       <c r="P24" s="26"/>
     </row>
     <row r="25" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="54"/>
+      <c r="A25" s="97"/>
       <c r="B25" s="18">
         <v>7443</v>
       </c>
@@ -18719,7 +18723,7 @@
       <c r="P25" s="26"/>
     </row>
     <row r="26" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="54"/>
+      <c r="A26" s="97"/>
       <c r="B26" s="18">
         <v>7445</v>
       </c>
@@ -18741,7 +18745,7 @@
       <c r="P26" s="26"/>
     </row>
     <row r="27" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="54"/>
+      <c r="A27" s="97"/>
       <c r="B27" s="18">
         <v>7444</v>
       </c>
@@ -18763,7 +18767,7 @@
       <c r="P27" s="26"/>
     </row>
     <row r="28" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="54"/>
+      <c r="A28" s="97"/>
       <c r="B28" s="18">
         <v>7446</v>
       </c>
@@ -18785,7 +18789,7 @@
       <c r="P28" s="26"/>
     </row>
     <row r="29" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="54"/>
+      <c r="A29" s="97"/>
       <c r="B29" s="18">
         <v>7448</v>
       </c>
@@ -18807,7 +18811,7 @@
       <c r="P29" s="26"/>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="54"/>
+      <c r="A30" s="97"/>
       <c r="B30" s="18">
         <v>7450</v>
       </c>
@@ -18829,16 +18833,16 @@
       <c r="P30" s="26"/>
     </row>
     <row r="31" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="66" t="s">
+      <c r="A31" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B31" s="67"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="68"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="54"/>
+      <c r="D31" s="54"/>
+      <c r="E31" s="54"/>
+      <c r="F31" s="54"/>
+      <c r="G31" s="54"/>
+      <c r="H31" s="55"/>
       <c r="I31" s="38"/>
       <c r="J31" s="38"/>
       <c r="K31" s="38"/>
@@ -18849,7 +18853,7 @@
       <c r="P31" s="26"/>
     </row>
     <row r="32" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="54" t="s">
+      <c r="A32" s="97" t="s">
         <v>694</v>
       </c>
       <c r="B32" s="15" t="s">
@@ -18873,7 +18877,7 @@
       <c r="P32" s="26"/>
     </row>
     <row r="33" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="54"/>
+      <c r="A33" s="97"/>
       <c r="B33" s="15" t="s">
         <v>489</v>
       </c>
@@ -18895,7 +18899,7 @@
       <c r="P33" s="26"/>
     </row>
     <row r="34" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="54"/>
+      <c r="A34" s="97"/>
       <c r="B34" s="15" t="s">
         <v>486</v>
       </c>
@@ -18917,7 +18921,7 @@
       <c r="P34" s="26"/>
     </row>
     <row r="35" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="54"/>
+      <c r="A35" s="97"/>
       <c r="B35" s="15" t="s">
         <v>468</v>
       </c>
@@ -18939,7 +18943,7 @@
       <c r="P35" s="26"/>
     </row>
     <row r="36" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="54"/>
+      <c r="A36" s="97"/>
       <c r="B36" s="15" t="s">
         <v>379</v>
       </c>
@@ -18961,7 +18965,7 @@
       <c r="P36" s="26"/>
     </row>
     <row r="37" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="54"/>
+      <c r="A37" s="97"/>
       <c r="B37" s="15" t="s">
         <v>384</v>
       </c>
@@ -18983,7 +18987,7 @@
       <c r="P37" s="26"/>
     </row>
     <row r="38" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="54"/>
+      <c r="A38" s="97"/>
       <c r="B38" s="15" t="s">
         <v>444</v>
       </c>
@@ -19005,7 +19009,7 @@
       <c r="P38" s="26"/>
     </row>
     <row r="39" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="54"/>
+      <c r="A39" s="97"/>
       <c r="B39" s="15" t="s">
         <v>478</v>
       </c>
@@ -19027,16 +19031,16 @@
       <c r="P39" s="26"/>
     </row>
     <row r="40" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="66" t="s">
+      <c r="A40" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B40" s="67"/>
-      <c r="C40" s="67"/>
-      <c r="D40" s="67"/>
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="68"/>
+      <c r="B40" s="54"/>
+      <c r="C40" s="54"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="54"/>
+      <c r="F40" s="54"/>
+      <c r="G40" s="54"/>
+      <c r="H40" s="55"/>
       <c r="I40" s="38"/>
       <c r="J40" s="38"/>
       <c r="K40" s="38"/>
@@ -19047,7 +19051,7 @@
       <c r="P40" s="26"/>
     </row>
     <row r="41" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="53" t="s">
+      <c r="A41" s="96" t="s">
         <v>696</v>
       </c>
       <c r="B41" s="29" t="s">
@@ -19071,7 +19075,7 @@
       <c r="P41" s="26"/>
     </row>
     <row r="42" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="53"/>
+      <c r="A42" s="96"/>
       <c r="B42" s="29" t="s">
         <v>493</v>
       </c>
@@ -19093,7 +19097,7 @@
       <c r="P42" s="26"/>
     </row>
     <row r="43" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="53"/>
+      <c r="A43" s="96"/>
       <c r="B43" s="29" t="s">
         <v>498</v>
       </c>
@@ -19115,7 +19119,7 @@
       <c r="P43" s="26"/>
     </row>
     <row r="44" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="53"/>
+      <c r="A44" s="96"/>
       <c r="B44" s="29" t="s">
         <v>465</v>
       </c>
@@ -19137,7 +19141,7 @@
       <c r="P44" s="26"/>
     </row>
     <row r="45" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="53"/>
+      <c r="A45" s="96"/>
       <c r="B45" s="29" t="s">
         <v>494</v>
       </c>
@@ -19159,7 +19163,7 @@
       <c r="P45" s="26"/>
     </row>
     <row r="46" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="53"/>
+      <c r="A46" s="96"/>
       <c r="B46" s="29" t="s">
         <v>400</v>
       </c>
@@ -19181,7 +19185,7 @@
       <c r="P46" s="26"/>
     </row>
     <row r="47" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="53"/>
+      <c r="A47" s="96"/>
       <c r="B47" s="29" t="s">
         <v>573</v>
       </c>
@@ -19203,7 +19207,7 @@
       <c r="P47" s="26"/>
     </row>
     <row r="48" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="53"/>
+      <c r="A48" s="96"/>
       <c r="B48" s="29" t="s">
         <v>469</v>
       </c>
@@ -19225,7 +19229,7 @@
       <c r="P48" s="26"/>
     </row>
     <row r="49" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="53"/>
+      <c r="A49" s="96"/>
       <c r="B49" s="29" t="s">
         <v>485</v>
       </c>
@@ -19247,16 +19251,16 @@
       <c r="P49" s="26"/>
     </row>
     <row r="50" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="66" t="s">
+      <c r="A50" s="98" t="s">
         <v>502</v>
       </c>
-      <c r="B50" s="67"/>
-      <c r="C50" s="67"/>
-      <c r="D50" s="67"/>
-      <c r="E50" s="67"/>
-      <c r="F50" s="67"/>
-      <c r="G50" s="67"/>
-      <c r="H50" s="68"/>
+      <c r="B50" s="54"/>
+      <c r="C50" s="54"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="54"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="54"/>
+      <c r="H50" s="55"/>
       <c r="I50" s="38"/>
       <c r="J50" s="38"/>
       <c r="K50" s="38"/>
@@ -19267,7 +19271,7 @@
       <c r="P50" s="26"/>
     </row>
     <row r="51" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="54" t="s">
+      <c r="A51" s="97" t="s">
         <v>698</v>
       </c>
       <c r="B51" s="29" t="s">
@@ -19291,7 +19295,7 @@
       <c r="P51" s="26"/>
     </row>
     <row r="52" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="54"/>
+      <c r="A52" s="97"/>
       <c r="B52" s="29" t="s">
         <v>483</v>
       </c>
@@ -19313,7 +19317,7 @@
       <c r="P52" s="26"/>
     </row>
     <row r="53" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="54"/>
+      <c r="A53" s="97"/>
       <c r="B53" s="29" t="s">
         <v>341</v>
       </c>
@@ -19335,7 +19339,7 @@
       <c r="P53" s="26"/>
     </row>
     <row r="54" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="54"/>
+      <c r="A54" s="97"/>
       <c r="B54" s="29" t="s">
         <v>377</v>
       </c>
@@ -19357,7 +19361,7 @@
       <c r="P54" s="26"/>
     </row>
     <row r="55" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="54"/>
+      <c r="A55" s="97"/>
       <c r="B55" s="29" t="s">
         <v>574</v>
       </c>
@@ -19379,16 +19383,16 @@
       <c r="P55" s="26"/>
     </row>
     <row r="56" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="66" t="s">
+      <c r="A56" s="98" t="s">
         <v>113</v>
       </c>
-      <c r="B56" s="67"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="67"/>
-      <c r="E56" s="67"/>
-      <c r="F56" s="67"/>
-      <c r="G56" s="67"/>
-      <c r="H56" s="68"/>
+      <c r="B56" s="54"/>
+      <c r="C56" s="54"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="54"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="54"/>
+      <c r="H56" s="55"/>
       <c r="I56" s="38"/>
       <c r="J56" s="38"/>
       <c r="K56" s="38"/>
@@ -19399,7 +19403,7 @@
       <c r="P56" s="26"/>
     </row>
     <row r="57" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="54" t="s">
+      <c r="A57" s="97" t="s">
         <v>699</v>
       </c>
       <c r="B57" s="15" t="s">
@@ -19423,7 +19427,7 @@
       <c r="P57" s="26"/>
     </row>
     <row r="58" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="54"/>
+      <c r="A58" s="97"/>
       <c r="B58" s="15" t="s">
         <v>700</v>
       </c>
@@ -19445,7 +19449,7 @@
       <c r="P58" s="26"/>
     </row>
     <row r="59" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="54"/>
+      <c r="A59" s="97"/>
       <c r="B59" s="15" t="s">
         <v>701</v>
       </c>
@@ -19467,7 +19471,7 @@
       <c r="P59" s="26"/>
     </row>
     <row r="60" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="54"/>
+      <c r="A60" s="97"/>
       <c r="B60" s="15" t="s">
         <v>702</v>
       </c>
@@ -19489,7 +19493,7 @@
       <c r="P60" s="26"/>
     </row>
     <row r="61" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="54"/>
+      <c r="A61" s="97"/>
       <c r="B61" s="15" t="s">
         <v>703</v>
       </c>
@@ -19511,7 +19515,7 @@
       <c r="P61" s="26"/>
     </row>
     <row r="62" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="54"/>
+      <c r="A62" s="97"/>
       <c r="B62" s="15" t="s">
         <v>577</v>
       </c>
@@ -19533,7 +19537,7 @@
       <c r="P62" s="26"/>
     </row>
     <row r="63" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="54"/>
+      <c r="A63" s="97"/>
       <c r="B63" s="15" t="s">
         <v>578</v>
       </c>
@@ -19555,7 +19559,7 @@
       <c r="P63" s="26"/>
     </row>
     <row r="64" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="54"/>
+      <c r="A64" s="97"/>
       <c r="B64" s="15" t="s">
         <v>580</v>
       </c>
@@ -19577,7 +19581,7 @@
       <c r="P64" s="26"/>
     </row>
     <row r="65" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="54"/>
+      <c r="A65" s="97"/>
       <c r="B65" s="15" t="s">
         <v>579</v>
       </c>
@@ -19599,16 +19603,16 @@
       <c r="P65" s="26"/>
     </row>
     <row r="66" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="73" t="s">
+      <c r="A66" s="102" t="s">
         <v>113</v>
       </c>
-      <c r="B66" s="74"/>
-      <c r="C66" s="74"/>
-      <c r="D66" s="74"/>
-      <c r="E66" s="74"/>
-      <c r="F66" s="74"/>
-      <c r="G66" s="74"/>
-      <c r="H66" s="75"/>
+      <c r="B66" s="57"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="58"/>
       <c r="I66" s="47"/>
       <c r="J66" s="47"/>
       <c r="K66" s="47"/>
@@ -19619,16 +19623,16 @@
       <c r="P66" s="28"/>
     </row>
     <row r="67" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="70" t="s">
+      <c r="A67" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="B67" s="71"/>
-      <c r="C67" s="71"/>
-      <c r="D67" s="71"/>
-      <c r="E67" s="71"/>
-      <c r="F67" s="71"/>
-      <c r="G67" s="71"/>
-      <c r="H67" s="72"/>
+      <c r="B67" s="60"/>
+      <c r="C67" s="60"/>
+      <c r="D67" s="60"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="61"/>
       <c r="I67" s="48"/>
       <c r="J67" s="48"/>
       <c r="K67" s="48"/>
@@ -19658,18 +19662,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A30"/>
-    <mergeCell ref="A31:H31"/>
-    <mergeCell ref="A40:H40"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A32:A39"/>
-    <mergeCell ref="A41:A49"/>
-    <mergeCell ref="A56:H56"/>
-    <mergeCell ref="A66:H66"/>
-    <mergeCell ref="A67:H67"/>
-    <mergeCell ref="A51:A55"/>
-    <mergeCell ref="A57:A65"/>
     <mergeCell ref="A2:P2"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
@@ -19686,6 +19678,18 @@
     <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="E6:E7"/>
+    <mergeCell ref="A56:H56"/>
+    <mergeCell ref="A66:H66"/>
+    <mergeCell ref="A67:H67"/>
+    <mergeCell ref="A51:A55"/>
+    <mergeCell ref="A57:A65"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A30"/>
+    <mergeCell ref="A31:H31"/>
+    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A32:A39"/>
+    <mergeCell ref="A41:A49"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -22170,20 +22174,20 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-      <c r="J2" s="55"/>
-      <c r="K2" s="55"/>
-      <c r="L2" s="55"/>
-      <c r="M2" s="55"/>
-      <c r="N2" s="55"/>
+      <c r="A2" s="83"/>
+      <c r="B2" s="83"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="83"/>
+      <c r="I2" s="83"/>
+      <c r="J2" s="83"/>
+      <c r="K2" s="83"/>
+      <c r="L2" s="83"/>
+      <c r="M2" s="83"/>
+      <c r="N2" s="83"/>
     </row>
     <row r="3" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="31"/>
@@ -22214,67 +22218,67 @@
       <c r="N5" s="8"/>
     </row>
     <row r="6" spans="1:14" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56" t="s">
+      <c r="A6" s="91" t="s">
         <v>409</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="88" t="s">
         <v>612</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="86" t="s">
         <v>613</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="86" t="s">
         <v>614</v>
       </c>
-      <c r="E6" s="60" t="s">
+      <c r="E6" s="86" t="s">
         <v>615</v>
       </c>
-      <c r="F6" s="62" t="s">
+      <c r="F6" s="81" t="s">
         <v>616</v>
       </c>
-      <c r="G6" s="62" t="s">
+      <c r="G6" s="81" t="s">
         <v>571</v>
       </c>
-      <c r="H6" s="62" t="s">
+      <c r="H6" s="81" t="s">
         <v>575</v>
       </c>
-      <c r="I6" s="62" t="s">
+      <c r="I6" s="81" t="s">
         <v>581</v>
       </c>
-      <c r="J6" s="62" t="s">
+      <c r="J6" s="81" t="s">
         <v>582</v>
       </c>
-      <c r="K6" s="62" t="s">
+      <c r="K6" s="81" t="s">
         <v>583</v>
       </c>
-      <c r="L6" s="62" t="s">
+      <c r="L6" s="81" t="s">
         <v>596</v>
       </c>
-      <c r="M6" s="62" t="s">
+      <c r="M6" s="81" t="s">
         <v>617</v>
       </c>
-      <c r="N6" s="64" t="s">
+      <c r="N6" s="84" t="s">
         <v>618</v>
       </c>
     </row>
     <row r="7" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="57"/>
-      <c r="B7" s="59"/>
-      <c r="C7" s="61"/>
-      <c r="D7" s="61"/>
-      <c r="E7" s="61"/>
-      <c r="F7" s="63"/>
-      <c r="G7" s="63"/>
-      <c r="H7" s="63"/>
-      <c r="I7" s="63"/>
-      <c r="J7" s="63"/>
-      <c r="K7" s="63"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="63"/>
-      <c r="N7" s="65"/>
+      <c r="A7" s="92"/>
+      <c r="B7" s="89"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="87"/>
+      <c r="E7" s="87"/>
+      <c r="F7" s="82"/>
+      <c r="G7" s="82"/>
+      <c r="H7" s="82"/>
+      <c r="I7" s="82"/>
+      <c r="J7" s="82"/>
+      <c r="K7" s="82"/>
+      <c r="L7" s="82"/>
+      <c r="M7" s="82"/>
+      <c r="N7" s="85"/>
     </row>
     <row r="8" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="69" t="s">
+      <c r="A8" s="101" t="s">
         <v>707</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -22296,7 +22300,7 @@
       <c r="N8" s="27"/>
     </row>
     <row r="9" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="53"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="13" t="s">
         <v>495</v>
       </c>
@@ -22316,7 +22320,7 @@
       <c r="N9" s="26"/>
     </row>
     <row r="10" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="53"/>
+      <c r="A10" s="96"/>
       <c r="B10" s="11" t="s">
         <v>183</v>
       </c>
@@ -22336,7 +22340,7 @@
       <c r="N10" s="26"/>
     </row>
     <row r="11" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="53"/>
+      <c r="A11" s="96"/>
       <c r="B11" s="11" t="s">
         <v>490</v>
       </c>
@@ -22356,7 +22360,7 @@
       <c r="N11" s="26"/>
     </row>
     <row r="12" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="53"/>
+      <c r="A12" s="96"/>
       <c r="B12" s="11" t="s">
         <v>187</v>
       </c>
@@ -22376,7 +22380,7 @@
       <c r="N12" s="26"/>
     </row>
     <row r="13" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="53"/>
+      <c r="A13" s="96"/>
       <c r="B13" s="11" t="s">
         <v>402</v>
       </c>
@@ -22396,7 +22400,7 @@
       <c r="N13" s="26"/>
     </row>
     <row r="14" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="53" t="s">
+      <c r="A14" s="96" t="s">
         <v>708</v>
       </c>
       <c r="B14" s="11" t="s">
@@ -22418,7 +22422,7 @@
       <c r="N14" s="26"/>
     </row>
     <row r="15" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="53"/>
+      <c r="A15" s="96"/>
       <c r="B15" s="11" t="s">
         <v>191</v>
       </c>
@@ -22438,7 +22442,7 @@
       <c r="N15" s="26"/>
     </row>
     <row r="16" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="53"/>
+      <c r="A16" s="96"/>
       <c r="B16" s="11" t="s">
         <v>178</v>
       </c>
@@ -22458,7 +22462,7 @@
       <c r="N16" s="26"/>
     </row>
     <row r="17" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="53"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="11" t="s">
         <v>174</v>
       </c>
@@ -22500,14 +22504,14 @@
       <c r="N18" s="26"/>
     </row>
     <row r="19" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="73" t="s">
+      <c r="A19" s="102" t="s">
         <v>113</v>
       </c>
-      <c r="B19" s="74"/>
-      <c r="C19" s="74"/>
-      <c r="D19" s="74"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="75"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="58"/>
       <c r="G19" s="47"/>
       <c r="H19" s="47"/>
       <c r="I19" s="47"/>
@@ -22518,14 +22522,14 @@
       <c r="N19" s="28"/>
     </row>
     <row r="20" spans="1:14" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="70" t="s">
+      <c r="A20" s="59" t="s">
         <v>93</v>
       </c>
-      <c r="B20" s="71"/>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="71"/>
-      <c r="F20" s="72"/>
+      <c r="B20" s="60"/>
+      <c r="C20" s="60"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="61"/>
       <c r="G20" s="48"/>
       <c r="H20" s="48"/>
       <c r="I20" s="48"/>
@@ -22569,11 +22573,6 @@
     </row>
   </sheetData>
   <mergeCells count="19">
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="J6:J7"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A20:F20"/>
     <mergeCell ref="K6:K7"/>
     <mergeCell ref="L6:L7"/>
     <mergeCell ref="M6:M7"/>
@@ -22588,6 +22587,11 @@
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
     <mergeCell ref="I6:I7"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="J6:J7"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A20:F20"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
